--- a/unit_stats.xlsx
+++ b/unit_stats.xlsx
@@ -2584,7 +2584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q58"/>
+  <dimension ref="A1:Q64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3179,7 +3179,7 @@
         <v>57</v>
       </c>
       <c r="D11" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -3283,89 +3283,89 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Beast_MogallClass</t>
+          <t>Lowlander_Archer</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G13" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>EvilEye</t>
+          <t>SteelBow</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="N13" t="n">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Q13" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Lowlander_SwordCav</t>
+          <t>Beast_MogallClass</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F14" t="n">
         <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -3375,29 +3375,29 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>IronSword</t>
+          <t>EvilEye</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="N14" t="n">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Q14" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Lowlander_LanceCav</t>
+          <t>Lowlander_SwordCav</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -3432,14 +3432,14 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>IronLance</t>
+          <t>IronSword</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N15" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -3454,29 +3454,29 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lowlander_Soldier</t>
+          <t>Lowlander_LanceCav</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D16" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
+        <v>8</v>
+      </c>
+      <c r="G16" t="n">
         <v>7</v>
       </c>
-      <c r="G16" t="n">
-        <v>5</v>
-      </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -3485,7 +3485,7 @@
         <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -3493,149 +3493,149 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="N16" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q16" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Lowlander_Mage</t>
+          <t>Lowlander_Soldier</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Ridersbane</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N17" t="n">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Beast_SwordBone</t>
+          <t>Lowlander_Mage</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G18" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H18" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>IronSword</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N18" t="n">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Q18" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Lowlander_Archer</t>
+          <t>Beast_SwordBone</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -3644,39 +3644,39 @@
         <v>12</v>
       </c>
       <c r="G19" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>SteelBow</t>
+          <t>IronSword</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="N19" t="n">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q19" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -3796,29 +3796,29 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Beast_Bael</t>
+          <t>Beast_Tarvos</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>6</v>
       </c>
       <c r="C22" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D22" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G22" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I22" t="n">
         <v>3</v>
@@ -3827,18 +3827,18 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>SharpClaw</t>
+          <t>SteelAxe</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="N22" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3847,70 +3847,70 @@
         <v>8</v>
       </c>
       <c r="Q22" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Lowlander_Myrmidon</t>
+          <t>Beast_Bael</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>6</v>
       </c>
       <c r="C23" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E23" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G23" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H23" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I23" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>LightBrand</t>
+          <t>SharpClaw</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="N23" t="n">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Q23" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Beast_AxeBone</t>
+          <t>Beast_BowBone</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -3920,13 +3920,13 @@
         <v>37</v>
       </c>
       <c r="D24" t="n">
+        <v>12</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
         <v>13</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>12</v>
       </c>
       <c r="G24" t="n">
         <v>11</v>
@@ -3945,20 +3945,20 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>SteelAxe</t>
+          <t>SteelBow</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N24" t="n">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Q24" t="n">
         <v>22</v>
@@ -3967,343 +3967,343 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Beast_AxeBone</t>
+          <t>Lowlander_Myrmidon</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D25" t="n">
+        <v>7</v>
+      </c>
+      <c r="E25" t="n">
+        <v>6</v>
+      </c>
+      <c r="F25" t="n">
         <v>13</v>
       </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>12</v>
-      </c>
       <c r="G25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H25" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>8</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>HandAxe</t>
+          <t>LightBrand</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="N25" t="n">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Q25" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ch4LowlanderBoss_LowMage</t>
+          <t>Beast_AxeBone</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D26" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E26" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G26" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H26" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I26" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>8</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>SteelAxe</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>26</v>
       </c>
       <c r="N26" t="n">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="O26" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q26" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ch4LowlanderBoss_LowMage</t>
+          <t>Beast_AxeBone</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E27" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G27" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H27" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I27" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>8</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Unfamiliarity</t>
+          <t>HandAxe</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>271</v>
+        <v>19</v>
       </c>
       <c r="N27" t="n">
-        <v>140</v>
+        <v>94</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q27" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Beast_BowBone</t>
+          <t>Ch4LowlanderBoss_LowMage</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C28" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D28" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G28" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H28" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K28" t="n">
         <v>8</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Longbow</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N28" t="n">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q28" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Lowlander_LowMage</t>
+          <t>Ch4LowlanderBoss_LowMage</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C29" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H29" t="n">
         <v>6</v>
       </c>
       <c r="I29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K29" t="n">
         <v>8</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Exploitation</t>
+          <t>Unfamiliarity</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>28</v>
+        <v>271</v>
       </c>
       <c r="N29" t="n">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q29" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Dragon_Headsman</t>
+          <t>Lowlander_LowMage</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C30" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D30" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="F30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G30" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I30" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K30" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>IronLance</t>
+          <t>Exploitation</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="N30" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q30" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31">
@@ -4344,20 +4344,20 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>SteelBlade</t>
+          <t>IronLance</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="N31" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q31" t="n">
         <v>17</v>
@@ -4366,58 +4366,58 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Teacher_Veteran</t>
+          <t>Dragon_Headsman</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>10</v>
       </c>
       <c r="C32" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D32" t="n">
         <v>12</v>
       </c>
       <c r="E32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G32" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H32" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K32" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>IronLance</t>
+          <t>SteelBlade</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N32" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33">
@@ -4458,20 +4458,20 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>SteelBlade</t>
+          <t>IronLance</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="N33" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="Q33" t="n">
         <v>32</v>
@@ -4480,58 +4480,58 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Pillow_LowVoice</t>
+          <t>Teacher_Veteran</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>10</v>
       </c>
       <c r="C34" t="n">
+        <v>38</v>
+      </c>
+      <c r="D34" t="n">
+        <v>12</v>
+      </c>
+      <c r="E34" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" t="n">
+        <v>15</v>
+      </c>
+      <c r="G34" t="n">
+        <v>11</v>
+      </c>
+      <c r="H34" t="n">
+        <v>11</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2</v>
+      </c>
+      <c r="J34" t="n">
+        <v>10</v>
+      </c>
+      <c r="K34" t="n">
+        <v>10</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
         <v>25</v>
       </c>
-      <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="n">
-        <v>10</v>
-      </c>
-      <c r="F34" t="n">
-        <v>10</v>
-      </c>
-      <c r="G34" t="n">
-        <v>7</v>
-      </c>
-      <c r="H34" t="n">
-        <v>3</v>
-      </c>
-      <c r="I34" t="n">
-        <v>7</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>8</v>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>IronLance</t>
-        </is>
-      </c>
-      <c r="M34" t="n">
-        <v>8</v>
-      </c>
       <c r="N34" t="n">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q34" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35">
@@ -4572,20 +4572,20 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>SteelBlade</t>
+          <t>IronLance</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="N35" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q35" t="n">
         <v>14</v>
@@ -4594,32 +4594,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x81_Soldier</t>
+          <t>Pillow_LowVoice</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>10</v>
       </c>
       <c r="C36" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D36" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F36" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G36" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4629,23 +4629,23 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>IronLance</t>
+          <t>SteelBlade</t>
         </is>
       </c>
       <c r="M36" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="N36" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="Q36" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37">
@@ -4686,20 +4686,20 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>SteelBlade</t>
+          <t>IronLance</t>
         </is>
       </c>
       <c r="M37" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N37" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>-4</v>
+        <v>4</v>
       </c>
       <c r="Q37" t="n">
         <v>8</v>
@@ -4708,7 +4708,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x80_Soldier</t>
+          <t>0x81_Soldier</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -4743,20 +4743,20 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>IronLance</t>
+          <t>SteelBlade</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N38" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="Q38" t="n">
         <v>8</v>
@@ -4800,20 +4800,20 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>SteelBlade</t>
+          <t>IronLance</t>
         </is>
       </c>
       <c r="M39" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N39" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>-4</v>
+        <v>4</v>
       </c>
       <c r="Q39" t="n">
         <v>8</v>
@@ -4822,51 +4822,71 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xF5_CivMan</t>
+          <t>0x80_Soldier</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>10</v>
       </c>
       <c r="C40" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="n">
+        <v>6</v>
+      </c>
+      <c r="G40" t="n">
+        <v>4</v>
+      </c>
+      <c r="H40" t="n">
         <v>1</v>
       </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="n">
-        <v>2</v>
-      </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>23</v>
+      </c>
+      <c r="N40" t="n">
+        <v>97</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0xF6_CivWoman</t>
+          <t>0xF5_CivMan</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>10</v>
       </c>
       <c r="C41" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -4884,26 +4904,26 @@
         <v>2</v>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0xF5_Peer</t>
+          <t>0xF6_CivWoman</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>10</v>
       </c>
       <c r="C42" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -4912,7 +4932,7 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -4921,147 +4941,147 @@
         <v>2</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0xF6_MageGeneral</t>
+          <t>0xF5_Peer</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>10</v>
       </c>
       <c r="C43" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I43" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Eagle_MageGeneral</t>
+          <t>0xF6_MageGeneral</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>10</v>
       </c>
       <c r="C44" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D44" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H44" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I44" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J44" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x80_CivWoman</t>
+          <t>Eagle_MageGeneral</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>10</v>
       </c>
       <c r="C45" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K45" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x80_UpstartM</t>
+          <t>0x80_CivWoman</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>10</v>
       </c>
       <c r="C46" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
       </c>
       <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
         <v>1</v>
       </c>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
@@ -5069,121 +5089,121 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Prince_Noble</t>
+          <t>0x80_UpstartM</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>10</v>
       </c>
       <c r="C47" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D47" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Songbird_Bard</t>
+          <t>Prince_Noble</t>
         </is>
       </c>
       <c r="B48" t="n">
+        <v>10</v>
+      </c>
+      <c r="C48" t="n">
+        <v>27</v>
+      </c>
+      <c r="D48" t="n">
+        <v>8</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>15</v>
+      </c>
+      <c r="G48" t="n">
+        <v>13</v>
+      </c>
+      <c r="H48" t="n">
+        <v>7</v>
+      </c>
+      <c r="I48" t="n">
+        <v>2</v>
+      </c>
+      <c r="J48" t="n">
         <v>3</v>
       </c>
-      <c r="C48" t="n">
-        <v>19</v>
-      </c>
-      <c r="D48" t="n">
-        <v>2</v>
-      </c>
-      <c r="E48" t="n">
-        <v>2</v>
-      </c>
-      <c r="F48" t="n">
-        <v>5</v>
-      </c>
-      <c r="G48" t="n">
-        <v>9</v>
-      </c>
-      <c r="H48" t="n">
-        <v>2</v>
-      </c>
-      <c r="I48" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" t="n">
-        <v>8</v>
-      </c>
       <c r="K48" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x80_CivMan</t>
+          <t>Songbird_Bard</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C49" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F49" t="n">
+        <v>5</v>
+      </c>
+      <c r="G49" t="n">
+        <v>9</v>
+      </c>
+      <c r="H49" t="n">
+        <v>2</v>
+      </c>
+      <c r="I49" t="n">
         <v>1</v>
       </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="n">
-        <v>2</v>
-      </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K49" t="n">
         <v>6</v>
@@ -5192,14 +5212,14 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x81_CivWoman</t>
+          <t>0x80_CivMan</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>10</v>
       </c>
       <c r="C50" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -5217,26 +5237,26 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x82_CivMan</t>
+          <t>0x81_CivWoman</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>10</v>
       </c>
       <c r="C51" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -5254,26 +5274,26 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x83_CivWoman</t>
+          <t>0x82_CivMan</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>10</v>
       </c>
       <c r="C52" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
@@ -5291,26 +5311,26 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x84_Peer</t>
+          <t>0x83_CivWoman</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>10</v>
       </c>
       <c r="C53" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -5319,7 +5339,7 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -5328,19 +5348,19 @@
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x85_CivMan</t>
+          <t>0x84_Peer</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -5356,7 +5376,7 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -5365,19 +5385,19 @@
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x86_Peer</t>
+          <t>0x85_CivMan</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -5393,7 +5413,7 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -5402,26 +5422,26 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x87_CivWoman</t>
+          <t>0x86_Peer</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>10</v>
       </c>
       <c r="C56" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -5430,7 +5450,7 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -5439,26 +5459,26 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x88_CivMan</t>
+          <t>0x87_CivWoman</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>10</v>
       </c>
       <c r="C57" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -5476,70 +5496,292 @@
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>0x88_CivMan</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>10</v>
+      </c>
+      <c r="C58" t="n">
+        <v>12</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>2</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>0xAE_MogallClass</t>
         </is>
       </c>
-      <c r="B58" t="n">
-        <v>10</v>
-      </c>
-      <c r="C58" t="n">
+      <c r="B59" t="n">
+        <v>10</v>
+      </c>
+      <c r="C59" t="n">
         <v>37</v>
       </c>
-      <c r="D58" t="n">
-        <v>12</v>
-      </c>
-      <c r="E58" t="n">
+      <c r="D59" t="n">
+        <v>12</v>
+      </c>
+      <c r="E59" t="n">
         <v>18</v>
       </c>
-      <c r="F58" t="n">
-        <v>10</v>
-      </c>
-      <c r="G58" t="n">
+      <c r="F59" t="n">
+        <v>10</v>
+      </c>
+      <c r="G59" t="n">
         <v>13</v>
       </c>
-      <c r="H58" t="n">
+      <c r="H59" t="n">
         <v>3</v>
       </c>
-      <c r="I58" t="n">
+      <c r="I59" t="n">
         <v>15</v>
       </c>
-      <c r="J58" t="n">
-        <v>2</v>
-      </c>
-      <c r="K58" t="n">
+      <c r="J59" t="n">
+        <v>2</v>
+      </c>
+      <c r="K59" t="n">
         <v>9</v>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>EvilEye</t>
         </is>
       </c>
-      <c r="M58" t="n">
+      <c r="M59" t="n">
         <v>25</v>
       </c>
-      <c r="N58" t="n">
+      <c r="N59" t="n">
         <v>117</v>
       </c>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="n">
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
         <v>13</v>
       </c>
-      <c r="Q58" t="n">
+      <c r="Q59" t="n">
         <v>28</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>0x80_Sage</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>10</v>
+      </c>
+      <c r="C60" t="n">
+        <v>24</v>
+      </c>
+      <c r="D60" t="n">
+        <v>4</v>
+      </c>
+      <c r="E60" t="n">
+        <v>8</v>
+      </c>
+      <c r="F60" t="n">
+        <v>12</v>
+      </c>
+      <c r="G60" t="n">
+        <v>10</v>
+      </c>
+      <c r="H60" t="n">
+        <v>5</v>
+      </c>
+      <c r="I60" t="n">
+        <v>10</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>0x81_Druid</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>10</v>
+      </c>
+      <c r="C61" t="n">
+        <v>36</v>
+      </c>
+      <c r="D61" t="n">
+        <v>5</v>
+      </c>
+      <c r="E61" t="n">
+        <v>9</v>
+      </c>
+      <c r="F61" t="n">
+        <v>12</v>
+      </c>
+      <c r="G61" t="n">
+        <v>8</v>
+      </c>
+      <c r="H61" t="n">
+        <v>6</v>
+      </c>
+      <c r="I61" t="n">
+        <v>14</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>0x82_Druid</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>10</v>
+      </c>
+      <c r="C62" t="n">
+        <v>36</v>
+      </c>
+      <c r="D62" t="n">
+        <v>5</v>
+      </c>
+      <c r="E62" t="n">
+        <v>9</v>
+      </c>
+      <c r="F62" t="n">
+        <v>12</v>
+      </c>
+      <c r="G62" t="n">
+        <v>8</v>
+      </c>
+      <c r="H62" t="n">
+        <v>6</v>
+      </c>
+      <c r="I62" t="n">
+        <v>14</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>0x83_Druid</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>10</v>
+      </c>
+      <c r="C63" t="n">
+        <v>36</v>
+      </c>
+      <c r="D63" t="n">
+        <v>5</v>
+      </c>
+      <c r="E63" t="n">
+        <v>9</v>
+      </c>
+      <c r="F63" t="n">
+        <v>12</v>
+      </c>
+      <c r="G63" t="n">
+        <v>8</v>
+      </c>
+      <c r="H63" t="n">
+        <v>6</v>
+      </c>
+      <c r="I63" t="n">
+        <v>14</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>0x81_Peer</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>10</v>
+      </c>
+      <c r="C64" t="n">
+        <v>12</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -11809,7 +12051,7 @@
         <v>59</v>
       </c>
       <c r="D24" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -13978,7 +14220,7 @@
         <v>55</v>
       </c>
       <c r="D24" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -19351,7 +19593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q58"/>
+  <dimension ref="A1:Q64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -19946,7 +20188,7 @@
         <v>63</v>
       </c>
       <c r="D11" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -20050,89 +20292,89 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Beast_MogallClass</t>
+          <t>Lowlander_Archer</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G13" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I13" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J13" t="n">
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>EvilEye</t>
+          <t>SteelBow</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="N13" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="Q13" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Lowlander_SwordCav</t>
+          <t>Beast_MogallClass</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F14" t="n">
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H14" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="J14" t="n">
         <v>3</v>
@@ -20142,29 +20384,29 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>IronSword</t>
+          <t>EvilEye</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="N14" t="n">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Q14" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Lowlander_LanceCav</t>
+          <t>Lowlander_SwordCav</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -20199,14 +20441,14 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>IronLance</t>
+          <t>IronSword</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N15" t="n">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -20221,38 +20463,38 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lowlander_Soldier</t>
+          <t>Lowlander_LanceCav</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" t="n">
         <v>9</v>
       </c>
-      <c r="G16" t="n">
-        <v>6</v>
-      </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -20260,149 +20502,149 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N16" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Q16" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Lowlander_Mage</t>
+          <t>Lowlander_Soldier</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E17" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G17" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Ridersbane</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N17" t="n">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Beast_SwordBone</t>
+          <t>Lowlander_Mage</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F18" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G18" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H18" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>IronSword</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N18" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q18" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Lowlander_Archer</t>
+          <t>Beast_SwordBone</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -20411,39 +20653,39 @@
         <v>14</v>
       </c>
       <c r="G19" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H19" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>SteelBow</t>
+          <t>IronSword</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="N19" t="n">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Q19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20">
@@ -20563,140 +20805,140 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Beast_Bael</t>
+          <t>Beast_Tarvos</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>6</v>
       </c>
       <c r="C22" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D22" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G22" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I22" t="n">
         <v>4</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>SharpClaw</t>
+          <t>SteelAxe</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="N22" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q22" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Lowlander_Myrmidon</t>
+          <t>Beast_Bael</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>6</v>
       </c>
       <c r="C23" t="n">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="D23" t="n">
+        <v>17</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>12</v>
+      </c>
+      <c r="G23" t="n">
         <v>9</v>
       </c>
-      <c r="E23" t="n">
-        <v>8</v>
-      </c>
-      <c r="F23" t="n">
+      <c r="H23" t="n">
+        <v>11</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
         <v>15</v>
       </c>
-      <c r="G23" t="n">
-        <v>15</v>
-      </c>
-      <c r="H23" t="n">
-        <v>5</v>
-      </c>
-      <c r="I23" t="n">
-        <v>7</v>
-      </c>
-      <c r="J23" t="n">
-        <v>3</v>
-      </c>
-      <c r="K23" t="n">
-        <v>8</v>
-      </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>LightBrand</t>
+          <t>SharpClaw</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="N23" t="n">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Q23" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Beast_AxeBone</t>
+          <t>Beast_BowBone</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D24" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H24" t="n">
         <v>11</v>
@@ -20712,365 +20954,365 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>SteelAxe</t>
+          <t>SteelBow</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="N24" t="n">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="Q24" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Beast_AxeBone</t>
+          <t>Lowlander_Myrmidon</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="D25" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F25" t="n">
+        <v>15</v>
+      </c>
+      <c r="G25" t="n">
+        <v>15</v>
+      </c>
+      <c r="H25" t="n">
+        <v>5</v>
+      </c>
+      <c r="I25" t="n">
+        <v>7</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K25" t="n">
+        <v>8</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>LightBrand</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>17</v>
+      </c>
+      <c r="N25" t="n">
+        <v>113</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
         <v>14</v>
       </c>
-      <c r="G25" t="n">
-        <v>12</v>
-      </c>
-      <c r="H25" t="n">
-        <v>11</v>
-      </c>
-      <c r="I25" t="n">
-        <v>4</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>8</v>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>HandAxe</t>
-        </is>
-      </c>
-      <c r="M25" t="n">
-        <v>22</v>
-      </c>
-      <c r="N25" t="n">
-        <v>98</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>8</v>
-      </c>
       <c r="Q25" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ch4LowlanderBoss_LowMage</t>
+          <t>Beast_AxeBone</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C26" t="n">
         <v>42</v>
       </c>
       <c r="D26" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E26" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G26" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H26" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I26" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>8</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>SteelAxe</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>29</v>
       </c>
       <c r="N26" t="n">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="O26" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ch4LowlanderBoss_LowMage</t>
+          <t>Beast_AxeBone</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C27" t="n">
         <v>42</v>
       </c>
       <c r="D27" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E27" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H27" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I27" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>8</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Unfamiliarity</t>
+          <t>HandAxe</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>274</v>
+        <v>22</v>
       </c>
       <c r="N27" t="n">
-        <v>145</v>
+        <v>98</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Beast_BowBone</t>
+          <t>Ch4LowlanderBoss_LowMage</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C28" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D28" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G28" t="n">
+        <v>10</v>
+      </c>
+      <c r="H28" t="n">
+        <v>6</v>
+      </c>
+      <c r="I28" t="n">
         <v>13</v>
       </c>
-      <c r="H28" t="n">
-        <v>11</v>
-      </c>
-      <c r="I28" t="n">
-        <v>4</v>
-      </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K28" t="n">
         <v>8</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Longbow</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="M28" t="n">
+        <v>29</v>
+      </c>
+      <c r="N28" t="n">
+        <v>125</v>
+      </c>
+      <c r="O28" t="n">
+        <v>30</v>
+      </c>
+      <c r="P28" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q28" t="n">
         <v>23</v>
-      </c>
-      <c r="N28" t="n">
-        <v>105</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>26</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Lowlander_LowMage</t>
+          <t>Ch4LowlanderBoss_LowMage</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C29" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H29" t="n">
         <v>6</v>
       </c>
       <c r="I29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K29" t="n">
         <v>8</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Exploitation</t>
+          <t>Unfamiliarity</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>31</v>
+        <v>274</v>
       </c>
       <c r="N29" t="n">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q29" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Dragon_Headsman</t>
+          <t>Lowlander_LowMage</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C30" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D30" t="n">
         <v>12</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F30" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G30" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I30" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="J30" t="n">
+        <v>4</v>
+      </c>
+      <c r="K30" t="n">
+        <v>8</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Exploitation</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>31</v>
+      </c>
+      <c r="N30" t="n">
+        <v>118</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
         <v>5</v>
       </c>
-      <c r="K30" t="n">
-        <v>12</v>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>IronLance</t>
-        </is>
-      </c>
-      <c r="M30" t="n">
-        <v>20</v>
-      </c>
-      <c r="N30" t="n">
-        <v>115</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>6</v>
-      </c>
       <c r="Q30" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31">
@@ -21111,20 +21353,20 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>SteelBlade</t>
+          <t>IronLance</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="N31" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q31" t="n">
         <v>17</v>
@@ -21133,58 +21375,58 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Teacher_Veteran</t>
+          <t>Dragon_Headsman</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>10</v>
       </c>
       <c r="C32" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D32" t="n">
         <v>12</v>
       </c>
       <c r="E32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G32" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H32" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K32" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>IronLance</t>
+          <t>SteelBlade</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N32" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33">
@@ -21225,20 +21467,20 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>SteelBlade</t>
+          <t>IronLance</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="N33" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="Q33" t="n">
         <v>32</v>
@@ -21247,58 +21489,58 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Pillow_LowVoice</t>
+          <t>Teacher_Veteran</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>10</v>
       </c>
       <c r="C34" t="n">
+        <v>38</v>
+      </c>
+      <c r="D34" t="n">
+        <v>12</v>
+      </c>
+      <c r="E34" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" t="n">
+        <v>15</v>
+      </c>
+      <c r="G34" t="n">
+        <v>11</v>
+      </c>
+      <c r="H34" t="n">
+        <v>11</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2</v>
+      </c>
+      <c r="J34" t="n">
+        <v>10</v>
+      </c>
+      <c r="K34" t="n">
+        <v>10</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
         <v>25</v>
       </c>
-      <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="n">
-        <v>10</v>
-      </c>
-      <c r="F34" t="n">
-        <v>10</v>
-      </c>
-      <c r="G34" t="n">
-        <v>7</v>
-      </c>
-      <c r="H34" t="n">
-        <v>3</v>
-      </c>
-      <c r="I34" t="n">
-        <v>7</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>8</v>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>IronLance</t>
-        </is>
-      </c>
-      <c r="M34" t="n">
-        <v>8</v>
-      </c>
       <c r="N34" t="n">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q34" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35">
@@ -21339,20 +21581,20 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>SteelBlade</t>
+          <t>IronLance</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="N35" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q35" t="n">
         <v>14</v>
@@ -21361,32 +21603,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x81_Soldier</t>
+          <t>Pillow_LowVoice</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>10</v>
       </c>
       <c r="C36" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D36" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F36" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G36" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -21396,23 +21638,23 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>IronLance</t>
+          <t>SteelBlade</t>
         </is>
       </c>
       <c r="M36" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="N36" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="Q36" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37">
@@ -21453,20 +21695,20 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>SteelBlade</t>
+          <t>IronLance</t>
         </is>
       </c>
       <c r="M37" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N37" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>-4</v>
+        <v>4</v>
       </c>
       <c r="Q37" t="n">
         <v>8</v>
@@ -21475,7 +21717,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x80_Soldier</t>
+          <t>0x81_Soldier</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -21510,20 +21752,20 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>IronLance</t>
+          <t>SteelBlade</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N38" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="Q38" t="n">
         <v>8</v>
@@ -21567,20 +21809,20 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>SteelBlade</t>
+          <t>IronLance</t>
         </is>
       </c>
       <c r="M39" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N39" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>-4</v>
+        <v>4</v>
       </c>
       <c r="Q39" t="n">
         <v>8</v>
@@ -21589,51 +21831,71 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xF5_CivMan</t>
+          <t>0x80_Soldier</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>10</v>
       </c>
       <c r="C40" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="n">
+        <v>6</v>
+      </c>
+      <c r="G40" t="n">
+        <v>4</v>
+      </c>
+      <c r="H40" t="n">
         <v>1</v>
       </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="n">
-        <v>2</v>
-      </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>23</v>
+      </c>
+      <c r="N40" t="n">
+        <v>97</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0xF6_CivWoman</t>
+          <t>0xF5_CivMan</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>10</v>
       </c>
       <c r="C41" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -21651,26 +21913,26 @@
         <v>2</v>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0xF5_Peer</t>
+          <t>0xF6_CivWoman</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>10</v>
       </c>
       <c r="C42" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -21679,7 +21941,7 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -21688,147 +21950,147 @@
         <v>2</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0xF6_MageGeneral</t>
+          <t>0xF5_Peer</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>10</v>
       </c>
       <c r="C43" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I43" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Eagle_MageGeneral</t>
+          <t>0xF6_MageGeneral</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>10</v>
       </c>
       <c r="C44" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D44" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H44" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I44" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J44" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x80_CivWoman</t>
+          <t>Eagle_MageGeneral</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>10</v>
       </c>
       <c r="C45" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K45" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x80_UpstartM</t>
+          <t>0x80_CivWoman</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>10</v>
       </c>
       <c r="C46" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
       </c>
       <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
         <v>1</v>
       </c>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
@@ -21836,121 +22098,121 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Prince_Noble</t>
+          <t>0x80_UpstartM</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>10</v>
       </c>
       <c r="C47" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D47" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Songbird_Bard</t>
+          <t>Prince_Noble</t>
         </is>
       </c>
       <c r="B48" t="n">
+        <v>10</v>
+      </c>
+      <c r="C48" t="n">
+        <v>27</v>
+      </c>
+      <c r="D48" t="n">
+        <v>8</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>15</v>
+      </c>
+      <c r="G48" t="n">
+        <v>13</v>
+      </c>
+      <c r="H48" t="n">
+        <v>7</v>
+      </c>
+      <c r="I48" t="n">
+        <v>2</v>
+      </c>
+      <c r="J48" t="n">
         <v>3</v>
       </c>
-      <c r="C48" t="n">
-        <v>19</v>
-      </c>
-      <c r="D48" t="n">
-        <v>2</v>
-      </c>
-      <c r="E48" t="n">
-        <v>2</v>
-      </c>
-      <c r="F48" t="n">
-        <v>5</v>
-      </c>
-      <c r="G48" t="n">
-        <v>9</v>
-      </c>
-      <c r="H48" t="n">
-        <v>2</v>
-      </c>
-      <c r="I48" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" t="n">
-        <v>8</v>
-      </c>
       <c r="K48" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x80_CivMan</t>
+          <t>Songbird_Bard</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C49" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F49" t="n">
+        <v>5</v>
+      </c>
+      <c r="G49" t="n">
+        <v>9</v>
+      </c>
+      <c r="H49" t="n">
+        <v>2</v>
+      </c>
+      <c r="I49" t="n">
         <v>1</v>
       </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="n">
-        <v>2</v>
-      </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K49" t="n">
         <v>6</v>
@@ -21959,14 +22221,14 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x81_CivWoman</t>
+          <t>0x80_CivMan</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>10</v>
       </c>
       <c r="C50" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -21984,26 +22246,26 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x82_CivMan</t>
+          <t>0x81_CivWoman</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>10</v>
       </c>
       <c r="C51" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -22021,26 +22283,26 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x83_CivWoman</t>
+          <t>0x82_CivMan</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>10</v>
       </c>
       <c r="C52" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
@@ -22058,26 +22320,26 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x84_Peer</t>
+          <t>0x83_CivWoman</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>10</v>
       </c>
       <c r="C53" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -22086,7 +22348,7 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -22095,19 +22357,19 @@
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x85_CivMan</t>
+          <t>0x84_Peer</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -22123,7 +22385,7 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -22132,19 +22394,19 @@
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x86_Peer</t>
+          <t>0x85_CivMan</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -22160,7 +22422,7 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -22169,26 +22431,26 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x87_CivWoman</t>
+          <t>0x86_Peer</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>10</v>
       </c>
       <c r="C56" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -22197,7 +22459,7 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -22206,26 +22468,26 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x88_CivMan</t>
+          <t>0x87_CivWoman</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>10</v>
       </c>
       <c r="C57" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -22243,70 +22505,292 @@
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>0x88_CivMan</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>10</v>
+      </c>
+      <c r="C58" t="n">
+        <v>12</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>2</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>0xAE_MogallClass</t>
         </is>
       </c>
-      <c r="B58" t="n">
-        <v>10</v>
-      </c>
-      <c r="C58" t="n">
+      <c r="B59" t="n">
+        <v>10</v>
+      </c>
+      <c r="C59" t="n">
         <v>40</v>
       </c>
-      <c r="D58" t="n">
+      <c r="D59" t="n">
         <v>15</v>
       </c>
-      <c r="E58" t="n">
+      <c r="E59" t="n">
         <v>21</v>
       </c>
-      <c r="F58" t="n">
-        <v>12</v>
-      </c>
-      <c r="G58" t="n">
+      <c r="F59" t="n">
+        <v>12</v>
+      </c>
+      <c r="G59" t="n">
         <v>15</v>
       </c>
-      <c r="H58" t="n">
-        <v>4</v>
-      </c>
-      <c r="I58" t="n">
+      <c r="H59" t="n">
+        <v>4</v>
+      </c>
+      <c r="I59" t="n">
         <v>17</v>
       </c>
-      <c r="J58" t="n">
-        <v>4</v>
-      </c>
-      <c r="K58" t="n">
+      <c r="J59" t="n">
+        <v>4</v>
+      </c>
+      <c r="K59" t="n">
         <v>9</v>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>EvilEye</t>
         </is>
       </c>
-      <c r="M58" t="n">
+      <c r="M59" t="n">
         <v>28</v>
       </c>
-      <c r="N58" t="n">
+      <c r="N59" t="n">
         <v>123</v>
       </c>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="n">
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
         <v>15</v>
       </c>
-      <c r="Q58" t="n">
+      <c r="Q59" t="n">
         <v>34</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>0x80_Sage</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>10</v>
+      </c>
+      <c r="C60" t="n">
+        <v>24</v>
+      </c>
+      <c r="D60" t="n">
+        <v>4</v>
+      </c>
+      <c r="E60" t="n">
+        <v>8</v>
+      </c>
+      <c r="F60" t="n">
+        <v>12</v>
+      </c>
+      <c r="G60" t="n">
+        <v>10</v>
+      </c>
+      <c r="H60" t="n">
+        <v>5</v>
+      </c>
+      <c r="I60" t="n">
+        <v>10</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>0x81_Druid</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>10</v>
+      </c>
+      <c r="C61" t="n">
+        <v>36</v>
+      </c>
+      <c r="D61" t="n">
+        <v>5</v>
+      </c>
+      <c r="E61" t="n">
+        <v>9</v>
+      </c>
+      <c r="F61" t="n">
+        <v>12</v>
+      </c>
+      <c r="G61" t="n">
+        <v>8</v>
+      </c>
+      <c r="H61" t="n">
+        <v>6</v>
+      </c>
+      <c r="I61" t="n">
+        <v>14</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>0x82_Druid</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>10</v>
+      </c>
+      <c r="C62" t="n">
+        <v>36</v>
+      </c>
+      <c r="D62" t="n">
+        <v>5</v>
+      </c>
+      <c r="E62" t="n">
+        <v>9</v>
+      </c>
+      <c r="F62" t="n">
+        <v>12</v>
+      </c>
+      <c r="G62" t="n">
+        <v>8</v>
+      </c>
+      <c r="H62" t="n">
+        <v>6</v>
+      </c>
+      <c r="I62" t="n">
+        <v>14</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>0x83_Druid</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>10</v>
+      </c>
+      <c r="C63" t="n">
+        <v>36</v>
+      </c>
+      <c r="D63" t="n">
+        <v>5</v>
+      </c>
+      <c r="E63" t="n">
+        <v>9</v>
+      </c>
+      <c r="F63" t="n">
+        <v>12</v>
+      </c>
+      <c r="G63" t="n">
+        <v>8</v>
+      </c>
+      <c r="H63" t="n">
+        <v>6</v>
+      </c>
+      <c r="I63" t="n">
+        <v>14</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>0x81_Peer</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>10</v>
+      </c>
+      <c r="C64" t="n">
+        <v>12</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/unit_stats.xlsx
+++ b/unit_stats.xlsx
@@ -17,6 +17,10 @@
     <sheet name="Ch3 Normal" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Ch4 Hard" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Ch4 Normal" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Ch5 Hard" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Ch5 Normal" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Ch5d Hard" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Ch5d Normal" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1247,7 +1251,7 @@
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H14" t="n">
         <v>10</v>
@@ -1276,10 +1280,10 @@
         <v>15</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q14" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -1304,7 +1308,7 @@
         <v>10</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
         <v>10</v>
@@ -1333,10 +1337,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q15" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -1463,7 +1467,7 @@
         <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
@@ -1475,16 +1479,16 @@
         <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" t="n">
         <v>5</v>
       </c>
-      <c r="I18" t="n">
-        <v>6</v>
-      </c>
       <c r="J18" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K18" t="n">
         <v>6</v>
@@ -1498,16 +1502,16 @@
         <v>17</v>
       </c>
       <c r="N18" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="O18" t="n">
         <v>20</v>
       </c>
       <c r="P18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q18" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1520,7 +1524,7 @@
         <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
@@ -1532,16 +1536,16 @@
         <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" t="n">
         <v>5</v>
       </c>
-      <c r="I19" t="n">
-        <v>6</v>
-      </c>
       <c r="J19" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K19" t="n">
         <v>6</v>
@@ -1555,16 +1559,16 @@
         <v>18</v>
       </c>
       <c r="N19" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q19" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -3872,7 +3876,7 @@
         <v>10</v>
       </c>
       <c r="G23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H23" t="n">
         <v>10</v>
@@ -3901,10 +3905,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q23" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
@@ -5782,6 +5786,942 @@
       </c>
       <c r="K64" t="n">
         <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="4" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="5" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="6" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="7" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>UnitID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Lv</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Str</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Mag</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Skl</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Spd</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Def</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Res</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Luck</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Con</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Atk</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Crit</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>AS</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Dragon_Veteran</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C2" t="n">
+        <v>72</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>21</v>
+      </c>
+      <c r="G2" t="n">
+        <v>17</v>
+      </c>
+      <c r="H2" t="n">
+        <v>15</v>
+      </c>
+      <c r="I2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2" t="n">
+        <v>11</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>32</v>
+      </c>
+      <c r="N2" t="n">
+        <v>137</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Dragon_Veteran</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" t="n">
+        <v>72</v>
+      </c>
+      <c r="D3" t="n">
+        <v>24</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>21</v>
+      </c>
+      <c r="G3" t="n">
+        <v>17</v>
+      </c>
+      <c r="H3" t="n">
+        <v>15</v>
+      </c>
+      <c r="I3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>11</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>37</v>
+      </c>
+      <c r="N3" t="n">
+        <v>132</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="4" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="5" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="6" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="7" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>UnitID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Lv</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Str</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Mag</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Skl</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Spd</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Def</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Res</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Luck</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Con</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Atk</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Crit</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>AS</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Dragon_Veteran</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C2" t="n">
+        <v>72</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>21</v>
+      </c>
+      <c r="G2" t="n">
+        <v>17</v>
+      </c>
+      <c r="H2" t="n">
+        <v>15</v>
+      </c>
+      <c r="I2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2" t="n">
+        <v>11</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>32</v>
+      </c>
+      <c r="N2" t="n">
+        <v>137</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Dragon_Veteran</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" t="n">
+        <v>72</v>
+      </c>
+      <c r="D3" t="n">
+        <v>24</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>21</v>
+      </c>
+      <c r="G3" t="n">
+        <v>17</v>
+      </c>
+      <c r="H3" t="n">
+        <v>15</v>
+      </c>
+      <c r="I3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>11</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>37</v>
+      </c>
+      <c r="N3" t="n">
+        <v>132</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="4" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="5" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="6" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="7" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>UnitID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Lv</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Str</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Mag</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Skl</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Spd</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Def</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Res</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Luck</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Con</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Atk</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Crit</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>AS</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Dragon_Veteran</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C2" t="n">
+        <v>72</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>21</v>
+      </c>
+      <c r="G2" t="n">
+        <v>17</v>
+      </c>
+      <c r="H2" t="n">
+        <v>15</v>
+      </c>
+      <c r="I2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2" t="n">
+        <v>11</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>32</v>
+      </c>
+      <c r="N2" t="n">
+        <v>137</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Dragon_Veteran</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" t="n">
+        <v>72</v>
+      </c>
+      <c r="D3" t="n">
+        <v>24</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>21</v>
+      </c>
+      <c r="G3" t="n">
+        <v>17</v>
+      </c>
+      <c r="H3" t="n">
+        <v>15</v>
+      </c>
+      <c r="I3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>11</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>37</v>
+      </c>
+      <c r="N3" t="n">
+        <v>132</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="4" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="5" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="6" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="7" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>UnitID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Lv</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Str</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Mag</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Skl</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Spd</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Def</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Res</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Luck</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Con</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Atk</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Crit</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>AS</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Dragon_Veteran</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C2" t="n">
+        <v>72</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>21</v>
+      </c>
+      <c r="G2" t="n">
+        <v>17</v>
+      </c>
+      <c r="H2" t="n">
+        <v>15</v>
+      </c>
+      <c r="I2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2" t="n">
+        <v>11</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>32</v>
+      </c>
+      <c r="N2" t="n">
+        <v>137</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Dragon_Veteran</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" t="n">
+        <v>72</v>
+      </c>
+      <c r="D3" t="n">
+        <v>24</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>21</v>
+      </c>
+      <c r="G3" t="n">
+        <v>17</v>
+      </c>
+      <c r="H3" t="n">
+        <v>15</v>
+      </c>
+      <c r="I3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>11</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>37</v>
+      </c>
+      <c r="N3" t="n">
+        <v>132</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -6610,7 +7550,7 @@
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H14" t="n">
         <v>10</v>
@@ -6639,10 +7579,10 @@
         <v>15</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q14" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -6667,7 +7607,7 @@
         <v>10</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
         <v>10</v>
@@ -6696,10 +7636,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q15" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -6826,7 +7766,7 @@
         <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
@@ -6838,16 +7778,16 @@
         <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" t="n">
         <v>5</v>
       </c>
-      <c r="I18" t="n">
-        <v>6</v>
-      </c>
       <c r="J18" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K18" t="n">
         <v>6</v>
@@ -6861,16 +7801,16 @@
         <v>17</v>
       </c>
       <c r="N18" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="O18" t="n">
         <v>20</v>
       </c>
       <c r="P18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q18" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6883,7 +7823,7 @@
         <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
@@ -6895,16 +7835,16 @@
         <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" t="n">
         <v>5</v>
       </c>
-      <c r="I19" t="n">
-        <v>6</v>
-      </c>
       <c r="J19" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K19" t="n">
         <v>6</v>
@@ -6918,16 +7858,16 @@
         <v>18</v>
       </c>
       <c r="N19" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q19" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -9275,7 +10215,7 @@
         <v>15</v>
       </c>
       <c r="G23" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H23" t="n">
         <v>5</v>
@@ -9304,10 +10244,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q23" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -10649,7 +11589,7 @@
         <v>15</v>
       </c>
       <c r="G23" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H23" t="n">
         <v>5</v>
@@ -10678,10 +11618,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q23" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -12687,7 +13627,7 @@
         <v>10</v>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H35" t="n">
         <v>10</v>
@@ -12716,10 +13656,10 @@
         <v>15</v>
       </c>
       <c r="P35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q35" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36">
@@ -12744,7 +13684,7 @@
         <v>10</v>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H36" t="n">
         <v>10</v>
@@ -12773,10 +13713,10 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q36" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37">
@@ -14856,7 +15796,7 @@
         <v>10</v>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H35" t="n">
         <v>10</v>
@@ -14885,10 +15825,10 @@
         <v>15</v>
       </c>
       <c r="P35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q35" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36">
@@ -14913,7 +15853,7 @@
         <v>10</v>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H36" t="n">
         <v>10</v>
@@ -14942,10 +15882,10 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q36" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37">
@@ -17198,7 +18138,7 @@
         <v>5</v>
       </c>
       <c r="C40" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D40" t="n">
         <v>6</v>
@@ -17210,16 +18150,16 @@
         <v>10</v>
       </c>
       <c r="G40" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H40" t="n">
+        <v>3</v>
+      </c>
+      <c r="I40" t="n">
         <v>5</v>
       </c>
-      <c r="I40" t="n">
-        <v>6</v>
-      </c>
       <c r="J40" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K40" t="n">
         <v>6</v>
@@ -17233,16 +18173,16 @@
         <v>17</v>
       </c>
       <c r="N40" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="O40" t="n">
         <v>20</v>
       </c>
       <c r="P40" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q40" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41">
@@ -17255,7 +18195,7 @@
         <v>5</v>
       </c>
       <c r="C41" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D41" t="n">
         <v>6</v>
@@ -17267,16 +18207,16 @@
         <v>10</v>
       </c>
       <c r="G41" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H41" t="n">
+        <v>3</v>
+      </c>
+      <c r="I41" t="n">
         <v>5</v>
       </c>
-      <c r="I41" t="n">
-        <v>6</v>
-      </c>
       <c r="J41" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K41" t="n">
         <v>6</v>
@@ -17290,16 +18230,16 @@
         <v>18</v>
       </c>
       <c r="N41" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q41" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -19478,7 +20418,7 @@
         <v>5</v>
       </c>
       <c r="C40" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D40" t="n">
         <v>6</v>
@@ -19490,16 +20430,16 @@
         <v>10</v>
       </c>
       <c r="G40" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H40" t="n">
+        <v>3</v>
+      </c>
+      <c r="I40" t="n">
         <v>5</v>
       </c>
-      <c r="I40" t="n">
-        <v>6</v>
-      </c>
       <c r="J40" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K40" t="n">
         <v>6</v>
@@ -19513,16 +20453,16 @@
         <v>17</v>
       </c>
       <c r="N40" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="O40" t="n">
         <v>20</v>
       </c>
       <c r="P40" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q40" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41">
@@ -19535,7 +20475,7 @@
         <v>5</v>
       </c>
       <c r="C41" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D41" t="n">
         <v>6</v>
@@ -19547,16 +20487,16 @@
         <v>10</v>
       </c>
       <c r="G41" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H41" t="n">
+        <v>3</v>
+      </c>
+      <c r="I41" t="n">
         <v>5</v>
       </c>
-      <c r="I41" t="n">
-        <v>6</v>
-      </c>
       <c r="J41" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K41" t="n">
         <v>6</v>
@@ -19570,16 +20510,16 @@
         <v>18</v>
       </c>
       <c r="N41" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q41" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -20881,7 +21821,7 @@
         <v>12</v>
       </c>
       <c r="G23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H23" t="n">
         <v>11</v>
@@ -20910,10 +21850,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q23" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24">

--- a/unit_stats.xlsx
+++ b/unit_stats.xlsx
@@ -5799,10 +5799,820 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="4" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="5" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="6" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="7" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>UnitID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Lv</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Str</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Mag</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Skl</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Spd</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Def</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Res</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Luck</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Con</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Atk</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Crit</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>AS</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Dragon_Veteran</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C2" t="n">
+        <v>72</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>21</v>
+      </c>
+      <c r="G2" t="n">
+        <v>17</v>
+      </c>
+      <c r="H2" t="n">
+        <v>15</v>
+      </c>
+      <c r="I2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2" t="n">
+        <v>11</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>32</v>
+      </c>
+      <c r="N2" t="n">
+        <v>137</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Dragon_Veteran</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" t="n">
+        <v>72</v>
+      </c>
+      <c r="D3" t="n">
+        <v>24</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>21</v>
+      </c>
+      <c r="G3" t="n">
+        <v>17</v>
+      </c>
+      <c r="H3" t="n">
+        <v>15</v>
+      </c>
+      <c r="I3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>11</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>37</v>
+      </c>
+      <c r="N3" t="n">
+        <v>132</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ch5Eagle_MageGeneral</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>34</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>19</v>
+      </c>
+      <c r="G4" t="n">
+        <v>20</v>
+      </c>
+      <c r="H4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I4" t="n">
+        <v>17</v>
+      </c>
+      <c r="J4" t="n">
+        <v>14</v>
+      </c>
+      <c r="K4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>AblatioPhoton</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>31</v>
+      </c>
+      <c r="N4" t="n">
+        <v>172</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Ch5Eagle_MageGeneral</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>34</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>19</v>
+      </c>
+      <c r="G5" t="n">
+        <v>20</v>
+      </c>
+      <c r="H5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J5" t="n">
+        <v>14</v>
+      </c>
+      <c r="K5" t="n">
+        <v>8</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Elfire</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>12</v>
+      </c>
+      <c r="N5" t="n">
+        <v>147</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Storm_Myrmidon</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C6" t="n">
+        <v>34</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G6" t="n">
+        <v>15</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>8</v>
+      </c>
+      <c r="K6" t="n">
+        <v>10</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>SteelSword</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>17</v>
+      </c>
+      <c r="N6" t="n">
+        <v>111</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="4" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="5" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="6" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="7" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>UnitID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Lv</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Str</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Mag</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Skl</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Spd</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Def</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Res</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Luck</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Con</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Atk</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Crit</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>AS</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Dragon_Veteran</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C2" t="n">
+        <v>72</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>21</v>
+      </c>
+      <c r="G2" t="n">
+        <v>17</v>
+      </c>
+      <c r="H2" t="n">
+        <v>15</v>
+      </c>
+      <c r="I2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2" t="n">
+        <v>11</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>32</v>
+      </c>
+      <c r="N2" t="n">
+        <v>137</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Dragon_Veteran</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" t="n">
+        <v>72</v>
+      </c>
+      <c r="D3" t="n">
+        <v>24</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>21</v>
+      </c>
+      <c r="G3" t="n">
+        <v>17</v>
+      </c>
+      <c r="H3" t="n">
+        <v>15</v>
+      </c>
+      <c r="I3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>11</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>37</v>
+      </c>
+      <c r="N3" t="n">
+        <v>132</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ch5Eagle_MageGeneral</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>34</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>19</v>
+      </c>
+      <c r="G4" t="n">
+        <v>20</v>
+      </c>
+      <c r="H4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I4" t="n">
+        <v>17</v>
+      </c>
+      <c r="J4" t="n">
+        <v>14</v>
+      </c>
+      <c r="K4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>AblatioPhoton</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>31</v>
+      </c>
+      <c r="N4" t="n">
+        <v>172</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Ch5Eagle_MageGeneral</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>34</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>19</v>
+      </c>
+      <c r="G5" t="n">
+        <v>20</v>
+      </c>
+      <c r="H5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J5" t="n">
+        <v>14</v>
+      </c>
+      <c r="K5" t="n">
+        <v>8</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Elfire</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>12</v>
+      </c>
+      <c r="N5" t="n">
+        <v>147</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Storm_Myrmidon</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C6" t="n">
+        <v>34</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G6" t="n">
+        <v>15</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>8</v>
+      </c>
+      <c r="K6" t="n">
+        <v>10</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>SteelSword</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>17</v>
+      </c>
+      <c r="N6" t="n">
+        <v>111</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="4" customWidth="1" min="2" max="2"/>
     <col width="4" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
@@ -5814,10 +6624,10 @@
     <col width="6" customWidth="1" min="10" max="10"/>
     <col width="5" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="5" customWidth="1" min="13" max="13"/>
-    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
     <col width="6" customWidth="1" min="15" max="15"/>
-    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
     <col width="7" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
@@ -6022,21 +6832,95 @@
         <v>39</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>JabberwockBoss_Jabberwock</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C4" t="n">
+        <v>57</v>
+      </c>
+      <c r="D4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Beast_Revenant</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C5" t="n">
+        <v>53</v>
+      </c>
+      <c r="D5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="4" customWidth="1" min="2" max="2"/>
     <col width="4" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
@@ -6048,10 +6932,10 @@
     <col width="6" customWidth="1" min="10" max="10"/>
     <col width="5" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="5" customWidth="1" min="13" max="13"/>
-    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
     <col width="6" customWidth="1" min="15" max="15"/>
-    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
     <col width="7" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
@@ -6256,472 +7140,78 @@
         <v>39</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Q3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="4" customWidth="1" min="2" max="2"/>
-    <col width="4" customWidth="1" min="3" max="3"/>
-    <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="5" customWidth="1" min="7" max="7"/>
-    <col width="5" customWidth="1" min="8" max="8"/>
-    <col width="5" customWidth="1" min="9" max="9"/>
-    <col width="6" customWidth="1" min="10" max="10"/>
-    <col width="5" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="5" customWidth="1" min="13" max="13"/>
-    <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="6" customWidth="1" min="15" max="15"/>
-    <col width="4" customWidth="1" min="16" max="16"/>
-    <col width="7" customWidth="1" min="17" max="17"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>UnitID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Lv</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Str</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Mag</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Skl</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Spd</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Def</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Res</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Luck</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Con</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Weapon</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Atk</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Hit</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Crit</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>AS</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Avoid</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Dragon_Veteran</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>10</v>
-      </c>
-      <c r="C2" t="n">
-        <v>72</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24</v>
-      </c>
-      <c r="E2" t="n">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>JabberwockBoss_Jabberwock</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C4" t="n">
+        <v>57</v>
+      </c>
+      <c r="D4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Beast_Revenant</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C5" t="n">
+        <v>53</v>
+      </c>
+      <c r="D5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" t="n">
         <v>3</v>
       </c>
-      <c r="F2" t="n">
-        <v>21</v>
-      </c>
-      <c r="G2" t="n">
-        <v>17</v>
-      </c>
-      <c r="H2" t="n">
-        <v>15</v>
-      </c>
-      <c r="I2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K2" t="n">
-        <v>11</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>IronLance</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>32</v>
-      </c>
-      <c r="N2" t="n">
-        <v>137</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Dragon_Veteran</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>10</v>
-      </c>
-      <c r="C3" t="n">
-        <v>72</v>
-      </c>
-      <c r="D3" t="n">
-        <v>24</v>
-      </c>
-      <c r="E3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F3" t="n">
-        <v>21</v>
-      </c>
-      <c r="G3" t="n">
-        <v>17</v>
-      </c>
-      <c r="H3" t="n">
-        <v>15</v>
-      </c>
-      <c r="I3" t="n">
-        <v>8</v>
-      </c>
-      <c r="J3" t="n">
-        <v>5</v>
-      </c>
-      <c r="K3" t="n">
-        <v>11</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>SteelBlade</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>37</v>
-      </c>
-      <c r="N3" t="n">
-        <v>132</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>39</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Q3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="4" customWidth="1" min="2" max="2"/>
-    <col width="4" customWidth="1" min="3" max="3"/>
-    <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="5" customWidth="1" min="7" max="7"/>
-    <col width="5" customWidth="1" min="8" max="8"/>
-    <col width="5" customWidth="1" min="9" max="9"/>
-    <col width="6" customWidth="1" min="10" max="10"/>
-    <col width="5" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="5" customWidth="1" min="13" max="13"/>
-    <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="6" customWidth="1" min="15" max="15"/>
-    <col width="4" customWidth="1" min="16" max="16"/>
-    <col width="7" customWidth="1" min="17" max="17"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>UnitID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Lv</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Str</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Mag</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Skl</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Spd</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Def</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Res</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Luck</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Con</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Weapon</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Atk</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Hit</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Crit</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>AS</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Avoid</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Dragon_Veteran</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>10</v>
-      </c>
-      <c r="C2" t="n">
-        <v>72</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24</v>
-      </c>
-      <c r="E2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F2" t="n">
-        <v>21</v>
-      </c>
-      <c r="G2" t="n">
-        <v>17</v>
-      </c>
-      <c r="H2" t="n">
-        <v>15</v>
-      </c>
-      <c r="I2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K2" t="n">
-        <v>11</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>IronLance</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>32</v>
-      </c>
-      <c r="N2" t="n">
-        <v>137</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Dragon_Veteran</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>10</v>
-      </c>
-      <c r="C3" t="n">
-        <v>72</v>
-      </c>
-      <c r="D3" t="n">
-        <v>24</v>
-      </c>
-      <c r="E3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F3" t="n">
-        <v>21</v>
-      </c>
-      <c r="G3" t="n">
-        <v>17</v>
-      </c>
-      <c r="H3" t="n">
-        <v>15</v>
-      </c>
-      <c r="I3" t="n">
-        <v>8</v>
-      </c>
-      <c r="J3" t="n">
-        <v>5</v>
-      </c>
-      <c r="K3" t="n">
-        <v>11</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>SteelBlade</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>37</v>
-      </c>
-      <c r="N3" t="n">
-        <v>132</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>39</v>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/unit_stats.xlsx
+++ b/unit_stats.xlsx
@@ -6609,10 +6609,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
     <col width="4" customWidth="1" min="2" max="2"/>
     <col width="4" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
@@ -6842,7 +6842,7 @@
         <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D4" t="n">
         <v>11</v>
@@ -6854,13 +6854,13 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -6872,38 +6872,229 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Beast_Revenant</t>
+          <t>JabberwockBlocker_Revenant</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G5" t="n">
         <v>5</v>
       </c>
-      <c r="G5" t="n">
-        <v>3</v>
-      </c>
       <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>4</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>7</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>RottenClaw</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>22</v>
+      </c>
+      <c r="N5" t="n">
+        <v>107</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>JabberwockBlocker_BowBone</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C6" t="n">
+        <v>23</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>16</v>
+      </c>
+      <c r="G6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Longbow</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>17</v>
+      </c>
+      <c r="N6" t="n">
+        <v>108</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>JabberwockSiege_MogallClass</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" t="n">
+        <v>9</v>
+      </c>
+      <c r="D7" t="n">
+        <v>14</v>
+      </c>
+      <c r="E7" t="n">
+        <v>20</v>
+      </c>
+      <c r="F7" t="n">
+        <v>11</v>
+      </c>
+      <c r="G7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>16</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>9</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Shadowshot</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>33</v>
+      </c>
+      <c r="N7" t="n">
+        <v>105</v>
+      </c>
+      <c r="O7" t="n">
+        <v>5</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>JabberwockAttacker_Mauthedoog</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C8" t="n">
+        <v>32</v>
+      </c>
+      <c r="D8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>28</v>
+      </c>
+      <c r="G8" t="n">
+        <v>28</v>
+      </c>
+      <c r="H8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>11</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>FireFang</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>20</v>
+      </c>
+      <c r="N8" t="n">
+        <v>159</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -6917,10 +7108,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
     <col width="4" customWidth="1" min="2" max="2"/>
     <col width="4" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
@@ -7150,7 +7341,7 @@
         <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D4" t="n">
         <v>11</v>
@@ -7162,13 +7353,13 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -7180,26 +7371,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Beast_Revenant</t>
+          <t>JabberwockBlocker_Revenant</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
@@ -7212,6 +7403,197 @@
       </c>
       <c r="K5" t="n">
         <v>7</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>RottenClaw</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>19</v>
+      </c>
+      <c r="N5" t="n">
+        <v>104</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>JabberwockBlocker_BowBone</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C6" t="n">
+        <v>19</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" t="n">
+        <v>11</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Longbow</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>15</v>
+      </c>
+      <c r="N6" t="n">
+        <v>103</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>JabberwockSiege_MogallClass</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" t="n">
+        <v>11</v>
+      </c>
+      <c r="E7" t="n">
+        <v>17</v>
+      </c>
+      <c r="F7" t="n">
+        <v>9</v>
+      </c>
+      <c r="G7" t="n">
+        <v>7</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>15</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>9</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Shadowshot</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>30</v>
+      </c>
+      <c r="N7" t="n">
+        <v>100</v>
+      </c>
+      <c r="O7" t="n">
+        <v>5</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>JabberwockAttacker_Mauthedoog</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C8" t="n">
+        <v>28</v>
+      </c>
+      <c r="D8" t="n">
+        <v>13</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>25</v>
+      </c>
+      <c r="G8" t="n">
+        <v>25</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>11</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>FireFang</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>18</v>
+      </c>
+      <c r="N8" t="n">
+        <v>152</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/unit_stats.xlsx
+++ b/unit_stats.xlsx
@@ -7781,7 +7781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W49"/>
+  <dimension ref="A1:W57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8086,10 +8086,10 @@
         <v>7</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>5</v>
@@ -8118,7 +8118,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="N4" s="2" t="n">
         <v>101</v>
@@ -8136,19 +8136,19 @@
         <v>11</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="T4" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="V4" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="U4" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="V4" s="2" t="n">
-        <v>18</v>
-      </c>
       <c r="W4" s="2" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
@@ -8493,7 +8493,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>105</v>
@@ -8718,7 +8718,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N12" s="2" t="n">
         <v>117</v>
@@ -8980,67 +8980,67 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>0x80_General</t>
+          <t>SoldierChar_Knight</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
         <v>7</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D17" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="E17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="H17" s="3" t="n">
-        <v>16</v>
-      </c>
       <c r="I17" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>PatientKatti</t>
+          <t>SteelLance</t>
         </is>
       </c>
       <c r="M17" s="3" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>126</v>
+        <v>89</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>31</v>
@@ -9049,7 +9049,7 @@
         <v>22</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18">
@@ -9090,17 +9090,17 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>SteelSword</t>
+          <t>PatientKatti</t>
         </is>
       </c>
       <c r="M18" s="3" t="n">
         <v>23</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>5</v>
@@ -9130,76 +9130,76 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>0x81_CivWoman</t>
+          <t>0x80_General</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
         <v>7</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>PatientKatti</t>
+          <t>SteelSword</t>
         </is>
       </c>
       <c r="M19" s="3" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>-3</v>
+        <v>5</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20">
@@ -9240,26 +9240,26 @@
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>SteelSword</t>
+          <t>PatientKatti</t>
         </is>
       </c>
       <c r="M20" s="3" t="n">
         <v>10</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>12</v>
@@ -9280,14 +9280,14 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>0x81_CivMan</t>
+          <t>0x81_CivWoman</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
         <v>7</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
@@ -9305,51 +9305,51 @@
         <v>0</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>PatientKatti</t>
+          <t>SteelSword</t>
         </is>
       </c>
       <c r="M21" s="3" t="n">
         <v>10</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -9390,26 +9390,26 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>SteelSword</t>
+          <t>PatientKatti</t>
         </is>
       </c>
       <c r="M22" s="3" t="n">
         <v>10</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="Q22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>14</v>
@@ -9430,110 +9430,110 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Eagle_MageGeneral</t>
+          <t>0x81_CivMan</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
         <v>7</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>SteelSword</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S23" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="T23" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="U23" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="E23" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="H23" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="J23" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="K23" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>Quickblade</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="N23" s="3" t="n">
-        <v>137</v>
-      </c>
-      <c r="O23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q23" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="R23" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="S23" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="T23" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="U23" s="3" t="n">
-        <v>42</v>
-      </c>
       <c r="V23" s="3" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Gryphon_Peer</t>
+          <t>Eagle_MageGeneral</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
         <v>7</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F24" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I24" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="G24" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="I24" s="3" t="n">
-        <v>10</v>
-      </c>
       <c r="J24" s="3" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>8</v>
@@ -9544,102 +9544,118 @@
         </is>
       </c>
       <c r="M24" s="3" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>0xF2_CivWoman</t>
+          <t>Gryphon_Peer</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
         <v>7</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="L25" s="3" t="n"/>
-      <c r="M25" s="3" t="n"/>
-      <c r="N25" s="3" t="n"/>
-      <c r="O25" s="3" t="n"/>
-      <c r="P25" s="3" t="n"/>
-      <c r="Q25" s="3" t="n"/>
-      <c r="R25" s="3" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Quickblade</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q25" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>19</v>
+      </c>
       <c r="S25" s="3" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>0x82_CivWoman</t>
+          <t>0xF2_CivWoman</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
@@ -9661,7 +9677,7 @@
         <v>0</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>1</v>
@@ -9683,7 +9699,7 @@
         <v>12</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>9</v>
@@ -9692,20 +9708,20 @@
         <v>6</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>0x83_CivMan</t>
+          <t>0x82_CivWoman</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
         <v>7</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>0</v>
@@ -9723,13 +9739,13 @@
         <v>0</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L27" s="3" t="n"/>
       <c r="M27" s="3" t="n"/>
@@ -9739,42 +9755,42 @@
       <c r="Q27" s="3" t="n"/>
       <c r="R27" s="3" t="n"/>
       <c r="S27" s="3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>0x84_CivBoy</t>
+          <t>0x83_CivMan</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
         <v>7</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G28" s="3" t="n">
         <v>0</v>
       </c>
@@ -9782,13 +9798,13 @@
         <v>0</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L28" s="3" t="n"/>
       <c r="M28" s="3" t="n"/>
@@ -9798,35 +9814,35 @@
       <c r="Q28" s="3" t="n"/>
       <c r="R28" s="3" t="n"/>
       <c r="S28" s="3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>0x85_CivGirl</t>
+          <t>0x84_CivBoy</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
         <v>7</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>0</v>
@@ -9841,13 +9857,13 @@
         <v>0</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L29" s="3" t="n"/>
       <c r="M29" s="3" t="n"/>
@@ -9857,10 +9873,10 @@
       <c r="Q29" s="3" t="n"/>
       <c r="R29" s="3" t="n"/>
       <c r="S29" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>7</v>
@@ -9869,44 +9885,44 @@
         <v>5</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>0x86_CivBoy</t>
+          <t>0x85_CivGirl</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
         <v>7</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="J30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L30" s="3" t="n"/>
       <c r="M30" s="3" t="n"/>
@@ -9916,10 +9932,10 @@
       <c r="Q30" s="3" t="n"/>
       <c r="R30" s="3" t="n"/>
       <c r="S30" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>7</v>
@@ -9928,38 +9944,38 @@
         <v>5</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>0xF1_CivWoman</t>
+          <t>0x86_CivBoy</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
         <v>7</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>0</v>
@@ -9975,32 +9991,32 @@
       <c r="Q31" s="3" t="n"/>
       <c r="R31" s="3" t="n"/>
       <c r="S31" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>0xF1_CivMan</t>
+          <t>0xF1_CivWoman</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
         <v>7</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>0</v>
@@ -10018,13 +10034,13 @@
         <v>2</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L32" s="3" t="n"/>
       <c r="M32" s="3" t="n"/>
@@ -10034,41 +10050,41 @@
       <c r="Q32" s="3" t="n"/>
       <c r="R32" s="3" t="n"/>
       <c r="S32" s="3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>0xF1_CivBoy</t>
+          <t>0xF1_CivMan</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
         <v>7</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>0</v>
@@ -10077,13 +10093,13 @@
         <v>2</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L33" s="3" t="n"/>
       <c r="M33" s="3" t="n"/>
@@ -10093,35 +10109,35 @@
       <c r="Q33" s="3" t="n"/>
       <c r="R33" s="3" t="n"/>
       <c r="S33" s="3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>0xF1_CivGirl</t>
+          <t>0xF1_CivBoy</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
         <v>7</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0</v>
@@ -10136,13 +10152,13 @@
         <v>2</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L34" s="3" t="n"/>
       <c r="M34" s="3" t="n"/>
@@ -10152,10 +10168,10 @@
       <c r="Q34" s="3" t="n"/>
       <c r="R34" s="3" t="n"/>
       <c r="S34" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>7</v>
@@ -10164,44 +10180,44 @@
         <v>5</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Baron_General</t>
+          <t>0xF1_CivGirl</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
         <v>7</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="L35" s="3" t="n"/>
       <c r="M35" s="3" t="n"/>
@@ -10211,123 +10227,107 @@
       <c r="Q35" s="3" t="n"/>
       <c r="R35" s="3" t="n"/>
       <c r="S35" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="T35" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="V35" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="W35" s="3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Baron_General</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="L36" s="3" t="n"/>
+      <c r="M36" s="3" t="n"/>
+      <c r="N36" s="3" t="n"/>
+      <c r="O36" s="3" t="n"/>
+      <c r="P36" s="3" t="n"/>
+      <c r="Q36" s="3" t="n"/>
+      <c r="R36" s="3" t="n"/>
+      <c r="S36" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="T35" s="3" t="n">
+      <c r="T36" s="3" t="n">
         <v>79</v>
       </c>
-      <c r="U35" s="3" t="n">
+      <c r="U36" s="3" t="n">
         <v>56</v>
       </c>
-      <c r="V35" s="3" t="n">
+      <c r="V36" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="W35" s="3" t="n">
+      <c r="W36" s="3" t="n">
         <v>51</v>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>Beast_Cyclops</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="G37" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="H37" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="I37" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="J37" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K37" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>SilverAxe</t>
-        </is>
-      </c>
-      <c r="M37" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="N37" s="4" t="n">
-        <v>115</v>
-      </c>
-      <c r="O37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q37" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="R37" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="S37" s="4" t="n">
-        <v>88</v>
-      </c>
-      <c r="T37" s="4" t="n">
-        <v>104</v>
-      </c>
-      <c r="U37" s="4" t="n">
-        <v>68</v>
-      </c>
-      <c r="V37" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="W37" s="4" t="n">
-        <v>64</v>
-      </c>
-    </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Beast_BowBone</t>
+          <t>Beast_Tarvos</t>
         </is>
       </c>
       <c r="B38" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G38" s="4" t="n">
         <v>14</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I38" s="4" t="n">
         <v>5</v>
@@ -10336,58 +10336,58 @@
         <v>1</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>SteelBow</t>
+          <t>SteelAxe</t>
         </is>
       </c>
       <c r="M38" s="4" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="O38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P38" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Q38" s="4" t="n">
         <v>29</v>
       </c>
       <c r="R38" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="T38" s="4" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="U38" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="V38" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="W38" s="4" t="n">
         <v>37</v>
-      </c>
-      <c r="V38" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="W38" s="4" t="n">
-        <v>33</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Beast_LanceBone</t>
+          <t>Beast_AxeBone</t>
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D39" s="4" t="n">
         <v>17</v>
@@ -10415,69 +10415,69 @@
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>SteelSword</t>
+          <t>Hammer</t>
         </is>
       </c>
       <c r="M39" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="O39" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P39" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Q39" s="4" t="n">
         <v>25</v>
       </c>
       <c r="R39" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="S39" s="4" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T39" s="4" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="U39" s="4" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V39" s="4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W39" s="4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Beast_SwordBone</t>
+          <t>Beast_Revenant</t>
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C40" s="4" t="n">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E40" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I40" s="4" t="n">
         <v>5</v>
@@ -10486,93 +10486,93 @@
         <v>1</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>SteelLance</t>
+          <t>RottenClaw</t>
         </is>
       </c>
       <c r="M40" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="O40" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P40" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q40" s="4" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="R40" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="S40" s="4" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="T40" s="4" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="U40" s="4" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="V40" s="4" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="W40" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Beast_Jabberwock</t>
+          <t>Lowlander_Fighter</t>
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C41" s="4" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="D41" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="E41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="4" t="n">
-        <v>4</v>
-      </c>
       <c r="G41" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I41" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J41" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J41" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K41" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>FetidClaw</t>
+          <t>Hammer</t>
         </is>
       </c>
       <c r="M41" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="O41" s="4" t="n">
         <v>0</v>
@@ -10581,416 +10581,416 @@
         <v>4</v>
       </c>
       <c r="Q41" s="4" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="R41" s="4" t="n">
         <v>8</v>
       </c>
       <c r="S41" s="4" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="T41" s="4" t="n">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="U41" s="4" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="V41" s="4" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="W41" s="4" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>0x87_MogallClass</t>
+          <t>Lowlander_HighMage</t>
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C42" s="4" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G42" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J42" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K42" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>Thunder</t>
+        </is>
+      </c>
+      <c r="M42" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="N42" s="4" t="n">
+        <v>116</v>
+      </c>
+      <c r="O42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q42" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="R42" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="H42" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I42" s="4" t="n">
+      <c r="S42" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="T42" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="U42" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="V42" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="W42" s="4" t="n">
         <v>16</v>
-      </c>
-      <c r="J42" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K42" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>EvilEye</t>
-        </is>
-      </c>
-      <c r="M42" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="N42" s="4" t="n">
-        <v>118</v>
-      </c>
-      <c r="O42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q42" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="R42" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="S42" s="4" t="n">
-        <v>54</v>
-      </c>
-      <c r="T42" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="U42" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="V42" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="W42" s="4" t="n">
-        <v>22</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>0x87_Bael</t>
+          <t>Lowlander_Soldier</t>
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C43" s="4" t="n">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E43" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I43" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J43" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K43" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>SavageGore</t>
+        </is>
+      </c>
+      <c r="M43" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="N43" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="O43" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="P43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="R43" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="J43" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K43" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="L43" s="4" t="inlineStr">
-        <is>
-          <t>SharpClaw</t>
-        </is>
-      </c>
-      <c r="M43" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="N43" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="O43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q43" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="R43" s="4" t="n">
-        <v>12</v>
-      </c>
       <c r="S43" s="4" t="n">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="T43" s="4" t="n">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="U43" s="4" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="V43" s="4" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="W43" s="4" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Beast_Bael</t>
+          <t>Lowlander_Archer</t>
         </is>
       </c>
       <c r="B44" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C44" s="4" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E44" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I44" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J44" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="J44" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="K44" s="4" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>SharpClaw</t>
+          <t>SteelBow</t>
         </is>
       </c>
       <c r="M44" s="4" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="O44" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P44" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q44" s="4" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="R44" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S44" s="4" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="T44" s="4" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="U44" s="4" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="V44" s="4" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="W44" s="4" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>0x87_Cyclops</t>
+          <t>Beast_SwordBone</t>
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E45" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>SharpClaw</t>
+          <t>Armorslayer</t>
         </is>
       </c>
       <c r="M45" s="4" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="O45" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P45" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="Q45" s="4" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="R45" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="S45" s="4" t="n">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="T45" s="4" t="n">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="U45" s="4" t="n">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="V45" s="4" t="n">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="W45" s="4" t="n">
-        <v>68</v>
+        <v>32</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>0x87_Revenant</t>
+          <t>Lowlander_LowMage</t>
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>SharpClaw</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="M46" s="4" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P46" s="4" t="n">
-        <v>-2</v>
+        <v>8</v>
       </c>
       <c r="Q46" s="4" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="R46" s="4" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="S46" s="4" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="T46" s="4" t="n">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="U46" s="4" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="V46" s="4" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W46" s="4" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>0x87_Mercenary</t>
+          <t>Beast_LanceBone</t>
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C47" s="4" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E47" s="4" t="n">
         <v>0</v>
@@ -10999,94 +10999,94 @@
         <v>14</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>SharpClaw</t>
+          <t>HeavySpear</t>
         </is>
       </c>
       <c r="M47" s="4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="O47" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P47" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q47" s="4" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="R47" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="S47" s="4" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="T47" s="4" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="U47" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="V47" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="V47" s="4" t="n">
-        <v>18</v>
-      </c>
       <c r="W47" s="4" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>0x87_LowMage</t>
+          <t>Beast_Bael</t>
         </is>
       </c>
       <c r="B48" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C48" s="4" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G48" s="4" t="n">
         <v>8</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>2</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
@@ -11094,50 +11094,50 @@
         </is>
       </c>
       <c r="M48" s="4" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O48" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P48" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q48" s="4" t="n">
         <v>18</v>
       </c>
       <c r="R48" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="S48" s="4" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="T48" s="4" t="n">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="U48" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="V48" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="W48" s="4" t="n">
         <v>39</v>
-      </c>
-      <c r="V48" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="W48" s="4" t="n">
-        <v>24</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>0x87_Gargoyle</t>
+          <t>Beast_Cyclops</t>
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C49" s="4" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="D49" s="4" t="n">
         <v>19</v>
@@ -11146,59 +11146,659 @@
         <v>0</v>
       </c>
       <c r="F49" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="I49" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J49" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="L49" s="4" t="inlineStr">
+        <is>
+          <t>SilverAxe</t>
+        </is>
+      </c>
+      <c r="M49" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="N49" s="4" t="n">
+        <v>115</v>
+      </c>
+      <c r="O49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q49" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="R49" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="S49" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="T49" s="4" t="n">
+        <v>104</v>
+      </c>
+      <c r="U49" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="V49" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="W49" s="4" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Beast_Jabberwock</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>FetidClaw</t>
+        </is>
+      </c>
+      <c r="M50" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="N50" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="O50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q50" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="R50" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="S50" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="T50" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="U50" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="V50" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="W50" s="4" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>0x87_MogallClass</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I51" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="J51" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K51" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L51" s="4" t="inlineStr">
+        <is>
+          <t>EvilEye</t>
+        </is>
+      </c>
+      <c r="M51" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="N51" s="4" t="n">
+        <v>118</v>
+      </c>
+      <c r="O51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q51" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="R51" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="S51" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="T51" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="U51" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="V51" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="W51" s="4" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>0x87_Bael</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="I52" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J52" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="L52" s="4" t="inlineStr">
+        <is>
+          <t>SharpClaw</t>
+        </is>
+      </c>
+      <c r="M52" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="N52" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="O52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q52" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="R52" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="S52" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="T52" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="U52" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="V52" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="W52" s="4" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>0x87_Cyclops</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="E53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="I53" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J53" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="L53" s="4" t="inlineStr">
+        <is>
+          <t>SharpClaw</t>
+        </is>
+      </c>
+      <c r="M53" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="N53" s="4" t="n">
+        <v>114</v>
+      </c>
+      <c r="O53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q53" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="R53" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="S53" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="T53" s="4" t="n">
+        <v>111</v>
+      </c>
+      <c r="U53" s="4" t="n">
+        <v>73</v>
+      </c>
+      <c r="V53" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="W53" s="4" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>0x87_Revenant</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>SharpClaw</t>
+        </is>
+      </c>
+      <c r="M54" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="N54" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="O54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q54" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="R54" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S54" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="T54" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="U54" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="V54" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="W54" s="4" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>0x87_Mercenary</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="G55" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="G49" s="4" t="n">
+      <c r="H55" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I55" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J55" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K55" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L55" s="4" t="inlineStr">
+        <is>
+          <t>SharpClaw</t>
+        </is>
+      </c>
+      <c r="M55" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="N55" s="4" t="n">
+        <v>106</v>
+      </c>
+      <c r="O55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q55" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="R55" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="S55" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="T55" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="U55" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="V55" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="W55" s="4" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>0x87_LowMage</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="D56" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="J56" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K56" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>SharpClaw</t>
+        </is>
+      </c>
+      <c r="M56" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="N56" s="4" t="n">
+        <v>103</v>
+      </c>
+      <c r="O56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q56" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="R56" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S56" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="T56" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="U56" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="V56" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="W56" s="4" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>0x87_Gargoyle</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="G57" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="H49" s="4" t="n">
+      <c r="H57" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="I49" s="4" t="n">
+      <c r="I57" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="J49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="4" t="n">
+      <c r="J57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="L49" s="4" t="inlineStr">
+      <c r="L57" s="4" t="inlineStr">
         <is>
           <t>SharpClaw</t>
         </is>
       </c>
-      <c r="M49" s="4" t="n">
+      <c r="M57" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="N49" s="4" t="n">
+      <c r="N57" s="4" t="n">
         <v>101</v>
       </c>
-      <c r="O49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" s="4" t="n">
+      <c r="O57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="Q49" s="4" t="n">
+      <c r="Q57" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="R49" s="4" t="n">
+      <c r="R57" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="S49" s="4" t="n">
+      <c r="S57" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="T49" s="4" t="n">
+      <c r="T57" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="U49" s="4" t="n">
+      <c r="U57" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="V49" s="4" t="n">
+      <c r="V57" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="W49" s="4" t="n">
+      <c r="W57" s="4" t="n">
         <v>35</v>
       </c>
     </row>
@@ -11213,7 +11813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W49"/>
+  <dimension ref="A1:W57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -11518,10 +12118,10 @@
         <v>7</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>5</v>
@@ -11550,7 +12150,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="N4" s="2" t="n">
         <v>101</v>
@@ -11568,19 +12168,19 @@
         <v>11</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="T4" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="V4" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="U4" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="V4" s="2" t="n">
-        <v>18</v>
-      </c>
       <c r="W4" s="2" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
@@ -11925,7 +12525,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>105</v>
@@ -12150,7 +12750,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N12" s="2" t="n">
         <v>117</v>
@@ -12412,76 +13012,76 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>0x80_General</t>
+          <t>SoldierChar_Knight</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
         <v>7</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D17" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="E17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="H17" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="I17" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="J17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>15</v>
-      </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>PatientKatti</t>
+          <t>SteelLance</t>
         </is>
       </c>
       <c r="M17" s="3" t="n">
         <v>23</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>126</v>
+        <v>83</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="P17" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q17" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="Q17" s="3" t="n">
-        <v>10</v>
-      </c>
       <c r="R17" s="3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18">
@@ -12522,17 +13122,17 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>SteelSword</t>
+          <t>PatientKatti</t>
         </is>
       </c>
       <c r="M18" s="3" t="n">
         <v>23</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>5</v>
@@ -12562,76 +13162,76 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>0x81_CivWoman</t>
+          <t>0x80_General</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
         <v>7</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>PatientKatti</t>
+          <t>SteelSword</t>
         </is>
       </c>
       <c r="M19" s="3" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>-3</v>
+        <v>5</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20">
@@ -12672,26 +13272,26 @@
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>SteelSword</t>
+          <t>PatientKatti</t>
         </is>
       </c>
       <c r="M20" s="3" t="n">
         <v>10</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>12</v>
@@ -12712,14 +13312,14 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>0x81_CivMan</t>
+          <t>0x81_CivWoman</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
         <v>7</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
@@ -12737,51 +13337,51 @@
         <v>0</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>PatientKatti</t>
+          <t>SteelSword</t>
         </is>
       </c>
       <c r="M21" s="3" t="n">
         <v>10</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -12822,26 +13422,26 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>SteelSword</t>
+          <t>PatientKatti</t>
         </is>
       </c>
       <c r="M22" s="3" t="n">
         <v>10</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="Q22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>14</v>
@@ -12862,110 +13462,110 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Eagle_MageGeneral</t>
+          <t>0x81_CivMan</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
         <v>7</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>SteelSword</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S23" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="T23" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="U23" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="E23" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="H23" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="J23" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="K23" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>Quickblade</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="N23" s="3" t="n">
-        <v>137</v>
-      </c>
-      <c r="O23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q23" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="R23" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="S23" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="T23" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="U23" s="3" t="n">
-        <v>42</v>
-      </c>
       <c r="V23" s="3" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Gryphon_Peer</t>
+          <t>Eagle_MageGeneral</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
         <v>7</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F24" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I24" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="G24" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="I24" s="3" t="n">
-        <v>10</v>
-      </c>
       <c r="J24" s="3" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>8</v>
@@ -12976,102 +13576,118 @@
         </is>
       </c>
       <c r="M24" s="3" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>0xF2_CivWoman</t>
+          <t>Gryphon_Peer</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
         <v>7</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="L25" s="3" t="n"/>
-      <c r="M25" s="3" t="n"/>
-      <c r="N25" s="3" t="n"/>
-      <c r="O25" s="3" t="n"/>
-      <c r="P25" s="3" t="n"/>
-      <c r="Q25" s="3" t="n"/>
-      <c r="R25" s="3" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Quickblade</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q25" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>19</v>
+      </c>
       <c r="S25" s="3" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>0x82_CivWoman</t>
+          <t>0xF2_CivWoman</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
@@ -13093,7 +13709,7 @@
         <v>0</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>1</v>
@@ -13115,7 +13731,7 @@
         <v>12</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>9</v>
@@ -13124,20 +13740,20 @@
         <v>6</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>0x83_CivMan</t>
+          <t>0x82_CivWoman</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
         <v>7</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>0</v>
@@ -13155,13 +13771,13 @@
         <v>0</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L27" s="3" t="n"/>
       <c r="M27" s="3" t="n"/>
@@ -13171,42 +13787,42 @@
       <c r="Q27" s="3" t="n"/>
       <c r="R27" s="3" t="n"/>
       <c r="S27" s="3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>0x84_CivBoy</t>
+          <t>0x83_CivMan</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
         <v>7</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G28" s="3" t="n">
         <v>0</v>
       </c>
@@ -13214,13 +13830,13 @@
         <v>0</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L28" s="3" t="n"/>
       <c r="M28" s="3" t="n"/>
@@ -13230,35 +13846,35 @@
       <c r="Q28" s="3" t="n"/>
       <c r="R28" s="3" t="n"/>
       <c r="S28" s="3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>0x85_CivGirl</t>
+          <t>0x84_CivBoy</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
         <v>7</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>0</v>
@@ -13273,13 +13889,13 @@
         <v>0</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L29" s="3" t="n"/>
       <c r="M29" s="3" t="n"/>
@@ -13289,10 +13905,10 @@
       <c r="Q29" s="3" t="n"/>
       <c r="R29" s="3" t="n"/>
       <c r="S29" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>7</v>
@@ -13301,44 +13917,44 @@
         <v>5</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>0x86_CivBoy</t>
+          <t>0x85_CivGirl</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
         <v>7</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="J30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L30" s="3" t="n"/>
       <c r="M30" s="3" t="n"/>
@@ -13348,10 +13964,10 @@
       <c r="Q30" s="3" t="n"/>
       <c r="R30" s="3" t="n"/>
       <c r="S30" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>7</v>
@@ -13360,38 +13976,38 @@
         <v>5</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>0xF1_CivWoman</t>
+          <t>0x86_CivBoy</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
         <v>7</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>0</v>
@@ -13407,32 +14023,32 @@
       <c r="Q31" s="3" t="n"/>
       <c r="R31" s="3" t="n"/>
       <c r="S31" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>0xF1_CivMan</t>
+          <t>0xF1_CivWoman</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
         <v>7</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>0</v>
@@ -13450,13 +14066,13 @@
         <v>2</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L32" s="3" t="n"/>
       <c r="M32" s="3" t="n"/>
@@ -13466,41 +14082,41 @@
       <c r="Q32" s="3" t="n"/>
       <c r="R32" s="3" t="n"/>
       <c r="S32" s="3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>0xF1_CivBoy</t>
+          <t>0xF1_CivMan</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
         <v>7</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>0</v>
@@ -13509,13 +14125,13 @@
         <v>2</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L33" s="3" t="n"/>
       <c r="M33" s="3" t="n"/>
@@ -13525,35 +14141,35 @@
       <c r="Q33" s="3" t="n"/>
       <c r="R33" s="3" t="n"/>
       <c r="S33" s="3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>0xF1_CivGirl</t>
+          <t>0xF1_CivBoy</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
         <v>7</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0</v>
@@ -13568,13 +14184,13 @@
         <v>2</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L34" s="3" t="n"/>
       <c r="M34" s="3" t="n"/>
@@ -13584,10 +14200,10 @@
       <c r="Q34" s="3" t="n"/>
       <c r="R34" s="3" t="n"/>
       <c r="S34" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>7</v>
@@ -13596,44 +14212,44 @@
         <v>5</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Baron_General</t>
+          <t>0xF1_CivGirl</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
         <v>7</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="L35" s="3" t="n"/>
       <c r="M35" s="3" t="n"/>
@@ -13643,123 +14259,107 @@
       <c r="Q35" s="3" t="n"/>
       <c r="R35" s="3" t="n"/>
       <c r="S35" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="T35" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="V35" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="W35" s="3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Baron_General</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="L36" s="3" t="n"/>
+      <c r="M36" s="3" t="n"/>
+      <c r="N36" s="3" t="n"/>
+      <c r="O36" s="3" t="n"/>
+      <c r="P36" s="3" t="n"/>
+      <c r="Q36" s="3" t="n"/>
+      <c r="R36" s="3" t="n"/>
+      <c r="S36" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="T35" s="3" t="n">
+      <c r="T36" s="3" t="n">
         <v>79</v>
       </c>
-      <c r="U35" s="3" t="n">
+      <c r="U36" s="3" t="n">
         <v>56</v>
       </c>
-      <c r="V35" s="3" t="n">
+      <c r="V36" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="W35" s="3" t="n">
+      <c r="W36" s="3" t="n">
         <v>51</v>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>Beast_Cyclops</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>74</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G37" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="H37" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="I37" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="J37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>SilverAxe</t>
-        </is>
-      </c>
-      <c r="M37" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="N37" s="4" t="n">
-        <v>110</v>
-      </c>
-      <c r="O37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q37" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="R37" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="S37" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="T37" s="4" t="n">
-        <v>96</v>
-      </c>
-      <c r="U37" s="4" t="n">
-        <v>61</v>
-      </c>
-      <c r="V37" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="W37" s="4" t="n">
-        <v>59</v>
-      </c>
-    </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Beast_BowBone</t>
+          <t>Beast_Tarvos</t>
         </is>
       </c>
       <c r="B38" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G38" s="4" t="n">
         <v>12</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I38" s="4" t="n">
         <v>4</v>
@@ -13768,58 +14368,58 @@
         <v>0</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>SteelBow</t>
+          <t>SteelAxe</t>
         </is>
       </c>
       <c r="M38" s="4" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="O38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P38" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Q38" s="4" t="n">
         <v>24</v>
       </c>
       <c r="R38" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T38" s="4" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="U38" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="V38" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="W38" s="4" t="n">
         <v>33</v>
-      </c>
-      <c r="V38" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="W38" s="4" t="n">
-        <v>30</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Beast_LanceBone</t>
+          <t>Beast_AxeBone</t>
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D39" s="4" t="n">
         <v>14</v>
@@ -13828,7 +14428,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G39" s="4" t="n">
         <v>11</v>
@@ -13847,35 +14447,35 @@
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>SteelSword</t>
+          <t>Hammer</t>
         </is>
       </c>
       <c r="M39" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="O39" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P39" s="4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="Q39" s="4" t="n">
         <v>22</v>
       </c>
       <c r="R39" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="S39" s="4" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="T39" s="4" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U39" s="4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V39" s="4" t="n">
         <v>23</v>
@@ -13887,29 +14487,29 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Beast_SwordBone</t>
+          <t>Beast_Revenant</t>
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C40" s="4" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E40" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I40" s="4" t="n">
         <v>4</v>
@@ -13918,318 +14518,318 @@
         <v>0</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>SteelLance</t>
+          <t>RottenClaw</t>
         </is>
       </c>
       <c r="M40" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="O40" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P40" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q40" s="4" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="R40" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="S40" s="4" t="n">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="T40" s="4" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="U40" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="V40" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="V40" s="4" t="n">
-        <v>23</v>
-      </c>
       <c r="W40" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Beast_Jabberwock</t>
+          <t>Lowlander_Fighter</t>
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C41" s="4" t="n">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="D41" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="E41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G41" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H41" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I41" s="4" t="n">
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
+      <c r="M41" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="N41" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="O41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>FetidClaw</t>
-        </is>
-      </c>
-      <c r="M41" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="N41" s="4" t="n">
-        <v>93</v>
-      </c>
-      <c r="O41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" s="4" t="n">
-        <v>4</v>
-      </c>
       <c r="Q41" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="R41" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S41" s="4" t="n">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="T41" s="4" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="U41" s="4" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="V41" s="4" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="W41" s="4" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>0x87_MogallClass</t>
+          <t>Lowlander_HighMage</t>
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C42" s="4" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>EvilEye</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="M42" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="O42" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P42" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Q42" s="4" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="R42" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="S42" s="4" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="T42" s="4" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="U42" s="4" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="V42" s="4" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="W42" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>0x87_Bael</t>
+          <t>Lowlander_Soldier</t>
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C43" s="4" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E43" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>SharpClaw</t>
+          <t>SavageGore</t>
         </is>
       </c>
       <c r="M43" s="4" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="N43" s="4" t="n">
         <v>95</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="P43" s="4" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="Q43" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="R43" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="S43" s="4" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="T43" s="4" t="n">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="U43" s="4" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="V43" s="4" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="W43" s="4" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Beast_Bael</t>
+          <t>Lowlander_Archer</t>
         </is>
       </c>
       <c r="B44" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C44" s="4" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E44" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G44" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J44" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K44" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="H44" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="I44" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" s="4" t="n">
-        <v>15</v>
-      </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>SharpClaw</t>
+          <t>SteelBow</t>
         </is>
       </c>
       <c r="M44" s="4" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="O44" s="4" t="n">
         <v>0</v>
@@ -14238,191 +14838,191 @@
         <v>7</v>
       </c>
       <c r="Q44" s="4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="R44" s="4" t="n">
         <v>11</v>
       </c>
       <c r="S44" s="4" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="T44" s="4" t="n">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="U44" s="4" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="V44" s="4" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="W44" s="4" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>0x87_Cyclops</t>
+          <t>Beast_SwordBone</t>
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E45" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H45" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>Armorslayer</t>
+        </is>
+      </c>
+      <c r="M45" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="I45" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="J45" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K45" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="L45" s="4" t="inlineStr">
-        <is>
-          <t>SharpClaw</t>
-        </is>
-      </c>
-      <c r="M45" s="4" t="n">
-        <v>36</v>
-      </c>
       <c r="N45" s="4" t="n">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="O45" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P45" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Q45" s="4" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="R45" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="S45" s="4" t="n">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="T45" s="4" t="n">
-        <v>104</v>
+        <v>48</v>
       </c>
       <c r="U45" s="4" t="n">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="V45" s="4" t="n">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="W45" s="4" t="n">
-        <v>64</v>
+        <v>29</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>0x87_Revenant</t>
+          <t>Lowlander_LowMage</t>
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H46" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J46" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I46" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J46" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K46" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>SharpClaw</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="M46" s="4" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P46" s="4" t="n">
-        <v>-3</v>
+        <v>6</v>
       </c>
       <c r="Q46" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="R46" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="S46" s="4" t="n">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="T46" s="4" t="n">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="U46" s="4" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="V46" s="4" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="W46" s="4" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>0x87_Mercenary</t>
+          <t>Beast_LanceBone</t>
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C47" s="4" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E47" s="4" t="n">
         <v>0</v>
@@ -14434,91 +15034,91 @@
         <v>11</v>
       </c>
       <c r="H47" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>HeavySpear</t>
+        </is>
+      </c>
+      <c r="M47" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="N47" s="4" t="n">
+        <v>104</v>
+      </c>
+      <c r="O47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="I47" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J47" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K47" s="4" t="n">
+      <c r="Q47" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="R47" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="L47" s="4" t="inlineStr">
-        <is>
-          <t>SharpClaw</t>
-        </is>
-      </c>
-      <c r="M47" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="N47" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="O47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q47" s="4" t="n">
+      <c r="S47" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="T47" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="U47" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="V47" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="R47" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="S47" s="4" t="n">
+      <c r="W47" s="4" t="n">
         <v>29</v>
-      </c>
-      <c r="T47" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="U47" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="V47" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="W47" s="4" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>0x87_LowMage</t>
+          <t>Beast_Bael</t>
         </is>
       </c>
       <c r="B48" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C48" s="4" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F48" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H48" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="G48" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H48" s="4" t="n">
-        <v>5</v>
-      </c>
       <c r="I48" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
@@ -14526,50 +15126,50 @@
         </is>
       </c>
       <c r="M48" s="4" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="O48" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P48" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q48" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="R48" s="4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="S48" s="4" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="T48" s="4" t="n">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="U48" s="4" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="V48" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="W48" s="4" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>0x87_Gargoyle</t>
+          <t>Beast_Cyclops</t>
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C49" s="4" t="n">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="D49" s="4" t="n">
         <v>17</v>
@@ -14578,59 +15178,659 @@
         <v>0</v>
       </c>
       <c r="F49" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="I49" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="L49" s="4" t="inlineStr">
+        <is>
+          <t>SilverAxe</t>
+        </is>
+      </c>
+      <c r="M49" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="N49" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="O49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q49" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="R49" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="S49" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="T49" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="U49" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="V49" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="W49" s="4" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Beast_Jabberwock</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="D50" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="G49" s="4" t="n">
+      <c r="E50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>FetidClaw</t>
+        </is>
+      </c>
+      <c r="M50" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="N50" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="O50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q50" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="R50" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="S50" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="T50" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="U50" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="V50" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="W50" s="4" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>0x87_MogallClass</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I51" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="H49" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="I49" s="4" t="n">
+      <c r="J51" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L51" s="4" t="inlineStr">
+        <is>
+          <t>EvilEye</t>
+        </is>
+      </c>
+      <c r="M51" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="N51" s="4" t="n">
+        <v>112</v>
+      </c>
+      <c r="O51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q51" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="R51" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="S51" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="T51" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="U51" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="V51" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="W51" s="4" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>0x87_Bael</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I52" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="J49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="4" t="n">
+      <c r="J52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="L52" s="4" t="inlineStr">
+        <is>
+          <t>SharpClaw</t>
+        </is>
+      </c>
+      <c r="M52" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="N52" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="O52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q52" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="R52" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="S52" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="T52" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="U52" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="V52" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="W52" s="4" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>0x87_Cyclops</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="E53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="I53" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J53" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="L53" s="4" t="inlineStr">
+        <is>
+          <t>SharpClaw</t>
+        </is>
+      </c>
+      <c r="M53" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="N53" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="O53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q53" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="R53" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="S53" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="T53" s="4" t="n">
+        <v>104</v>
+      </c>
+      <c r="U53" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="V53" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="W53" s="4" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>0x87_Revenant</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>SharpClaw</t>
+        </is>
+      </c>
+      <c r="M54" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="N54" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="O54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q54" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="R54" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S54" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="T54" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="U54" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="V54" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="W54" s="4" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>0x87_Mercenary</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="D55" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="L49" s="4" t="inlineStr">
+      <c r="E55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H55" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I55" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L55" s="4" t="inlineStr">
         <is>
           <t>SharpClaw</t>
         </is>
       </c>
-      <c r="M49" s="4" t="n">
+      <c r="M55" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="N55" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="O55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q55" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="R55" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="S55" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="T55" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="U55" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="V55" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="W55" s="4" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>0x87_LowMage</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C56" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="N49" s="4" t="n">
+      <c r="D56" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J56" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>SharpClaw</t>
+        </is>
+      </c>
+      <c r="M56" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="N56" s="4" t="n">
+        <v>98</v>
+      </c>
+      <c r="O56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="R56" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="S56" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="T56" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="U56" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="V56" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="W56" s="4" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>0x87_Gargoyle</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I57" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L57" s="4" t="inlineStr">
+        <is>
+          <t>SharpClaw</t>
+        </is>
+      </c>
+      <c r="M57" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="N57" s="4" t="n">
         <v>97</v>
       </c>
-      <c r="O49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" s="4" t="n">
+      <c r="O57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="Q49" s="4" t="n">
+      <c r="Q57" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="R49" s="4" t="n">
+      <c r="R57" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="S49" s="4" t="n">
+      <c r="S57" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="T49" s="4" t="n">
+      <c r="T57" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="U49" s="4" t="n">
+      <c r="U57" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="V49" s="4" t="n">
+      <c r="V57" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="W49" s="4" t="n">
+      <c r="W57" s="4" t="n">
         <v>32</v>
       </c>
     </row>
@@ -30788,7 +31988,7 @@
         </is>
       </c>
       <c r="M37" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N37" s="4" t="n">
         <v>115</v>
@@ -33850,7 +35050,7 @@
         </is>
       </c>
       <c r="M37" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="N37" s="4" t="n">
         <v>110</v>

--- a/unit_stats.xlsx
+++ b/unit_stats.xlsx
@@ -1844,13 +1844,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P18" s="2" t="n">
         <v>13</v>
@@ -7781,7 +7781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W57"/>
+  <dimension ref="A1:W59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -11130,389 +11130,389 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Beast_Cyclops</t>
+          <t>Lowlander_Mercenary</t>
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C49" s="4" t="n">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E49" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>SilverAxe</t>
+          <t>Lancereaver</t>
         </is>
       </c>
       <c r="M49" s="4" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="O49" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P49" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q49" s="4" t="n">
         <v>31</v>
       </c>
       <c r="R49" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="S49" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="T49" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="U49" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="V49" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="S49" s="4" t="n">
-        <v>88</v>
-      </c>
-      <c r="T49" s="4" t="n">
-        <v>104</v>
-      </c>
-      <c r="U49" s="4" t="n">
-        <v>68</v>
-      </c>
-      <c r="V49" s="4" t="n">
-        <v>48</v>
-      </c>
       <c r="W49" s="4" t="n">
-        <v>64</v>
+        <v>24</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Beast_Jabberwock</t>
+          <t>Beast_Cyclops</t>
         </is>
       </c>
       <c r="B50" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C50" s="4" t="n">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E50" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H50" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J50" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I50" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J50" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K50" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>SilverAxe</t>
+        </is>
+      </c>
+      <c r="M50" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="N50" s="4" t="n">
+        <v>115</v>
+      </c>
+      <c r="O50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="L50" s="4" t="inlineStr">
-        <is>
-          <t>FetidClaw</t>
-        </is>
-      </c>
-      <c r="M50" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="N50" s="4" t="n">
-        <v>93</v>
-      </c>
-      <c r="O50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" s="4" t="n">
-        <v>4</v>
-      </c>
       <c r="Q50" s="4" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="R50" s="4" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="S50" s="4" t="n">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="T50" s="4" t="n">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="U50" s="4" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="V50" s="4" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="W50" s="4" t="n">
-        <v>29</v>
+        <v>64</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>0x87_MogallClass</t>
+          <t>Beast_Gargoyle</t>
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C51" s="4" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G51" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="H51" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="H51" s="4" t="n">
-        <v>3</v>
-      </c>
       <c r="I51" s="4" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K51" s="4" t="n">
         <v>9</v>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>EvilEye</t>
+          <t>SteelLance</t>
         </is>
       </c>
       <c r="M51" s="4" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="O51" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P51" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q51" s="4" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="R51" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="S51" s="4" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="T51" s="4" t="n">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="U51" s="4" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="V51" s="4" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="W51" s="4" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>0x87_Bael</t>
+          <t>Beast_Jabberwock</t>
         </is>
       </c>
       <c r="B52" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C52" s="4" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E52" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52" s="4" t="n">
         <v>15</v>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>SharpClaw</t>
+          <t>FetidClaw</t>
         </is>
       </c>
       <c r="M52" s="4" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="O52" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P52" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q52" s="4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="R52" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="S52" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="T52" s="4" t="n">
         <v>58</v>
-      </c>
-      <c r="T52" s="4" t="n">
-        <v>65</v>
       </c>
       <c r="U52" s="4" t="n">
         <v>44</v>
       </c>
       <c r="V52" s="4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="W52" s="4" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>0x87_Cyclops</t>
+          <t>0x87_MogallClass</t>
         </is>
       </c>
       <c r="B53" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C53" s="4" t="n">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G53" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I53" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="H53" s="4" t="n">
+      <c r="J53" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K53" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L53" s="4" t="inlineStr">
+        <is>
+          <t>EvilEye</t>
+        </is>
+      </c>
+      <c r="M53" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="I53" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="J53" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K53" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="L53" s="4" t="inlineStr">
-        <is>
-          <t>SharpClaw</t>
-        </is>
-      </c>
-      <c r="M53" s="4" t="n">
-        <v>38</v>
-      </c>
       <c r="N53" s="4" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="O53" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P53" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q53" s="4" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="R53" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="S53" s="4" t="n">
-        <v>95</v>
+        <v>54</v>
       </c>
       <c r="T53" s="4" t="n">
-        <v>111</v>
+        <v>41</v>
       </c>
       <c r="U53" s="4" t="n">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="V53" s="4" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="W53" s="4" t="n">
-        <v>68</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>0x87_Revenant</t>
+          <t>0x87_Bael</t>
         </is>
       </c>
       <c r="B54" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C54" s="4" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D54" s="4" t="n">
         <v>17</v>
@@ -11521,22 +11521,22 @@
         <v>0</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H54" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J54" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I54" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="J54" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K54" s="4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
@@ -11547,218 +11547,218 @@
         <v>34</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="O54" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P54" s="4" t="n">
-        <v>-2</v>
+        <v>8</v>
       </c>
       <c r="Q54" s="4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="R54" s="4" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="S54" s="4" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="T54" s="4" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U54" s="4" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="V54" s="4" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="W54" s="4" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>0x87_Mercenary</t>
+          <t>0x87_Cyclops</t>
         </is>
       </c>
       <c r="B55" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C55" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="H55" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="I55" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J55" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="L55" s="4" t="inlineStr">
+        <is>
+          <t>SharpClaw</t>
+        </is>
+      </c>
+      <c r="M55" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="N55" s="4" t="n">
+        <v>114</v>
+      </c>
+      <c r="O55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q55" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="D55" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="E55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="G55" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="H55" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="I55" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J55" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K55" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="L55" s="4" t="inlineStr">
-        <is>
-          <t>SharpClaw</t>
-        </is>
-      </c>
-      <c r="M55" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="N55" s="4" t="n">
-        <v>106</v>
-      </c>
-      <c r="O55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q55" s="4" t="n">
-        <v>29</v>
-      </c>
       <c r="R55" s="4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="S55" s="4" t="n">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="T55" s="4" t="n">
-        <v>39</v>
+        <v>111</v>
       </c>
       <c r="U55" s="4" t="n">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="V55" s="4" t="n">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="W55" s="4" t="n">
-        <v>22</v>
+        <v>68</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>0x87_LowMage</t>
+          <t>0x87_Revenant</t>
         </is>
       </c>
       <c r="B56" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="D56" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="E56" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="F56" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="G56" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="H56" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="I56" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="J56" s="4" t="n">
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>SharpClaw</t>
+        </is>
+      </c>
+      <c r="M56" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="N56" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="O56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q56" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="R56" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K56" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>SharpClaw</t>
-        </is>
-      </c>
-      <c r="M56" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="N56" s="4" t="n">
-        <v>103</v>
-      </c>
-      <c r="O56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q56" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="R56" s="4" t="n">
-        <v>6</v>
-      </c>
       <c r="S56" s="4" t="n">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="T56" s="4" t="n">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="U56" s="4" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="V56" s="4" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="W56" s="4" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>0x87_Gargoyle</t>
+          <t>0x87_Mercenary</t>
         </is>
       </c>
       <c r="B57" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C57" s="4" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E57" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F57" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="G57" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="G57" s="4" t="n">
-        <v>16</v>
-      </c>
       <c r="H57" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K57" s="4" t="n">
         <v>9</v>
@@ -11769,36 +11769,186 @@
         </is>
       </c>
       <c r="M57" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="N57" s="4" t="n">
+        <v>106</v>
+      </c>
+      <c r="O57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q57" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="R57" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="S57" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="T57" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="U57" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="V57" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="W57" s="4" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>0x87_LowMage</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="J58" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K58" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L58" s="4" t="inlineStr">
+        <is>
+          <t>SharpClaw</t>
+        </is>
+      </c>
+      <c r="M58" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="N58" s="4" t="n">
+        <v>103</v>
+      </c>
+      <c r="O58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q58" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="R58" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S58" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="T58" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="U58" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="V58" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="W58" s="4" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>0x87_Gargoyle</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="H59" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="I59" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>SharpClaw</t>
+        </is>
+      </c>
+      <c r="M59" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="N57" s="4" t="n">
+      <c r="N59" s="4" t="n">
         <v>101</v>
       </c>
-      <c r="O57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" s="4" t="n">
+      <c r="O59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="Q57" s="4" t="n">
+      <c r="Q59" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="R57" s="4" t="n">
+      <c r="R59" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="S57" s="4" t="n">
+      <c r="S59" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="T57" s="4" t="n">
+      <c r="T59" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="U57" s="4" t="n">
+      <c r="U59" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="V57" s="4" t="n">
+      <c r="V59" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="W57" s="4" t="n">
+      <c r="W59" s="4" t="n">
         <v>35</v>
       </c>
     </row>
@@ -11813,7 +11963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W57"/>
+  <dimension ref="A1:W59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -15162,46 +15312,46 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Beast_Cyclops</t>
+          <t>Lowlander_Mercenary</t>
         </is>
       </c>
       <c r="B49" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I49" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C49" s="4" t="n">
-        <v>74</v>
-      </c>
-      <c r="D49" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="E49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G49" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="H49" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="I49" s="4" t="n">
-        <v>6</v>
-      </c>
       <c r="J49" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>SilverAxe</t>
+          <t>Lancereaver</t>
         </is>
       </c>
       <c r="M49" s="4" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="N49" s="4" t="n">
         <v>110</v>
@@ -15210,209 +15360,209 @@
         <v>0</v>
       </c>
       <c r="P49" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q49" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R49" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S49" s="4" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="T49" s="4" t="n">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="U49" s="4" t="n">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="V49" s="4" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="W49" s="4" t="n">
-        <v>59</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Beast_Jabberwock</t>
+          <t>Beast_Cyclops</t>
         </is>
       </c>
       <c r="B50" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C50" s="4" t="n">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E50" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>FetidClaw</t>
+          <t>SilverAxe</t>
         </is>
       </c>
       <c r="M50" s="4" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="O50" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P50" s="4" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="Q50" s="4" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="R50" s="4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="S50" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="T50" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="U50" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="V50" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="W50" s="4" t="n">
         <v>59</v>
-      </c>
-      <c r="T50" s="4" t="n">
-        <v>58</v>
-      </c>
-      <c r="U50" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="V50" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="W50" s="4" t="n">
-        <v>29</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>0x87_MogallClass</t>
+          <t>Beast_Gargoyle</t>
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C51" s="4" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51" s="4" t="n">
         <v>9</v>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>EvilEye</t>
+          <t>SteelLance</t>
         </is>
       </c>
       <c r="M51" s="4" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="O51" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P51" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q51" s="4" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="R51" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S51" s="4" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="T51" s="4" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="U51" s="4" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="V51" s="4" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="W51" s="4" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>0x87_Bael</t>
+          <t>Beast_Jabberwock</t>
         </is>
       </c>
       <c r="B52" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C52" s="4" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E52" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>0</v>
@@ -15422,129 +15572,129 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>SharpClaw</t>
+          <t>FetidClaw</t>
         </is>
       </c>
       <c r="M52" s="4" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="O52" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P52" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q52" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="R52" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="S52" s="4" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="T52" s="4" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="U52" s="4" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="V52" s="4" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="W52" s="4" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>0x87_Cyclops</t>
+          <t>0x87_MogallClass</t>
         </is>
       </c>
       <c r="B53" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C53" s="4" t="n">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>SharpClaw</t>
+          <t>EvilEye</t>
         </is>
       </c>
       <c r="M53" s="4" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="O53" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P53" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q53" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="R53" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="S53" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="T53" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="U53" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="V53" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="R53" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="S53" s="4" t="n">
-        <v>88</v>
-      </c>
-      <c r="T53" s="4" t="n">
-        <v>104</v>
-      </c>
-      <c r="U53" s="4" t="n">
-        <v>68</v>
-      </c>
-      <c r="V53" s="4" t="n">
-        <v>48</v>
-      </c>
       <c r="W53" s="4" t="n">
-        <v>64</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>0x87_Revenant</t>
+          <t>0x87_Bael</t>
         </is>
       </c>
       <c r="B54" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C54" s="4" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D54" s="4" t="n">
         <v>14</v>
@@ -15553,22 +15703,22 @@
         <v>0</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
@@ -15579,71 +15729,71 @@
         <v>31</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="O54" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P54" s="4" t="n">
-        <v>-3</v>
+        <v>7</v>
       </c>
       <c r="Q54" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="R54" s="4" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="S54" s="4" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="T54" s="4" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U54" s="4" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="V54" s="4" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="W54" s="4" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>0x87_Mercenary</t>
+          <t>0x87_Cyclops</t>
         </is>
       </c>
       <c r="B55" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C55" s="4" t="n">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E55" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
@@ -15651,146 +15801,146 @@
         </is>
       </c>
       <c r="M55" s="4" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="O55" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P55" s="4" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Q55" s="4" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="R55" s="4" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="S55" s="4" t="n">
-        <v>29</v>
+        <v>88</v>
       </c>
       <c r="T55" s="4" t="n">
-        <v>33</v>
+        <v>104</v>
       </c>
       <c r="U55" s="4" t="n">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="V55" s="4" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="W55" s="4" t="n">
-        <v>19</v>
+        <v>64</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>0x87_LowMage</t>
+          <t>0x87_Revenant</t>
         </is>
       </c>
       <c r="B56" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="D56" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G56" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E56" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="F56" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="G56" s="4" t="n">
-        <v>6</v>
-      </c>
       <c r="H56" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>SharpClaw</t>
+        </is>
+      </c>
+      <c r="M56" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="N56" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="O56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q56" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="R56" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="K56" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>SharpClaw</t>
-        </is>
-      </c>
-      <c r="M56" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="N56" s="4" t="n">
-        <v>98</v>
-      </c>
-      <c r="O56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="R56" s="4" t="n">
-        <v>4</v>
-      </c>
       <c r="S56" s="4" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="T56" s="4" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="U56" s="4" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="V56" s="4" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="W56" s="4" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>0x87_Gargoyle</t>
+          <t>0x87_Mercenary</t>
         </is>
       </c>
       <c r="B57" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C57" s="4" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E57" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F57" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G57" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="G57" s="4" t="n">
-        <v>14</v>
-      </c>
       <c r="H57" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K57" s="4" t="n">
         <v>9</v>
@@ -15801,36 +15951,186 @@
         </is>
       </c>
       <c r="M57" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="N57" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="O57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q57" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="R57" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="S57" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="T57" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="U57" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="V57" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="W57" s="4" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>0x87_LowMage</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C58" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="N57" s="4" t="n">
+      <c r="D58" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J58" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L58" s="4" t="inlineStr">
+        <is>
+          <t>SharpClaw</t>
+        </is>
+      </c>
+      <c r="M58" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="N58" s="4" t="n">
+        <v>98</v>
+      </c>
+      <c r="O58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="R58" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="S58" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="T58" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="U58" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="V58" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="W58" s="4" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>0x87_Gargoyle</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="H59" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I59" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>SharpClaw</t>
+        </is>
+      </c>
+      <c r="M59" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="N59" s="4" t="n">
         <v>97</v>
       </c>
-      <c r="O57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" s="4" t="n">
+      <c r="O59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="Q57" s="4" t="n">
+      <c r="Q59" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="R57" s="4" t="n">
+      <c r="R59" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="S57" s="4" t="n">
+      <c r="S59" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="T57" s="4" t="n">
+      <c r="T59" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="U57" s="4" t="n">
+      <c r="U59" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="V57" s="4" t="n">
+      <c r="V59" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="W57" s="4" t="n">
+      <c r="W59" s="4" t="n">
         <v>32</v>
       </c>
     </row>
@@ -18564,13 +18864,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P18" s="2" t="n">
         <v>13</v>
@@ -31237,13 +31537,13 @@
         </is>
       </c>
       <c r="M26" s="3" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>13</v>
@@ -34299,13 +34599,13 @@
         </is>
       </c>
       <c r="M26" s="3" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>13</v>

--- a/unit_stats.xlsx
+++ b/unit_stats.xlsx
@@ -2263,7 +2263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W72"/>
+  <dimension ref="A1:W73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5608,108 +5608,92 @@
         <v>51</v>
       </c>
     </row>
-    <row r="48"/>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>Beast_Tarvos</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="n">
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Devil_Monolith</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C49" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="D49" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="E49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="G49" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="H49" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="I49" s="4" t="n">
+      <c r="C48" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="I48" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="J48" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="J49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>SteelAxe</t>
-        </is>
-      </c>
-      <c r="M49" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="N49" s="4" t="n">
-        <v>87</v>
-      </c>
-      <c r="O49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q49" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="R49" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="S49" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="T49" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="U49" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="V49" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="W49" s="4" t="n">
-        <v>33</v>
-      </c>
-    </row>
+      <c r="K48" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="L48" s="3" t="n"/>
+      <c r="M48" s="3" t="n"/>
+      <c r="N48" s="3" t="n"/>
+      <c r="O48" s="3" t="n"/>
+      <c r="P48" s="3" t="n"/>
+      <c r="Q48" s="3" t="n"/>
+      <c r="R48" s="3" t="n"/>
+      <c r="S48" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="T48" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="U48" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="V48" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="W48" s="3" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Beast_AxeBone</t>
+          <t>Beast_Tarvos</t>
         </is>
       </c>
       <c r="B50" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C50" s="4" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E50" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I50" s="4" t="n">
         <v>4</v>
@@ -5718,73 +5702,73 @@
         <v>0</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>Hammer</t>
+          <t>SteelAxe</t>
         </is>
       </c>
       <c r="M50" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="O50" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P50" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q50" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="R50" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="S50" s="4" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="T50" s="4" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="U50" s="4" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="V50" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="W50" s="4" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Beast_Revenant</t>
+          <t>Beast_AxeBone</t>
         </is>
       </c>
       <c r="B51" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C51" s="4" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E51" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I51" s="4" t="n">
         <v>4</v>
@@ -5793,339 +5777,339 @@
         <v>0</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>RottenClaw</t>
+          <t>Hammer</t>
         </is>
       </c>
       <c r="M51" s="4" t="n">
         <v>26</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="O51" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P51" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q51" s="4" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="R51" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S51" s="4" t="n">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="T51" s="4" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="U51" s="4" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="V51" s="4" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="W51" s="4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_Fighter</t>
+          <t>Beast_Revenant</t>
         </is>
       </c>
       <c r="B52" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C52" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L52" s="4" t="inlineStr">
+        <is>
+          <t>RottenClaw</t>
+        </is>
+      </c>
+      <c r="M52" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="N52" s="4" t="n">
+        <v>102</v>
+      </c>
+      <c r="O52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="R52" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="S52" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="T52" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="U52" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="V52" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="D52" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="E52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="G52" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H52" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I52" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="J52" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K52" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="L52" s="4" t="inlineStr">
-        <is>
-          <t>Hammer</t>
-        </is>
-      </c>
-      <c r="M52" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="N52" s="4" t="n">
-        <v>84</v>
-      </c>
-      <c r="O52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q52" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="R52" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="S52" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="T52" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="U52" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="V52" s="4" t="n">
-        <v>23</v>
-      </c>
       <c r="W52" s="4" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_HighMage</t>
+          <t>Lowlander_Fighter</t>
         </is>
       </c>
       <c r="B53" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C53" s="4" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F53" s="4" t="n">
         <v>9</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H53" s="4" t="n">
         <v>4</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Hammer</t>
         </is>
       </c>
       <c r="M53" s="4" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="O53" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P53" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Q53" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="R53" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="S53" s="4" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="T53" s="4" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="U53" s="4" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="V53" s="4" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="W53" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_Soldier</t>
+          <t>Lowlander_HighMage</t>
         </is>
       </c>
       <c r="B54" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C54" s="4" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>SavageGore</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="M54" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="N54" s="4" t="n">
+        <v>109</v>
+      </c>
+      <c r="O54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q54" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="R54" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="S54" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="N54" s="4" t="n">
-        <v>95</v>
-      </c>
-      <c r="O54" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="P54" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q54" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="R54" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="S54" s="4" t="n">
-        <v>35</v>
-      </c>
       <c r="T54" s="4" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="U54" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="V54" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W54" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_Archer</t>
+          <t>Lowlander_Soldier</t>
         </is>
       </c>
       <c r="B55" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C55" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H55" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L55" s="4" t="inlineStr">
+        <is>
+          <t>SavageGore</t>
+        </is>
+      </c>
+      <c r="M55" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="N55" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="O55" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="P55" s="4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q55" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="R55" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S55" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="T55" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="U55" s="4" t="n">
         <v>26</v>
-      </c>
-      <c r="D55" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="E55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="G55" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="H55" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="I55" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="J55" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K55" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L55" s="4" t="inlineStr">
-        <is>
-          <t>SteelBow</t>
-        </is>
-      </c>
-      <c r="M55" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="N55" s="4" t="n">
-        <v>106</v>
-      </c>
-      <c r="O55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q55" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="R55" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="S55" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="T55" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="U55" s="4" t="n">
-        <v>24</v>
       </c>
       <c r="V55" s="4" t="n">
         <v>18</v>
@@ -6137,17 +6121,17 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Beast_SwordBone</t>
+          <t>Lowlander_Archer</t>
         </is>
       </c>
       <c r="B56" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E56" s="4" t="n">
         <v>0</v>
@@ -6156,402 +6140,402 @@
         <v>12</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J56" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>Armorslayer</t>
+          <t>SteelBow</t>
         </is>
       </c>
       <c r="M56" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="N56" s="4" t="n">
+        <v>106</v>
+      </c>
+      <c r="O56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q56" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="R56" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="S56" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="T56" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="U56" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="N56" s="4" t="n">
-        <v>119</v>
-      </c>
-      <c r="O56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q56" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="R56" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="S56" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="T56" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="U56" s="4" t="n">
-        <v>32</v>
-      </c>
       <c r="V56" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="W56" s="4" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_LowMage</t>
+          <t>Beast_SwordBone</t>
         </is>
       </c>
       <c r="B57" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C57" s="4" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I57" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L57" s="4" t="inlineStr">
+        <is>
+          <t>Armorslayer</t>
+        </is>
+      </c>
+      <c r="M57" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="N57" s="4" t="n">
+        <v>119</v>
+      </c>
+      <c r="O57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q57" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="R57" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="F57" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="G57" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H57" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="I57" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="J57" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K57" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L57" s="4" t="inlineStr">
-        <is>
-          <t>Pain</t>
-        </is>
-      </c>
-      <c r="M57" s="4" t="n">
+      <c r="S57" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="T57" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="U57" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="V57" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="N57" s="4" t="n">
-        <v>115</v>
-      </c>
-      <c r="O57" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="P57" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q57" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="R57" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="S57" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="T57" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="U57" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="V57" s="4" t="n">
-        <v>26</v>
-      </c>
       <c r="W57" s="4" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Beast_LanceBone</t>
+          <t>Lowlander_LowMage</t>
         </is>
       </c>
       <c r="B58" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C58" s="4" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F58" s="4" t="n">
         <v>12</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K58" s="4" t="n">
         <v>8</v>
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>HeavySpear</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="M58" s="4" t="n">
         <v>23</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P58" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q58" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="R58" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="S58" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="T58" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="U58" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="V58" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="W58" s="4" t="n">
         <v>22</v>
-      </c>
-      <c r="R58" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="S58" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="T58" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="U58" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="V58" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="W58" s="4" t="n">
-        <v>29</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Beast_Bael</t>
+          <t>Beast_LanceBone</t>
         </is>
       </c>
       <c r="B59" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C59" s="4" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E59" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>SharpClaw</t>
+          <t>HeavySpear</t>
         </is>
       </c>
       <c r="M59" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="N59" s="4" t="n">
+        <v>104</v>
+      </c>
+      <c r="O59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q59" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="R59" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="S59" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="T59" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="U59" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="N59" s="4" t="n">
-        <v>96</v>
-      </c>
-      <c r="O59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q59" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="R59" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="S59" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="T59" s="4" t="n">
-        <v>61</v>
-      </c>
-      <c r="U59" s="4" t="n">
-        <v>40</v>
-      </c>
       <c r="V59" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="W59" s="4" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_Mercenary</t>
+          <t>Beast_Bael</t>
         </is>
       </c>
       <c r="B60" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E60" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>Lancereaver</t>
+          <t>SharpClaw</t>
         </is>
       </c>
       <c r="M60" s="4" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="O60" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P60" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q60" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="R60" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="S60" s="4" t="n">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="T60" s="4" t="n">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="U60" s="4" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="V60" s="4" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="W60" s="4" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Beast_Cyclops</t>
+          <t>Lowlander_Mercenary</t>
         </is>
       </c>
       <c r="B61" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H61" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I61" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C61" s="4" t="n">
-        <v>74</v>
-      </c>
-      <c r="D61" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="E61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G61" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="H61" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="I61" s="4" t="n">
-        <v>6</v>
-      </c>
       <c r="J61" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>SilverAxe</t>
+          <t>Lancereaver</t>
         </is>
       </c>
       <c r="M61" s="4" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="N61" s="4" t="n">
         <v>110</v>
@@ -6560,41 +6544,41 @@
         <v>0</v>
       </c>
       <c r="P61" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Q61" s="4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="R61" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="S61" s="4" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="T61" s="4" t="n">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="U61" s="4" t="n">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="V61" s="4" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="W61" s="4" t="n">
-        <v>59</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Beast_Gargoyle</t>
+          <t>Beast_Cyclops</t>
         </is>
       </c>
       <c r="B62" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C62" s="4" t="n">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="D62" s="4" t="n">
         <v>17</v>
@@ -6603,141 +6587,141 @@
         <v>0</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
-          <t>SteelLance</t>
+          <t>SilverAxe</t>
         </is>
       </c>
       <c r="M62" s="4" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="O62" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P62" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q62" s="4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="R62" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="S62" s="4" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="T62" s="4" t="n">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="U62" s="4" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="V62" s="4" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="W62" s="4" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_AxeCav</t>
+          <t>Beast_Gargoyle</t>
         </is>
       </c>
       <c r="B63" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C63" s="4" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E63" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J63" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K63" s="4" t="n">
         <v>9</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
-          <t>IronAxe</t>
+          <t>SteelLance</t>
         </is>
       </c>
       <c r="M63" s="4" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="O63" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P63" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q63" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="R63" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="R63" s="4" t="n">
-        <v>10</v>
-      </c>
       <c r="S63" s="4" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="T63" s="4" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="U63" s="4" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="V63" s="4" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="W63" s="4" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_SwordCav</t>
+          <t>Lowlander_AxeCav</t>
         </is>
       </c>
       <c r="B64" s="4" t="n">
@@ -6772,26 +6756,26 @@
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
-          <t>SteelSword</t>
+          <t>IronAxe</t>
         </is>
       </c>
       <c r="M64" s="4" t="n">
         <v>19</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="O64" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P64" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q64" s="4" t="n">
         <v>15</v>
       </c>
       <c r="R64" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S64" s="4" t="n">
         <v>31</v>
@@ -6812,338 +6796,338 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Beast_Jabberwock</t>
+          <t>Lowlander_SwordCav</t>
         </is>
       </c>
       <c r="B65" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C65" s="4" t="n">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E65" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H65" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I65" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I65" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="J65" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K65" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L65" s="4" t="inlineStr">
+        <is>
+          <t>SteelSword</t>
+        </is>
+      </c>
+      <c r="M65" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="N65" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="O65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q65" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="L65" s="4" t="inlineStr">
-        <is>
-          <t>FetidClaw</t>
-        </is>
-      </c>
-      <c r="M65" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="N65" s="4" t="n">
-        <v>93</v>
-      </c>
-      <c r="O65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q65" s="4" t="n">
-        <v>8</v>
-      </c>
       <c r="R65" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="S65" s="4" t="n">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="T65" s="4" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="U65" s="4" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="V65" s="4" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="W65" s="4" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>0x87_MogallClass</t>
+          <t>Beast_Jabberwock</t>
         </is>
       </c>
       <c r="B66" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
-          <t>EvilEye</t>
+          <t>FetidClaw</t>
         </is>
       </c>
       <c r="M66" s="4" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="O66" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P66" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="Q66" s="4" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="R66" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="S66" s="4" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="T66" s="4" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="U66" s="4" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="V66" s="4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="W66" s="4" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>0x87_Bael</t>
+          <t>0x87_MogallClass</t>
         </is>
       </c>
       <c r="B67" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C67" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E67" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G67" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H67" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I67" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="J67" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K67" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L67" s="4" t="inlineStr">
+        <is>
+          <t>EvilEye</t>
+        </is>
+      </c>
+      <c r="M67" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="N67" s="4" t="n">
+        <v>112</v>
+      </c>
+      <c r="O67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q67" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="R67" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="S67" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="D67" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="E67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G67" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="H67" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="I67" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="L67" s="4" t="inlineStr">
-        <is>
-          <t>SharpClaw</t>
-        </is>
-      </c>
-      <c r="M67" s="4" t="n">
+      <c r="T67" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="U67" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="V67" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="N67" s="4" t="n">
-        <v>95</v>
-      </c>
-      <c r="O67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q67" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="R67" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="S67" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="T67" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="U67" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="V67" s="4" t="n">
-        <v>27</v>
-      </c>
       <c r="W67" s="4" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>0x87_Cyclops</t>
+          <t>0x87_Bael</t>
         </is>
       </c>
       <c r="B68" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E68" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G68" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H68" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I68" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="H68" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="I68" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="J68" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K68" s="4" t="n">
-        <v>17</v>
-      </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
           <t>SharpClaw</t>
         </is>
       </c>
       <c r="M68" s="4" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="O68" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P68" s="4" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="Q68" s="4" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="R68" s="4" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="S68" s="4" t="n">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="T68" s="4" t="n">
-        <v>104</v>
+        <v>59</v>
       </c>
       <c r="U68" s="4" t="n">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="V68" s="4" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="W68" s="4" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>0x87_Revenant</t>
+          <t>0x87_Cyclops</t>
         </is>
       </c>
       <c r="B69" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C69" s="4" t="n">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E69" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H69" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="I69" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J69" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I69" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J69" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K69" s="4" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
@@ -7151,149 +7135,149 @@
         </is>
       </c>
       <c r="M69" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="N69" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="O69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q69" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="N69" s="4" t="n">
-        <v>87</v>
-      </c>
-      <c r="O69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P69" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="Q69" s="4" t="n">
-        <v>8</v>
-      </c>
       <c r="R69" s="4" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="S69" s="4" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="T69" s="4" t="n">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="U69" s="4" t="n">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="V69" s="4" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="W69" s="4" t="n">
-        <v>29</v>
+        <v>64</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>0x87_Mercenary</t>
+          <t>0x87_Revenant</t>
         </is>
       </c>
       <c r="B70" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C70" s="4" t="n">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E70" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I70" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L70" s="4" t="inlineStr">
+        <is>
+          <t>SharpClaw</t>
+        </is>
+      </c>
+      <c r="M70" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="N70" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="O70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" s="4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q70" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="R70" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J70" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K70" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="L70" s="4" t="inlineStr">
-        <is>
-          <t>SharpClaw</t>
-        </is>
-      </c>
-      <c r="M70" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="N70" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="O70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q70" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="R70" s="4" t="n">
-        <v>9</v>
-      </c>
       <c r="S70" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="T70" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="U70" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="V70" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="W70" s="4" t="n">
         <v>29</v>
-      </c>
-      <c r="T70" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="U70" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="V70" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="W70" s="4" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>0x87_LowMage</t>
+          <t>0x87_Mercenary</t>
         </is>
       </c>
       <c r="B71" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C71" s="4" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H71" s="4" t="n">
         <v>5</v>
       </c>
       <c r="I71" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
@@ -7301,74 +7285,74 @@
         </is>
       </c>
       <c r="M71" s="4" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N71" s="4" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="O71" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P71" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q71" s="4" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="R71" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="S71" s="4" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="T71" s="4" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="U71" s="4" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="V71" s="4" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="W71" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>0x87_Gargoyle</t>
+          <t>0x87_LowMage</t>
         </is>
       </c>
       <c r="B72" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C72" s="4" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F72" s="4" t="n">
         <v>11</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
@@ -7376,36 +7360,111 @@
         </is>
       </c>
       <c r="M72" s="4" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="N72" s="4" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O72" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P72" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q72" s="4" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="R72" s="4" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="S72" s="4" t="n">
         <v>43</v>
       </c>
       <c r="T72" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="U72" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="V72" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="W72" s="4" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>0x87_Gargoyle</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C73" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="D73" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="E73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="H73" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I73" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L73" s="4" t="inlineStr">
+        <is>
+          <t>SharpClaw</t>
+        </is>
+      </c>
+      <c r="M73" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="N73" s="4" t="n">
+        <v>97</v>
+      </c>
+      <c r="O73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q73" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="R73" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="S73" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="T73" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="U72" s="4" t="n">
+      <c r="U73" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="V72" s="4" t="n">
+      <c r="V73" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="W72" s="4" t="n">
+      <c r="W73" s="4" t="n">
         <v>32</v>
       </c>
     </row>
@@ -33132,7 +33191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W72"/>
+  <dimension ref="A1:W73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -36477,93 +36536,77 @@
         <v>51</v>
       </c>
     </row>
-    <row r="48"/>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>Beast_Tarvos</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="n">
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Devil_Monolith</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C49" s="4" t="n">
+      <c r="C48" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="D49" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="E49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="4" t="n">
+      <c r="D48" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F48" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="G49" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="H49" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="I49" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="J49" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K49" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>SteelAxe</t>
-        </is>
-      </c>
-      <c r="M49" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="N49" s="4" t="n">
-        <v>94</v>
-      </c>
-      <c r="O49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q49" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="R49" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="S49" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="T49" s="4" t="n">
-        <v>61</v>
-      </c>
-      <c r="U49" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="V49" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="W49" s="4" t="n">
-        <v>37</v>
-      </c>
-    </row>
+      <c r="G48" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="I48" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="J48" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K48" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="L48" s="3" t="n"/>
+      <c r="M48" s="3" t="n"/>
+      <c r="N48" s="3" t="n"/>
+      <c r="O48" s="3" t="n"/>
+      <c r="P48" s="3" t="n"/>
+      <c r="Q48" s="3" t="n"/>
+      <c r="R48" s="3" t="n"/>
+      <c r="S48" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="T48" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="U48" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="V48" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="W48" s="3" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Beast_AxeBone</t>
+          <t>Beast_Tarvos</t>
         </is>
       </c>
       <c r="B50" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C50" s="4" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D50" s="4" t="n">
         <v>17</v>
@@ -36575,10 +36618,10 @@
         <v>14</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I50" s="4" t="n">
         <v>5</v>
@@ -36587,15 +36630,15 @@
         <v>1</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>Hammer</t>
+          <t>SteelAxe</t>
         </is>
       </c>
       <c r="M50" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N50" s="4" t="n">
         <v>94</v>
@@ -36604,56 +36647,56 @@
         <v>0</v>
       </c>
       <c r="P50" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q50" s="4" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="R50" s="4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="S50" s="4" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="T50" s="4" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="U50" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="V50" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="W50" s="4" t="n">
         <v>37</v>
-      </c>
-      <c r="V50" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="W50" s="4" t="n">
-        <v>32</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Beast_Revenant</t>
+          <t>Beast_AxeBone</t>
         </is>
       </c>
       <c r="B51" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C51" s="4" t="n">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E51" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I51" s="4" t="n">
         <v>5</v>
@@ -36662,93 +36705,93 @@
         <v>1</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>RottenClaw</t>
+          <t>Hammer</t>
         </is>
       </c>
       <c r="M51" s="4" t="n">
         <v>29</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="O51" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P51" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q51" s="4" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="R51" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S51" s="4" t="n">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="T51" s="4" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="U51" s="4" t="n">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="V51" s="4" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="W51" s="4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_Fighter</t>
+          <t>Beast_Revenant</t>
         </is>
       </c>
       <c r="B52" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C52" s="4" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E52" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H52" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I52" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="I52" s="4" t="n">
-        <v>9</v>
-      </c>
       <c r="J52" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>Hammer</t>
+          <t>RottenClaw</t>
         </is>
       </c>
       <c r="M52" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="O52" s="4" t="n">
         <v>0</v>
@@ -36757,244 +36800,244 @@
         <v>4</v>
       </c>
       <c r="Q52" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="R52" s="4" t="n">
         <v>8</v>
       </c>
       <c r="S52" s="4" t="n">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="T52" s="4" t="n">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="U52" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="V52" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="V52" s="4" t="n">
-        <v>28</v>
-      </c>
       <c r="W52" s="4" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_HighMage</t>
+          <t>Lowlander_Fighter</t>
         </is>
       </c>
       <c r="B53" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C53" s="4" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>2</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Hammer</t>
         </is>
       </c>
       <c r="M53" s="4" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="O53" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P53" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Q53" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="R53" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="S53" s="4" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="T53" s="4" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="U53" s="4" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="V53" s="4" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="W53" s="4" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_Soldier</t>
+          <t>Lowlander_HighMage</t>
         </is>
       </c>
       <c r="B54" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C54" s="4" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="D54" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J54" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K54" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>Thunder</t>
+        </is>
+      </c>
+      <c r="M54" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="N54" s="4" t="n">
+        <v>116</v>
+      </c>
+      <c r="O54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q54" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="R54" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="S54" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="T54" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="U54" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="V54" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="W54" s="4" t="n">
         <v>16</v>
-      </c>
-      <c r="E54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="G54" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H54" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I54" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J54" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K54" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L54" s="4" t="inlineStr">
-        <is>
-          <t>SavageGore</t>
-        </is>
-      </c>
-      <c r="M54" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="N54" s="4" t="n">
-        <v>101</v>
-      </c>
-      <c r="O54" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="P54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="R54" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="S54" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="T54" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="U54" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="V54" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="W54" s="4" t="n">
-        <v>21</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_Archer</t>
+          <t>Lowlander_Soldier</t>
         </is>
       </c>
       <c r="B55" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C55" s="4" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E55" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F55" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H55" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I55" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J55" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K55" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L55" s="4" t="inlineStr">
+        <is>
+          <t>SavageGore</t>
+        </is>
+      </c>
+      <c r="M55" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="N55" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="O55" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="P55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="G55" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="H55" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="I55" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="J55" s="4" t="n">
+      <c r="R55" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="K55" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L55" s="4" t="inlineStr">
-        <is>
-          <t>SteelBow</t>
-        </is>
-      </c>
-      <c r="M55" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="N55" s="4" t="n">
-        <v>114</v>
-      </c>
-      <c r="O55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q55" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="R55" s="4" t="n">
-        <v>13</v>
-      </c>
       <c r="S55" s="4" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="T55" s="4" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="U55" s="4" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="V55" s="4" t="n">
         <v>21</v>
@@ -37006,607 +37049,607 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Beast_SwordBone</t>
+          <t>Lowlander_Archer</t>
         </is>
       </c>
       <c r="B56" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E56" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J56" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>Armorslayer</t>
+          <t>SteelBow</t>
         </is>
       </c>
       <c r="M56" s="4" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="O56" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P56" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q56" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R56" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S56" s="4" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="T56" s="4" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="U56" s="4" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="V56" s="4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="W56" s="4" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_LowMage</t>
+          <t>Beast_SwordBone</t>
         </is>
       </c>
       <c r="B57" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C57" s="4" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F57" s="4" t="n">
         <v>14</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K57" s="4" t="n">
         <v>8</v>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Armorslayer</t>
         </is>
       </c>
       <c r="M57" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="N57" s="4" t="n">
+        <v>124</v>
+      </c>
+      <c r="O57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q57" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="R57" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="S57" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="T57" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="U57" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="V57" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="N57" s="4" t="n">
-        <v>120</v>
-      </c>
-      <c r="O57" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="P57" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q57" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="R57" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="S57" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="T57" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="U57" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="V57" s="4" t="n">
-        <v>30</v>
-      </c>
       <c r="W57" s="4" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Beast_LanceBone</t>
+          <t>Lowlander_LowMage</t>
         </is>
       </c>
       <c r="B58" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C58" s="4" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F58" s="4" t="n">
         <v>14</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K58" s="4" t="n">
         <v>8</v>
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>HeavySpear</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="M58" s="4" t="n">
         <v>26</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P58" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q58" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="R58" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="S58" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T58" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="U58" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="V58" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="W58" s="4" t="n">
         <v>25</v>
-      </c>
-      <c r="R58" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="S58" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="T58" s="4" t="n">
-        <v>54</v>
-      </c>
-      <c r="U58" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="V58" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="W58" s="4" t="n">
-        <v>32</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Beast_Bael</t>
+          <t>Beast_LanceBone</t>
         </is>
       </c>
       <c r="B59" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C59" s="4" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E59" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>SharpClaw</t>
+          <t>HeavySpear</t>
         </is>
       </c>
       <c r="M59" s="4" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="O59" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P59" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q59" s="4" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="R59" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="S59" s="4" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="T59" s="4" t="n">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="U59" s="4" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="V59" s="4" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="W59" s="4" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_Mercenary</t>
+          <t>Beast_Bael</t>
         </is>
       </c>
       <c r="B60" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E60" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F60" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H60" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I60" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J60" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K60" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="G60" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="H60" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="I60" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J60" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K60" s="4" t="n">
-        <v>10</v>
-      </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>Lancereaver</t>
+          <t>SharpClaw</t>
         </is>
       </c>
       <c r="M60" s="4" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="O60" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P60" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Q60" s="4" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="R60" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="S60" s="4" t="n">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T60" s="4" t="n">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="U60" s="4" t="n">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="V60" s="4" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="W60" s="4" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Beast_Cyclops</t>
+          <t>Lowlander_Mercenary</t>
         </is>
       </c>
       <c r="B61" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C61" s="4" t="n">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="D61" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="E61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H61" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="I61" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J61" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K61" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>Lancereaver</t>
+        </is>
+      </c>
+      <c r="M61" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="N61" s="4" t="n">
+        <v>118</v>
+      </c>
+      <c r="O61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q61" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="R61" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="S61" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="T61" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="U61" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="V61" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="E61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="G61" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="H61" s="4" t="n">
+      <c r="W61" s="4" t="n">
         <v>24</v>
-      </c>
-      <c r="I61" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="J61" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K61" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="L61" s="4" t="inlineStr">
-        <is>
-          <t>SilverAxe</t>
-        </is>
-      </c>
-      <c r="M61" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="N61" s="4" t="n">
-        <v>115</v>
-      </c>
-      <c r="O61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q61" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="R61" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="S61" s="4" t="n">
-        <v>88</v>
-      </c>
-      <c r="T61" s="4" t="n">
-        <v>104</v>
-      </c>
-      <c r="U61" s="4" t="n">
-        <v>68</v>
-      </c>
-      <c r="V61" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="W61" s="4" t="n">
-        <v>64</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Beast_Gargoyle</t>
+          <t>Beast_Cyclops</t>
         </is>
       </c>
       <c r="B62" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C62" s="4" t="n">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E62" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
-          <t>SteelLance</t>
+          <t>SilverAxe</t>
         </is>
       </c>
       <c r="M62" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="N62" s="4" t="n">
+        <v>115</v>
+      </c>
+      <c r="O62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q62" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="N62" s="4" t="n">
-        <v>99</v>
-      </c>
-      <c r="O62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q62" s="4" t="n">
-        <v>35</v>
-      </c>
       <c r="R62" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="S62" s="4" t="n">
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="T62" s="4" t="n">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="U62" s="4" t="n">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="V62" s="4" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="W62" s="4" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_AxeCav</t>
+          <t>Beast_Gargoyle</t>
         </is>
       </c>
       <c r="B63" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C63" s="4" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E63" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J63" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K63" s="4" t="n">
         <v>9</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
-          <t>IronAxe</t>
+          <t>SteelLance</t>
         </is>
       </c>
       <c r="M63" s="4" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="O63" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P63" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Q63" s="4" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="R63" s="4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="S63" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="T63" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="U63" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="V63" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="W63" s="4" t="n">
         <v>37</v>
-      </c>
-      <c r="T63" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="U63" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="V63" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="W63" s="4" t="n">
-        <v>26</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_SwordCav</t>
+          <t>Lowlander_AxeCav</t>
         </is>
       </c>
       <c r="B64" s="4" t="n">
@@ -37641,26 +37684,26 @@
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
-          <t>SteelSword</t>
+          <t>IronAxe</t>
         </is>
       </c>
       <c r="M64" s="4" t="n">
         <v>21</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="O64" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P64" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q64" s="4" t="n">
         <v>21</v>
       </c>
       <c r="R64" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="S64" s="4" t="n">
         <v>37</v>
@@ -37681,14 +37724,14 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Beast_Jabberwock</t>
+          <t>Lowlander_SwordCav</t>
         </is>
       </c>
       <c r="B65" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C65" s="4" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>11</v>
@@ -37697,547 +37740,547 @@
         <v>0</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H65" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I65" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
-          <t>FetidClaw</t>
+          <t>SteelSword</t>
         </is>
       </c>
       <c r="M65" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="O65" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P65" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Q65" s="4" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="R65" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="S65" s="4" t="n">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="T65" s="4" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="U65" s="4" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="V65" s="4" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="W65" s="4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>0x87_MogallClass</t>
+          <t>Beast_Jabberwock</t>
         </is>
       </c>
       <c r="B66" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
-          <t>EvilEye</t>
+          <t>FetidClaw</t>
         </is>
       </c>
       <c r="M66" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="O66" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P66" s="4" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="Q66" s="4" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="R66" s="4" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="S66" s="4" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="T66" s="4" t="n">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="U66" s="4" t="n">
         <v>44</v>
       </c>
       <c r="V66" s="4" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="W66" s="4" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>0x87_Bael</t>
+          <t>0x87_MogallClass</t>
         </is>
       </c>
       <c r="B67" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C67" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E67" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G67" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="H67" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I67" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="J67" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K67" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L67" s="4" t="inlineStr">
+        <is>
+          <t>EvilEye</t>
+        </is>
+      </c>
+      <c r="M67" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="N67" s="4" t="n">
+        <v>118</v>
+      </c>
+      <c r="O67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q67" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="R67" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="S67" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="D67" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="E67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="G67" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="H67" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="I67" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J67" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K67" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="L67" s="4" t="inlineStr">
-        <is>
-          <t>SharpClaw</t>
-        </is>
-      </c>
-      <c r="M67" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="N67" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="O67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q67" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="R67" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="S67" s="4" t="n">
-        <v>58</v>
-      </c>
       <c r="T67" s="4" t="n">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="U67" s="4" t="n">
         <v>44</v>
       </c>
       <c r="V67" s="4" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="W67" s="4" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>0x87_Cyclops</t>
+          <t>0x87_Bael</t>
         </is>
       </c>
       <c r="B68" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E68" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K68" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="L68" s="4" t="inlineStr">
+        <is>
+          <t>SharpClaw</t>
+        </is>
+      </c>
+      <c r="M68" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="N68" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="O68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q68" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="L68" s="4" t="inlineStr">
-        <is>
-          <t>SharpClaw</t>
-        </is>
-      </c>
-      <c r="M68" s="4" t="n">
+      <c r="R68" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="S68" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="T68" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="U68" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="V68" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="W68" s="4" t="n">
         <v>38</v>
-      </c>
-      <c r="N68" s="4" t="n">
-        <v>114</v>
-      </c>
-      <c r="O68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P68" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q68" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="R68" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="S68" s="4" t="n">
-        <v>95</v>
-      </c>
-      <c r="T68" s="4" t="n">
-        <v>111</v>
-      </c>
-      <c r="U68" s="4" t="n">
-        <v>73</v>
-      </c>
-      <c r="V68" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="W68" s="4" t="n">
-        <v>68</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>0x87_Revenant</t>
+          <t>0x87_Cyclops</t>
         </is>
       </c>
       <c r="B69" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C69" s="4" t="n">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="D69" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="E69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="G69" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="H69" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="I69" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J69" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K69" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="E69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="G69" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H69" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I69" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="J69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" s="4" t="n">
-        <v>7</v>
-      </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
           <t>SharpClaw</t>
         </is>
       </c>
       <c r="M69" s="4" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="N69" s="4" t="n">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="O69" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P69" s="4" t="n">
-        <v>-2</v>
+        <v>16</v>
       </c>
       <c r="Q69" s="4" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="R69" s="4" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="S69" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="T69" s="4" t="n">
+        <v>111</v>
+      </c>
+      <c r="U69" s="4" t="n">
+        <v>73</v>
+      </c>
+      <c r="V69" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="W69" s="4" t="n">
         <v>68</v>
-      </c>
-      <c r="T69" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="U69" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="V69" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="W69" s="4" t="n">
-        <v>32</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>0x87_Mercenary</t>
+          <t>0x87_Revenant</t>
         </is>
       </c>
       <c r="B70" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C70" s="4" t="n">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E70" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I70" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L70" s="4" t="inlineStr">
+        <is>
+          <t>SharpClaw</t>
+        </is>
+      </c>
+      <c r="M70" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="N70" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="O70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q70" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="R70" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J70" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K70" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="L70" s="4" t="inlineStr">
-        <is>
-          <t>SharpClaw</t>
-        </is>
-      </c>
-      <c r="M70" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="N70" s="4" t="n">
-        <v>106</v>
-      </c>
-      <c r="O70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q70" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="R70" s="4" t="n">
-        <v>11</v>
-      </c>
       <c r="S70" s="4" t="n">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="T70" s="4" t="n">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="U70" s="4" t="n">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="V70" s="4" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="W70" s="4" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>0x87_LowMage</t>
+          <t>0x87_Mercenary</t>
         </is>
       </c>
       <c r="B71" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C71" s="4" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D71" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="E71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="G71" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H71" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I71" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J71" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K71" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L71" s="4" t="inlineStr">
+        <is>
+          <t>SharpClaw</t>
+        </is>
+      </c>
+      <c r="M71" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="N71" s="4" t="n">
+        <v>106</v>
+      </c>
+      <c r="O71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="E71" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="F71" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="G71" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="H71" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="I71" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="J71" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K71" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L71" s="4" t="inlineStr">
-        <is>
-          <t>SharpClaw</t>
-        </is>
-      </c>
-      <c r="M71" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="N71" s="4" t="n">
-        <v>103</v>
-      </c>
-      <c r="O71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="Q71" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="R71" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="S71" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="T71" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="U71" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="V71" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="R71" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="S71" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="T71" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="U71" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="V71" s="4" t="n">
-        <v>30</v>
-      </c>
       <c r="W71" s="4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>0x87_Gargoyle</t>
+          <t>0x87_LowMage</t>
         </is>
       </c>
       <c r="B72" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C72" s="4" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F72" s="4" t="n">
         <v>13</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
@@ -38245,36 +38288,111 @@
         </is>
       </c>
       <c r="M72" s="4" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="N72" s="4" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O72" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P72" s="4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Q72" s="4" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="R72" s="4" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="S72" s="4" t="n">
         <v>49</v>
       </c>
       <c r="T72" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="U72" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="V72" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="W72" s="4" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>0x87_Gargoyle</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C73" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="D73" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="E73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="H73" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="I73" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L73" s="4" t="inlineStr">
+        <is>
+          <t>SharpClaw</t>
+        </is>
+      </c>
+      <c r="M73" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="N73" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="O73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q73" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="R73" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="S73" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="T73" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="U72" s="4" t="n">
+      <c r="U73" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="V72" s="4" t="n">
+      <c r="V73" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="W72" s="4" t="n">
+      <c r="W73" s="4" t="n">
         <v>35</v>
       </c>
     </row>

--- a/unit_stats.xlsx
+++ b/unit_stats.xlsx
@@ -27882,7 +27882,7 @@
         </is>
       </c>
       <c r="M72" s="4" t="n">
-        <v>274</v>
+        <v>29</v>
       </c>
       <c r="N72" s="4" t="n">
         <v>145</v>
@@ -32997,7 +32997,7 @@
         </is>
       </c>
       <c r="M72" s="4" t="n">
-        <v>271</v>
+        <v>26</v>
       </c>
       <c r="N72" s="4" t="n">
         <v>140</v>

--- a/unit_stats.xlsx
+++ b/unit_stats.xlsx
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N3" s="2" t="n">
         <v>125</v>
@@ -2263,10 +2263,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W73"/>
+  <dimension ref="A1:W74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N3" s="2" t="n">
         <v>125</v>
@@ -3714,7 +3714,7 @@
         <v>2</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>9</v>
@@ -3728,7 +3728,7 @@
         <v>18</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="O19" s="2" t="n">
         <v>0</v>
@@ -3737,7 +3737,7 @@
         <v>11</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R19" s="2" t="n">
         <v>15</v>
@@ -3789,7 +3789,7 @@
         <v>2</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>9</v>
@@ -3803,7 +3803,7 @@
         <v>13</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>0</v>
@@ -3812,7 +3812,7 @@
         <v>11</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R20" s="2" t="n">
         <v>15</v>
@@ -3864,21 +3864,21 @@
         <v>2</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>9</v>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>IronLance</t>
+          <t>Swordbreaker</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="O21" s="2" t="n">
         <v>0</v>
@@ -3887,7 +3887,7 @@
         <v>13</v>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R21" s="2" t="n">
         <v>17</v>
@@ -7466,6 +7466,81 @@
       </c>
       <c r="W73" s="4" t="n">
         <v>32</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>JabberwockBlocker_Revenant</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C74" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="D74" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H74" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I74" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L74" s="4" t="inlineStr">
+        <is>
+          <t>FetidClaw</t>
+        </is>
+      </c>
+      <c r="M74" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="N74" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="O74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="R74" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="S74" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="T74" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="U74" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="V74" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="W74" s="4" t="n">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -8771,7 +8846,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N3" s="2" t="n">
         <v>125</v>
@@ -10579,7 +10654,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N3" s="2" t="n">
         <v>125</v>
@@ -13389,7 +13464,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N3" s="2" t="n">
         <v>125</v>
@@ -16199,7 +16274,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N3" s="2" t="n">
         <v>125</v>
@@ -17388,7 +17463,7 @@
         <v>2</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>9</v>
@@ -17402,7 +17477,7 @@
         <v>18</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="O19" s="2" t="n">
         <v>0</v>
@@ -17411,7 +17486,7 @@
         <v>10</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="R19" s="2" t="n">
         <v>14</v>
@@ -17463,7 +17538,7 @@
         <v>2</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>9</v>
@@ -17477,7 +17552,7 @@
         <v>13</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>0</v>
@@ -17486,7 +17561,7 @@
         <v>10</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="R20" s="2" t="n">
         <v>14</v>
@@ -17538,21 +17613,21 @@
         <v>2</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>9</v>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>IronLance</t>
+          <t>Swordbreaker</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="O21" s="2" t="n">
         <v>0</v>
@@ -17561,7 +17636,7 @@
         <v>12</v>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="R21" s="2" t="n">
         <v>16</v>
@@ -17700,7 +17775,7 @@
         </is>
       </c>
       <c r="M24" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N24" s="3" t="n">
         <v>97</v>
@@ -17850,7 +17925,7 @@
         </is>
       </c>
       <c r="M26" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>111</v>
@@ -18000,7 +18075,7 @@
         </is>
       </c>
       <c r="M28" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>99</v>
@@ -18371,7 +18446,7 @@
         </is>
       </c>
       <c r="M35" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N35" s="4" t="n">
         <v>105</v>
@@ -18671,7 +18746,7 @@
         </is>
       </c>
       <c r="M39" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N39" s="4" t="n">
         <v>113</v>
@@ -19711,7 +19786,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N3" s="2" t="n">
         <v>125</v>
@@ -20900,7 +20975,7 @@
         <v>2</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>9</v>
@@ -20914,7 +20989,7 @@
         <v>18</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="O19" s="2" t="n">
         <v>0</v>
@@ -20923,7 +20998,7 @@
         <v>10</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="R19" s="2" t="n">
         <v>14</v>
@@ -20975,7 +21050,7 @@
         <v>2</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>9</v>
@@ -20989,7 +21064,7 @@
         <v>13</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>0</v>
@@ -20998,7 +21073,7 @@
         <v>10</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="R20" s="2" t="n">
         <v>14</v>
@@ -21050,21 +21125,21 @@
         <v>2</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>9</v>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>IronLance</t>
+          <t>Swordbreaker</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="O21" s="2" t="n">
         <v>0</v>
@@ -21073,7 +21148,7 @@
         <v>12</v>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="R21" s="2" t="n">
         <v>16</v>
@@ -21212,7 +21287,7 @@
         </is>
       </c>
       <c r="M24" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N24" s="3" t="n">
         <v>97</v>
@@ -21362,7 +21437,7 @@
         </is>
       </c>
       <c r="M26" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>111</v>
@@ -21512,7 +21587,7 @@
         </is>
       </c>
       <c r="M28" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>99</v>
@@ -21883,7 +21958,7 @@
         </is>
       </c>
       <c r="M35" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N35" s="4" t="n">
         <v>100</v>
@@ -22183,7 +22258,7 @@
         </is>
       </c>
       <c r="M39" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N39" s="4" t="n">
         <v>108</v>
@@ -23223,7 +23298,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N3" s="2" t="n">
         <v>125</v>
@@ -24412,7 +24487,7 @@
         <v>2</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>9</v>
@@ -24426,7 +24501,7 @@
         <v>18</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="O19" s="2" t="n">
         <v>0</v>
@@ -24435,7 +24510,7 @@
         <v>10</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="R19" s="2" t="n">
         <v>14</v>
@@ -24487,7 +24562,7 @@
         <v>2</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>9</v>
@@ -24501,7 +24576,7 @@
         <v>13</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>0</v>
@@ -24510,7 +24585,7 @@
         <v>10</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="R20" s="2" t="n">
         <v>14</v>
@@ -24562,21 +24637,21 @@
         <v>2</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>9</v>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>IronLance</t>
+          <t>Swordbreaker</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="O21" s="2" t="n">
         <v>0</v>
@@ -24585,7 +24660,7 @@
         <v>12</v>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="R21" s="2" t="n">
         <v>16</v>
@@ -24992,7 +25067,7 @@
         </is>
       </c>
       <c r="M28" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>97</v>
@@ -25142,7 +25217,7 @@
         </is>
       </c>
       <c r="M30" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>97</v>
@@ -28338,7 +28413,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N3" s="2" t="n">
         <v>125</v>
@@ -29527,7 +29602,7 @@
         <v>2</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>9</v>
@@ -29541,7 +29616,7 @@
         <v>18</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="O19" s="2" t="n">
         <v>0</v>
@@ -29550,7 +29625,7 @@
         <v>10</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="R19" s="2" t="n">
         <v>14</v>
@@ -29602,7 +29677,7 @@
         <v>2</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>9</v>
@@ -29616,7 +29691,7 @@
         <v>13</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>0</v>
@@ -29625,7 +29700,7 @@
         <v>10</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="R20" s="2" t="n">
         <v>14</v>
@@ -29677,21 +29752,21 @@
         <v>2</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>9</v>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>IronLance</t>
+          <t>Swordbreaker</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="O21" s="2" t="n">
         <v>0</v>
@@ -29700,7 +29775,7 @@
         <v>12</v>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="R21" s="2" t="n">
         <v>16</v>
@@ -30107,7 +30182,7 @@
         </is>
       </c>
       <c r="M28" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>97</v>
@@ -30257,7 +30332,7 @@
         </is>
       </c>
       <c r="M30" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>97</v>
@@ -33191,10 +33266,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W73"/>
+  <dimension ref="A1:W74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
@@ -33453,7 +33528,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N3" s="2" t="n">
         <v>125</v>
@@ -34642,7 +34717,7 @@
         <v>2</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>9</v>
@@ -34656,7 +34731,7 @@
         <v>18</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="O19" s="2" t="n">
         <v>0</v>
@@ -34665,7 +34740,7 @@
         <v>11</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R19" s="2" t="n">
         <v>15</v>
@@ -34717,7 +34792,7 @@
         <v>2</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>9</v>
@@ -34731,7 +34806,7 @@
         <v>13</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>0</v>
@@ -34740,7 +34815,7 @@
         <v>11</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R20" s="2" t="n">
         <v>15</v>
@@ -34792,21 +34867,21 @@
         <v>2</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>9</v>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>IronLance</t>
+          <t>Swordbreaker</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="O21" s="2" t="n">
         <v>0</v>
@@ -34815,7 +34890,7 @@
         <v>13</v>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R21" s="2" t="n">
         <v>17</v>
@@ -38396,6 +38471,81 @@
         <v>35</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>JabberwockBlocker_Revenant</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C74" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="D74" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H74" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I74" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L74" s="4" t="inlineStr">
+        <is>
+          <t>FetidClaw</t>
+        </is>
+      </c>
+      <c r="M74" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="N74" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="O74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="R74" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="S74" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="T74" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="U74" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="V74" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="W74" s="4" t="n">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/unit_stats.xlsx
+++ b/unit_stats.xlsx
@@ -2263,7 +2263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W74"/>
+  <dimension ref="A1:W75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -5971,29 +5971,29 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_HighMage</t>
+          <t>Lowlander_Myrmidon</t>
         </is>
       </c>
       <c r="B54" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C54" s="4" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I54" s="4" t="n">
         <v>6</v>
@@ -6002,189 +6002,189 @@
         <v>1</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>SilverSword</t>
         </is>
       </c>
       <c r="M54" s="4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="O54" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P54" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Q54" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="R54" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="R54" s="4" t="n">
-        <v>12</v>
-      </c>
       <c r="S54" s="4" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="T54" s="4" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="U54" s="4" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="V54" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="W54" s="4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_Soldier</t>
+          <t>Lowlander_HighMage</t>
         </is>
       </c>
       <c r="B55" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C55" s="4" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>SavageGore</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="M55" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="N55" s="4" t="n">
+        <v>109</v>
+      </c>
+      <c r="O55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q55" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="R55" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="S55" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="N55" s="4" t="n">
-        <v>95</v>
-      </c>
-      <c r="O55" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="P55" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q55" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="R55" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="S55" s="4" t="n">
-        <v>35</v>
-      </c>
       <c r="T55" s="4" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="U55" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="V55" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W55" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_Archer</t>
+          <t>Lowlander_Soldier</t>
         </is>
       </c>
       <c r="B56" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C56" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="D56" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>SavageGore</t>
+        </is>
+      </c>
+      <c r="M56" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="N56" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="O56" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="P56" s="4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q56" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="R56" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S56" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="T56" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="U56" s="4" t="n">
         <v>26</v>
-      </c>
-      <c r="D56" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="E56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="G56" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="H56" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="I56" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="J56" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K56" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>SteelBow</t>
-        </is>
-      </c>
-      <c r="M56" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="N56" s="4" t="n">
-        <v>106</v>
-      </c>
-      <c r="O56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q56" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="R56" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="S56" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="T56" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="U56" s="4" t="n">
-        <v>24</v>
       </c>
       <c r="V56" s="4" t="n">
         <v>18</v>
@@ -6196,17 +6196,17 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Beast_SwordBone</t>
+          <t>Lowlander_Archer</t>
         </is>
       </c>
       <c r="B57" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C57" s="4" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E57" s="4" t="n">
         <v>0</v>
@@ -6215,402 +6215,402 @@
         <v>12</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>Armorslayer</t>
+          <t>SteelBow</t>
         </is>
       </c>
       <c r="M57" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="N57" s="4" t="n">
+        <v>106</v>
+      </c>
+      <c r="O57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q57" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="R57" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="S57" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="T57" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="U57" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="N57" s="4" t="n">
-        <v>119</v>
-      </c>
-      <c r="O57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q57" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="R57" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="S57" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="T57" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="U57" s="4" t="n">
-        <v>32</v>
-      </c>
       <c r="V57" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="W57" s="4" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_LowMage</t>
+          <t>Beast_SwordBone</t>
         </is>
       </c>
       <c r="B58" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C58" s="4" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L58" s="4" t="inlineStr">
+        <is>
+          <t>Armorslayer</t>
+        </is>
+      </c>
+      <c r="M58" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="N58" s="4" t="n">
+        <v>119</v>
+      </c>
+      <c r="O58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q58" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="R58" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="F58" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="G58" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H58" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="I58" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="J58" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K58" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L58" s="4" t="inlineStr">
-        <is>
-          <t>Pain</t>
-        </is>
-      </c>
-      <c r="M58" s="4" t="n">
+      <c r="S58" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="T58" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="U58" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="V58" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="N58" s="4" t="n">
-        <v>115</v>
-      </c>
-      <c r="O58" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="P58" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q58" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="R58" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="S58" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="T58" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="U58" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="V58" s="4" t="n">
-        <v>26</v>
-      </c>
       <c r="W58" s="4" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Beast_LanceBone</t>
+          <t>Lowlander_LowMage</t>
         </is>
       </c>
       <c r="B59" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C59" s="4" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F59" s="4" t="n">
         <v>12</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K59" s="4" t="n">
         <v>8</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>HeavySpear</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="M59" s="4" t="n">
         <v>23</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P59" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q59" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="R59" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="S59" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="T59" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="U59" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="V59" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="W59" s="4" t="n">
         <v>22</v>
-      </c>
-      <c r="R59" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="S59" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="T59" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="U59" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="V59" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="W59" s="4" t="n">
-        <v>29</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Beast_Bael</t>
+          <t>Beast_LanceBone</t>
         </is>
       </c>
       <c r="B60" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E60" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>SharpClaw</t>
+          <t>HeavySpear</t>
         </is>
       </c>
       <c r="M60" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="N60" s="4" t="n">
+        <v>104</v>
+      </c>
+      <c r="O60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q60" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="R60" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="S60" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="T60" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="U60" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="N60" s="4" t="n">
-        <v>96</v>
-      </c>
-      <c r="O60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q60" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="R60" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="S60" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="T60" s="4" t="n">
-        <v>61</v>
-      </c>
-      <c r="U60" s="4" t="n">
-        <v>40</v>
-      </c>
       <c r="V60" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="W60" s="4" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_Mercenary</t>
+          <t>Beast_Bael</t>
         </is>
       </c>
       <c r="B61" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C61" s="4" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E61" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>Lancereaver</t>
+          <t>SharpClaw</t>
         </is>
       </c>
       <c r="M61" s="4" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="O61" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P61" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q61" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="R61" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="S61" s="4" t="n">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="T61" s="4" t="n">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="U61" s="4" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="V61" s="4" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="W61" s="4" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Beast_Cyclops</t>
+          <t>Lowlander_Mercenary</t>
         </is>
       </c>
       <c r="B62" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C62" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H62" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I62" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C62" s="4" t="n">
-        <v>74</v>
-      </c>
-      <c r="D62" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="E62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G62" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="H62" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="I62" s="4" t="n">
-        <v>6</v>
-      </c>
       <c r="J62" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
-          <t>SilverAxe</t>
+          <t>Lancereaver</t>
         </is>
       </c>
       <c r="M62" s="4" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="N62" s="4" t="n">
         <v>110</v>
@@ -6619,41 +6619,41 @@
         <v>0</v>
       </c>
       <c r="P62" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Q62" s="4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="R62" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="S62" s="4" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="T62" s="4" t="n">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="U62" s="4" t="n">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="V62" s="4" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="W62" s="4" t="n">
-        <v>59</v>
+        <v>20</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Beast_Gargoyle</t>
+          <t>Beast_Cyclops</t>
         </is>
       </c>
       <c r="B63" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C63" s="4" t="n">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="D63" s="4" t="n">
         <v>17</v>
@@ -6662,141 +6662,141 @@
         <v>0</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
-          <t>SteelLance</t>
+          <t>SilverAxe</t>
         </is>
       </c>
       <c r="M63" s="4" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="O63" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P63" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q63" s="4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="R63" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="S63" s="4" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="T63" s="4" t="n">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="U63" s="4" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="V63" s="4" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="W63" s="4" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_AxeCav</t>
+          <t>Beast_Gargoyle</t>
         </is>
       </c>
       <c r="B64" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E64" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K64" s="4" t="n">
         <v>9</v>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
-          <t>IronAxe</t>
+          <t>SteelLance</t>
         </is>
       </c>
       <c r="M64" s="4" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="O64" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P64" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q64" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="R64" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="R64" s="4" t="n">
-        <v>10</v>
-      </c>
       <c r="S64" s="4" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="T64" s="4" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="U64" s="4" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="V64" s="4" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="W64" s="4" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_SwordCav</t>
+          <t>Lowlander_AxeCav</t>
         </is>
       </c>
       <c r="B65" s="4" t="n">
@@ -6831,26 +6831,26 @@
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
-          <t>SteelSword</t>
+          <t>IronAxe</t>
         </is>
       </c>
       <c r="M65" s="4" t="n">
         <v>19</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="O65" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P65" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q65" s="4" t="n">
         <v>15</v>
       </c>
       <c r="R65" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S65" s="4" t="n">
         <v>31</v>
@@ -6871,338 +6871,338 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Beast_Jabberwock</t>
+          <t>Lowlander_SwordCav</t>
         </is>
       </c>
       <c r="B66" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E66" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H66" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I66" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I66" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="J66" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K66" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L66" s="4" t="inlineStr">
+        <is>
+          <t>SteelSword</t>
+        </is>
+      </c>
+      <c r="M66" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="N66" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="O66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q66" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="L66" s="4" t="inlineStr">
-        <is>
-          <t>FetidClaw</t>
-        </is>
-      </c>
-      <c r="M66" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="N66" s="4" t="n">
-        <v>93</v>
-      </c>
-      <c r="O66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q66" s="4" t="n">
-        <v>8</v>
-      </c>
       <c r="R66" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="S66" s="4" t="n">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="T66" s="4" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="U66" s="4" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="V66" s="4" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="W66" s="4" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>0x87_MogallClass</t>
+          <t>Beast_Jabberwock</t>
         </is>
       </c>
       <c r="B67" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="J67" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
-          <t>EvilEye</t>
+          <t>FetidClaw</t>
         </is>
       </c>
       <c r="M67" s="4" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="N67" s="4" t="n">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="O67" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P67" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="Q67" s="4" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="R67" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="S67" s="4" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="T67" s="4" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="U67" s="4" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="V67" s="4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="W67" s="4" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>0x87_Bael</t>
+          <t>0x87_MogallClass</t>
         </is>
       </c>
       <c r="B68" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C68" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E68" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H68" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I68" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="J68" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K68" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L68" s="4" t="inlineStr">
+        <is>
+          <t>EvilEye</t>
+        </is>
+      </c>
+      <c r="M68" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="N68" s="4" t="n">
+        <v>112</v>
+      </c>
+      <c r="O68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q68" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="R68" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="S68" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="D68" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="E68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G68" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="H68" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="I68" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="L68" s="4" t="inlineStr">
-        <is>
-          <t>SharpClaw</t>
-        </is>
-      </c>
-      <c r="M68" s="4" t="n">
+      <c r="T68" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="U68" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="V68" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="N68" s="4" t="n">
-        <v>95</v>
-      </c>
-      <c r="O68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P68" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q68" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="R68" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="S68" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="T68" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="U68" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="V68" s="4" t="n">
-        <v>27</v>
-      </c>
       <c r="W68" s="4" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>0x87_Cyclops</t>
+          <t>0x87_Bael</t>
         </is>
       </c>
       <c r="B69" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C69" s="4" t="n">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E69" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G69" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H69" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I69" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="H69" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="I69" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="J69" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K69" s="4" t="n">
-        <v>17</v>
-      </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
           <t>SharpClaw</t>
         </is>
       </c>
       <c r="M69" s="4" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="N69" s="4" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="O69" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P69" s="4" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="Q69" s="4" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="R69" s="4" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="S69" s="4" t="n">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="T69" s="4" t="n">
-        <v>104</v>
+        <v>59</v>
       </c>
       <c r="U69" s="4" t="n">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="V69" s="4" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="W69" s="4" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>0x87_Revenant</t>
+          <t>0x87_Cyclops</t>
         </is>
       </c>
       <c r="B70" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C70" s="4" t="n">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E70" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H70" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="I70" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J70" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I70" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J70" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K70" s="4" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
@@ -7210,149 +7210,149 @@
         </is>
       </c>
       <c r="M70" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="N70" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="O70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q70" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="N70" s="4" t="n">
-        <v>87</v>
-      </c>
-      <c r="O70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="Q70" s="4" t="n">
-        <v>8</v>
-      </c>
       <c r="R70" s="4" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="S70" s="4" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="T70" s="4" t="n">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="U70" s="4" t="n">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="V70" s="4" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="W70" s="4" t="n">
-        <v>29</v>
+        <v>64</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>0x87_Mercenary</t>
+          <t>0x87_Revenant</t>
         </is>
       </c>
       <c r="B71" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C71" s="4" t="n">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E71" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H71" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I71" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L71" s="4" t="inlineStr">
+        <is>
+          <t>SharpClaw</t>
+        </is>
+      </c>
+      <c r="M71" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="N71" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="O71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" s="4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q71" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="R71" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J71" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K71" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="L71" s="4" t="inlineStr">
-        <is>
-          <t>SharpClaw</t>
-        </is>
-      </c>
-      <c r="M71" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="N71" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="O71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q71" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="R71" s="4" t="n">
-        <v>9</v>
-      </c>
       <c r="S71" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="T71" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="U71" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="V71" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="W71" s="4" t="n">
         <v>29</v>
-      </c>
-      <c r="T71" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="U71" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="V71" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="W71" s="4" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>0x87_LowMage</t>
+          <t>0x87_Mercenary</t>
         </is>
       </c>
       <c r="B72" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C72" s="4" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H72" s="4" t="n">
         <v>5</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
@@ -7360,74 +7360,74 @@
         </is>
       </c>
       <c r="M72" s="4" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N72" s="4" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="O72" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P72" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q72" s="4" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="R72" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="S72" s="4" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="T72" s="4" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="U72" s="4" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="V72" s="4" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="W72" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>0x87_Gargoyle</t>
+          <t>0x87_LowMage</t>
         </is>
       </c>
       <c r="B73" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C73" s="4" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F73" s="4" t="n">
         <v>11</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H73" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
@@ -7435,111 +7435,186 @@
         </is>
       </c>
       <c r="M73" s="4" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="N73" s="4" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O73" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P73" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q73" s="4" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="R73" s="4" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="S73" s="4" t="n">
         <v>43</v>
       </c>
       <c r="T73" s="4" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="U73" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="V73" s="4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="W73" s="4" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
+          <t>0x87_Gargoyle</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C74" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="D74" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="E74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="H74" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I74" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L74" s="4" t="inlineStr">
+        <is>
+          <t>SharpClaw</t>
+        </is>
+      </c>
+      <c r="M74" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="N74" s="4" t="n">
+        <v>97</v>
+      </c>
+      <c r="O74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q74" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="R74" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="S74" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="T74" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="U74" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="V74" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="W74" s="4" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
           <t>JabberwockBlocker_Revenant</t>
         </is>
       </c>
-      <c r="B74" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="C74" s="4" t="n">
+      <c r="B75" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C75" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="D74" s="4" t="n">
+      <c r="D75" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E74" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" s="4" t="n">
+      <c r="E75" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G74" s="4" t="n">
+      <c r="G75" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H74" s="4" t="n">
+      <c r="H75" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I74" s="4" t="n">
+      <c r="I75" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="J74" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K74" s="4" t="n">
+      <c r="J75" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="L74" s="4" t="inlineStr">
+      <c r="L75" s="4" t="inlineStr">
         <is>
           <t>FetidClaw</t>
         </is>
       </c>
-      <c r="M74" s="4" t="n">
+      <c r="M75" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="N74" s="4" t="n">
+      <c r="N75" s="4" t="n">
         <v>95</v>
       </c>
-      <c r="O74" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P74" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q74" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="R74" s="4" t="n">
+      <c r="O75" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="R75" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="S74" s="4" t="n">
+      <c r="S75" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="T74" s="4" t="n">
+      <c r="T75" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="U74" s="4" t="n">
+      <c r="U75" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="V74" s="4" t="n">
+      <c r="V75" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="W74" s="4" t="n">
+      <c r="W75" s="4" t="n">
         <v>17</v>
       </c>
     </row>
@@ -19007,76 +19082,76 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Combatant_Myrmidon</t>
+          <t>Combatant_Archer</t>
         </is>
       </c>
       <c r="B43" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C43" s="4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D43" s="4" t="n">
         <v>8</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H43" s="4" t="n">
         <v>5</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>2</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>SlimSword</t>
+          <t>IronBow</t>
         </is>
       </c>
       <c r="M43" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="O43" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P43" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Q43" s="4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="R43" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="S43" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="T43" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="U43" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="V43" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="S43" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="T43" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="U43" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="V43" s="4" t="n">
-        <v>20</v>
-      </c>
       <c r="W43" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44">
@@ -19157,151 +19232,151 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Combatant_WyvernRider</t>
+          <t>Combatant_Myrmidon</t>
         </is>
       </c>
       <c r="B45" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>2</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>SteelLance</t>
+          <t>LightBrand</t>
         </is>
       </c>
       <c r="M45" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="O45" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P45" s="4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="Q45" s="4" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="R45" s="4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="S45" s="4" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="T45" s="4" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="U45" s="4" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="V45" s="4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="W45" s="4" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Combatant_Archer</t>
+          <t>Combatant_WyvernRider</t>
         </is>
       </c>
       <c r="B46" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E46" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>2</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>SteelBow</t>
+          <t>SteelLance</t>
         </is>
       </c>
       <c r="M46" s="4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="O46" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P46" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q46" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="R46" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="S46" s="4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T46" s="4" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="U46" s="4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="V46" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="W46" s="4" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="47">
@@ -22519,76 +22594,76 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Combatant_Myrmidon</t>
+          <t>Combatant_Archer</t>
         </is>
       </c>
       <c r="B43" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C43" s="4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D43" s="4" t="n">
         <v>7</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H43" s="4" t="n">
         <v>4</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>SlimSword</t>
+          <t>IronBow</t>
         </is>
       </c>
       <c r="M43" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="O43" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P43" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Q43" s="4" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="R43" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="S43" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="T43" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="U43" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="V43" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="S43" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="T43" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="U43" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="V43" s="4" t="n">
-        <v>18</v>
-      </c>
       <c r="W43" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44">
@@ -22669,7 +22744,7 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Combatant_WyvernRider</t>
+          <t>Combatant_Myrmidon</t>
         </is>
       </c>
       <c r="B45" s="4" t="n">
@@ -22679,141 +22754,141 @@
         <v>26</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F45" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I45" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G45" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="H45" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="I45" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="J45" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>SteelLance</t>
+          <t>LightBrand</t>
         </is>
       </c>
       <c r="M45" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="O45" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P45" s="4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="Q45" s="4" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="R45" s="4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="S45" s="4" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="T45" s="4" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="U45" s="4" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="V45" s="4" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="W45" s="4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Combatant_Archer</t>
+          <t>Combatant_WyvernRider</t>
         </is>
       </c>
       <c r="B46" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D46" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G46" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="E46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="G46" s="4" t="n">
-        <v>8</v>
-      </c>
       <c r="H46" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>SteelLance</t>
+        </is>
+      </c>
+      <c r="M46" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="N46" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="O46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I46" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J46" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K46" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L46" s="4" t="inlineStr">
-        <is>
-          <t>SteelBow</t>
-        </is>
-      </c>
-      <c r="M46" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="N46" s="4" t="n">
-        <v>103</v>
-      </c>
-      <c r="O46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" s="4" t="n">
-        <v>6</v>
-      </c>
       <c r="Q46" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R46" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="S46" s="4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="T46" s="4" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="U46" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="V46" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="W46" s="4" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="47">
@@ -33266,7 +33341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W74"/>
+  <dimension ref="A1:W75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -36974,220 +37049,220 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_HighMage</t>
+          <t>Lowlander_Myrmidon</t>
         </is>
       </c>
       <c r="B54" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C54" s="4" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D54" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I54" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="E54" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="F54" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="G54" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H54" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I54" s="4" t="n">
-        <v>8</v>
-      </c>
       <c r="J54" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>SilverSword</t>
         </is>
       </c>
       <c r="M54" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="O54" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P54" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="Q54" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="R54" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="S54" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="T54" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="U54" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="V54" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="W54" s="4" t="n">
         <v>22</v>
-      </c>
-      <c r="R54" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="S54" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="T54" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="U54" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="V54" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="W54" s="4" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_Soldier</t>
+          <t>Lowlander_HighMage</t>
         </is>
       </c>
       <c r="B55" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C55" s="4" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="D55" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H55" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I55" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J55" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K55" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L55" s="4" t="inlineStr">
+        <is>
+          <t>Thunder</t>
+        </is>
+      </c>
+      <c r="M55" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="N55" s="4" t="n">
+        <v>116</v>
+      </c>
+      <c r="O55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q55" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="R55" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="S55" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="T55" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="U55" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="V55" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="W55" s="4" t="n">
         <v>16</v>
-      </c>
-      <c r="E55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="G55" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H55" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I55" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J55" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K55" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L55" s="4" t="inlineStr">
-        <is>
-          <t>SavageGore</t>
-        </is>
-      </c>
-      <c r="M55" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="N55" s="4" t="n">
-        <v>101</v>
-      </c>
-      <c r="O55" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="P55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="R55" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="S55" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="T55" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="U55" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="V55" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="W55" s="4" t="n">
-        <v>21</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_Archer</t>
+          <t>Lowlander_Soldier</t>
         </is>
       </c>
       <c r="B56" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E56" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F56" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J56" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K56" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>SavageGore</t>
+        </is>
+      </c>
+      <c r="M56" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="N56" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="O56" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="P56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="G56" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="H56" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="I56" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="J56" s="4" t="n">
+      <c r="R56" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="K56" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>SteelBow</t>
-        </is>
-      </c>
-      <c r="M56" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="N56" s="4" t="n">
-        <v>114</v>
-      </c>
-      <c r="O56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q56" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="R56" s="4" t="n">
-        <v>13</v>
-      </c>
       <c r="S56" s="4" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="T56" s="4" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="U56" s="4" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="V56" s="4" t="n">
         <v>21</v>
@@ -37199,607 +37274,607 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Beast_SwordBone</t>
+          <t>Lowlander_Archer</t>
         </is>
       </c>
       <c r="B57" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C57" s="4" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E57" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>Armorslayer</t>
+          <t>SteelBow</t>
         </is>
       </c>
       <c r="M57" s="4" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="O57" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P57" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q57" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R57" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S57" s="4" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="T57" s="4" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="U57" s="4" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="V57" s="4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="W57" s="4" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_LowMage</t>
+          <t>Beast_SwordBone</t>
         </is>
       </c>
       <c r="B58" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C58" s="4" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F58" s="4" t="n">
         <v>14</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K58" s="4" t="n">
         <v>8</v>
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Armorslayer</t>
         </is>
       </c>
       <c r="M58" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="N58" s="4" t="n">
+        <v>124</v>
+      </c>
+      <c r="O58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q58" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="R58" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="S58" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="T58" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="U58" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="V58" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="N58" s="4" t="n">
-        <v>120</v>
-      </c>
-      <c r="O58" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="P58" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q58" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="R58" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="S58" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="T58" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="U58" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="V58" s="4" t="n">
-        <v>30</v>
-      </c>
       <c r="W58" s="4" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Beast_LanceBone</t>
+          <t>Lowlander_LowMage</t>
         </is>
       </c>
       <c r="B59" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C59" s="4" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F59" s="4" t="n">
         <v>14</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K59" s="4" t="n">
         <v>8</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>HeavySpear</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="M59" s="4" t="n">
         <v>26</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P59" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q59" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="R59" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="S59" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T59" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="U59" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="V59" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="W59" s="4" t="n">
         <v>25</v>
-      </c>
-      <c r="R59" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="S59" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="T59" s="4" t="n">
-        <v>54</v>
-      </c>
-      <c r="U59" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="V59" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="W59" s="4" t="n">
-        <v>32</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Beast_Bael</t>
+          <t>Beast_LanceBone</t>
         </is>
       </c>
       <c r="B60" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E60" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>SharpClaw</t>
+          <t>HeavySpear</t>
         </is>
       </c>
       <c r="M60" s="4" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="O60" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P60" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q60" s="4" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="R60" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="S60" s="4" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="T60" s="4" t="n">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="U60" s="4" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="V60" s="4" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="W60" s="4" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_Mercenary</t>
+          <t>Beast_Bael</t>
         </is>
       </c>
       <c r="B61" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C61" s="4" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E61" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F61" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H61" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I61" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J61" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K61" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="G61" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="H61" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="I61" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J61" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K61" s="4" t="n">
-        <v>10</v>
-      </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>Lancereaver</t>
+          <t>SharpClaw</t>
         </is>
       </c>
       <c r="M61" s="4" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="O61" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P61" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Q61" s="4" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="R61" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="S61" s="4" t="n">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="T61" s="4" t="n">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="U61" s="4" t="n">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="V61" s="4" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="W61" s="4" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Beast_Cyclops</t>
+          <t>Lowlander_Mercenary</t>
         </is>
       </c>
       <c r="B62" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C62" s="4" t="n">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="D62" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H62" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="I62" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J62" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K62" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L62" s="4" t="inlineStr">
+        <is>
+          <t>Lancereaver</t>
+        </is>
+      </c>
+      <c r="M62" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="N62" s="4" t="n">
+        <v>118</v>
+      </c>
+      <c r="O62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q62" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="R62" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="S62" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="T62" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="U62" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="V62" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="E62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="G62" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="H62" s="4" t="n">
+      <c r="W62" s="4" t="n">
         <v>24</v>
-      </c>
-      <c r="I62" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="J62" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K62" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="L62" s="4" t="inlineStr">
-        <is>
-          <t>SilverAxe</t>
-        </is>
-      </c>
-      <c r="M62" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="N62" s="4" t="n">
-        <v>115</v>
-      </c>
-      <c r="O62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q62" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="R62" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="S62" s="4" t="n">
-        <v>88</v>
-      </c>
-      <c r="T62" s="4" t="n">
-        <v>104</v>
-      </c>
-      <c r="U62" s="4" t="n">
-        <v>68</v>
-      </c>
-      <c r="V62" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="W62" s="4" t="n">
-        <v>64</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Beast_Gargoyle</t>
+          <t>Beast_Cyclops</t>
         </is>
       </c>
       <c r="B63" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C63" s="4" t="n">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E63" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
-          <t>SteelLance</t>
+          <t>SilverAxe</t>
         </is>
       </c>
       <c r="M63" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="N63" s="4" t="n">
+        <v>115</v>
+      </c>
+      <c r="O63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q63" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="N63" s="4" t="n">
-        <v>99</v>
-      </c>
-      <c r="O63" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q63" s="4" t="n">
-        <v>35</v>
-      </c>
       <c r="R63" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="S63" s="4" t="n">
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="T63" s="4" t="n">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="U63" s="4" t="n">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="V63" s="4" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="W63" s="4" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_AxeCav</t>
+          <t>Beast_Gargoyle</t>
         </is>
       </c>
       <c r="B64" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E64" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K64" s="4" t="n">
         <v>9</v>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
-          <t>IronAxe</t>
+          <t>SteelLance</t>
         </is>
       </c>
       <c r="M64" s="4" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="O64" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P64" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Q64" s="4" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="R64" s="4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="S64" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="T64" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="U64" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="V64" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="W64" s="4" t="n">
         <v>37</v>
-      </c>
-      <c r="T64" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="U64" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="V64" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="W64" s="4" t="n">
-        <v>26</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_SwordCav</t>
+          <t>Lowlander_AxeCav</t>
         </is>
       </c>
       <c r="B65" s="4" t="n">
@@ -37834,26 +37909,26 @@
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
-          <t>SteelSword</t>
+          <t>IronAxe</t>
         </is>
       </c>
       <c r="M65" s="4" t="n">
         <v>21</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="O65" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P65" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q65" s="4" t="n">
         <v>21</v>
       </c>
       <c r="R65" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="S65" s="4" t="n">
         <v>37</v>
@@ -37874,14 +37949,14 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Beast_Jabberwock</t>
+          <t>Lowlander_SwordCav</t>
         </is>
       </c>
       <c r="B66" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="D66" s="4" t="n">
         <v>11</v>
@@ -37890,547 +37965,547 @@
         <v>0</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I66" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
-          <t>FetidClaw</t>
+          <t>SteelSword</t>
         </is>
       </c>
       <c r="M66" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="O66" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P66" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Q66" s="4" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="R66" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="S66" s="4" t="n">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="T66" s="4" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="U66" s="4" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="V66" s="4" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="W66" s="4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>0x87_MogallClass</t>
+          <t>Beast_Jabberwock</t>
         </is>
       </c>
       <c r="B67" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J67" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
-          <t>EvilEye</t>
+          <t>FetidClaw</t>
         </is>
       </c>
       <c r="M67" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N67" s="4" t="n">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="O67" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P67" s="4" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="Q67" s="4" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="R67" s="4" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="S67" s="4" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="T67" s="4" t="n">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="U67" s="4" t="n">
         <v>44</v>
       </c>
       <c r="V67" s="4" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="W67" s="4" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>0x87_Bael</t>
+          <t>0x87_MogallClass</t>
         </is>
       </c>
       <c r="B68" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C68" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E68" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="H68" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I68" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="J68" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K68" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L68" s="4" t="inlineStr">
+        <is>
+          <t>EvilEye</t>
+        </is>
+      </c>
+      <c r="M68" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="N68" s="4" t="n">
+        <v>118</v>
+      </c>
+      <c r="O68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q68" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="R68" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="S68" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="D68" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="E68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="G68" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="H68" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="I68" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J68" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K68" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="L68" s="4" t="inlineStr">
-        <is>
-          <t>SharpClaw</t>
-        </is>
-      </c>
-      <c r="M68" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="N68" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="O68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P68" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q68" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="R68" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="S68" s="4" t="n">
-        <v>58</v>
-      </c>
       <c r="T68" s="4" t="n">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="U68" s="4" t="n">
         <v>44</v>
       </c>
       <c r="V68" s="4" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="W68" s="4" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>0x87_Cyclops</t>
+          <t>0x87_Bael</t>
         </is>
       </c>
       <c r="B69" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C69" s="4" t="n">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E69" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H69" s="4" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K69" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="L69" s="4" t="inlineStr">
+        <is>
+          <t>SharpClaw</t>
+        </is>
+      </c>
+      <c r="M69" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="N69" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="O69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q69" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="L69" s="4" t="inlineStr">
-        <is>
-          <t>SharpClaw</t>
-        </is>
-      </c>
-      <c r="M69" s="4" t="n">
+      <c r="R69" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="S69" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="T69" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="U69" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="V69" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="W69" s="4" t="n">
         <v>38</v>
-      </c>
-      <c r="N69" s="4" t="n">
-        <v>114</v>
-      </c>
-      <c r="O69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P69" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q69" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="R69" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="S69" s="4" t="n">
-        <v>95</v>
-      </c>
-      <c r="T69" s="4" t="n">
-        <v>111</v>
-      </c>
-      <c r="U69" s="4" t="n">
-        <v>73</v>
-      </c>
-      <c r="V69" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="W69" s="4" t="n">
-        <v>68</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>0x87_Revenant</t>
+          <t>0x87_Cyclops</t>
         </is>
       </c>
       <c r="B70" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C70" s="4" t="n">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="D70" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="E70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="H70" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="I70" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J70" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K70" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="E70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="G70" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H70" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I70" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="J70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" s="4" t="n">
-        <v>7</v>
-      </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
           <t>SharpClaw</t>
         </is>
       </c>
       <c r="M70" s="4" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="O70" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P70" s="4" t="n">
-        <v>-2</v>
+        <v>16</v>
       </c>
       <c r="Q70" s="4" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="R70" s="4" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="S70" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="T70" s="4" t="n">
+        <v>111</v>
+      </c>
+      <c r="U70" s="4" t="n">
+        <v>73</v>
+      </c>
+      <c r="V70" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="W70" s="4" t="n">
         <v>68</v>
-      </c>
-      <c r="T70" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="U70" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="V70" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="W70" s="4" t="n">
-        <v>32</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>0x87_Mercenary</t>
+          <t>0x87_Revenant</t>
         </is>
       </c>
       <c r="B71" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C71" s="4" t="n">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E71" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H71" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I71" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L71" s="4" t="inlineStr">
+        <is>
+          <t>SharpClaw</t>
+        </is>
+      </c>
+      <c r="M71" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="N71" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="O71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q71" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="R71" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J71" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K71" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="L71" s="4" t="inlineStr">
-        <is>
-          <t>SharpClaw</t>
-        </is>
-      </c>
-      <c r="M71" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="N71" s="4" t="n">
-        <v>106</v>
-      </c>
-      <c r="O71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q71" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="R71" s="4" t="n">
-        <v>11</v>
-      </c>
       <c r="S71" s="4" t="n">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="T71" s="4" t="n">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="U71" s="4" t="n">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="V71" s="4" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="W71" s="4" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>0x87_LowMage</t>
+          <t>0x87_Mercenary</t>
         </is>
       </c>
       <c r="B72" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C72" s="4" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D72" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="E72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H72" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I72" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J72" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K72" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L72" s="4" t="inlineStr">
+        <is>
+          <t>SharpClaw</t>
+        </is>
+      </c>
+      <c r="M72" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="N72" s="4" t="n">
+        <v>106</v>
+      </c>
+      <c r="O72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="E72" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="F72" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="G72" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="H72" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="I72" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="J72" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K72" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L72" s="4" t="inlineStr">
-        <is>
-          <t>SharpClaw</t>
-        </is>
-      </c>
-      <c r="M72" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="N72" s="4" t="n">
-        <v>103</v>
-      </c>
-      <c r="O72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P72" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="Q72" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="R72" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="S72" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="T72" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="U72" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="V72" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="R72" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="S72" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="T72" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="U72" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="V72" s="4" t="n">
-        <v>30</v>
-      </c>
       <c r="W72" s="4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>0x87_Gargoyle</t>
+          <t>0x87_LowMage</t>
         </is>
       </c>
       <c r="B73" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C73" s="4" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F73" s="4" t="n">
         <v>13</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H73" s="4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
@@ -38438,65 +38513,65 @@
         </is>
       </c>
       <c r="M73" s="4" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="N73" s="4" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O73" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P73" s="4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Q73" s="4" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="R73" s="4" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="S73" s="4" t="n">
         <v>49</v>
       </c>
       <c r="T73" s="4" t="n">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="U73" s="4" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="V73" s="4" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="W73" s="4" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>JabberwockBlocker_Revenant</t>
+          <t>0x87_Gargoyle</t>
         </is>
       </c>
       <c r="B74" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C74" s="4" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E74" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I74" s="4" t="n">
         <v>4</v>
@@ -38505,44 +38580,119 @@
         <v>0</v>
       </c>
       <c r="K74" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L74" s="4" t="inlineStr">
+        <is>
+          <t>SharpClaw</t>
+        </is>
+      </c>
+      <c r="M74" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="N74" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="O74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q74" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="R74" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="S74" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="T74" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="U74" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="V74" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="W74" s="4" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>JabberwockBlocker_Revenant</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C75" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="D75" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E75" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H75" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J75" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="L74" s="4" t="inlineStr">
+      <c r="L75" s="4" t="inlineStr">
         <is>
           <t>FetidClaw</t>
         </is>
       </c>
-      <c r="M74" s="4" t="n">
+      <c r="M75" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="N74" s="4" t="n">
+      <c r="N75" s="4" t="n">
         <v>95</v>
       </c>
-      <c r="O74" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P74" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q74" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="R74" s="4" t="n">
+      <c r="O75" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="R75" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="S74" s="4" t="n">
+      <c r="S75" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="T74" s="4" t="n">
+      <c r="T75" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="U74" s="4" t="n">
+      <c r="U75" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="V74" s="4" t="n">
+      <c r="V75" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="W74" s="4" t="n">
+      <c r="W75" s="4" t="n">
         <v>17</v>
       </c>
     </row>

--- a/unit_stats.xlsx
+++ b/unit_stats.xlsx
@@ -5693,10 +5693,10 @@
         <v>12</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>0</v>
@@ -5728,19 +5728,19 @@
         <v>12</v>
       </c>
       <c r="S50" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="T50" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="T50" s="4" t="n">
-        <v>55</v>
-      </c>
       <c r="U50" s="4" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="V50" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="W50" s="4" t="n">
         <v>25</v>
-      </c>
-      <c r="W50" s="4" t="n">
-        <v>33</v>
       </c>
     </row>
     <row r="51">
@@ -6306,26 +6306,26 @@
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>Armorslayer</t>
+          <t>SteelSword</t>
         </is>
       </c>
       <c r="M58" s="4" t="n">
         <v>24</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="O58" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P58" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q58" s="4" t="n">
         <v>22</v>
       </c>
       <c r="R58" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="S58" s="4" t="n">
         <v>42</v>
@@ -6456,26 +6456,26 @@
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>HeavySpear</t>
+          <t>SteelLance</t>
         </is>
       </c>
       <c r="M60" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="O60" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P60" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q60" s="4" t="n">
         <v>22</v>
       </c>
       <c r="R60" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S60" s="4" t="n">
         <v>42</v>
@@ -6521,7 +6521,7 @@
         <v>11</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>1</v>
@@ -6553,16 +6553,16 @@
         <v>11</v>
       </c>
       <c r="S61" s="4" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="T61" s="4" t="n">
         <v>61</v>
       </c>
       <c r="U61" s="4" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="V61" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="W61" s="4" t="n">
         <v>36</v>
@@ -7121,7 +7121,7 @@
         <v>10</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>0</v>
@@ -7153,16 +7153,16 @@
         <v>11</v>
       </c>
       <c r="S69" s="4" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="T69" s="4" t="n">
         <v>59</v>
       </c>
       <c r="U69" s="4" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="V69" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="W69" s="4" t="n">
         <v>34</v>
@@ -12916,10 +12916,10 @@
         <v>13</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>0</v>
@@ -12951,19 +12951,19 @@
         <v>17</v>
       </c>
       <c r="S35" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="T35" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="T35" s="4" t="n">
-        <v>56</v>
-      </c>
       <c r="U35" s="4" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="V35" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="W35" s="4" t="n">
         <v>26</v>
-      </c>
-      <c r="W35" s="4" t="n">
-        <v>34</v>
       </c>
     </row>
     <row r="36">
@@ -15726,10 +15726,10 @@
         <v>11</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>0</v>
@@ -15761,19 +15761,19 @@
         <v>15</v>
       </c>
       <c r="S35" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="T35" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="T35" s="4" t="n">
-        <v>51</v>
-      </c>
       <c r="U35" s="4" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="V35" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="W35" s="4" t="n">
         <v>23</v>
-      </c>
-      <c r="W35" s="4" t="n">
-        <v>31</v>
       </c>
     </row>
     <row r="36">
@@ -27490,10 +27490,10 @@
         <v>14</v>
       </c>
       <c r="H65" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>0</v>
@@ -27525,19 +27525,19 @@
         <v>14</v>
       </c>
       <c r="S65" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="T65" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="T65" s="4" t="n">
-        <v>59</v>
-      </c>
       <c r="U65" s="4" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="V65" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="W65" s="4" t="n">
         <v>27</v>
-      </c>
-      <c r="W65" s="4" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="66">
@@ -27568,7 +27568,7 @@
         <v>11</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>1</v>
@@ -27600,16 +27600,16 @@
         <v>12</v>
       </c>
       <c r="S66" s="4" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="T66" s="4" t="n">
         <v>65</v>
       </c>
       <c r="U66" s="4" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="V66" s="4" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="W66" s="4" t="n">
         <v>38</v>
@@ -32605,10 +32605,10 @@
         <v>12</v>
       </c>
       <c r="H65" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>0</v>
@@ -32640,19 +32640,19 @@
         <v>12</v>
       </c>
       <c r="S65" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="T65" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="T65" s="4" t="n">
-        <v>53</v>
-      </c>
       <c r="U65" s="4" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="V65" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="W65" s="4" t="n">
         <v>24</v>
-      </c>
-      <c r="W65" s="4" t="n">
-        <v>32</v>
       </c>
     </row>
     <row r="66">
@@ -32683,7 +32683,7 @@
         <v>10</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>0</v>
@@ -32715,16 +32715,16 @@
         <v>11</v>
       </c>
       <c r="S66" s="4" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="T66" s="4" t="n">
         <v>59</v>
       </c>
       <c r="U66" s="4" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="V66" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="W66" s="4" t="n">
         <v>34</v>
@@ -36771,10 +36771,10 @@
         <v>14</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>1</v>
@@ -36806,19 +36806,19 @@
         <v>14</v>
       </c>
       <c r="S50" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="T50" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="T50" s="4" t="n">
-        <v>61</v>
-      </c>
       <c r="U50" s="4" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="V50" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="W50" s="4" t="n">
         <v>29</v>
-      </c>
-      <c r="W50" s="4" t="n">
-        <v>37</v>
       </c>
     </row>
     <row r="51">
@@ -37384,26 +37384,26 @@
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>Armorslayer</t>
+          <t>SteelSword</t>
         </is>
       </c>
       <c r="M58" s="4" t="n">
         <v>27</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="O58" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P58" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q58" s="4" t="n">
         <v>25</v>
       </c>
       <c r="R58" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="S58" s="4" t="n">
         <v>48</v>
@@ -37534,26 +37534,26 @@
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>HeavySpear</t>
+          <t>SteelLance</t>
         </is>
       </c>
       <c r="M60" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="O60" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P60" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q60" s="4" t="n">
         <v>25</v>
       </c>
       <c r="R60" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S60" s="4" t="n">
         <v>48</v>
@@ -37599,7 +37599,7 @@
         <v>12</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>2</v>
@@ -37631,16 +37631,16 @@
         <v>12</v>
       </c>
       <c r="S61" s="4" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="T61" s="4" t="n">
         <v>67</v>
       </c>
       <c r="U61" s="4" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="V61" s="4" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="W61" s="4" t="n">
         <v>39</v>
@@ -38199,7 +38199,7 @@
         <v>11</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>1</v>
@@ -38231,16 +38231,16 @@
         <v>12</v>
       </c>
       <c r="S69" s="4" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="T69" s="4" t="n">
         <v>65</v>
       </c>
       <c r="U69" s="4" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="V69" s="4" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="W69" s="4" t="n">
         <v>38</v>

--- a/unit_stats.xlsx
+++ b/unit_stats.xlsx
@@ -1436,7 +1436,7 @@
         <v>10</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>11</v>
@@ -1451,7 +1451,7 @@
         <v>11</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>0</v>
@@ -1486,19 +1486,19 @@
         <v>15</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15"/>
@@ -3243,7 +3243,7 @@
         <v>6</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>12</v>
@@ -3258,7 +3258,7 @@
         <v>4</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I13" s="2" t="n">
         <v>1</v>
@@ -3293,19 +3293,19 @@
         <v>8</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="W13" s="2" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3318,7 +3318,7 @@
         <v>6</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>12</v>
@@ -3333,7 +3333,7 @@
         <v>4</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>1</v>
@@ -3368,19 +3368,19 @@
         <v>8</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="W14" s="2" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15">
@@ -9640,7 +9640,7 @@
         <v>10</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>11</v>
@@ -9655,7 +9655,7 @@
         <v>11</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>0</v>
@@ -9690,19 +9690,19 @@
         <v>15</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15"/>
@@ -11447,7 +11447,7 @@
         <v>6</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>12</v>
@@ -11462,7 +11462,7 @@
         <v>4</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I13" s="2" t="n">
         <v>1</v>
@@ -11497,19 +11497,19 @@
         <v>8</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="W13" s="2" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -11522,7 +11522,7 @@
         <v>6</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>12</v>
@@ -11537,7 +11537,7 @@
         <v>4</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>1</v>
@@ -11572,19 +11572,19 @@
         <v>8</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="W14" s="2" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15">
@@ -14257,7 +14257,7 @@
         <v>6</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>12</v>
@@ -14272,7 +14272,7 @@
         <v>4</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I13" s="2" t="n">
         <v>1</v>
@@ -14307,19 +14307,19 @@
         <v>8</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="W13" s="2" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -14332,7 +14332,7 @@
         <v>6</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>12</v>
@@ -14347,7 +14347,7 @@
         <v>4</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>1</v>
@@ -14382,19 +14382,19 @@
         <v>8</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="W14" s="2" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15">
@@ -17067,7 +17067,7 @@
         <v>6</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>12</v>
@@ -17082,7 +17082,7 @@
         <v>4</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I13" s="2" t="n">
         <v>1</v>
@@ -17117,19 +17117,19 @@
         <v>8</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="W13" s="2" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -17142,7 +17142,7 @@
         <v>6</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>12</v>
@@ -17157,7 +17157,7 @@
         <v>4</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>1</v>
@@ -17192,19 +17192,19 @@
         <v>8</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="W14" s="2" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15">
@@ -20579,7 +20579,7 @@
         <v>6</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>12</v>
@@ -20594,7 +20594,7 @@
         <v>4</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I13" s="2" t="n">
         <v>1</v>
@@ -20629,19 +20629,19 @@
         <v>8</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="W13" s="2" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -20654,7 +20654,7 @@
         <v>6</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>12</v>
@@ -20669,7 +20669,7 @@
         <v>4</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>1</v>
@@ -20704,19 +20704,19 @@
         <v>8</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="W14" s="2" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15">
@@ -24091,7 +24091,7 @@
         <v>6</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>12</v>
@@ -24106,7 +24106,7 @@
         <v>4</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I13" s="2" t="n">
         <v>1</v>
@@ -24141,19 +24141,19 @@
         <v>8</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="W13" s="2" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -24166,7 +24166,7 @@
         <v>6</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>12</v>
@@ -24181,7 +24181,7 @@
         <v>4</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>1</v>
@@ -24216,19 +24216,19 @@
         <v>8</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="W14" s="2" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15">
@@ -29206,7 +29206,7 @@
         <v>6</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>12</v>
@@ -29221,7 +29221,7 @@
         <v>4</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I13" s="2" t="n">
         <v>1</v>
@@ -29256,19 +29256,19 @@
         <v>8</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="W13" s="2" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -29281,7 +29281,7 @@
         <v>6</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>12</v>
@@ -29296,7 +29296,7 @@
         <v>4</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>1</v>
@@ -29331,19 +29331,19 @@
         <v>8</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="W14" s="2" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15">
@@ -34321,7 +34321,7 @@
         <v>6</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>12</v>
@@ -34336,7 +34336,7 @@
         <v>4</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I13" s="2" t="n">
         <v>1</v>
@@ -34371,19 +34371,19 @@
         <v>8</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="W13" s="2" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -34396,7 +34396,7 @@
         <v>6</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>12</v>
@@ -34411,7 +34411,7 @@
         <v>4</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>1</v>
@@ -34446,19 +34446,19 @@
         <v>8</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="W14" s="2" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15">

--- a/unit_stats.xlsx
+++ b/unit_stats.xlsx
@@ -5001,7 +5001,7 @@
         </is>
       </c>
       <c r="M36" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>137</v>
@@ -5076,7 +5076,7 @@
         </is>
       </c>
       <c r="M37" s="3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N37" s="3" t="n">
         <v>128</v>
@@ -36679,7 +36679,7 @@
         </is>
       </c>
       <c r="M36" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>137</v>
@@ -36754,7 +36754,7 @@
         </is>
       </c>
       <c r="M37" s="3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N37" s="3" t="n">
         <v>128</v>

--- a/unit_stats.xlsx
+++ b/unit_stats.xlsx
@@ -7949,10 +7949,10 @@
         <v>9</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>0</v>
@@ -7968,19 +7968,19 @@
       <c r="Q2" s="4" t="n"/>
       <c r="R2" s="4" t="n"/>
       <c r="S2" s="4" t="n">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="T2" s="4" t="n">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="V2" s="4" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="W2" s="4" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
@@ -8464,10 +8464,10 @@
         <v>9</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>0</v>
@@ -8483,19 +8483,19 @@
       <c r="Q2" s="4" t="n"/>
       <c r="R2" s="4" t="n"/>
       <c r="S2" s="4" t="n">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="T2" s="4" t="n">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="V2" s="4" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="W2" s="4" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">

--- a/unit_stats.xlsx
+++ b/unit_stats.xlsx
@@ -7779,20 +7779,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:W13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="4" customWidth="1" min="2" max="2"/>
-    <col width="4" customWidth="1" min="3" max="3"/>
-    <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="5" customWidth="1" min="7" max="7"/>
-    <col width="5" customWidth="1" min="8" max="8"/>
-    <col width="5" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
     <col width="6" customWidth="1" min="10" max="10"/>
-    <col width="5" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
     <col width="6" customWidth="1" min="14" max="14"/>
@@ -7925,361 +7925,716 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>0x80_CivMan</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L2" s="3" t="n"/>
+      <c r="M2" s="3" t="n"/>
+      <c r="N2" s="3" t="n"/>
+      <c r="O2" s="3" t="n"/>
+      <c r="P2" s="3" t="n"/>
+      <c r="Q2" s="3" t="n"/>
+      <c r="R2" s="3" t="n"/>
+      <c r="S2" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="T2" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>0x80_CivWoman</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L3" s="3" t="n"/>
+      <c r="M3" s="3" t="n"/>
+      <c r="N3" s="3" t="n"/>
+      <c r="O3" s="3" t="n"/>
+      <c r="P3" s="3" t="n"/>
+      <c r="Q3" s="3" t="n"/>
+      <c r="R3" s="3" t="n"/>
+      <c r="S3" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>0x80_CivGirl</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="3" t="n"/>
+      <c r="N4" s="3" t="n"/>
+      <c r="O4" s="3" t="n"/>
+      <c r="P4" s="3" t="n"/>
+      <c r="Q4" s="3" t="n"/>
+      <c r="R4" s="3" t="n"/>
+      <c r="S4" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>0x80_CivBoy</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="n"/>
+      <c r="N5" s="3" t="n"/>
+      <c r="O5" s="3" t="n"/>
+      <c r="P5" s="3" t="n"/>
+      <c r="Q5" s="3" t="n"/>
+      <c r="R5" s="3" t="n"/>
+      <c r="S5" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="U5" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="V5" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>0x81_Veteran</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="3" t="n"/>
+      <c r="N6" s="3" t="n"/>
+      <c r="O6" s="3" t="n"/>
+      <c r="P6" s="3" t="n"/>
+      <c r="Q6" s="3" t="n"/>
+      <c r="R6" s="3" t="n"/>
+      <c r="S6" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>0x82_Bard</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L7" s="3" t="n"/>
+      <c r="M7" s="3" t="n"/>
+      <c r="N7" s="3" t="n"/>
+      <c r="O7" s="3" t="n"/>
+      <c r="P7" s="3" t="n"/>
+      <c r="Q7" s="3" t="n"/>
+      <c r="R7" s="3" t="n"/>
+      <c r="S7" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>JabberwockBoss_Jabberwock</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="C2" s="4" t="n">
+      <c r="B9" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C9" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="D2" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="4" t="n">
+      <c r="D9" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="H2" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="I2" s="4" t="n">
+      <c r="H9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I9" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="J2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="4" t="n">
+      <c r="J9" s="4" t="n">
+        <v>-8</v>
+      </c>
+      <c r="K9" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="L2" s="4" t="n"/>
-      <c r="M2" s="4" t="n"/>
-      <c r="N2" s="4" t="n"/>
-      <c r="O2" s="4" t="n"/>
-      <c r="P2" s="4" t="n"/>
-      <c r="Q2" s="4" t="n"/>
-      <c r="R2" s="4" t="n"/>
-      <c r="S2" s="4" t="n">
+      <c r="L9" s="4" t="n"/>
+      <c r="M9" s="4" t="n"/>
+      <c r="N9" s="4" t="n"/>
+      <c r="O9" s="4" t="n"/>
+      <c r="P9" s="4" t="n"/>
+      <c r="Q9" s="4" t="n"/>
+      <c r="R9" s="4" t="n"/>
+      <c r="S9" s="4" t="n">
         <v>76</v>
       </c>
-      <c r="T2" s="4" t="n">
+      <c r="T9" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="U2" s="4" t="n">
+      <c r="U9" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="V2" s="4" t="n">
+      <c r="V9" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="W2" s="4" t="n">
+      <c r="W9" s="4" t="n">
         <v>41</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>JabberwockBlocker_Revenant</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C3" s="4" t="n">
+      <c r="B10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="D3" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="G3" s="4" t="n">
+      <c r="D10" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G10" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="I10" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="J3" s="4" t="n">
+      <c r="J10" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="K3" s="4" t="n">
+      <c r="K10" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>RottenClaw</t>
         </is>
       </c>
-      <c r="M3" s="4" t="n">
+      <c r="M10" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="N3" s="4" t="n">
+      <c r="N10" s="4" t="n">
         <v>107</v>
       </c>
-      <c r="O3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="4" t="n">
+      <c r="O10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="Q3" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="R3" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="S3" s="4" t="n">
+      <c r="Q10" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="R10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="S10" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="T3" s="4" t="n">
+      <c r="T10" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="U10" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="V3" s="4" t="n">
+      <c r="V10" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="W3" s="4" t="n">
+      <c r="W10" s="4" t="n">
         <v>24</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>JabberwockBlocker_BowBone</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C4" s="4" t="n">
+      <c r="B11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="D4" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="4" t="n">
+      <c r="D11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="H4" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="I4" s="4" t="n">
+      <c r="H11" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="J4" s="4" t="n">
+      <c r="J11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="K11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>Longbow</t>
         </is>
       </c>
-      <c r="M4" s="4" t="n">
+      <c r="M11" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="N4" s="4" t="n">
+      <c r="N11" s="4" t="n">
         <v>108</v>
       </c>
-      <c r="O4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q4" s="4" t="n">
+      <c r="O11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q11" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="R4" s="4" t="n">
+      <c r="R11" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="S4" s="4" t="n">
+      <c r="S11" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="T4" s="4" t="n">
+      <c r="T11" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="U4" s="4" t="n">
+      <c r="U11" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="V4" s="4" t="n">
+      <c r="V11" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="W4" s="4" t="n">
+      <c r="W11" s="4" t="n">
         <v>23</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>JabberwockSiege_MogallClass</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C5" s="4" t="n">
+      <c r="B12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D12" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E12" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="F5" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="H5" s="4" t="n">
+      <c r="F12" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H12" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I5" s="4" t="n">
+      <c r="I12" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="J5" s="4" t="n">
+      <c r="J12" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K5" s="4" t="n">
+      <c r="K12" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>Shadowshot</t>
         </is>
       </c>
-      <c r="M5" s="4" t="n">
+      <c r="M12" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="N5" s="4" t="n">
+      <c r="N12" s="4" t="n">
         <v>105</v>
       </c>
-      <c r="O5" s="4" t="n">
+      <c r="O12" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="P5" s="4" t="n">
+      <c r="P12" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="Q5" s="4" t="n">
+      <c r="Q12" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="R5" s="4" t="n">
+      <c r="R12" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="S5" s="4" t="n">
+      <c r="S12" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="T5" s="4" t="n">
+      <c r="T12" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="U5" s="4" t="n">
+      <c r="U12" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="V5" s="4" t="n">
+      <c r="V12" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="W5" s="4" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="W12" s="4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>JabberwockAttacker_Mauthedoog</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C6" s="4" t="n">
+      <c r="B13" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D13" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="4" t="n">
+      <c r="E13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="H6" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="I6" s="4" t="n">
+      <c r="H13" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I13" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="J6" s="4" t="n">
+      <c r="J13" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K6" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="K13" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>FireFang</t>
         </is>
       </c>
-      <c r="M6" s="4" t="n">
+      <c r="M13" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="N6" s="4" t="n">
+      <c r="N13" s="4" t="n">
         <v>159</v>
       </c>
-      <c r="O6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="4" t="n">
+      <c r="O13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="Q6" s="4" t="n">
+      <c r="Q13" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="R6" s="4" t="n">
+      <c r="R13" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="S6" s="4" t="n">
+      <c r="S13" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="T6" s="4" t="n">
+      <c r="T13" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="U6" s="4" t="n">
+      <c r="U13" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="V6" s="4" t="n">
+      <c r="V13" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="W6" s="4" t="n">
+      <c r="W13" s="4" t="n">
         <v>22</v>
       </c>
     </row>
@@ -8294,20 +8649,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:W13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="4" customWidth="1" min="2" max="2"/>
-    <col width="4" customWidth="1" min="3" max="3"/>
-    <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="5" customWidth="1" min="7" max="7"/>
-    <col width="5" customWidth="1" min="8" max="8"/>
-    <col width="5" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
     <col width="6" customWidth="1" min="10" max="10"/>
-    <col width="5" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
     <col width="6" customWidth="1" min="14" max="14"/>
@@ -8440,361 +8795,716 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>0x80_CivMan</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L2" s="3" t="n"/>
+      <c r="M2" s="3" t="n"/>
+      <c r="N2" s="3" t="n"/>
+      <c r="O2" s="3" t="n"/>
+      <c r="P2" s="3" t="n"/>
+      <c r="Q2" s="3" t="n"/>
+      <c r="R2" s="3" t="n"/>
+      <c r="S2" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="T2" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>0x80_CivWoman</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L3" s="3" t="n"/>
+      <c r="M3" s="3" t="n"/>
+      <c r="N3" s="3" t="n"/>
+      <c r="O3" s="3" t="n"/>
+      <c r="P3" s="3" t="n"/>
+      <c r="Q3" s="3" t="n"/>
+      <c r="R3" s="3" t="n"/>
+      <c r="S3" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>0x80_CivGirl</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="3" t="n"/>
+      <c r="N4" s="3" t="n"/>
+      <c r="O4" s="3" t="n"/>
+      <c r="P4" s="3" t="n"/>
+      <c r="Q4" s="3" t="n"/>
+      <c r="R4" s="3" t="n"/>
+      <c r="S4" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>0x80_CivBoy</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="n"/>
+      <c r="N5" s="3" t="n"/>
+      <c r="O5" s="3" t="n"/>
+      <c r="P5" s="3" t="n"/>
+      <c r="Q5" s="3" t="n"/>
+      <c r="R5" s="3" t="n"/>
+      <c r="S5" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="U5" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="V5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>0x81_Veteran</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="3" t="n"/>
+      <c r="N6" s="3" t="n"/>
+      <c r="O6" s="3" t="n"/>
+      <c r="P6" s="3" t="n"/>
+      <c r="Q6" s="3" t="n"/>
+      <c r="R6" s="3" t="n"/>
+      <c r="S6" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>0x82_Bard</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L7" s="3" t="n"/>
+      <c r="M7" s="3" t="n"/>
+      <c r="N7" s="3" t="n"/>
+      <c r="O7" s="3" t="n"/>
+      <c r="P7" s="3" t="n"/>
+      <c r="Q7" s="3" t="n"/>
+      <c r="R7" s="3" t="n"/>
+      <c r="S7" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>JabberwockBoss_Jabberwock</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="C2" s="4" t="n">
+      <c r="B9" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C9" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="D2" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="4" t="n">
+      <c r="D9" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="H2" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="I2" s="4" t="n">
+      <c r="H9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I9" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="J2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="4" t="n">
+      <c r="J9" s="4" t="n">
+        <v>-8</v>
+      </c>
+      <c r="K9" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="L2" s="4" t="n"/>
-      <c r="M2" s="4" t="n"/>
-      <c r="N2" s="4" t="n"/>
-      <c r="O2" s="4" t="n"/>
-      <c r="P2" s="4" t="n"/>
-      <c r="Q2" s="4" t="n"/>
-      <c r="R2" s="4" t="n"/>
-      <c r="S2" s="4" t="n">
+      <c r="L9" s="4" t="n"/>
+      <c r="M9" s="4" t="n"/>
+      <c r="N9" s="4" t="n"/>
+      <c r="O9" s="4" t="n"/>
+      <c r="P9" s="4" t="n"/>
+      <c r="Q9" s="4" t="n"/>
+      <c r="R9" s="4" t="n"/>
+      <c r="S9" s="4" t="n">
         <v>76</v>
       </c>
-      <c r="T2" s="4" t="n">
+      <c r="T9" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="U2" s="4" t="n">
+      <c r="U9" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="V2" s="4" t="n">
+      <c r="V9" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="W2" s="4" t="n">
+      <c r="W9" s="4" t="n">
         <v>41</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>JabberwockBlocker_Revenant</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C3" s="4" t="n">
+      <c r="B10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="D3" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="4" t="n">
+      <c r="D10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="I10" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="J3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="4" t="n">
+      <c r="J10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>RottenClaw</t>
         </is>
       </c>
-      <c r="M3" s="4" t="n">
+      <c r="M10" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="N3" s="4" t="n">
+      <c r="N10" s="4" t="n">
         <v>104</v>
       </c>
-      <c r="O3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="4" t="n">
+      <c r="O10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="Q3" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="R3" s="4" t="n">
+      <c r="Q10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="R10" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="S3" s="4" t="n">
+      <c r="S10" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="T3" s="4" t="n">
+      <c r="T10" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="U10" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="V3" s="4" t="n">
+      <c r="V10" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="W3" s="4" t="n">
+      <c r="W10" s="4" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>JabberwockBlocker_BowBone</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C4" s="4" t="n">
+      <c r="B11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="D4" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="4" t="n">
+      <c r="D11" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="G4" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="I4" s="4" t="n">
+      <c r="G11" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="I11" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="J4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="J11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>Longbow</t>
         </is>
       </c>
-      <c r="M4" s="4" t="n">
+      <c r="M11" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="N4" s="4" t="n">
+      <c r="N11" s="4" t="n">
         <v>103</v>
       </c>
-      <c r="O4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q4" s="4" t="n">
+      <c r="O11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q11" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="R4" s="4" t="n">
+      <c r="R11" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="S4" s="4" t="n">
+      <c r="S11" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="T4" s="4" t="n">
+      <c r="T11" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="U4" s="4" t="n">
+      <c r="U11" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="V4" s="4" t="n">
+      <c r="V11" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="W4" s="4" t="n">
+      <c r="W11" s="4" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>JabberwockSiege_MogallClass</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="E5" s="4" t="n">
+      <c r="B12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E12" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F12" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="I5" s="4" t="n">
+      <c r="I12" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="J5" s="4" t="n">
+      <c r="J12" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K5" s="4" t="n">
+      <c r="K12" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>Shadowshot</t>
         </is>
       </c>
-      <c r="M5" s="4" t="n">
+      <c r="M12" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="N5" s="4" t="n">
+      <c r="N12" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="O5" s="4" t="n">
+      <c r="O12" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="P5" s="4" t="n">
+      <c r="P12" s="4" t="n">
         <v>-4</v>
       </c>
-      <c r="Q5" s="4" t="n">
+      <c r="Q12" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="R5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="4" t="n">
+      <c r="R12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="T5" s="4" t="n">
+      <c r="T12" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="U5" s="4" t="n">
+      <c r="U12" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="V5" s="4" t="n">
+      <c r="V12" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="W5" s="4" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="W12" s="4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>JabberwockAttacker_Mauthedoog</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C6" s="4" t="n">
+      <c r="B13" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D13" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="4" t="n">
+      <c r="E13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="I6" s="4" t="n">
+      <c r="I13" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="J6" s="4" t="n">
+      <c r="J13" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K6" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="K13" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>FireFang</t>
         </is>
       </c>
-      <c r="M6" s="4" t="n">
+      <c r="M13" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="N6" s="4" t="n">
+      <c r="N13" s="4" t="n">
         <v>152</v>
       </c>
-      <c r="O6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="4" t="n">
+      <c r="O13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="Q6" s="4" t="n">
+      <c r="Q13" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="R6" s="4" t="n">
+      <c r="R13" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="S6" s="4" t="n">
+      <c r="S13" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="T6" s="4" t="n">
+      <c r="T13" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="U6" s="4" t="n">
+      <c r="U13" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="V6" s="4" t="n">
+      <c r="V13" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="W6" s="4" t="n">
+      <c r="W13" s="4" t="n">
         <v>19</v>
       </c>
     </row>

--- a/unit_stats.xlsx
+++ b/unit_stats.xlsx
@@ -4225,7 +4225,7 @@
         <v>4</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F26" s="3" t="n">
         <v>19</v>
@@ -4251,7 +4251,7 @@
         </is>
       </c>
       <c r="M26" s="3" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>172</v>
@@ -4300,7 +4300,7 @@
         <v>4</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>19</v>
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="M27" s="3" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>147</v>
@@ -4362,20 +4362,20 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Skull_Fighter</t>
+          <t>Ch5Skull_Fighter</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
         <v>8</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>15</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>11</v>
@@ -4384,7 +4384,7 @@
         <v>9</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>9</v>
@@ -4419,19 +4419,19 @@
         <v>10</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29">
@@ -36613,7 +36613,7 @@
         <v>4</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F26" s="3" t="n">
         <v>19</v>
@@ -36639,7 +36639,7 @@
         </is>
       </c>
       <c r="M26" s="3" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>172</v>
@@ -36688,7 +36688,7 @@
         <v>4</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>19</v>
@@ -36714,7 +36714,7 @@
         </is>
       </c>
       <c r="M27" s="3" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>147</v>
@@ -36750,20 +36750,20 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Skull_Fighter</t>
+          <t>Ch5Skull_Fighter</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
         <v>8</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>19</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>13</v>
@@ -36772,7 +36772,7 @@
         <v>10</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>11</v>
@@ -36807,19 +36807,19 @@
         <v>11</v>
       </c>
       <c r="S28" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="T28" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="U28" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="T28" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="U28" s="3" t="n">
-        <v>44</v>
-      </c>
       <c r="V28" s="3" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29">

--- a/unit_stats.xlsx
+++ b/unit_stats.xlsx
@@ -1068,7 +1068,7 @@
         <v>14</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U7" s="2" t="n">
         <v>32</v>
@@ -1214,7 +1214,7 @@
         <v>7</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U9" s="2" t="n">
         <v>42</v>
@@ -1404,7 +1404,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>10</v>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="N12" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>110</v>
@@ -1483,7 +1483,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>10</v>
@@ -1510,7 +1510,7 @@
         </is>
       </c>
       <c r="N13" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>110</v>
@@ -1607,7 +1607,7 @@
         <v>17</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="U14" s="2" t="n">
         <v>35</v>
@@ -1703,7 +1703,7 @@
         <v>10</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>11</v>
@@ -1757,19 +1757,19 @@
       </c>
       <c r="T17" s="3" t="n"/>
       <c r="U17" s="3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18"/>
@@ -2099,7 +2099,7 @@
         <v>3</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>4</v>
@@ -2153,19 +2153,19 @@
       </c>
       <c r="T23" s="4" t="n"/>
       <c r="U23" s="4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
@@ -2574,7 +2574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y78"/>
+  <dimension ref="A1:Y82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2792,7 +2792,7 @@
         <v>15</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="U2" s="2" t="n">
         <v>40</v>
@@ -2871,7 +2871,7 @@
         <v>9</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="U3" s="2" t="n">
         <v>40</v>
@@ -2950,7 +2950,7 @@
         <v>15</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="U4" s="2" t="n">
         <v>40</v>
@@ -3029,7 +3029,7 @@
         <v>16</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="U5" s="2" t="n">
         <v>35</v>
@@ -3108,7 +3108,7 @@
         <v>16</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U6" s="2" t="n">
         <v>35</v>
@@ -3187,7 +3187,7 @@
         <v>16</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U7" s="2" t="n">
         <v>35</v>
@@ -3333,7 +3333,7 @@
         <v>8</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U9" s="2" t="n">
         <v>47</v>
@@ -3523,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>12</v>
@@ -3550,7 +3550,7 @@
         </is>
       </c>
       <c r="N12" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>114</v>
@@ -3568,7 +3568,7 @@
         <v>12</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>36</v>
@@ -3602,7 +3602,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>12</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="N13" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>114</v>
@@ -3647,7 +3647,7 @@
         <v>12</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U13" s="2" t="n">
         <v>36</v>
@@ -3821,7 +3821,7 @@
         <v>6</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>12</v>
@@ -3872,22 +3872,22 @@
         <v>8</v>
       </c>
       <c r="T16" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="W16" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X16" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y16" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17">
@@ -3900,7 +3900,7 @@
         <v>6</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>12</v>
@@ -3952,19 +3952,19 @@
       </c>
       <c r="T17" s="2" t="n"/>
       <c r="U17" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="W17" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X17" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y17" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18">
@@ -4028,7 +4028,7 @@
         <v>9</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="U18" s="2" t="n">
         <v>36</v>
@@ -4107,7 +4107,7 @@
         <v>14</v>
       </c>
       <c r="T19" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="U19" s="2" t="n">
         <v>36</v>
@@ -4186,7 +4186,7 @@
         <v>18</v>
       </c>
       <c r="T20" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="U20" s="2" t="n">
         <v>32</v>
@@ -4342,7 +4342,7 @@
         <v>15</v>
       </c>
       <c r="T22" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="U22" s="2" t="n">
         <v>34</v>
@@ -4575,7 +4575,7 @@
         <v>16</v>
       </c>
       <c r="T25" s="2" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U25" s="2" t="n">
         <v>47</v>
@@ -4674,7 +4674,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Ch5Eagle_MageGeneral</t>
+          <t>Ch5Eagle_Ch5MageGeneral</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
@@ -4753,7 +4753,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Ch5Eagle_MageGeneral</t>
+          <t>Ch5Eagle_Ch5MageGeneral</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
@@ -6413,7 +6413,7 @@
         <v>11</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
@@ -6458,80 +6458,80 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Beast_AxeBone</t>
+          <t>Lowlander_Fighter</t>
         </is>
       </c>
       <c r="B54" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C54" s="4" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E54" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L54" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="M54" s="4" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
+      <c r="N54" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="O54" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="P54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="M54" s="4" t="inlineStr">
-        <is>
-          <t>Hammer</t>
-        </is>
-      </c>
-      <c r="N54" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="O54" s="4" t="n">
-        <v>89</v>
-      </c>
-      <c r="P54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="4" t="n">
-        <v>4</v>
-      </c>
       <c r="R54" s="4" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="S54" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T54" s="4" t="n"/>
       <c r="U54" s="4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="V54" s="4" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="W54" s="4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="X54" s="4" t="n">
         <v>23</v>
       </c>
       <c r="Y54" s="4" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55">
@@ -6571,7 +6571,7 @@
         <v>7</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
@@ -6616,108 +6616,108 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_Fighter</t>
+          <t>Lowlander_Myrmidon</t>
         </is>
       </c>
       <c r="B56" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D56" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F56" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="E56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="4" t="n">
-        <v>9</v>
-      </c>
       <c r="G56" s="4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M56" s="4" t="inlineStr">
         <is>
-          <t>Hammer</t>
+          <t>SilverSword</t>
         </is>
       </c>
       <c r="N56" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="O56" s="4" t="n">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="P56" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q56" s="4" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="R56" s="4" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="S56" s="4" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="T56" s="4" t="n"/>
       <c r="U56" s="4" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="V56" s="4" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="W56" s="4" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="X56" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Y56" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_Myrmidon</t>
+          <t>Lowlander_HighMage</t>
         </is>
       </c>
       <c r="B57" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C57" s="4" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I57" s="4" t="n">
         <v>6</v>
@@ -6726,201 +6726,201 @@
         <v>1</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>SilverSword</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="N57" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="P57" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q57" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="R57" s="4" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="S57" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="T57" s="4" t="n"/>
       <c r="U57" s="4" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="V57" s="4" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="W57" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="X57" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="Y57" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_HighMage</t>
+          <t>Lowlander_Soldier</t>
         </is>
       </c>
       <c r="B58" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C58" s="4" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M58" s="4" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>SavageGore</t>
         </is>
       </c>
       <c r="N58" s="4" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="P58" s="4" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="Q58" s="4" t="n">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="R58" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="S58" s="4" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="T58" s="4" t="n"/>
       <c r="U58" s="4" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="V58" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="W58" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="W58" s="4" t="n">
-        <v>22</v>
-      </c>
       <c r="X58" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y58" s="4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_Soldier</t>
+          <t>Lowlander_Archer</t>
         </is>
       </c>
       <c r="B59" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C59" s="4" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E59" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F59" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H59" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I59" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J59" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K59" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G59" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H59" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I59" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J59" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K59" s="4" t="n">
-        <v>8</v>
-      </c>
       <c r="L59" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
-          <t>SavageGore</t>
+          <t>SteelBow</t>
         </is>
       </c>
       <c r="N59" s="4" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="P59" s="4" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="Q59" s="4" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R59" s="4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="S59" s="4" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="T59" s="4" t="n"/>
       <c r="U59" s="4" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="V59" s="4" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="W59" s="4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="X59" s="4" t="n">
         <v>18</v>
@@ -6932,17 +6932,17 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_Archer</t>
+          <t>Beast_SwordBone</t>
         </is>
       </c>
       <c r="B60" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E60" s="4" t="n">
         <v>0</v>
@@ -6951,298 +6951,298 @@
         <v>12</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H60" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I60" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L60" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="I60" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="J60" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K60" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L60" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="M60" s="4" t="inlineStr">
         <is>
-          <t>SteelBow</t>
+          <t>SteelSword</t>
         </is>
       </c>
       <c r="N60" s="4" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="P60" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q60" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="R60" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="S60" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T60" s="4" t="n"/>
       <c r="U60" s="4" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="V60" s="4" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="W60" s="4" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="X60" s="4" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="Y60" s="4" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Beast_SwordBone</t>
+          <t>Lowlander_LowMage</t>
         </is>
       </c>
       <c r="B61" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C61" s="4" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F61" s="4" t="n">
         <v>12</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K61" s="4" t="n">
         <v>8</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>SteelSword</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="N61" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="P61" s="4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Q61" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="R61" s="4" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="S61" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" s="4" t="n"/>
       <c r="U61" s="4" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="V61" s="4" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="W61" s="4" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="X61" s="4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Y61" s="4" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_LowMage</t>
+          <t>Beast_LanceBone</t>
         </is>
       </c>
       <c r="B62" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C62" s="4" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F62" s="4" t="n">
         <v>12</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K62" s="4" t="n">
         <v>8</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M62" s="4" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>SteelLance</t>
         </is>
       </c>
       <c r="N62" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="P62" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Q62" s="4" t="n">
         <v>6</v>
       </c>
       <c r="R62" s="4" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="S62" s="4" t="n">
         <v>10</v>
       </c>
       <c r="T62" s="4" t="n"/>
       <c r="U62" s="4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="V62" s="4" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="W62" s="4" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="X62" s="4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Y62" s="4" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Beast_LanceBone</t>
+          <t>Lowlander_Knight</t>
         </is>
       </c>
       <c r="B63" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C63" s="4" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E63" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J63" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L63" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M63" s="4" t="inlineStr">
+        <is>
+          <t>HeavySpear</t>
+        </is>
+      </c>
+      <c r="N63" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="O63" s="4" t="n">
+        <v>73</v>
+      </c>
+      <c r="P63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="M63" s="4" t="inlineStr">
-        <is>
-          <t>SteelLance</t>
-        </is>
-      </c>
-      <c r="N63" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="O63" s="4" t="n">
-        <v>94</v>
-      </c>
-      <c r="P63" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q63" s="4" t="n">
-        <v>6</v>
-      </c>
       <c r="R63" s="4" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="S63" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T63" s="4" t="n"/>
       <c r="U63" s="4" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="V63" s="4" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="W63" s="4" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="X63" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="Y63" s="4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="64">
@@ -7282,7 +7282,7 @@
         <v>15</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M64" s="4" t="inlineStr">
         <is>
@@ -7327,17 +7327,17 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_Mercenary</t>
+          <t>Beast_AxeBone</t>
         </is>
       </c>
       <c r="B65" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C65" s="4" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E65" s="4" t="n">
         <v>0</v>
@@ -7346,109 +7346,109 @@
         <v>12</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H65" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>Lancereaver</t>
+          <t>IronAxe</t>
         </is>
       </c>
       <c r="N65" s="4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="O65" s="4" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P65" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q65" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R65" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S65" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T65" s="4" t="n"/>
       <c r="U65" s="4" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="V65" s="4" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="W65" s="4" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="X65" s="4" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="Y65" s="4" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Beast_Cyclops</t>
+          <t>Lowlander_Mercenary</t>
         </is>
       </c>
       <c r="B66" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E66" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M66" s="4" t="inlineStr">
         <is>
-          <t>SilverAxe</t>
+          <t>Lancereaver</t>
         </is>
       </c>
       <c r="N66" s="4" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="O66" s="4" t="n">
         <v>110</v>
@@ -7457,42 +7457,42 @@
         <v>0</v>
       </c>
       <c r="Q66" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="R66" s="4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="S66" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="T66" s="4" t="n"/>
       <c r="U66" s="4" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="V66" s="4" t="n">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="W66" s="4" t="n">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="X66" s="4" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="Y66" s="4" t="n">
-        <v>59</v>
+        <v>20</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Beast_Gargoyle</t>
+          <t>Beast_Cyclops</t>
         </is>
       </c>
       <c r="B67" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="D67" s="4" t="n">
         <v>17</v>
@@ -7501,149 +7501,149 @@
         <v>0</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G67" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H67" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I67" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="H67" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="I67" s="4" t="n">
-        <v>4</v>
-      </c>
       <c r="J67" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="L67" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M67" s="4" t="inlineStr">
         <is>
-          <t>SteelLance</t>
+          <t>SilverAxe</t>
         </is>
       </c>
       <c r="N67" s="4" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="O67" s="4" t="n">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="P67" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q67" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R67" s="4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="S67" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T67" s="4" t="n"/>
       <c r="U67" s="4" t="n">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="V67" s="4" t="n">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="W67" s="4" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="X67" s="4" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="Y67" s="4" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_AxeCav</t>
+          <t>Beast_Gargoyle</t>
         </is>
       </c>
       <c r="B68" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E68" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K68" s="4" t="n">
         <v>9</v>
       </c>
       <c r="L68" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M68" s="4" t="inlineStr">
         <is>
-          <t>IronAxe</t>
+          <t>SteelLance</t>
         </is>
       </c>
       <c r="N68" s="4" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="O68" s="4" t="n">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="P68" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q68" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="R68" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="S68" s="4" t="n">
         <v>15</v>
-      </c>
-      <c r="S68" s="4" t="n">
-        <v>10</v>
       </c>
       <c r="T68" s="4" t="n"/>
       <c r="U68" s="4" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="V68" s="4" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="W68" s="4" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="X68" s="4" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="Y68" s="4" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_SwordCav</t>
+          <t>Lowlander_AxeCav</t>
         </is>
       </c>
       <c r="B69" s="4" t="n">
@@ -7677,30 +7677,30 @@
         <v>9</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M69" s="4" t="inlineStr">
         <is>
-          <t>SteelSword</t>
+          <t>IronAxe</t>
         </is>
       </c>
       <c r="N69" s="4" t="n">
         <v>19</v>
       </c>
       <c r="O69" s="4" t="n">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="P69" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q69" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R69" s="4" t="n">
         <v>15</v>
       </c>
       <c r="S69" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T69" s="4" t="n"/>
       <c r="U69" s="4" t="n">
@@ -7722,339 +7722,339 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Beast_Jabberwock</t>
+          <t>Lowlander_SwordCav</t>
         </is>
       </c>
       <c r="B70" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C70" s="4" t="n">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E70" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K70" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L70" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M70" s="4" t="inlineStr">
+        <is>
+          <t>SteelSword</t>
+        </is>
+      </c>
+      <c r="N70" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="O70" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="P70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="R70" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="L70" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M70" s="4" t="inlineStr">
-        <is>
-          <t>FetidClaw</t>
-        </is>
-      </c>
-      <c r="N70" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="O70" s="4" t="n">
-        <v>93</v>
-      </c>
-      <c r="P70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q70" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="R70" s="4" t="n">
-        <v>8</v>
-      </c>
       <c r="S70" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T70" s="4" t="n"/>
       <c r="U70" s="4" t="n">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="V70" s="4" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="W70" s="4" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="X70" s="4" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="Y70" s="4" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>0x87_MogallClass</t>
+          <t>Lowlander_FalcoKnight</t>
         </is>
       </c>
       <c r="B71" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C71" s="4" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="D71" s="4" t="n">
         <v>10</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H71" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I71" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="J71" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K71" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L71" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M71" s="4" t="inlineStr">
+        <is>
+          <t>LightBrand</t>
+        </is>
+      </c>
+      <c r="N71" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="J71" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K71" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="L71" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M71" s="4" t="inlineStr">
-        <is>
-          <t>EvilEye</t>
-        </is>
-      </c>
-      <c r="N71" s="4" t="n">
-        <v>23</v>
-      </c>
       <c r="O71" s="4" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="P71" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q71" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="R71" s="4" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="S71" s="4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="T71" s="4" t="n"/>
       <c r="U71" s="4" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="V71" s="4" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="W71" s="4" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="X71" s="4" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="Y71" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>0x87_Bael</t>
+          <t>Lowlander_WyvernRider</t>
         </is>
       </c>
       <c r="B72" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C72" s="4" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E72" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G72" s="4" t="n">
         <v>7</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K72" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L72" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M72" s="4" t="inlineStr">
+        <is>
+          <t>SteelLance</t>
+        </is>
+      </c>
+      <c r="N72" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="O72" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="P72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R72" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="L72" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="M72" s="4" t="inlineStr">
-        <is>
-          <t>SharpClaw</t>
-        </is>
-      </c>
-      <c r="N72" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="O72" s="4" t="n">
-        <v>95</v>
-      </c>
-      <c r="P72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="R72" s="4" t="n">
-        <v>14</v>
-      </c>
       <c r="S72" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T72" s="4" t="n"/>
       <c r="U72" s="4" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="V72" s="4" t="n">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="W72" s="4" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="X72" s="4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="Y72" s="4" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>0x87_Cyclops</t>
+          <t>Lowlander_PegasusKnight</t>
         </is>
       </c>
       <c r="B73" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C73" s="4" t="n">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G73" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H73" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I73" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J73" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K73" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L73" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M73" s="4" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="N73" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="H73" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="I73" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="J73" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K73" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="L73" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M73" s="4" t="inlineStr">
-        <is>
-          <t>SharpClaw</t>
-        </is>
-      </c>
-      <c r="N73" s="4" t="n">
-        <v>36</v>
-      </c>
       <c r="O73" s="4" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="P73" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q73" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="R73" s="4" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="S73" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="T73" s="4" t="n"/>
       <c r="U73" s="4" t="n">
-        <v>88</v>
+        <v>36</v>
       </c>
       <c r="V73" s="4" t="n">
-        <v>104</v>
+        <v>30</v>
       </c>
       <c r="W73" s="4" t="n">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="X73" s="4" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="Y73" s="4" t="n">
-        <v>64</v>
+        <v>16</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>0x87_Revenant</t>
+          <t>Beast_Jabberwock</t>
         </is>
       </c>
       <c r="B74" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C74" s="4" t="n">
         <v>57</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E74" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G74" s="4" t="n">
         <v>4</v>
@@ -8063,52 +8063,52 @@
         <v>1</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="L74" s="4" t="n">
         <v>3</v>
       </c>
       <c r="M74" s="4" t="inlineStr">
         <is>
-          <t>SharpClaw</t>
+          <t>FetidClaw</t>
         </is>
       </c>
       <c r="N74" s="4" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="P74" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q74" s="4" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="R74" s="4" t="n">
         <v>8</v>
       </c>
       <c r="S74" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T74" s="4" t="n"/>
       <c r="U74" s="4" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="V74" s="4" t="n">
         <v>58</v>
       </c>
       <c r="W74" s="4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="X74" s="4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y74" s="4" t="n">
         <v>29</v>
@@ -8117,120 +8117,120 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>0x87_Mercenary</t>
+          <t>0x87_MogallClass</t>
         </is>
       </c>
       <c r="B75" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C75" s="4" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G75" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H75" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I75" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="J75" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K75" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="H75" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="I75" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J75" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K75" s="4" t="n">
-        <v>10</v>
-      </c>
       <c r="L75" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M75" s="4" t="inlineStr">
         <is>
-          <t>SharpClaw</t>
+          <t>EvilEye</t>
         </is>
       </c>
       <c r="N75" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="O75" s="4" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="P75" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q75" s="4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="R75" s="4" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="S75" s="4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="T75" s="4" t="n"/>
       <c r="U75" s="4" t="n">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="V75" s="4" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="W75" s="4" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="X75" s="4" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="Y75" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>0x87_LowMage</t>
+          <t>0x87_Bael</t>
         </is>
       </c>
       <c r="B76" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C76" s="4" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L76" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M76" s="4" t="inlineStr">
         <is>
@@ -8238,78 +8238,78 @@
         </is>
       </c>
       <c r="N76" s="4" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="P76" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q76" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R76" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S76" s="4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T76" s="4" t="n"/>
       <c r="U76" s="4" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="V76" s="4" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="W76" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="X76" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y76" s="4" t="n">
         <v>34</v>
-      </c>
-      <c r="X76" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="Y76" s="4" t="n">
-        <v>22</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>0x87_Gargoyle</t>
+          <t>0x87_Cyclops</t>
         </is>
       </c>
       <c r="B77" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C77" s="4" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="D77" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="E77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="E77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F77" s="4" t="n">
-        <v>11</v>
-      </c>
       <c r="G77" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H77" s="4" t="n">
         <v>12</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="L77" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M77" s="4" t="inlineStr">
         <is>
@@ -8317,63 +8317,63 @@
         </is>
       </c>
       <c r="N77" s="4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O77" s="4" t="n">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="P77" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q77" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="R77" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="S77" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="T77" s="4" t="n"/>
       <c r="U77" s="4" t="n">
-        <v>43</v>
+        <v>97</v>
       </c>
       <c r="V77" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="W77" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="X77" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="Y77" s="4" t="n">
         <v>52</v>
-      </c>
-      <c r="W77" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="X77" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="Y77" s="4" t="n">
-        <v>32</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>JabberwockBlocker_Revenant</t>
+          <t>0x87_Revenant</t>
         </is>
       </c>
       <c r="B78" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C78" s="4" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E78" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H78" s="4" t="n">
         <v>1</v>
@@ -8388,45 +8388,361 @@
         <v>7</v>
       </c>
       <c r="L78" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M78" s="4" t="inlineStr">
         <is>
-          <t>FetidClaw</t>
+          <t>SharpClaw</t>
         </is>
       </c>
       <c r="N78" s="4" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P78" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q78" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="R78" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S78" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T78" s="4" t="n"/>
       <c r="U78" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="V78" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="W78" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="X78" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y78" s="4" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>0x87_Mercenary</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C79" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H79" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I79" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J79" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K79" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L79" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M79" s="4" t="inlineStr">
+        <is>
+          <t>SharpClaw</t>
+        </is>
+      </c>
+      <c r="N79" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="O79" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="P79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R79" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="S79" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="T79" s="4" t="n"/>
+      <c r="U79" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="V79" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="W79" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="X79" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y79" s="4" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>0x87_LowMage</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C80" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E80" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H80" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I80" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J80" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K80" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L80" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M80" s="4" t="inlineStr">
+        <is>
+          <t>SharpClaw</t>
+        </is>
+      </c>
+      <c r="N80" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="O80" s="4" t="n">
+        <v>98</v>
+      </c>
+      <c r="P80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="S80" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T80" s="4" t="n"/>
+      <c r="U80" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="V80" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="W80" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="X80" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y80" s="4" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>0x87_Gargoyle</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C81" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="E81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G81" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="H81" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I81" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L81" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M81" s="4" t="inlineStr">
+        <is>
+          <t>SharpClaw</t>
+        </is>
+      </c>
+      <c r="N81" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="O81" s="4" t="n">
+        <v>97</v>
+      </c>
+      <c r="P81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="R81" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="S81" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="T81" s="4" t="n"/>
+      <c r="U81" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="V81" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="W81" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="X81" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y81" s="4" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>JabberwockBlocker_Revenant</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C82" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="D82" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H82" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L82" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M82" s="4" t="inlineStr">
+        <is>
+          <t>FetidClaw</t>
+        </is>
+      </c>
+      <c r="N82" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="O82" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="P82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S82" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T82" s="4" t="n"/>
+      <c r="U82" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="V78" s="4" t="n">
+      <c r="V82" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="W78" s="4" t="n">
+      <c r="W82" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="X78" s="4" t="n">
+      <c r="X82" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="Y78" s="4" t="n">
+      <c r="Y82" s="4" t="n">
         <v>17</v>
       </c>
     </row>
@@ -11236,7 +11552,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>10</v>
@@ -11263,7 +11579,7 @@
         </is>
       </c>
       <c r="N12" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>110</v>
@@ -11315,7 +11631,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>10</v>
@@ -11342,7 +11658,7 @@
         </is>
       </c>
       <c r="N13" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>110</v>
@@ -11533,7 +11849,7 @@
         <v>10</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>11</v>
@@ -11587,19 +11903,19 @@
       </c>
       <c r="T17" s="3" t="n"/>
       <c r="U17" s="3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18"/>
@@ -11929,7 +12245,7 @@
         <v>3</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>1</v>
@@ -11983,13 +12299,13 @@
       </c>
       <c r="T23" s="4" t="n"/>
       <c r="U23" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="X23" s="4" t="n">
         <v>14</v>
@@ -12622,7 +12938,7 @@
         <v>15</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="U2" s="2" t="n">
         <v>40</v>
@@ -12701,7 +13017,7 @@
         <v>9</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U3" s="2" t="n">
         <v>40</v>
@@ -12936,7 +13252,7 @@
         <v>14</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U6" s="2" t="n">
         <v>32</v>
@@ -13015,7 +13331,7 @@
         <v>14</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U7" s="2" t="n">
         <v>32</v>
@@ -13161,7 +13477,7 @@
         <v>7</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="U9" s="2" t="n">
         <v>43</v>
@@ -13317,7 +13633,7 @@
         <v>10</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="U11" s="2" t="n">
         <v>43</v>
@@ -13351,7 +13667,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>10</v>
@@ -13378,7 +13694,7 @@
         </is>
       </c>
       <c r="N12" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>110</v>
@@ -13396,7 +13712,7 @@
         <v>11</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>32</v>
@@ -13430,7 +13746,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>10</v>
@@ -13457,7 +13773,7 @@
         </is>
       </c>
       <c r="N13" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>110</v>
@@ -13475,7 +13791,7 @@
         <v>11</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="U13" s="2" t="n">
         <v>32</v>
@@ -13554,7 +13870,7 @@
         <v>17</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="U14" s="2" t="n">
         <v>35</v>
@@ -13649,7 +13965,7 @@
         <v>6</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>12</v>
@@ -13700,22 +14016,22 @@
         <v>8</v>
       </c>
       <c r="T16" s="2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="W16" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X16" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y16" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17">
@@ -13728,7 +14044,7 @@
         <v>6</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>12</v>
@@ -13780,19 +14096,19 @@
       </c>
       <c r="T17" s="2" t="n"/>
       <c r="U17" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="W17" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X17" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y17" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18">
@@ -13856,7 +14172,7 @@
         <v>8</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U18" s="2" t="n">
         <v>35</v>
@@ -14312,7 +14628,7 @@
         <v>4</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D27" s="4" t="n">
         <v>4</v>
@@ -14366,19 +14682,19 @@
       </c>
       <c r="T27" s="4" t="n"/>
       <c r="U27" s="4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28">
@@ -15795,7 +16111,7 @@
         <v>15</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="U2" s="2" t="n">
         <v>40</v>
@@ -15874,7 +16190,7 @@
         <v>9</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U3" s="2" t="n">
         <v>40</v>
@@ -16030,7 +16346,7 @@
         <v>14</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="U5" s="2" t="n">
         <v>32</v>
@@ -16109,7 +16425,7 @@
         <v>14</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U6" s="2" t="n">
         <v>32</v>
@@ -16334,7 +16650,7 @@
         <v>7</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="U9" s="2" t="n">
         <v>43</v>
@@ -16492,7 +16808,7 @@
         <v>10</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="U11" s="2" t="n">
         <v>43</v>
@@ -16526,7 +16842,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>10</v>
@@ -16553,7 +16869,7 @@
         </is>
       </c>
       <c r="N12" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>110</v>
@@ -16571,7 +16887,7 @@
         <v>11</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>32</v>
@@ -16605,7 +16921,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>10</v>
@@ -16632,7 +16948,7 @@
         </is>
       </c>
       <c r="N13" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>110</v>
@@ -16729,7 +17045,7 @@
         <v>17</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="U14" s="2" t="n">
         <v>35</v>
@@ -16796,7 +17112,7 @@
       <c r="R15" s="2" t="n"/>
       <c r="S15" s="2" t="n"/>
       <c r="T15" s="2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="U15" s="2" t="n">
         <v>35</v>
@@ -16824,7 +17140,7 @@
         <v>6</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>12</v>
@@ -16875,22 +17191,22 @@
         <v>8</v>
       </c>
       <c r="T16" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="W16" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X16" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y16" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17">
@@ -16903,7 +17219,7 @@
         <v>6</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>12</v>
@@ -16955,19 +17271,19 @@
       </c>
       <c r="T17" s="2" t="n"/>
       <c r="U17" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="W17" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X17" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y17" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18">
@@ -17031,7 +17347,7 @@
         <v>8</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="U18" s="2" t="n">
         <v>35</v>
@@ -17110,7 +17426,7 @@
         <v>13</v>
       </c>
       <c r="T19" s="2" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U19" s="2" t="n">
         <v>35</v>
@@ -17487,7 +17803,7 @@
         <v>4</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D27" s="4" t="n">
         <v>2</v>
@@ -17541,19 +17857,19 @@
       </c>
       <c r="T27" s="4" t="n"/>
       <c r="U27" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28">
@@ -18970,7 +19286,7 @@
         <v>15</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="U2" s="2" t="n">
         <v>40</v>
@@ -19049,7 +19365,7 @@
         <v>9</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U3" s="2" t="n">
         <v>40</v>
@@ -19285,7 +19601,9 @@
       <c r="S6" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="T6" s="2" t="n"/>
+      <c r="T6" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="U6" s="2" t="n">
         <v>33</v>
       </c>
@@ -19363,7 +19681,7 @@
         <v>15</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U7" s="2" t="n">
         <v>33</v>
@@ -19509,7 +19827,7 @@
         <v>7</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U9" s="2" t="n">
         <v>44</v>
@@ -19699,7 +20017,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>11</v>
@@ -19726,7 +20044,7 @@
         </is>
       </c>
       <c r="N12" s="2" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>112</v>
@@ -19778,7 +20096,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>11</v>
@@ -19805,7 +20123,7 @@
         </is>
       </c>
       <c r="N13" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>112</v>
@@ -19997,7 +20315,7 @@
         <v>6</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>12</v>
@@ -20051,19 +20369,19 @@
         <v>11</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="W16" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X16" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y16" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17">
@@ -20076,7 +20394,7 @@
         <v>6</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>12</v>
@@ -20128,19 +20446,19 @@
       </c>
       <c r="T17" s="2" t="n"/>
       <c r="U17" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="W17" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X17" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y17" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18">
@@ -20362,7 +20680,7 @@
         <v>17</v>
       </c>
       <c r="T20" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U20" s="2" t="n">
         <v>31</v>
@@ -20518,7 +20836,7 @@
         <v>14</v>
       </c>
       <c r="T22" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="U22" s="2" t="n">
         <v>33</v>
@@ -22202,7 +22520,7 @@
         <v>5</v>
       </c>
       <c r="C47" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D47" s="4" t="n">
         <v>5</v>
@@ -22256,13 +22574,13 @@
       </c>
       <c r="T47" s="4" t="n"/>
       <c r="U47" s="4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V47" s="4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W47" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="X47" s="4" t="n">
         <v>18</v>
@@ -23610,7 +23928,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>11</v>
@@ -23637,7 +23955,7 @@
         </is>
       </c>
       <c r="N12" s="2" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>112</v>
@@ -23689,7 +24007,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>11</v>
@@ -23716,7 +24034,7 @@
         </is>
       </c>
       <c r="N13" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>112</v>
@@ -23813,7 +24131,7 @@
         <v>17</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="U14" s="2" t="n">
         <v>35</v>
@@ -23908,7 +24226,7 @@
         <v>6</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>12</v>
@@ -23959,22 +24277,22 @@
         <v>8</v>
       </c>
       <c r="T16" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="W16" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X16" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y16" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17">
@@ -23987,7 +24305,7 @@
         <v>6</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>12</v>
@@ -24039,19 +24357,19 @@
       </c>
       <c r="T17" s="2" t="n"/>
       <c r="U17" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="W17" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X17" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y17" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18">
@@ -24115,7 +24433,7 @@
         <v>8</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U18" s="2" t="n">
         <v>35</v>
@@ -24194,7 +24512,7 @@
         <v>13</v>
       </c>
       <c r="T19" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U19" s="2" t="n">
         <v>35</v>
@@ -24273,7 +24591,7 @@
         <v>17</v>
       </c>
       <c r="T20" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="U20" s="2" t="n">
         <v>31</v>
@@ -24429,7 +24747,7 @@
         <v>14</v>
       </c>
       <c r="T22" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="U22" s="2" t="n">
         <v>33</v>
@@ -24584,9 +24902,7 @@
       <c r="S24" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="T24" s="2" t="n">
-        <v>4</v>
-      </c>
+      <c r="T24" s="2" t="n"/>
       <c r="U24" s="2" t="n">
         <v>33</v>
       </c>
@@ -26115,7 +26431,7 @@
         <v>5</v>
       </c>
       <c r="C47" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D47" s="4" t="n">
         <v>2</v>
@@ -26169,19 +26485,19 @@
       </c>
       <c r="T47" s="4" t="n"/>
       <c r="U47" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V47" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="W47" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="X47" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y47" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48">
@@ -26792,7 +27108,7 @@
         <v>15</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="U2" s="2" t="n">
         <v>40</v>
@@ -26871,7 +27187,7 @@
         <v>9</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U3" s="2" t="n">
         <v>40</v>
@@ -27029,7 +27345,7 @@
         <v>15</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U5" s="2" t="n">
         <v>34</v>
@@ -27108,7 +27424,7 @@
         <v>15</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U6" s="2" t="n">
         <v>34</v>
@@ -27187,7 +27503,7 @@
         <v>15</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="U7" s="2" t="n">
         <v>34</v>
@@ -27333,7 +27649,7 @@
         <v>8</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U9" s="2" t="n">
         <v>46</v>
@@ -27489,7 +27805,7 @@
         <v>11</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="U11" s="2" t="n">
         <v>46</v>
@@ -27523,7 +27839,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>11</v>
@@ -27550,7 +27866,7 @@
         </is>
       </c>
       <c r="N12" s="2" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>112</v>
@@ -27568,7 +27884,7 @@
         <v>12</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>35</v>
@@ -27602,7 +27918,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>11</v>
@@ -27629,7 +27945,7 @@
         </is>
       </c>
       <c r="N13" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>112</v>
@@ -27647,7 +27963,7 @@
         <v>12</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U13" s="2" t="n">
         <v>35</v>
@@ -27687,7 +28003,7 @@
         <v>11</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>4</v>
@@ -27717,16 +28033,16 @@
         <v>0</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="U14" s="2" t="n">
         <v>36</v>
@@ -27766,7 +28082,7 @@
         <v>11</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>4</v>
@@ -27821,7 +28137,7 @@
         <v>6</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>12</v>
@@ -27872,22 +28188,22 @@
         <v>8</v>
       </c>
       <c r="T16" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="W16" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X16" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y16" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17">
@@ -27900,7 +28216,7 @@
         <v>6</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>12</v>
@@ -27952,19 +28268,19 @@
       </c>
       <c r="T17" s="2" t="n"/>
       <c r="U17" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="W17" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X17" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y17" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18">
@@ -28028,7 +28344,7 @@
         <v>8</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U18" s="2" t="n">
         <v>35</v>
@@ -28107,7 +28423,7 @@
         <v>13</v>
       </c>
       <c r="T19" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U19" s="2" t="n">
         <v>35</v>
@@ -28186,7 +28502,7 @@
         <v>17</v>
       </c>
       <c r="T20" s="2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U20" s="2" t="n">
         <v>31</v>
@@ -28575,7 +28891,7 @@
         <v>16</v>
       </c>
       <c r="T25" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U25" s="2" t="n">
         <v>47</v>
@@ -31079,7 +31395,7 @@
         <v>6</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D64" s="4" t="n">
         <v>6</v>
@@ -31133,19 +31449,19 @@
       </c>
       <c r="T64" s="4" t="n"/>
       <c r="U64" s="4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V64" s="4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W64" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="X64" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Y64" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65">
@@ -32404,7 +32720,7 @@
         <v>15</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U2" s="2" t="n">
         <v>40</v>
@@ -32483,7 +32799,7 @@
         <v>9</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U3" s="2" t="n">
         <v>40</v>
@@ -32641,7 +32957,7 @@
         <v>15</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="U5" s="2" t="n">
         <v>34</v>
@@ -32866,7 +33182,7 @@
       <c r="R8" s="2" t="n"/>
       <c r="S8" s="2" t="n"/>
       <c r="T8" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="U8" s="2" t="n">
         <v>34</v>
@@ -32945,7 +33261,7 @@
         <v>8</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="U9" s="2" t="n">
         <v>46</v>
@@ -33101,7 +33417,7 @@
         <v>11</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U11" s="2" t="n">
         <v>46</v>
@@ -33135,7 +33451,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>11</v>
@@ -33162,7 +33478,7 @@
         </is>
       </c>
       <c r="N12" s="2" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>112</v>
@@ -33214,7 +33530,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>11</v>
@@ -33241,7 +33557,7 @@
         </is>
       </c>
       <c r="N13" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>112</v>
@@ -33259,7 +33575,7 @@
         <v>12</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U13" s="2" t="n">
         <v>35</v>
@@ -33299,7 +33615,7 @@
         <v>11</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>4</v>
@@ -33329,16 +33645,16 @@
         <v>0</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="U14" s="2" t="n">
         <v>36</v>
@@ -33378,7 +33694,7 @@
         <v>11</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>4</v>
@@ -33405,7 +33721,7 @@
       <c r="R15" s="2" t="n"/>
       <c r="S15" s="2" t="n"/>
       <c r="T15" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="U15" s="2" t="n">
         <v>36</v>
@@ -33433,7 +33749,7 @@
         <v>6</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>12</v>
@@ -33487,19 +33803,19 @@
         <v>21</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="W16" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X16" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y16" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17">
@@ -33512,7 +33828,7 @@
         <v>6</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>12</v>
@@ -33564,19 +33880,19 @@
       </c>
       <c r="T17" s="2" t="n"/>
       <c r="U17" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="W17" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X17" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y17" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18">
@@ -33640,7 +33956,7 @@
         <v>8</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="U18" s="2" t="n">
         <v>35</v>
@@ -33719,7 +34035,7 @@
         <v>13</v>
       </c>
       <c r="T19" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="U19" s="2" t="n">
         <v>35</v>
@@ -33798,7 +34114,7 @@
         <v>17</v>
       </c>
       <c r="T20" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="U20" s="2" t="n">
         <v>31</v>
@@ -33954,7 +34270,7 @@
         <v>14</v>
       </c>
       <c r="T22" s="2" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="U22" s="2" t="n">
         <v>33</v>
@@ -34110,7 +34426,7 @@
         <v>16</v>
       </c>
       <c r="T24" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U24" s="2" t="n">
         <v>33</v>
@@ -34189,7 +34505,7 @@
         <v>16</v>
       </c>
       <c r="T25" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="U25" s="2" t="n">
         <v>47</v>
@@ -36693,7 +37009,7 @@
         <v>6</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D64" s="4" t="n">
         <v>3</v>
@@ -36747,10 +37063,10 @@
       </c>
       <c r="T64" s="4" t="n"/>
       <c r="U64" s="4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V64" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="W64" s="4" t="n">
         <v>21</v>
@@ -37800,7 +38116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y78"/>
+  <dimension ref="A1:Y82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -38018,7 +38334,7 @@
         <v>15</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="U2" s="2" t="n">
         <v>40</v>
@@ -38097,7 +38413,7 @@
         <v>9</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="U3" s="2" t="n">
         <v>40</v>
@@ -38175,7 +38491,9 @@
       <c r="S4" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="T4" s="2" t="n"/>
+      <c r="T4" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="U4" s="2" t="n">
         <v>40</v>
       </c>
@@ -38253,7 +38571,7 @@
         <v>16</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="U5" s="2" t="n">
         <v>35</v>
@@ -38332,7 +38650,7 @@
         <v>16</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="U6" s="2" t="n">
         <v>35</v>
@@ -38411,7 +38729,7 @@
         <v>16</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U7" s="2" t="n">
         <v>35</v>
@@ -38557,7 +38875,7 @@
         <v>8</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="U9" s="2" t="n">
         <v>47</v>
@@ -38713,7 +39031,7 @@
         <v>11</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="U11" s="2" t="n">
         <v>47</v>
@@ -38747,7 +39065,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>12</v>
@@ -38774,7 +39092,7 @@
         </is>
       </c>
       <c r="N12" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>114</v>
@@ -38792,7 +39110,7 @@
         <v>12</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>36</v>
@@ -38826,7 +39144,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>12</v>
@@ -38853,7 +39171,7 @@
         </is>
       </c>
       <c r="N13" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>114</v>
@@ -38871,7 +39189,7 @@
         <v>12</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="U13" s="2" t="n">
         <v>36</v>
@@ -38950,7 +39268,7 @@
         <v>18</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="U14" s="2" t="n">
         <v>37</v>
@@ -39045,7 +39363,7 @@
         <v>6</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>12</v>
@@ -39096,22 +39414,22 @@
         <v>8</v>
       </c>
       <c r="T16" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="W16" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X16" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y16" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17">
@@ -39124,7 +39442,7 @@
         <v>6</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>12</v>
@@ -39176,19 +39494,19 @@
       </c>
       <c r="T17" s="2" t="n"/>
       <c r="U17" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="W17" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X17" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y17" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18">
@@ -39252,7 +39570,7 @@
         <v>9</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="U18" s="2" t="n">
         <v>36</v>
@@ -39331,7 +39649,7 @@
         <v>14</v>
       </c>
       <c r="T19" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U19" s="2" t="n">
         <v>36</v>
@@ -39410,7 +39728,7 @@
         <v>18</v>
       </c>
       <c r="T20" s="2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="U20" s="2" t="n">
         <v>32</v>
@@ -39566,7 +39884,7 @@
         <v>15</v>
       </c>
       <c r="T22" s="2" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="U22" s="2" t="n">
         <v>34</v>
@@ -39721,9 +40039,7 @@
       <c r="S24" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="T24" s="2" t="n">
-        <v>2</v>
-      </c>
+      <c r="T24" s="2" t="n"/>
       <c r="U24" s="2" t="n">
         <v>34</v>
       </c>
@@ -39801,7 +40117,7 @@
         <v>16</v>
       </c>
       <c r="T25" s="2" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="U25" s="2" t="n">
         <v>47</v>
@@ -39900,7 +40216,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Ch5Eagle_MageGeneral</t>
+          <t>Ch5Eagle_Ch5MageGeneral</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
@@ -39979,7 +40295,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Ch5Eagle_MageGeneral</t>
+          <t>Ch5Eagle_Ch5MageGeneral</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
@@ -41639,7 +41955,7 @@
         <v>11</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
@@ -41684,41 +42000,41 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Beast_AxeBone</t>
+          <t>Lowlander_Fighter</t>
         </is>
       </c>
       <c r="B54" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C54" s="4" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E54" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M54" s="4" t="inlineStr">
         <is>
@@ -41726,38 +42042,38 @@
         </is>
       </c>
       <c r="N54" s="4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="P54" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q54" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R54" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="S54" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T54" s="4" t="n"/>
       <c r="U54" s="4" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V54" s="4" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="W54" s="4" t="n">
         <v>37</v>
       </c>
       <c r="X54" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Y54" s="4" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="55">
@@ -41797,7 +42113,7 @@
         <v>7</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
@@ -41842,311 +42158,311 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_Fighter</t>
+          <t>Lowlander_Myrmidon</t>
         </is>
       </c>
       <c r="B56" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D56" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F56" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="E56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="4" t="n">
-        <v>11</v>
-      </c>
       <c r="G56" s="4" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J56" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M56" s="4" t="inlineStr">
         <is>
-          <t>Hammer</t>
+          <t>SilverSword</t>
         </is>
       </c>
       <c r="N56" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="O56" s="4" t="n">
-        <v>89</v>
+        <v>135</v>
       </c>
       <c r="P56" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q56" s="4" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="R56" s="4" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="S56" s="4" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T56" s="4" t="n"/>
       <c r="U56" s="4" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="V56" s="4" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="W56" s="4" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="X56" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="Y56" s="4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_Myrmidon</t>
+          <t>Lowlander_HighMage</t>
         </is>
       </c>
       <c r="B57" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C57" s="4" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>SilverSword</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="N57" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="P57" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q57" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="R57" s="4" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="S57" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="T57" s="4" t="n"/>
       <c r="U57" s="4" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="V57" s="4" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="W57" s="4" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="X57" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Y57" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_HighMage</t>
+          <t>Lowlander_Soldier</t>
         </is>
       </c>
       <c r="B58" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C58" s="4" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J58" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K58" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L58" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K58" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L58" s="4" t="n">
-        <v>4</v>
-      </c>
       <c r="M58" s="4" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>SavageGore</t>
         </is>
       </c>
       <c r="N58" s="4" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="P58" s="4" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="Q58" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R58" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="S58" s="4" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="T58" s="4" t="n"/>
       <c r="U58" s="4" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="V58" s="4" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="W58" s="4" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="X58" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y58" s="4" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_Soldier</t>
+          <t>Lowlander_Archer</t>
         </is>
       </c>
       <c r="B59" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C59" s="4" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E59" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F59" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H59" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I59" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J59" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K59" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L59" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M59" s="4" t="inlineStr">
+        <is>
+          <t>SteelBow</t>
+        </is>
+      </c>
+      <c r="N59" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="O59" s="4" t="n">
+        <v>114</v>
+      </c>
+      <c r="P59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="G59" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H59" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I59" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J59" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K59" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L59" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M59" s="4" t="inlineStr">
-        <is>
-          <t>SavageGore</t>
-        </is>
-      </c>
-      <c r="N59" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="O59" s="4" t="n">
-        <v>101</v>
-      </c>
-      <c r="P59" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="Q59" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" s="4" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="S59" s="4" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T59" s="4" t="n"/>
       <c r="U59" s="4" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="V59" s="4" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="W59" s="4" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="X59" s="4" t="n">
         <v>21</v>
@@ -42158,314 +42474,314 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_Archer</t>
+          <t>Beast_SwordBone</t>
         </is>
       </c>
       <c r="B60" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E60" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M60" s="4" t="inlineStr">
         <is>
-          <t>SteelBow</t>
+          <t>SteelSword</t>
         </is>
       </c>
       <c r="N60" s="4" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="P60" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q60" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="R60" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="S60" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="T60" s="4" t="n"/>
       <c r="U60" s="4" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="V60" s="4" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="W60" s="4" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="X60" s="4" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="Y60" s="4" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Beast_SwordBone</t>
+          <t>Lowlander_LowMage</t>
         </is>
       </c>
       <c r="B61" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C61" s="4" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F61" s="4" t="n">
         <v>14</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K61" s="4" t="n">
         <v>8</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>SteelSword</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="N61" s="4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="P61" s="4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Q61" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="R61" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="S61" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="T61" s="4" t="n"/>
       <c r="U61" s="4" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="V61" s="4" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="W61" s="4" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="X61" s="4" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="Y61" s="4" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_LowMage</t>
+          <t>Beast_LanceBone</t>
         </is>
       </c>
       <c r="B62" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C62" s="4" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F62" s="4" t="n">
         <v>14</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K62" s="4" t="n">
         <v>8</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M62" s="4" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>SteelLance</t>
         </is>
       </c>
       <c r="N62" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="P62" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Q62" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R62" s="4" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="S62" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T62" s="4" t="n"/>
       <c r="U62" s="4" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V62" s="4" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="W62" s="4" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="X62" s="4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="Y62" s="4" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Beast_LanceBone</t>
+          <t>Lowlander_Knight</t>
         </is>
       </c>
       <c r="B63" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C63" s="4" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E63" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J63" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M63" s="4" t="inlineStr">
         <is>
-          <t>SteelLance</t>
+          <t>HeavySpear</t>
         </is>
       </c>
       <c r="N63" s="4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O63" s="4" t="n">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="P63" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q63" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R63" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="S63" s="4" t="n">
         <v>7</v>
-      </c>
-      <c r="R63" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="S63" s="4" t="n">
-        <v>11</v>
       </c>
       <c r="T63" s="4" t="n"/>
       <c r="U63" s="4" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="V63" s="4" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="W63" s="4" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="X63" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="Y63" s="4" t="n">
         <v>32</v>
@@ -42508,7 +42824,7 @@
         <v>15</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M64" s="4" t="inlineStr">
         <is>
@@ -42553,323 +42869,323 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_Mercenary</t>
+          <t>Beast_AxeBone</t>
         </is>
       </c>
       <c r="B65" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C65" s="4" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D65" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="E65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="E65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" s="4" t="n">
-        <v>15</v>
-      </c>
       <c r="G65" s="4" t="n">
         <v>12</v>
       </c>
       <c r="H65" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>Lancereaver</t>
+          <t>IronAxe</t>
         </is>
       </c>
       <c r="N65" s="4" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="O65" s="4" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="P65" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q65" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R65" s="4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S65" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="T65" s="4" t="n"/>
       <c r="U65" s="4" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="V65" s="4" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="W65" s="4" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="X65" s="4" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="Y65" s="4" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Beast_Cyclops</t>
+          <t>Lowlander_Mercenary</t>
         </is>
       </c>
       <c r="B66" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E66" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M66" s="4" t="inlineStr">
         <is>
-          <t>SilverAxe</t>
+          <t>Lancereaver</t>
         </is>
       </c>
       <c r="N66" s="4" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="P66" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q66" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="R66" s="4" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="S66" s="4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="T66" s="4" t="n"/>
       <c r="U66" s="4" t="n">
-        <v>88</v>
+        <v>36</v>
       </c>
       <c r="V66" s="4" t="n">
-        <v>104</v>
+        <v>41</v>
       </c>
       <c r="W66" s="4" t="n">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="X66" s="4" t="n">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="Y66" s="4" t="n">
-        <v>64</v>
+        <v>24</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Beast_Gargoyle</t>
+          <t>Beast_Cyclops</t>
         </is>
       </c>
       <c r="B67" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E67" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G67" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H67" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I67" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="H67" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="I67" s="4" t="n">
-        <v>5</v>
-      </c>
       <c r="J67" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="L67" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M67" s="4" t="inlineStr">
         <is>
-          <t>SteelLance</t>
+          <t>SilverAxe</t>
         </is>
       </c>
       <c r="N67" s="4" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="O67" s="4" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="P67" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q67" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R67" s="4" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="S67" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T67" s="4" t="n"/>
       <c r="U67" s="4" t="n">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c r="V67" s="4" t="n">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="W67" s="4" t="n">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="X67" s="4" t="n">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="Y67" s="4" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_AxeCav</t>
+          <t>Beast_Gargoyle</t>
         </is>
       </c>
       <c r="B68" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E68" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K68" s="4" t="n">
         <v>9</v>
       </c>
       <c r="L68" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M68" s="4" t="inlineStr">
         <is>
-          <t>IronAxe</t>
+          <t>SteelLance</t>
         </is>
       </c>
       <c r="N68" s="4" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="O68" s="4" t="n">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="P68" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q68" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="R68" s="4" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="S68" s="4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="T68" s="4" t="n"/>
       <c r="U68" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="V68" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="W68" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="X68" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y68" s="4" t="n">
         <v>37</v>
-      </c>
-      <c r="V68" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="W68" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="X68" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y68" s="4" t="n">
-        <v>26</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_SwordCav</t>
+          <t>Lowlander_AxeCav</t>
         </is>
       </c>
       <c r="B69" s="4" t="n">
@@ -42903,30 +43219,30 @@
         <v>9</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M69" s="4" t="inlineStr">
         <is>
-          <t>SteelSword</t>
+          <t>IronAxe</t>
         </is>
       </c>
       <c r="N69" s="4" t="n">
         <v>21</v>
       </c>
       <c r="O69" s="4" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="P69" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q69" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R69" s="4" t="n">
         <v>21</v>
       </c>
       <c r="S69" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T69" s="4" t="n"/>
       <c r="U69" s="4" t="n">
@@ -42948,14 +43264,14 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Beast_Jabberwock</t>
+          <t>Lowlander_SwordCav</t>
         </is>
       </c>
       <c r="B70" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C70" s="4" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="D70" s="4" t="n">
         <v>11</v>
@@ -42964,456 +43280,456 @@
         <v>0</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I70" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M70" s="4" t="inlineStr">
         <is>
-          <t>FetidClaw</t>
+          <t>SteelSword</t>
         </is>
       </c>
       <c r="N70" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="O70" s="4" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="P70" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q70" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="R70" s="4" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="S70" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T70" s="4" t="n"/>
       <c r="U70" s="4" t="n">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="V70" s="4" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="W70" s="4" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="X70" s="4" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="Y70" s="4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>0x87_MogallClass</t>
+          <t>Lowlander_FalcoKnight</t>
         </is>
       </c>
       <c r="B71" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C71" s="4" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="D71" s="4" t="n">
         <v>12</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H71" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I71" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="J71" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K71" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L71" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M71" s="4" t="inlineStr">
+        <is>
+          <t>LightBrand</t>
+        </is>
+      </c>
+      <c r="N71" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="J71" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K71" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="L71" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M71" s="4" t="inlineStr">
-        <is>
-          <t>EvilEye</t>
-        </is>
-      </c>
-      <c r="N71" s="4" t="n">
-        <v>25</v>
-      </c>
       <c r="O71" s="4" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="P71" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q71" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="R71" s="4" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="S71" s="4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="T71" s="4" t="n"/>
       <c r="U71" s="4" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="V71" s="4" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="W71" s="4" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="X71" s="4" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Y71" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>0x87_Bael</t>
+          <t>Lowlander_WyvernRider</t>
         </is>
       </c>
       <c r="B72" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C72" s="4" t="n">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E72" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L72" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M72" s="4" t="inlineStr">
         <is>
-          <t>SharpClaw</t>
+          <t>SteelLance</t>
         </is>
       </c>
       <c r="N72" s="4" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="O72" s="4" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="P72" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q72" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R72" s="4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="S72" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T72" s="4" t="n"/>
       <c r="U72" s="4" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="V72" s="4" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="W72" s="4" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="X72" s="4" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="Y72" s="4" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>0x87_Cyclops</t>
+          <t>Lowlander_PegasusKnight</t>
         </is>
       </c>
       <c r="B73" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C73" s="4" t="n">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G73" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H73" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I73" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="J73" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K73" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L73" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M73" s="4" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="N73" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="O73" s="4" t="n">
+        <v>124</v>
+      </c>
+      <c r="P73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="R73" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="S73" s="4" t="n">
         <v>16</v>
-      </c>
-      <c r="H73" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="I73" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="J73" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K73" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="L73" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M73" s="4" t="inlineStr">
-        <is>
-          <t>SharpClaw</t>
-        </is>
-      </c>
-      <c r="N73" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="O73" s="4" t="n">
-        <v>114</v>
-      </c>
-      <c r="P73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q73" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="R73" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="S73" s="4" t="n">
-        <v>20</v>
       </c>
       <c r="T73" s="4" t="n"/>
       <c r="U73" s="4" t="n">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="V73" s="4" t="n">
-        <v>111</v>
+        <v>35</v>
       </c>
       <c r="W73" s="4" t="n">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="X73" s="4" t="n">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="Y73" s="4" t="n">
-        <v>68</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>0x87_Revenant</t>
+          <t>Beast_Jabberwock</t>
         </is>
       </c>
       <c r="B74" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C74" s="4" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E74" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H74" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="L74" s="4" t="n">
         <v>3</v>
       </c>
       <c r="M74" s="4" t="inlineStr">
         <is>
-          <t>SharpClaw</t>
+          <t>FetidClaw</t>
         </is>
       </c>
       <c r="N74" s="4" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="P74" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q74" s="4" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="R74" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="S74" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T74" s="4" t="n"/>
       <c r="U74" s="4" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="V74" s="4" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="W74" s="4" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="X74" s="4" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="Y74" s="4" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>0x87_Mercenary</t>
+          <t>0x87_MogallClass</t>
         </is>
       </c>
       <c r="B75" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C75" s="4" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F75" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G75" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="G75" s="4" t="n">
-        <v>11</v>
-      </c>
       <c r="H75" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>3</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L75" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M75" s="4" t="inlineStr">
         <is>
-          <t>SharpClaw</t>
+          <t>EvilEye</t>
         </is>
       </c>
       <c r="N75" s="4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O75" s="4" t="n">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="P75" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q75" s="4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="R75" s="4" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="S75" s="4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="T75" s="4" t="n"/>
       <c r="U75" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="V75" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="W75" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="X75" s="4" t="n">
         <v>35</v>
-      </c>
-      <c r="V75" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="W75" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="X75" s="4" t="n">
-        <v>18</v>
       </c>
       <c r="Y75" s="4" t="n">
         <v>22</v>
@@ -43422,41 +43738,41 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>0x87_LowMage</t>
+          <t>0x87_Bael</t>
         </is>
       </c>
       <c r="B76" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C76" s="4" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H76" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="I76" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J76" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K76" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="F76" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="G76" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="H76" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="I76" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="J76" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K76" s="4" t="n">
-        <v>8</v>
-      </c>
       <c r="L76" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M76" s="4" t="inlineStr">
         <is>
@@ -43464,78 +43780,78 @@
         </is>
       </c>
       <c r="N76" s="4" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="P76" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q76" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="R76" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="S76" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T76" s="4" t="n"/>
       <c r="U76" s="4" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="V76" s="4" t="n">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="W76" s="4" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="X76" s="4" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="Y76" s="4" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>0x87_Gargoyle</t>
+          <t>0x87_Cyclops</t>
         </is>
       </c>
       <c r="B77" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C77" s="4" t="n">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="D77" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="E77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="E77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F77" s="4" t="n">
+      <c r="G77" s="4" t="n">
         <v>13</v>
-      </c>
-      <c r="G77" s="4" t="n">
-        <v>16</v>
       </c>
       <c r="H77" s="4" t="n">
         <v>13</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="L77" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M77" s="4" t="inlineStr">
         <is>
@@ -43543,69 +43859,69 @@
         </is>
       </c>
       <c r="N77" s="4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O77" s="4" t="n">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="P77" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q77" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="R77" s="4" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="S77" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="T77" s="4" t="n"/>
       <c r="U77" s="4" t="n">
-        <v>49</v>
+        <v>104</v>
       </c>
       <c r="V77" s="4" t="n">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="W77" s="4" t="n">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="X77" s="4" t="n">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="Y77" s="4" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>JabberwockBlocker_Revenant</t>
+          <t>0x87_Revenant</t>
         </is>
       </c>
       <c r="B78" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C78" s="4" t="n">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="D78" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="E78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G78" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F78" s="4" t="n">
+      <c r="H78" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" s="4" t="n">
         <v>5</v>
-      </c>
-      <c r="G78" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H78" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I78" s="4" t="n">
-        <v>4</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>0</v>
@@ -43614,45 +43930,361 @@
         <v>7</v>
       </c>
       <c r="L78" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M78" s="4" t="inlineStr">
         <is>
-          <t>FetidClaw</t>
+          <t>SharpClaw</t>
         </is>
       </c>
       <c r="N78" s="4" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="P78" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q78" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="R78" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S78" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T78" s="4" t="n"/>
       <c r="U78" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="V78" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="W78" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="X78" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y78" s="4" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>0x87_Mercenary</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C79" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="E79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H79" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I79" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J79" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K79" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L79" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M79" s="4" t="inlineStr">
+        <is>
+          <t>SharpClaw</t>
+        </is>
+      </c>
+      <c r="N79" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="O79" s="4" t="n">
+        <v>106</v>
+      </c>
+      <c r="P79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="R79" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="S79" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="T79" s="4" t="n"/>
+      <c r="U79" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="V79" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="W79" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="X79" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y79" s="4" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>0x87_LowMage</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C80" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E80" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H80" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I80" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="J80" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K80" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L80" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M80" s="4" t="inlineStr">
+        <is>
+          <t>SharpClaw</t>
+        </is>
+      </c>
+      <c r="N80" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="O80" s="4" t="n">
+        <v>103</v>
+      </c>
+      <c r="P80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R80" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="S80" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="T80" s="4" t="n"/>
+      <c r="U80" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="V80" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="W80" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="X80" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y80" s="4" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>0x87_Gargoyle</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C81" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="E81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="G81" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="H81" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="I81" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L81" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M81" s="4" t="inlineStr">
+        <is>
+          <t>SharpClaw</t>
+        </is>
+      </c>
+      <c r="N81" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="O81" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="P81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="R81" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="S81" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T81" s="4" t="n"/>
+      <c r="U81" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="V81" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="W81" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="V78" s="4" t="n">
+      <c r="X81" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y81" s="4" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>JabberwockBlocker_Revenant</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C82" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="D82" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H82" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L82" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M82" s="4" t="inlineStr">
+        <is>
+          <t>FetidClaw</t>
+        </is>
+      </c>
+      <c r="N82" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="O82" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="P82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S82" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T82" s="4" t="n"/>
+      <c r="U82" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="V82" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="W78" s="4" t="n">
+      <c r="W82" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="X78" s="4" t="n">
+      <c r="X82" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="Y78" s="4" t="n">
+      <c r="Y82" s="4" t="n">
         <v>17</v>
       </c>
     </row>

--- a/unit_stats.xlsx
+++ b/unit_stats.xlsx
@@ -19,6 +19,8 @@
     <sheet name="Ch5 Normal" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Ch5d Hard" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Ch5d Normal" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Ch6 Hard" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Ch6 Normal" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2792,7 +2794,7 @@
         <v>15</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U2" s="2" t="n">
         <v>40</v>
@@ -2871,7 +2873,7 @@
         <v>9</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U3" s="2" t="n">
         <v>40</v>
@@ -3029,7 +3031,7 @@
         <v>16</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="U5" s="2" t="n">
         <v>35</v>
@@ -3108,7 +3110,7 @@
         <v>16</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U6" s="2" t="n">
         <v>35</v>
@@ -3187,7 +3189,7 @@
         <v>16</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U7" s="2" t="n">
         <v>35</v>
@@ -3333,7 +3335,7 @@
         <v>8</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="U9" s="2" t="n">
         <v>47</v>
@@ -3489,7 +3491,7 @@
         <v>11</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="U11" s="2" t="n">
         <v>47</v>
@@ -3568,7 +3570,7 @@
         <v>12</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>36</v>
@@ -3647,7 +3649,7 @@
         <v>12</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U13" s="2" t="n">
         <v>36</v>
@@ -3726,7 +3728,7 @@
         <v>18</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="U14" s="2" t="n">
         <v>37</v>
@@ -3793,7 +3795,7 @@
       <c r="R15" s="2" t="n"/>
       <c r="S15" s="2" t="n"/>
       <c r="T15" s="2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="U15" s="2" t="n">
         <v>37</v>
@@ -4028,7 +4030,7 @@
         <v>9</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U18" s="2" t="n">
         <v>36</v>
@@ -4186,7 +4188,7 @@
         <v>18</v>
       </c>
       <c r="T20" s="2" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="U20" s="2" t="n">
         <v>32</v>
@@ -4342,7 +4344,7 @@
         <v>15</v>
       </c>
       <c r="T22" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="U22" s="2" t="n">
         <v>34</v>
@@ -4575,7 +4577,7 @@
         <v>16</v>
       </c>
       <c r="T25" s="2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U25" s="2" t="n">
         <v>47</v>
@@ -6740,19 +6742,19 @@
         <v>18</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="P57" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q57" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R57" s="4" t="n">
         <v>17</v>
       </c>
       <c r="S57" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T57" s="4" t="n"/>
       <c r="U57" s="4" t="n">
@@ -7045,7 +7047,7 @@
         <v>8</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
@@ -10603,6 +10605,500 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Y2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="4" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="5" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="7" customWidth="1" min="18" max="18"/>
+    <col width="6" customWidth="1" min="19" max="19"/>
+    <col width="6" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="11" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>UnitID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Lv</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Str</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Mag</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Skl</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Spd</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Def</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Res</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Luck</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Con</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Atk</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Crit</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>AS</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>AS+4</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>WEXP</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Mag OHKO</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Phys OHKO</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Bomb OHKO</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Mag ORKO</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Phys ORKO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>0x81_Mercenary</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>IronSword</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="O2" s="4" t="n">
+        <v>136</v>
+      </c>
+      <c r="P2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="R2" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="S2" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="T2" s="4" t="n"/>
+      <c r="U2" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="V2" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="W2" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="X2" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y2" s="4" t="n">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Y2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="4" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="5" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="7" customWidth="1" min="18" max="18"/>
+    <col width="6" customWidth="1" min="19" max="19"/>
+    <col width="6" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="11" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>UnitID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Lv</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Str</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Mag</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Skl</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Spd</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Def</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Res</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Luck</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Con</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Atk</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Crit</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>AS</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>AS+4</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>WEXP</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Mag OHKO</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Phys OHKO</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Bomb OHKO</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Mag ORKO</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Phys ORKO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>0x81_Mercenary</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>IronSword</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="O2" s="4" t="n">
+        <v>128</v>
+      </c>
+      <c r="P2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="R2" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="S2" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="T2" s="4" t="n"/>
+      <c r="U2" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="V2" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="W2" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="X2" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y2" s="4" t="n">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -19286,7 +19782,7 @@
         <v>15</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="U2" s="2" t="n">
         <v>40</v>
@@ -19365,7 +19861,7 @@
         <v>9</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U3" s="2" t="n">
         <v>40</v>
@@ -19523,7 +20019,7 @@
         <v>15</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U5" s="2" t="n">
         <v>33</v>
@@ -19681,7 +20177,7 @@
         <v>15</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U7" s="2" t="n">
         <v>33</v>
@@ -20522,7 +21018,7 @@
         <v>8</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U18" s="2" t="n">
         <v>35</v>
@@ -20601,7 +21097,7 @@
         <v>13</v>
       </c>
       <c r="T19" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U19" s="2" t="n">
         <v>35</v>
@@ -22558,19 +23054,19 @@
         <v>19</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="P47" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q47" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R47" s="4" t="n">
         <v>17</v>
       </c>
       <c r="S47" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T47" s="4" t="n"/>
       <c r="U47" s="4" t="n">
@@ -26469,19 +26965,19 @@
         <v>16</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>106</v>
+        <v>76</v>
       </c>
       <c r="P47" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q47" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R47" s="4" t="n">
         <v>14</v>
       </c>
       <c r="S47" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T47" s="4" t="n"/>
       <c r="U47" s="4" t="n">
@@ -26890,7 +27386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y77"/>
+  <dimension ref="A1:Y78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -27108,7 +27604,7 @@
         <v>15</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U2" s="2" t="n">
         <v>40</v>
@@ -27187,7 +27683,7 @@
         <v>9</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U3" s="2" t="n">
         <v>40</v>
@@ -27503,7 +27999,7 @@
         <v>15</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U7" s="2" t="n">
         <v>34</v>
@@ -27649,7 +28145,7 @@
         <v>8</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="U9" s="2" t="n">
         <v>46</v>
@@ -27805,7 +28301,7 @@
         <v>11</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="U11" s="2" t="n">
         <v>46</v>
@@ -27884,7 +28380,7 @@
         <v>12</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>35</v>
@@ -27963,7 +28459,7 @@
         <v>12</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U13" s="2" t="n">
         <v>35</v>
@@ -28042,7 +28538,7 @@
         <v>18</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="U14" s="2" t="n">
         <v>36</v>
@@ -28188,7 +28684,7 @@
         <v>8</v>
       </c>
       <c r="T16" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U16" s="2" t="n">
         <v>41</v>
@@ -28502,7 +28998,7 @@
         <v>17</v>
       </c>
       <c r="T20" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="U20" s="2" t="n">
         <v>31</v>
@@ -30948,7 +31444,7 @@
         <v>10</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M58" s="4" t="inlineStr">
         <is>
@@ -31185,7 +31681,7 @@
         <v>9</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
@@ -31433,19 +31929,19 @@
         <v>20</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="P64" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q64" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R64" s="4" t="n">
         <v>20</v>
       </c>
       <c r="S64" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T64" s="4" t="n"/>
       <c r="U64" s="4" t="n">
@@ -31659,7 +32155,7 @@
         <v>9</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M67" s="4" t="inlineStr">
         <is>
@@ -32336,158 +32832,237 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_LowMage</t>
+          <t>Lowlander_Fighter</t>
         </is>
       </c>
       <c r="B76" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C76" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="D76" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="C76" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="D76" s="4" t="n">
-        <v>12</v>
-      </c>
       <c r="E76" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F76" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H76" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I76" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J76" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K76" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="L76" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M76" s="4" t="inlineStr">
+        <is>
+          <t>SilverAxe</t>
+        </is>
+      </c>
+      <c r="N76" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="O76" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="P76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="R76" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="G76" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="H76" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="I76" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="J76" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K76" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L76" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M76" s="4" t="inlineStr">
-        <is>
-          <t>Exploitation</t>
-        </is>
-      </c>
-      <c r="N76" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="O76" s="4" t="n">
-        <v>118</v>
-      </c>
-      <c r="P76" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="R76" s="4" t="n">
-        <v>26</v>
-      </c>
       <c r="S76" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T76" s="4" t="n"/>
       <c r="U76" s="4" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="V76" s="4" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="W76" s="4" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="X76" s="4" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="Y76" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>0xAE_MogallClass</t>
+          <t>Lowlander_LowMage</t>
         </is>
       </c>
       <c r="B77" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C77" s="4" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H77" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>4</v>
       </c>
       <c r="K77" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L77" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M77" s="4" t="inlineStr">
+        <is>
+          <t>Exploitation</t>
+        </is>
+      </c>
+      <c r="N77" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="O77" s="4" t="n">
+        <v>118</v>
+      </c>
+      <c r="P77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R77" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="S77" s="4" t="n">
         <v>9</v>
-      </c>
-      <c r="L77" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M77" s="4" t="inlineStr">
-        <is>
-          <t>EvilEye</t>
-        </is>
-      </c>
-      <c r="N77" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="O77" s="4" t="n">
-        <v>123</v>
-      </c>
-      <c r="P77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q77" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="R77" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="S77" s="4" t="n">
-        <v>19</v>
       </c>
       <c r="T77" s="4" t="n"/>
       <c r="U77" s="4" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="V77" s="4" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="W77" s="4" t="n">
         <v>47</v>
       </c>
       <c r="X77" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y77" s="4" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>0xAE_MogallClass</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C78" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="E78" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H78" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I78" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="J78" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K78" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L78" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M78" s="4" t="inlineStr">
+        <is>
+          <t>EvilEye</t>
+        </is>
+      </c>
+      <c r="N78" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="O78" s="4" t="n">
+        <v>123</v>
+      </c>
+      <c r="P78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="R78" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="S78" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="T78" s="4" t="n"/>
+      <c r="U78" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="V78" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="W78" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="X78" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="Y77" s="4" t="n">
+      <c r="Y78" s="4" t="n">
         <v>24</v>
       </c>
     </row>
@@ -32502,7 +33077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y77"/>
+  <dimension ref="A1:Y78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -33956,7 +34531,7 @@
         <v>8</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="U18" s="2" t="n">
         <v>35</v>
@@ -34035,7 +34610,7 @@
         <v>13</v>
       </c>
       <c r="T19" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="U19" s="2" t="n">
         <v>35</v>
@@ -34270,7 +34845,7 @@
         <v>14</v>
       </c>
       <c r="T22" s="2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="U22" s="2" t="n">
         <v>33</v>
@@ -34426,7 +35001,7 @@
         <v>16</v>
       </c>
       <c r="T24" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U24" s="2" t="n">
         <v>33</v>
@@ -36562,7 +37137,7 @@
         <v>10</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M58" s="4" t="inlineStr">
         <is>
@@ -36799,7 +37374,7 @@
         <v>9</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
@@ -37047,19 +37622,19 @@
         <v>17</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="P64" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q64" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R64" s="4" t="n">
         <v>15</v>
       </c>
       <c r="S64" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T64" s="4" t="n"/>
       <c r="U64" s="4" t="n">
@@ -37273,7 +37848,7 @@
         <v>9</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M67" s="4" t="inlineStr">
         <is>
@@ -37950,158 +38525,237 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>Lowlander_LowMage</t>
+          <t>Lowlander_Fighter</t>
         </is>
       </c>
       <c r="B76" s="4" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C76" s="4" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D76" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H76" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I76" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="L76" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M76" s="4" t="inlineStr">
+        <is>
+          <t>SilverAxe</t>
+        </is>
+      </c>
+      <c r="N76" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="O76" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="P76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R76" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="S76" s="4" t="n">
         <v>9</v>
-      </c>
-      <c r="E76" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="F76" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G76" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="H76" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="I76" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="J76" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K76" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L76" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M76" s="4" t="inlineStr">
-        <is>
-          <t>Exploitation</t>
-        </is>
-      </c>
-      <c r="N76" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="O76" s="4" t="n">
-        <v>113</v>
-      </c>
-      <c r="P76" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="R76" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="S76" s="4" t="n">
-        <v>7</v>
       </c>
       <c r="T76" s="4" t="n"/>
       <c r="U76" s="4" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="V76" s="4" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="W76" s="4" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="X76" s="4" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="Y76" s="4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>0xAE_MogallClass</t>
+          <t>Lowlander_LowMage</t>
         </is>
       </c>
       <c r="B77" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C77" s="4" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H77" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I77" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="J77" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="I77" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="J77" s="4" t="n">
+      <c r="K77" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L77" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K77" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="L77" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="M77" s="4" t="inlineStr">
         <is>
-          <t>EvilEye</t>
+          <t>Exploitation</t>
         </is>
       </c>
       <c r="N77" s="4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="O77" s="4" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="P77" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q77" s="4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="R77" s="4" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="S77" s="4" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="T77" s="4" t="n"/>
       <c r="U77" s="4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="V77" s="4" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="W77" s="4" t="n">
         <v>42</v>
       </c>
       <c r="X77" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y77" s="4" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>0xAE_MogallClass</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C78" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E78" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="H78" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I78" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J78" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K78" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L78" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M78" s="4" t="inlineStr">
+        <is>
+          <t>EvilEye</t>
+        </is>
+      </c>
+      <c r="N78" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="O78" s="4" t="n">
+        <v>117</v>
+      </c>
+      <c r="P78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="R78" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="S78" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="T78" s="4" t="n"/>
+      <c r="U78" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="V78" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="W78" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="X78" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="Y77" s="4" t="n">
+      <c r="Y78" s="4" t="n">
         <v>21</v>
       </c>
     </row>
@@ -38334,7 +38988,7 @@
         <v>15</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="U2" s="2" t="n">
         <v>40</v>
@@ -38413,7 +39067,7 @@
         <v>9</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="U3" s="2" t="n">
         <v>40</v>
@@ -38571,7 +39225,7 @@
         <v>16</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="U5" s="2" t="n">
         <v>35</v>
@@ -38650,7 +39304,7 @@
         <v>16</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="U6" s="2" t="n">
         <v>35</v>
@@ -38729,7 +39383,7 @@
         <v>16</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U7" s="2" t="n">
         <v>35</v>
@@ -39031,7 +39685,7 @@
         <v>11</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="U11" s="2" t="n">
         <v>47</v>
@@ -39110,7 +39764,7 @@
         <v>12</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>36</v>
@@ -39570,7 +40224,7 @@
         <v>9</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="U18" s="2" t="n">
         <v>36</v>
@@ -39649,7 +40303,7 @@
         <v>14</v>
       </c>
       <c r="T19" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U19" s="2" t="n">
         <v>36</v>
@@ -40117,7 +40771,7 @@
         <v>16</v>
       </c>
       <c r="T25" s="2" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="U25" s="2" t="n">
         <v>47</v>
@@ -42282,19 +42936,19 @@
         <v>21</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="P57" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q57" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R57" s="4" t="n">
         <v>22</v>
       </c>
       <c r="S57" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T57" s="4" t="n"/>
       <c r="U57" s="4" t="n">
@@ -42587,7 +43241,7 @@
         <v>8</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>

--- a/unit_stats.xlsx
+++ b/unit_stats.xlsx
@@ -10611,26 +10611,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y2"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="4" customWidth="1" min="2" max="2"/>
-    <col width="4" customWidth="1" min="3" max="3"/>
-    <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="5" customWidth="1" min="7" max="7"/>
-    <col width="5" customWidth="1" min="8" max="8"/>
-    <col width="5" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
     <col width="6" customWidth="1" min="10" max="10"/>
-    <col width="5" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
     <col width="7" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="6" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
-    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="17" max="17"/>
     <col width="7" customWidth="1" min="18" max="18"/>
     <col width="6" customWidth="1" min="19" max="19"/>
     <col width="6" customWidth="1" min="20" max="20"/>
@@ -10769,82 +10769,1821 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>0x81_Soldier</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="T2" s="3" t="n"/>
+      <c r="U2" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="X2" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>0x81_Soldier</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>-4</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="3" t="n"/>
+      <c r="U3" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>0x81_Fighter</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>104</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="T4" s="3" t="n"/>
+      <c r="U4" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>0x81_Fighter</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" s="3" t="n"/>
+      <c r="U5" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="V5" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>0x82_LanceCav</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" s="3" t="n"/>
+      <c r="U6" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>0x82_LanceCav</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" s="3" t="n"/>
+      <c r="U7" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>0x81_AxeCav</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" s="3" t="n"/>
+      <c r="U8" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="X8" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>0x81_AxeCav</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" s="3" t="n"/>
+      <c r="U9" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="V9" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="W9" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="X9" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y9" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Lion_Mage</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" s="3" t="n"/>
+      <c r="U10" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="V10" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="W10" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="X10" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y10" s="3" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Lion_Mage</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="T11" s="3" t="n"/>
+      <c r="U11" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="V11" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="W11" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="X11" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y11" s="3" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>0x81_Mercenary</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B13" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C13" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D13" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="E2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="4" t="n">
+      <c r="E13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="G2" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="H2" s="4" t="n">
+      <c r="G13" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H13" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="I2" s="4" t="n">
+      <c r="I13" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="J2" s="4" t="n">
+      <c r="J13" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="K2" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="L2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" s="4" t="inlineStr">
+      <c r="K13" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
         <is>
           <t>IronSword</t>
         </is>
       </c>
-      <c r="N2" s="4" t="n">
+      <c r="N13" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="O2" s="4" t="n">
+      <c r="O13" s="4" t="n">
         <v>136</v>
       </c>
-      <c r="P2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="R2" s="4" t="n">
+      <c r="P13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="R13" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="S2" s="4" t="n">
+      <c r="S13" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="T2" s="4" t="n"/>
-      <c r="U2" s="4" t="n">
+      <c r="T13" s="4" t="n"/>
+      <c r="U13" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="V2" s="4" t="n">
+      <c r="V13" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="W2" s="4" t="n">
+      <c r="W13" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="X2" s="4" t="n">
+      <c r="X13" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="Y2" s="4" t="n">
+      <c r="Y13" s="4" t="n">
         <v>25</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Skull_Fighter</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="O14" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="P14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="R14" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="S14" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="T14" s="4" t="n"/>
+      <c r="U14" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="V14" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="W14" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="X14" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y14" s="4" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Skull_Fighter</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="O15" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="P15" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q15" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R15" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="S15" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="T15" s="4" t="n"/>
+      <c r="U15" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="V15" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="W15" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="X15" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y15" s="4" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>0x82_Brigand</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="O16" s="4" t="n">
+        <v>94</v>
+      </c>
+      <c r="P16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="R16" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="S16" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="T16" s="4" t="n"/>
+      <c r="U16" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="V16" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="W16" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="X16" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y16" s="4" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>0x82_Brigand</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="O17" s="4" t="n">
+        <v>89</v>
+      </c>
+      <c r="P17" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q17" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R17" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="S17" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="T17" s="4" t="n"/>
+      <c r="U17" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="V17" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="W17" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="X17" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y17" s="4" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>0x83_Mercenary</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="O18" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="P18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="R18" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="S18" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="T18" s="4" t="n"/>
+      <c r="U18" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="V18" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="W18" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="X18" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y18" s="4" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>0x83_Mercenary</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="O19" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="P19" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q19" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R19" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="S19" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="T19" s="4" t="n"/>
+      <c r="U19" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="V19" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="W19" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y19" s="4" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>0x84_Fighter</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="O20" s="4" t="n">
+        <v>104</v>
+      </c>
+      <c r="P20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R20" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="S20" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="T20" s="4" t="n"/>
+      <c r="U20" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="V20" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="W20" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="X20" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y20" s="4" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>0x84_Fighter</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="O21" s="4" t="n">
+        <v>99</v>
+      </c>
+      <c r="P21" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="S21" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T21" s="4" t="n"/>
+      <c r="U21" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="V21" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="W21" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="X21" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y21" s="4" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>0x84_CivMan</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="O22" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="P22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="R22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" s="4" t="n"/>
+      <c r="U22" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="V22" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="W22" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="X22" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y22" s="4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>0x84_CivMan</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="O23" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="P23" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q23" s="4" t="n">
+        <v>-10</v>
+      </c>
+      <c r="R23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="T23" s="4" t="n"/>
+      <c r="U23" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="V23" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="W23" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="X23" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y23" s="4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>0x84_Mercenary</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="O24" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="P24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="R24" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="S24" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="T24" s="4" t="n"/>
+      <c r="U24" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="V24" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="W24" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="X24" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y24" s="4" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>0x84_Mercenary</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="N25" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="O25" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="P25" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q25" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R25" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="S25" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="T25" s="4" t="n"/>
+      <c r="U25" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="V25" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="W25" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="X25" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y25" s="4" t="n">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -10858,26 +12597,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y2"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="4" customWidth="1" min="2" max="2"/>
-    <col width="4" customWidth="1" min="3" max="3"/>
-    <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="5" customWidth="1" min="7" max="7"/>
-    <col width="5" customWidth="1" min="8" max="8"/>
-    <col width="5" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
     <col width="6" customWidth="1" min="10" max="10"/>
-    <col width="5" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
     <col width="7" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="6" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
-    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="17" max="17"/>
     <col width="7" customWidth="1" min="18" max="18"/>
     <col width="6" customWidth="1" min="19" max="19"/>
     <col width="6" customWidth="1" min="20" max="20"/>
@@ -11016,82 +12755,1821 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>0x81_Soldier</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="T2" s="3" t="n"/>
+      <c r="U2" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="X2" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>0x81_Soldier</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>-4</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="3" t="n"/>
+      <c r="U3" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>0x81_Fighter</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>104</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="T4" s="3" t="n"/>
+      <c r="U4" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>0x81_Fighter</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" s="3" t="n"/>
+      <c r="U5" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="V5" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>0x82_LanceCav</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" s="3" t="n"/>
+      <c r="U6" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>0x82_LanceCav</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" s="3" t="n"/>
+      <c r="U7" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>0x81_AxeCav</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" s="3" t="n"/>
+      <c r="U8" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="X8" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>0x81_AxeCav</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" s="3" t="n"/>
+      <c r="U9" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="V9" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="W9" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="X9" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y9" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Lion_Mage</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" s="3" t="n"/>
+      <c r="U10" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="V10" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="W10" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="X10" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y10" s="3" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Lion_Mage</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="T11" s="3" t="n"/>
+      <c r="U11" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="V11" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="W11" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="X11" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y11" s="3" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>0x81_Mercenary</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B13" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C13" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="D2" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="4" t="n">
+      <c r="D13" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="G2" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="I2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="4" t="n">
+      <c r="G13" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K2" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="L2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" s="4" t="inlineStr">
+      <c r="K13" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
         <is>
           <t>IronSword</t>
         </is>
       </c>
-      <c r="N2" s="4" t="n">
+      <c r="N13" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="O2" s="4" t="n">
+      <c r="O13" s="4" t="n">
         <v>128</v>
       </c>
-      <c r="P2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="R2" s="4" t="n">
+      <c r="P13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="R13" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="S2" s="4" t="n">
+      <c r="S13" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="T2" s="4" t="n"/>
-      <c r="U2" s="4" t="n">
+      <c r="T13" s="4" t="n"/>
+      <c r="U13" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="V2" s="4" t="n">
+      <c r="V13" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="W2" s="4" t="n">
+      <c r="W13" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="X2" s="4" t="n">
+      <c r="X13" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="Y2" s="4" t="n">
+      <c r="Y13" s="4" t="n">
         <v>21</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Skull_Fighter</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="O14" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="P14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="R14" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="S14" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="T14" s="4" t="n"/>
+      <c r="U14" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="V14" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="W14" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="X14" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y14" s="4" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Skull_Fighter</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="O15" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="P15" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q15" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R15" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="S15" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="T15" s="4" t="n"/>
+      <c r="U15" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="V15" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="W15" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="X15" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y15" s="4" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>0x82_Brigand</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="O16" s="4" t="n">
+        <v>94</v>
+      </c>
+      <c r="P16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="R16" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="S16" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="T16" s="4" t="n"/>
+      <c r="U16" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="V16" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="W16" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="X16" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y16" s="4" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>0x82_Brigand</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="O17" s="4" t="n">
+        <v>89</v>
+      </c>
+      <c r="P17" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q17" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R17" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="S17" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="T17" s="4" t="n"/>
+      <c r="U17" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="V17" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="W17" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="X17" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y17" s="4" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>0x83_Mercenary</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="O18" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="P18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="R18" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="S18" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="T18" s="4" t="n"/>
+      <c r="U18" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="V18" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="W18" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="X18" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y18" s="4" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>0x83_Mercenary</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="O19" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="P19" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q19" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R19" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="S19" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="T19" s="4" t="n"/>
+      <c r="U19" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="V19" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="W19" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y19" s="4" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>0x84_Fighter</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="O20" s="4" t="n">
+        <v>104</v>
+      </c>
+      <c r="P20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R20" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="S20" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="T20" s="4" t="n"/>
+      <c r="U20" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="V20" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="W20" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="X20" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y20" s="4" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>0x84_Fighter</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="O21" s="4" t="n">
+        <v>99</v>
+      </c>
+      <c r="P21" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="S21" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T21" s="4" t="n"/>
+      <c r="U21" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="V21" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="W21" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="X21" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y21" s="4" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>0x84_CivMan</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="O22" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="P22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="R22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" s="4" t="n"/>
+      <c r="U22" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="V22" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="W22" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="X22" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y22" s="4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>0x84_CivMan</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="O23" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="P23" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q23" s="4" t="n">
+        <v>-10</v>
+      </c>
+      <c r="R23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="T23" s="4" t="n"/>
+      <c r="U23" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="V23" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="W23" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="X23" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y23" s="4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>0x84_Mercenary</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="O24" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="P24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="R24" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="S24" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="T24" s="4" t="n"/>
+      <c r="U24" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="V24" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="W24" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="X24" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y24" s="4" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>0x84_Mercenary</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="N25" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="O25" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="P25" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q25" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R25" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="S25" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="T25" s="4" t="n"/>
+      <c r="U25" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="V25" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="W25" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="X25" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y25" s="4" t="n">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/unit_stats.xlsx
+++ b/unit_stats.xlsx
@@ -1280,7 +1280,7 @@
         <v>21</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>125</v>
+        <v>231</v>
       </c>
       <c r="P10" s="2" t="n">
         <v>20</v>
@@ -1357,7 +1357,7 @@
         <v>22</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>115</v>
+        <v>221</v>
       </c>
       <c r="P11" s="2" t="n">
         <v>0</v>
@@ -1436,7 +1436,7 @@
         <v>21</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>110</v>
+        <v>212</v>
       </c>
       <c r="P12" s="2" t="n">
         <v>30</v>
@@ -1515,7 +1515,7 @@
         <v>23</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="P13" s="2" t="n">
         <v>30</v>
@@ -1594,7 +1594,7 @@
         <v>28</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>119</v>
+        <v>225</v>
       </c>
       <c r="P14" s="2" t="n">
         <v>0</v>
@@ -3399,7 +3399,7 @@
         <v>23</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>129</v>
+        <v>235</v>
       </c>
       <c r="P10" s="2" t="n">
         <v>20</v>
@@ -3476,7 +3476,7 @@
         <v>22</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>119</v>
+        <v>225</v>
       </c>
       <c r="P11" s="2" t="n">
         <v>0</v>
@@ -3555,7 +3555,7 @@
         <v>23</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>114</v>
+        <v>216</v>
       </c>
       <c r="P12" s="2" t="n">
         <v>30</v>
@@ -3634,7 +3634,7 @@
         <v>25</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="P13" s="2" t="n">
         <v>30</v>
@@ -3713,7 +3713,7 @@
         <v>29</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>121</v>
+        <v>227</v>
       </c>
       <c r="P14" s="2" t="n">
         <v>0</v>
@@ -4173,7 +4173,7 @@
         <v>20</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>155</v>
+        <v>101</v>
       </c>
       <c r="P20" s="2" t="n">
         <v>30</v>
@@ -4721,7 +4721,7 @@
         <v>46</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>172</v>
+        <v>266</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>0</v>
@@ -4800,7 +4800,7 @@
         <v>27</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>147</v>
+        <v>113</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>0</v>
@@ -5037,7 +5037,7 @@
         <v>23</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>126</v>
+        <v>233</v>
       </c>
       <c r="P32" s="3" t="n">
         <v>50</v>
@@ -5195,7 +5195,7 @@
         <v>10</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>112</v>
+        <v>219</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>50</v>
@@ -5353,7 +5353,7 @@
         <v>10</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>112</v>
+        <v>219</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>50</v>
@@ -6584,7 +6584,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="4" t="n">
-        <v>102</v>
+        <v>188</v>
       </c>
       <c r="P55" s="4" t="n">
         <v>0</v>
@@ -6742,7 +6742,7 @@
         <v>18</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="P57" s="4" t="n">
         <v>0</v>
@@ -6821,7 +6821,7 @@
         <v>28</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>95</v>
+        <v>227</v>
       </c>
       <c r="P58" s="4" t="n">
         <v>35</v>
@@ -7058,7 +7058,7 @@
         <v>23</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="P61" s="4" t="n">
         <v>30</v>
@@ -7216,7 +7216,7 @@
         <v>24</v>
       </c>
       <c r="O63" s="4" t="n">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="P63" s="4" t="n">
         <v>0</v>
@@ -7295,7 +7295,7 @@
         <v>32</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>96</v>
+        <v>163</v>
       </c>
       <c r="P64" s="4" t="n">
         <v>0</v>
@@ -8085,7 +8085,7 @@
         <v>27</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>93</v>
+        <v>185</v>
       </c>
       <c r="P74" s="4" t="n">
         <v>0</v>
@@ -8164,7 +8164,7 @@
         <v>23</v>
       </c>
       <c r="O75" s="4" t="n">
-        <v>112</v>
+        <v>199</v>
       </c>
       <c r="P75" s="4" t="n">
         <v>0</v>
@@ -8243,7 +8243,7 @@
         <v>31</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>95</v>
+        <v>162</v>
       </c>
       <c r="P76" s="4" t="n">
         <v>0</v>
@@ -8322,7 +8322,7 @@
         <v>36</v>
       </c>
       <c r="O77" s="4" t="n">
-        <v>110</v>
+        <v>177</v>
       </c>
       <c r="P77" s="4" t="n">
         <v>0</v>
@@ -8401,7 +8401,7 @@
         <v>31</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>87</v>
+        <v>154</v>
       </c>
       <c r="P78" s="4" t="n">
         <v>0</v>
@@ -8480,7 +8480,7 @@
         <v>28</v>
       </c>
       <c r="O79" s="4" t="n">
-        <v>100</v>
+        <v>167</v>
       </c>
       <c r="P79" s="4" t="n">
         <v>0</v>
@@ -8559,7 +8559,7 @@
         <v>21</v>
       </c>
       <c r="O80" s="4" t="n">
-        <v>98</v>
+        <v>165</v>
       </c>
       <c r="P80" s="4" t="n">
         <v>0</v>
@@ -8638,7 +8638,7 @@
         <v>34</v>
       </c>
       <c r="O81" s="4" t="n">
-        <v>97</v>
+        <v>164</v>
       </c>
       <c r="P81" s="4" t="n">
         <v>0</v>
@@ -8717,7 +8717,7 @@
         <v>21</v>
       </c>
       <c r="O82" s="4" t="n">
-        <v>95</v>
+        <v>187</v>
       </c>
       <c r="P82" s="4" t="n">
         <v>0</v>
@@ -9406,7 +9406,7 @@
         <v>22</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>107</v>
+        <v>193</v>
       </c>
       <c r="P10" s="4" t="n">
         <v>0</v>
@@ -9564,7 +9564,7 @@
         <v>33</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>105</v>
+        <v>200</v>
       </c>
       <c r="P12" s="4" t="n">
         <v>5</v>
@@ -9643,7 +9643,7 @@
         <v>20</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>159</v>
+        <v>239</v>
       </c>
       <c r="P13" s="4" t="n">
         <v>0</v>
@@ -10332,7 +10332,7 @@
         <v>19</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>104</v>
+        <v>190</v>
       </c>
       <c r="P10" s="4" t="n">
         <v>0</v>
@@ -10490,7 +10490,7 @@
         <v>30</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>100</v>
+        <v>195</v>
       </c>
       <c r="P12" s="4" t="n">
         <v>5</v>
@@ -10569,7 +10569,7 @@
         <v>18</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>152</v>
+        <v>232</v>
       </c>
       <c r="P13" s="4" t="n">
         <v>0</v>
@@ -10611,10 +10611,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y25"/>
+  <dimension ref="A1:Y33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
@@ -11562,7 +11562,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>0x81_Mercenary</t>
+          <t>Thug_Mercenary</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
@@ -11596,18 +11596,18 @@
         <v>10</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>IronSword</t>
+          <t>SteelSword</t>
         </is>
       </c>
       <c r="N13" s="4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="P13" s="4" t="n">
         <v>0</v>
@@ -11641,272 +11641,272 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Skull_Fighter</t>
+          <t>GuardUnit_Mage</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E14" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F14" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="J14" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>IronLance</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="N14" s="4" t="n">
         <v>20</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="P14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T14" s="4" t="n"/>
       <c r="U14" s="4" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Skull_Fighter</t>
+          <t>GuardUnit_Knight</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>9</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>SteelBlade</t>
+          <t>SteelLance</t>
         </is>
       </c>
       <c r="N15" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>3</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="S15" s="4" t="n">
         <v>7</v>
       </c>
       <c r="T15" s="4" t="n"/>
       <c r="U15" s="4" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>0x82_Brigand</t>
+          <t>Thug_Fighter</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J16" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G16" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K16" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>IronLance</t>
+          <t>IronAxe</t>
         </is>
       </c>
       <c r="N16" s="4" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="P16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T16" s="4" t="n"/>
       <c r="U16" s="4" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>0x82_Brigand</t>
+          <t>Thug_Brigand</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H17" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G17" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="H17" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="I17" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17" s="4" t="n">
         <v>12</v>
@@ -11916,93 +11916,93 @@
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>SteelBlade</t>
+          <t>SteelLance</t>
         </is>
       </c>
       <c r="N17" s="4" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T17" s="4" t="n"/>
       <c r="U17" s="4" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="W17" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="X17" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y17" s="4" t="n">
         <v>23</v>
-      </c>
-      <c r="X17" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y17" s="4" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>0x83_Mercenary</t>
+          <t>GuardUnit_Archer</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L18" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>IronLance</t>
+          <t>Longbow</t>
         </is>
       </c>
       <c r="N18" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P18" s="4" t="n">
         <v>0</v>
@@ -12011,153 +12011,153 @@
         <v>8</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="S18" s="4" t="n">
         <v>12</v>
       </c>
       <c r="T18" s="4" t="n"/>
       <c r="U18" s="4" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="V18" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="W18" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="W18" s="4" t="n">
-        <v>18</v>
-      </c>
       <c r="X18" s="4" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>0x83_Mercenary</t>
+          <t>GuardUnit_WyvernRider</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C19" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>SteelLance</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="D19" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="H19" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="I19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="L19" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" s="4" t="inlineStr">
-        <is>
-          <t>SteelBlade</t>
-        </is>
-      </c>
-      <c r="N19" s="4" t="n">
+      <c r="O19" s="4" t="n">
+        <v>89</v>
+      </c>
+      <c r="P19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="R19" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="O19" s="4" t="n">
-        <v>105</v>
-      </c>
-      <c r="P19" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q19" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R19" s="4" t="n">
-        <v>16</v>
-      </c>
       <c r="S19" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T19" s="4" t="n"/>
       <c r="U19" s="4" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="V19" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="W19" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="X19" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y19" s="4" t="n">
         <v>30</v>
-      </c>
-      <c r="W19" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y19" s="4" t="n">
-        <v>17</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>0x84_Fighter</t>
+          <t>Muscle_Warrior</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G20" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H20" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H20" s="4" t="n">
-        <v>4</v>
-      </c>
       <c r="I20" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>IronLance</t>
+          <t>SteelBow</t>
         </is>
       </c>
       <c r="N20" s="4" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="O20" s="4" t="n">
         <v>104</v>
@@ -12166,148 +12166,148 @@
         <v>0</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T20" s="4" t="n"/>
       <c r="U20" s="4" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>0x84_Fighter</t>
+          <t>Muscle_Warrior</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C21" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>SilverAxe</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="O21" s="4" t="n">
+        <v>104</v>
+      </c>
+      <c r="P21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="R21" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="D21" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I21" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="J21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M21" s="4" t="inlineStr">
-        <is>
-          <t>SteelBlade</t>
-        </is>
-      </c>
-      <c r="N21" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="O21" s="4" t="n">
-        <v>99</v>
-      </c>
-      <c r="P21" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" s="4" t="n">
-        <v>10</v>
-      </c>
       <c r="S21" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T21" s="4" t="n"/>
       <c r="U21" s="4" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>0x84_CivMan</t>
+          <t>Skull_Fighter</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I22" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J22" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J22" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K22" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
@@ -12315,78 +12315,78 @@
         </is>
       </c>
       <c r="N22" s="4" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="P22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-2</v>
+        <v>7</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="T22" s="4" t="n"/>
       <c r="U22" s="4" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>0x84_CivMan</t>
+          <t>Skull_Fighter</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I23" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J23" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J23" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K23" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
@@ -12394,66 +12394,66 @@
         </is>
       </c>
       <c r="N23" s="4" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="P23" s="4" t="n">
         <v>20</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-10</v>
+        <v>3</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-6</v>
+        <v>7</v>
       </c>
       <c r="T23" s="4" t="n"/>
       <c r="U23" s="4" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>0x84_Mercenary</t>
+          <t>0x82_Brigand</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I24" s="4" t="n">
         <v>0</v>
@@ -12462,7 +12462,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L24" s="4" t="n">
         <v>1</v>
@@ -12473,116 +12473,748 @@
         </is>
       </c>
       <c r="N24" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="P24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T24" s="4" t="n"/>
       <c r="U24" s="4" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>0x84_Mercenary</t>
+          <t>0x82_Brigand</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C25" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="N25" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="D25" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="H25" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="I25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="L25" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" s="4" t="inlineStr">
-        <is>
-          <t>SteelBlade</t>
-        </is>
-      </c>
-      <c r="N25" s="4" t="n">
-        <v>23</v>
-      </c>
       <c r="O25" s="4" t="n">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="P25" s="4" t="n">
         <v>20</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T25" s="4" t="n"/>
       <c r="U25" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="V25" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="W25" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="X25" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y25" s="4" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>0x83_Mercenary</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C26" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="V25" s="4" t="n">
+      <c r="D26" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="N26" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="O26" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="P26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="R26" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="S26" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="T26" s="4" t="n"/>
+      <c r="U26" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="V26" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="W25" s="4" t="n">
+      <c r="W26" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="X25" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y25" s="4" t="n">
+      <c r="X26" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y26" s="4" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>0x83_Mercenary</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="O27" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="P27" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q27" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R27" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="S27" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="T27" s="4" t="n"/>
+      <c r="U27" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="V27" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="W27" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="X27" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y27" s="4" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>0x84_Fighter</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="L28" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="N28" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="O28" s="4" t="n">
+        <v>104</v>
+      </c>
+      <c r="P28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R28" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="S28" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="T28" s="4" t="n"/>
+      <c r="U28" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="V28" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="W28" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="X28" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y28" s="4" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>0x84_Fighter</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="L29" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="O29" s="4" t="n">
+        <v>99</v>
+      </c>
+      <c r="P29" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="S29" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T29" s="4" t="n"/>
+      <c r="U29" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="V29" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="W29" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="X29" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y29" s="4" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>0x84_CivMan</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="O30" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="P30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="R30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T30" s="4" t="n"/>
+      <c r="U30" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="V30" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="W30" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="X30" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y30" s="4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>0x84_CivMan</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L31" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="N31" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="O31" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="P31" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q31" s="4" t="n">
+        <v>-10</v>
+      </c>
+      <c r="R31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="T31" s="4" t="n"/>
+      <c r="U31" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="V31" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="W31" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="X31" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y31" s="4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>0x84_Mercenary</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L32" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="O32" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="P32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="R32" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="S32" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="T32" s="4" t="n"/>
+      <c r="U32" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="V32" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="W32" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="X32" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y32" s="4" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>0x84_Mercenary</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="O33" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="P33" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q33" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R33" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="S33" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="T33" s="4" t="n"/>
+      <c r="U33" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="V33" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="W33" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="X33" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y33" s="4" t="n">
         <v>17</v>
       </c>
     </row>
@@ -12597,10 +13229,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y25"/>
+  <dimension ref="A1:Y33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
@@ -13548,7 +14180,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>0x81_Mercenary</t>
+          <t>Thug_Mercenary</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
@@ -13582,18 +14214,18 @@
         <v>10</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>IronSword</t>
+          <t>SteelSword</t>
         </is>
       </c>
       <c r="N13" s="4" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="P13" s="4" t="n">
         <v>0</v>
@@ -13627,210 +14259,210 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Skull_Fighter</t>
+          <t>GuardUnit_Mage</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I14" s="4" t="n">
         <v>7</v>
       </c>
       <c r="J14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K14" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>IronLance</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="N14" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="P14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T14" s="4" t="n"/>
       <c r="U14" s="4" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Skull_Fighter</t>
+          <t>GuardUnit_Knight</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G15" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>7</v>
-      </c>
       <c r="H15" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>2</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>SteelBlade</t>
+          <t>SteelLance</t>
         </is>
       </c>
       <c r="N15" s="4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T15" s="4" t="n"/>
       <c r="U15" s="4" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>0x82_Brigand</t>
+          <t>Thug_Fighter</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>7</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>IronLance</t>
+          <t>IronAxe</t>
         </is>
       </c>
       <c r="N16" s="4" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="P16" s="4" t="n">
         <v>0</v>
@@ -13839,311 +14471,311 @@
         <v>7</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S16" s="4" t="n">
         <v>11</v>
       </c>
       <c r="T16" s="4" t="n"/>
       <c r="U16" s="4" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>0x82_Brigand</t>
+          <t>Thug_Brigand</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G17" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>SteelLance</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="O17" s="4" t="n">
+        <v>79</v>
+      </c>
+      <c r="P17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="H17" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="L17" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" s="4" t="inlineStr">
-        <is>
-          <t>SteelBlade</t>
-        </is>
-      </c>
-      <c r="N17" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="O17" s="4" t="n">
-        <v>89</v>
-      </c>
-      <c r="P17" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q17" s="4" t="n">
-        <v>3</v>
-      </c>
       <c r="R17" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T17" s="4" t="n"/>
       <c r="U17" s="4" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>0x83_Mercenary</t>
+          <t>GuardUnit_Archer</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D18" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="G18" s="4" t="n">
         <v>9</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>8</v>
       </c>
       <c r="H18" s="4" t="n">
         <v>5</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L18" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>IronLance</t>
+          <t>Longbow</t>
         </is>
       </c>
       <c r="N18" s="4" t="n">
         <v>17</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="P18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T18" s="4" t="n"/>
       <c r="U18" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="V18" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="W18" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="V18" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="W18" s="4" t="n">
+      <c r="X18" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="X18" s="4" t="n">
-        <v>12</v>
-      </c>
       <c r="Y18" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>0x83_Mercenary</t>
+          <t>GuardUnit_WyvernRider</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D19" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>SteelLance</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="O19" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="P19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R19" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="S19" s="4" t="n">
         <v>9</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="H19" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="I19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="L19" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" s="4" t="inlineStr">
-        <is>
-          <t>SteelBlade</t>
-        </is>
-      </c>
-      <c r="N19" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="O19" s="4" t="n">
-        <v>105</v>
-      </c>
-      <c r="P19" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q19" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R19" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="S19" s="4" t="n">
-        <v>6</v>
       </c>
       <c r="T19" s="4" t="n"/>
       <c r="U19" s="4" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>0x84_Fighter</t>
+          <t>Muscle_Warrior</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G20" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H20" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H20" s="4" t="n">
-        <v>4</v>
-      </c>
       <c r="I20" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>IronLance</t>
+          <t>SteelBow</t>
         </is>
       </c>
       <c r="N20" s="4" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="O20" s="4" t="n">
         <v>104</v>
@@ -14152,148 +14784,148 @@
         <v>0</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T20" s="4" t="n"/>
       <c r="U20" s="4" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>0x84_Fighter</t>
+          <t>Muscle_Warrior</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C21" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>SilverAxe</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="O21" s="4" t="n">
+        <v>104</v>
+      </c>
+      <c r="P21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="R21" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="D21" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I21" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="J21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M21" s="4" t="inlineStr">
-        <is>
-          <t>SteelBlade</t>
-        </is>
-      </c>
-      <c r="N21" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="O21" s="4" t="n">
-        <v>99</v>
-      </c>
-      <c r="P21" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" s="4" t="n">
-        <v>10</v>
-      </c>
       <c r="S21" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T21" s="4" t="n"/>
       <c r="U21" s="4" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>0x84_CivMan</t>
+          <t>Skull_Fighter</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I22" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J22" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J22" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K22" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
@@ -14301,78 +14933,78 @@
         </is>
       </c>
       <c r="N22" s="4" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="P22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-2</v>
+        <v>7</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="T22" s="4" t="n"/>
       <c r="U22" s="4" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>0x84_CivMan</t>
+          <t>Skull_Fighter</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I23" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J23" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J23" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K23" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
@@ -14380,66 +15012,66 @@
         </is>
       </c>
       <c r="N23" s="4" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="P23" s="4" t="n">
         <v>20</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-10</v>
+        <v>3</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-6</v>
+        <v>7</v>
       </c>
       <c r="T23" s="4" t="n"/>
       <c r="U23" s="4" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>0x84_Mercenary</t>
+          <t>0x82_Brigand</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I24" s="4" t="n">
         <v>0</v>
@@ -14448,7 +15080,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L24" s="4" t="n">
         <v>1</v>
@@ -14459,116 +15091,748 @@
         </is>
       </c>
       <c r="N24" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="P24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T24" s="4" t="n"/>
       <c r="U24" s="4" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>0x84_Mercenary</t>
+          <t>0x82_Brigand</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C25" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="N25" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="D25" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="H25" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="I25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="L25" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" s="4" t="inlineStr">
-        <is>
-          <t>SteelBlade</t>
-        </is>
-      </c>
-      <c r="N25" s="4" t="n">
-        <v>23</v>
-      </c>
       <c r="O25" s="4" t="n">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="P25" s="4" t="n">
         <v>20</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T25" s="4" t="n"/>
       <c r="U25" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="V25" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="W25" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="X25" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y25" s="4" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>0x83_Mercenary</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C26" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="V25" s="4" t="n">
+      <c r="D26" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="N26" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="O26" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="P26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="R26" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="S26" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="T26" s="4" t="n"/>
+      <c r="U26" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="V26" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="W25" s="4" t="n">
+      <c r="W26" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="X25" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y25" s="4" t="n">
+      <c r="X26" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y26" s="4" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>0x83_Mercenary</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="O27" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="P27" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q27" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R27" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="S27" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="T27" s="4" t="n"/>
+      <c r="U27" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="V27" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="W27" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="X27" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y27" s="4" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>0x84_Fighter</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="L28" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="N28" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="O28" s="4" t="n">
+        <v>104</v>
+      </c>
+      <c r="P28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R28" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="S28" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="T28" s="4" t="n"/>
+      <c r="U28" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="V28" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="W28" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="X28" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y28" s="4" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>0x84_Fighter</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="L29" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="O29" s="4" t="n">
+        <v>99</v>
+      </c>
+      <c r="P29" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="S29" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T29" s="4" t="n"/>
+      <c r="U29" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="V29" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="W29" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="X29" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y29" s="4" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>0x84_CivMan</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="O30" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="P30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="R30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T30" s="4" t="n"/>
+      <c r="U30" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="V30" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="W30" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="X30" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y30" s="4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>0x84_CivMan</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L31" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="N31" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="O31" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="P31" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q31" s="4" t="n">
+        <v>-10</v>
+      </c>
+      <c r="R31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="T31" s="4" t="n"/>
+      <c r="U31" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="V31" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="W31" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="X31" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y31" s="4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>0x84_Mercenary</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L32" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="O32" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="P32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="R32" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="S32" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="T32" s="4" t="n"/>
+      <c r="U32" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="V32" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="W32" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="X32" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y32" s="4" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>0x84_Mercenary</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="O33" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="P33" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q33" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R33" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="S33" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="T33" s="4" t="n"/>
+      <c r="U33" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="V33" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="W33" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="X33" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y33" s="4" t="n">
         <v>17</v>
       </c>
     </row>
@@ -15400,7 +16664,7 @@
         <v>21</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>125</v>
+        <v>231</v>
       </c>
       <c r="P10" s="2" t="n">
         <v>20</v>
@@ -15477,7 +16741,7 @@
         <v>22</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>115</v>
+        <v>221</v>
       </c>
       <c r="P11" s="2" t="n">
         <v>0</v>
@@ -15556,7 +16820,7 @@
         <v>21</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>110</v>
+        <v>212</v>
       </c>
       <c r="P12" s="2" t="n">
         <v>30</v>
@@ -15635,7 +16899,7 @@
         <v>23</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="P13" s="2" t="n">
         <v>30</v>
@@ -15712,7 +16976,7 @@
         <v>28</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>119</v>
+        <v>225</v>
       </c>
       <c r="P14" s="2" t="n">
         <v>0</v>
@@ -17515,7 +18779,7 @@
         <v>21</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>125</v>
+        <v>231</v>
       </c>
       <c r="P10" s="2" t="n">
         <v>20</v>
@@ -17592,7 +18856,7 @@
         <v>22</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>115</v>
+        <v>221</v>
       </c>
       <c r="P11" s="2" t="n">
         <v>0</v>
@@ -17671,7 +18935,7 @@
         <v>21</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>110</v>
+        <v>212</v>
       </c>
       <c r="P12" s="2" t="n">
         <v>30</v>
@@ -17750,7 +19014,7 @@
         <v>23</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="P13" s="2" t="n">
         <v>30</v>
@@ -17829,7 +19093,7 @@
         <v>28</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>119</v>
+        <v>225</v>
       </c>
       <c r="P14" s="2" t="n">
         <v>0</v>
@@ -18956,7 +20220,7 @@
         <v>26</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>104</v>
+        <v>190</v>
       </c>
       <c r="P31" s="4" t="n">
         <v>0</v>
@@ -19193,7 +20457,7 @@
         <v>24</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>115</v>
+        <v>202</v>
       </c>
       <c r="P34" s="4" t="n">
         <v>0</v>
@@ -19430,7 +20694,7 @@
         <v>20</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>157</v>
+        <v>237</v>
       </c>
       <c r="P37" s="4" t="n">
         <v>0</v>
@@ -19746,7 +21010,7 @@
         <v>23</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="P41" s="4" t="n">
         <v>30</v>
@@ -20688,7 +21952,7 @@
         <v>21</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>125</v>
+        <v>231</v>
       </c>
       <c r="P10" s="2" t="n">
         <v>20</v>
@@ -20767,7 +22031,7 @@
         <v>22</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>115</v>
+        <v>221</v>
       </c>
       <c r="P11" s="2" t="n">
         <v>0</v>
@@ -20846,7 +22110,7 @@
         <v>21</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>110</v>
+        <v>212</v>
       </c>
       <c r="P12" s="2" t="n">
         <v>30</v>
@@ -20925,7 +22189,7 @@
         <v>23</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="P13" s="2" t="n">
         <v>30</v>
@@ -21004,7 +22268,7 @@
         <v>28</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>119</v>
+        <v>225</v>
       </c>
       <c r="P14" s="2" t="n">
         <v>0</v>
@@ -22131,7 +23395,7 @@
         <v>24</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>100</v>
+        <v>186</v>
       </c>
       <c r="P31" s="4" t="n">
         <v>0</v>
@@ -22368,7 +23632,7 @@
         <v>22</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>109</v>
+        <v>196</v>
       </c>
       <c r="P34" s="4" t="n">
         <v>0</v>
@@ -22605,7 +23869,7 @@
         <v>18</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>152</v>
+        <v>232</v>
       </c>
       <c r="P37" s="4" t="n">
         <v>0</v>
@@ -22921,7 +24185,7 @@
         <v>21</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="P41" s="4" t="n">
         <v>30</v>
@@ -23865,7 +25129,7 @@
         <v>22</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>127</v>
+        <v>233</v>
       </c>
       <c r="P10" s="2" t="n">
         <v>20</v>
@@ -23942,7 +25206,7 @@
         <v>22</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>117</v>
+        <v>223</v>
       </c>
       <c r="P11" s="2" t="n">
         <v>0</v>
@@ -24021,7 +25285,7 @@
         <v>22</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>112</v>
+        <v>214</v>
       </c>
       <c r="P12" s="2" t="n">
         <v>30</v>
@@ -24100,7 +25364,7 @@
         <v>24</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="P13" s="2" t="n">
         <v>30</v>
@@ -24179,7 +25443,7 @@
         <v>28</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>119</v>
+        <v>225</v>
       </c>
       <c r="P14" s="2" t="n">
         <v>0</v>
@@ -24639,7 +25903,7 @@
         <v>20</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>154</v>
+        <v>100</v>
       </c>
       <c r="P20" s="2" t="n">
         <v>30</v>
@@ -26058,7 +27322,7 @@
         <v>23</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>111</v>
+        <v>243</v>
       </c>
       <c r="P41" s="4" t="n">
         <v>35</v>
@@ -26374,7 +27638,7 @@
         <v>25</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="P45" s="4" t="n">
         <v>30</v>
@@ -26532,7 +27796,7 @@
         <v>19</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="P47" s="4" t="n">
         <v>0</v>
@@ -26769,7 +28033,7 @@
         <v>29</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="P50" s="4" t="n">
         <v>0</v>
@@ -27774,7 +29038,7 @@
         <v>22</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>127</v>
+        <v>233</v>
       </c>
       <c r="P10" s="2" t="n">
         <v>20</v>
@@ -27853,7 +29117,7 @@
         <v>22</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>117</v>
+        <v>223</v>
       </c>
       <c r="P11" s="2" t="n">
         <v>0</v>
@@ -27932,7 +29196,7 @@
         <v>22</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>112</v>
+        <v>214</v>
       </c>
       <c r="P12" s="2" t="n">
         <v>30</v>
@@ -28011,7 +29275,7 @@
         <v>24</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="P13" s="2" t="n">
         <v>30</v>
@@ -28090,7 +29354,7 @@
         <v>28</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>119</v>
+        <v>225</v>
       </c>
       <c r="P14" s="2" t="n">
         <v>0</v>
@@ -28550,7 +29814,7 @@
         <v>20</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>154</v>
+        <v>100</v>
       </c>
       <c r="P20" s="2" t="n">
         <v>30</v>
@@ -29969,7 +31233,7 @@
         <v>22</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>106</v>
+        <v>238</v>
       </c>
       <c r="P41" s="4" t="n">
         <v>35</v>
@@ -30285,7 +31549,7 @@
         <v>23</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="P45" s="4" t="n">
         <v>30</v>
@@ -30443,7 +31707,7 @@
         <v>16</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="P47" s="4" t="n">
         <v>0</v>
@@ -30680,7 +31944,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="P50" s="4" t="n">
         <v>0</v>
@@ -31687,7 +32951,7 @@
         <v>22</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>127</v>
+        <v>233</v>
       </c>
       <c r="P10" s="2" t="n">
         <v>20</v>
@@ -31764,7 +33028,7 @@
         <v>22</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>117</v>
+        <v>223</v>
       </c>
       <c r="P11" s="2" t="n">
         <v>0</v>
@@ -31843,7 +33107,7 @@
         <v>22</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>112</v>
+        <v>214</v>
       </c>
       <c r="P12" s="2" t="n">
         <v>30</v>
@@ -31922,7 +33186,7 @@
         <v>24</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="P13" s="2" t="n">
         <v>30</v>
@@ -32001,7 +33265,7 @@
         <v>28</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>121</v>
+        <v>227</v>
       </c>
       <c r="P14" s="2" t="n">
         <v>0</v>
@@ -32461,7 +33725,7 @@
         <v>20</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>154</v>
+        <v>100</v>
       </c>
       <c r="P20" s="2" t="n">
         <v>30</v>
@@ -34854,7 +36118,7 @@
         <v>28</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>106</v>
+        <v>192</v>
       </c>
       <c r="P57" s="4" t="n">
         <v>0</v>
@@ -34933,7 +36197,7 @@
         <v>27</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>116</v>
+        <v>242</v>
       </c>
       <c r="P58" s="4" t="n">
         <v>35</v>
@@ -35091,7 +36355,7 @@
         <v>25</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>118</v>
+        <v>205</v>
       </c>
       <c r="P60" s="4" t="n">
         <v>0</v>
@@ -35407,7 +36671,7 @@
         <v>20</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="P64" s="4" t="n">
         <v>0</v>
@@ -35802,7 +37066,7 @@
         <v>34</v>
       </c>
       <c r="O69" s="4" t="n">
-        <v>100</v>
+        <v>167</v>
       </c>
       <c r="P69" s="4" t="n">
         <v>0</v>
@@ -36197,7 +37461,7 @@
         <v>29</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="P74" s="4" t="n">
         <v>30</v>
@@ -36276,7 +37540,7 @@
         <v>29</v>
       </c>
       <c r="O75" s="4" t="n">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="P75" s="4" t="n">
         <v>0</v>
@@ -36434,7 +37698,7 @@
         <v>31</v>
       </c>
       <c r="O77" s="4" t="n">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="P77" s="4" t="n">
         <v>0</v>
@@ -36513,7 +37777,7 @@
         <v>28</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>123</v>
+        <v>210</v>
       </c>
       <c r="P78" s="4" t="n">
         <v>0</v>
@@ -37378,7 +38642,7 @@
         <v>22</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>127</v>
+        <v>233</v>
       </c>
       <c r="P10" s="2" t="n">
         <v>20</v>
@@ -37455,7 +38719,7 @@
         <v>22</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>117</v>
+        <v>223</v>
       </c>
       <c r="P11" s="2" t="n">
         <v>0</v>
@@ -37534,7 +38798,7 @@
         <v>22</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>112</v>
+        <v>214</v>
       </c>
       <c r="P12" s="2" t="n">
         <v>30</v>
@@ -37613,7 +38877,7 @@
         <v>24</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="P13" s="2" t="n">
         <v>30</v>
@@ -37692,7 +38956,7 @@
         <v>28</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>121</v>
+        <v>227</v>
       </c>
       <c r="P14" s="2" t="n">
         <v>0</v>
@@ -38152,7 +39416,7 @@
         <v>20</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>154</v>
+        <v>100</v>
       </c>
       <c r="P20" s="2" t="n">
         <v>30</v>
@@ -40547,7 +41811,7 @@
         <v>25</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>102</v>
+        <v>188</v>
       </c>
       <c r="P57" s="4" t="n">
         <v>0</v>
@@ -40626,7 +41890,7 @@
         <v>25</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>110</v>
+        <v>236</v>
       </c>
       <c r="P58" s="4" t="n">
         <v>35</v>
@@ -40784,7 +42048,7 @@
         <v>23</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>112</v>
+        <v>199</v>
       </c>
       <c r="P60" s="4" t="n">
         <v>0</v>
@@ -41100,7 +42364,7 @@
         <v>17</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="P64" s="4" t="n">
         <v>0</v>
@@ -41495,7 +42759,7 @@
         <v>31</v>
       </c>
       <c r="O69" s="4" t="n">
-        <v>95</v>
+        <v>162</v>
       </c>
       <c r="P69" s="4" t="n">
         <v>0</v>
@@ -41890,7 +43154,7 @@
         <v>26</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="P74" s="4" t="n">
         <v>30</v>
@@ -41969,7 +43233,7 @@
         <v>26</v>
       </c>
       <c r="O75" s="4" t="n">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="P75" s="4" t="n">
         <v>0</v>
@@ -42127,7 +43391,7 @@
         <v>28</v>
       </c>
       <c r="O77" s="4" t="n">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="P77" s="4" t="n">
         <v>0</v>
@@ -42206,7 +43470,7 @@
         <v>25</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>117</v>
+        <v>204</v>
       </c>
       <c r="P78" s="4" t="n">
         <v>0</v>
@@ -43071,7 +44335,7 @@
         <v>23</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>129</v>
+        <v>235</v>
       </c>
       <c r="P10" s="2" t="n">
         <v>20</v>
@@ -43148,7 +44412,7 @@
         <v>22</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>119</v>
+        <v>225</v>
       </c>
       <c r="P11" s="2" t="n">
         <v>0</v>
@@ -43227,7 +44491,7 @@
         <v>23</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>114</v>
+        <v>216</v>
       </c>
       <c r="P12" s="2" t="n">
         <v>30</v>
@@ -43306,7 +44570,7 @@
         <v>25</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="P13" s="2" t="n">
         <v>30</v>
@@ -43385,7 +44649,7 @@
         <v>29</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>121</v>
+        <v>227</v>
       </c>
       <c r="P14" s="2" t="n">
         <v>0</v>
@@ -43845,7 +45109,7 @@
         <v>20</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>155</v>
+        <v>101</v>
       </c>
       <c r="P20" s="2" t="n">
         <v>30</v>
@@ -44393,7 +45657,7 @@
         <v>46</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>172</v>
+        <v>266</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>0</v>
@@ -44472,7 +45736,7 @@
         <v>27</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>147</v>
+        <v>113</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>0</v>
@@ -44709,7 +45973,7 @@
         <v>23</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>126</v>
+        <v>233</v>
       </c>
       <c r="P32" s="3" t="n">
         <v>50</v>
@@ -44867,7 +46131,7 @@
         <v>10</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>112</v>
+        <v>219</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>50</v>
@@ -45025,7 +46289,7 @@
         <v>10</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>112</v>
+        <v>219</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>50</v>
@@ -46256,7 +47520,7 @@
         <v>29</v>
       </c>
       <c r="O55" s="4" t="n">
-        <v>107</v>
+        <v>193</v>
       </c>
       <c r="P55" s="4" t="n">
         <v>0</v>
@@ -46414,7 +47678,7 @@
         <v>21</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="P57" s="4" t="n">
         <v>0</v>
@@ -46493,7 +47757,7 @@
         <v>31</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>101</v>
+        <v>233</v>
       </c>
       <c r="P58" s="4" t="n">
         <v>35</v>
@@ -46730,7 +47994,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="P61" s="4" t="n">
         <v>30</v>
@@ -46888,7 +48152,7 @@
         <v>27</v>
       </c>
       <c r="O63" s="4" t="n">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="P63" s="4" t="n">
         <v>0</v>
@@ -46967,7 +48231,7 @@
         <v>35</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>101</v>
+        <v>168</v>
       </c>
       <c r="P64" s="4" t="n">
         <v>0</v>
@@ -47757,7 +49021,7 @@
         <v>27</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>93</v>
+        <v>185</v>
       </c>
       <c r="P74" s="4" t="n">
         <v>0</v>
@@ -47836,7 +49100,7 @@
         <v>25</v>
       </c>
       <c r="O75" s="4" t="n">
-        <v>118</v>
+        <v>205</v>
       </c>
       <c r="P75" s="4" t="n">
         <v>0</v>
@@ -47915,7 +49179,7 @@
         <v>34</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>100</v>
+        <v>167</v>
       </c>
       <c r="P76" s="4" t="n">
         <v>0</v>
@@ -47994,7 +49258,7 @@
         <v>38</v>
       </c>
       <c r="O77" s="4" t="n">
-        <v>114</v>
+        <v>181</v>
       </c>
       <c r="P77" s="4" t="n">
         <v>0</v>
@@ -48073,7 +49337,7 @@
         <v>34</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>91</v>
+        <v>158</v>
       </c>
       <c r="P78" s="4" t="n">
         <v>0</v>
@@ -48152,7 +49416,7 @@
         <v>30</v>
       </c>
       <c r="O79" s="4" t="n">
-        <v>106</v>
+        <v>173</v>
       </c>
       <c r="P79" s="4" t="n">
         <v>0</v>
@@ -48231,7 +49495,7 @@
         <v>24</v>
       </c>
       <c r="O80" s="4" t="n">
-        <v>103</v>
+        <v>170</v>
       </c>
       <c r="P80" s="4" t="n">
         <v>0</v>
@@ -48310,7 +49574,7 @@
         <v>36</v>
       </c>
       <c r="O81" s="4" t="n">
-        <v>101</v>
+        <v>168</v>
       </c>
       <c r="P81" s="4" t="n">
         <v>0</v>
@@ -48389,7 +49653,7 @@
         <v>21</v>
       </c>
       <c r="O82" s="4" t="n">
-        <v>95</v>
+        <v>187</v>
       </c>
       <c r="P82" s="4" t="n">
         <v>0</v>

--- a/unit_stats.xlsx
+++ b/unit_stats.xlsx
@@ -12372,7 +12372,7 @@
         <v>10</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
@@ -15148,7 +15148,7 @@
         <v>10</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>

--- a/unit_stats.xlsx
+++ b/unit_stats.xlsx
@@ -21409,7 +21409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y15"/>
+  <dimension ref="A1:Y20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21682,7 +21682,7 @@
         <v>9</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
@@ -21724,416 +21724,416 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4"/>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>0x81_CivMan</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" s="3" t="n"/>
+      <c r="U4" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>6</v>
+      </c>
+    </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>0x81_Soldier</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G5" s="4" t="n">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>0x82_CivWoman</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="H5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L5" s="4" t="n">
+      <c r="O5" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" s="3" t="n"/>
+      <c r="U5" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="V5" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>0x83_CivBoy</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="D6" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>IronLance</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v>113</v>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="4" t="n">
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="R5" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="S5" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="T5" s="4" t="n"/>
-      <c r="U5" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="V5" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="W5" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="X5" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="Y5" s="4" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>0x81_HighMage</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="D6" s="4" t="n">
+      <c r="O6" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" s="3" t="n"/>
+      <c r="U6" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="W6" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="M6" s="4" t="inlineStr">
-        <is>
-          <t>Fire</t>
-        </is>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="O6" s="4" t="n">
-        <v>129</v>
-      </c>
-      <c r="P6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="R6" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="S6" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="T6" s="4" t="n"/>
-      <c r="U6" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="V6" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="W6" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="X6" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y6" s="4" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>0x81_Knight</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" s="4" t="inlineStr">
-        <is>
-          <t>SteelLance</t>
-        </is>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="O7" s="4" t="n">
-        <v>91</v>
-      </c>
-      <c r="P7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="S7" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="T7" s="4" t="n"/>
-      <c r="U7" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="V7" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="W7" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="X7" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="Y7" s="4" t="n">
-        <v>34</v>
-      </c>
-    </row>
+      <c r="X6" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>0x81_Fighter</t>
+          <t>0x81_Soldier</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L8" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K8" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v>3</v>
-      </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>SteelAxe</t>
+          <t>IronLance</t>
         </is>
       </c>
       <c r="N8" s="4" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="P8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T8" s="4" t="n"/>
       <c r="U8" s="4" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>0x81_Myrmidon</t>
+          <t>0x81_HighMage</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E9" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="F9" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>8</v>
-      </c>
       <c r="J9" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>IronSword</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="N9" s="4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="P9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="T9" s="4" t="n"/>
       <c r="U9" s="4" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>0x81_WyvernRider</t>
+          <t>0x81_Knight</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>0</v>
@@ -22142,77 +22142,77 @@
         <v>9</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>3</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>IronLance</t>
+          <t>SteelLance</t>
         </is>
       </c>
       <c r="N10" s="4" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="P10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="T10" s="4" t="n"/>
       <c r="U10" s="4" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>0x81_LanceCav</t>
+          <t>0x81_Fighter</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
@@ -22221,216 +22221,216 @@
         <v>12</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H11" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>SteelAxe</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="O11" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="P11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R11" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="S11" s="4" t="n">
         <v>9</v>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J11" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="L11" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" s="4" t="inlineStr">
-        <is>
-          <t>IronLance</t>
-        </is>
-      </c>
-      <c r="N11" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="O11" s="4" t="n">
-        <v>118</v>
-      </c>
-      <c r="P11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="R11" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="S11" s="4" t="n">
-        <v>14</v>
       </c>
       <c r="T11" s="4" t="n"/>
       <c r="U11" s="4" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="V11" s="4" t="n">
         <v>46</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>0x81_SwordCav</t>
+          <t>0x81_Myrmidon</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>4</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>Quickblade</t>
+          <t>IronSword</t>
         </is>
       </c>
       <c r="N12" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="P12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="T12" s="4" t="n"/>
       <c r="U12" s="4" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Captain_Hero</t>
+          <t>0x81_WyvernRider</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="I13" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="E13" s="4" t="n">
+      <c r="J13" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F13" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="J13" s="4" t="n">
-        <v>4</v>
-      </c>
       <c r="K13" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>Quickblade</t>
+          <t>IronLance</t>
         </is>
       </c>
       <c r="N13" s="4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="P13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="T13" s="4" t="n"/>
       <c r="U13" s="4" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="Y13" s="4" t="n">
         <v>31</v>
@@ -22439,7 +22439,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>0x81_Mercenary</t>
+          <t>0x81_LanceCav</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
@@ -22449,149 +22449,544 @@
         <v>37</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>4</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>Quickblade</t>
+          <t>IronLance</t>
         </is>
       </c>
       <c r="N14" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="P14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="T14" s="4" t="n"/>
       <c r="U14" s="4" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>0x81_Shaman</t>
+          <t>0x81_SwordCav</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D15" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H15" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="E15" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G15" s="4" t="n">
+      <c r="I15" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="H15" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="J15" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K15" s="4" t="n">
-        <v>8</v>
-      </c>
       <c r="L15" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Quickblade</t>
         </is>
       </c>
       <c r="N15" s="4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T15" s="4" t="n"/>
       <c r="U15" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="V15" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="W15" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="X15" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y15" s="4" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>0x81_Archer</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>Longbow</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="O16" s="4" t="n">
+        <v>112</v>
+      </c>
+      <c r="P16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="R16" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="S16" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="T16" s="4" t="n"/>
+      <c r="U16" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="V16" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="W16" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="X16" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y16" s="4" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Captain_Hero</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>Quickblade</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="O17" s="4" t="n">
+        <v>131</v>
+      </c>
+      <c r="P17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="R17" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="S17" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="T17" s="4" t="n"/>
+      <c r="U17" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="V17" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="W17" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="X17" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y17" s="4" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>0x81_Mercenary</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>Quickblade</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="O18" s="4" t="n">
+        <v>121</v>
+      </c>
+      <c r="P18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="R18" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="S18" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="T18" s="4" t="n"/>
+      <c r="U18" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="V18" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="W18" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="X18" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y18" s="4" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>0x81_Shaman</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="O19" s="4" t="n">
+        <v>123</v>
+      </c>
+      <c r="P19" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q19" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="R19" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="S19" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="T19" s="4" t="n"/>
+      <c r="U19" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="V15" s="4" t="n">
+      <c r="V19" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="W15" s="4" t="n">
+      <c r="W19" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="X15" s="4" t="n">
+      <c r="X19" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="Y15" s="4" t="n">
+      <c r="Y19" s="4" t="n">
         <v>26</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Recruiter_Hero</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>Quickblade</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="O20" s="4" t="n">
+        <v>129</v>
+      </c>
+      <c r="P20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="R20" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="S20" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="T20" s="4" t="n"/>
+      <c r="U20" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="V20" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="W20" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="X20" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y20" s="4" t="n">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -22605,7 +23000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y15"/>
+  <dimension ref="A1:Y20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -22878,7 +23273,7 @@
         <v>9</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
@@ -22920,349 +23315,349 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4"/>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>0x81_CivMan</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" s="3" t="n"/>
+      <c r="U4" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>6</v>
+      </c>
+    </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>0x81_Soldier</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" s="4" t="n">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>0x82_CivWoman</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="J5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L5" s="4" t="n">
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>IronLance</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v>108</v>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="R5" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="S5" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" s="4" t="n"/>
-      <c r="U5" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="V5" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="W5" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="X5" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y5" s="4" t="n">
-        <v>20</v>
+      <c r="J5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" s="3" t="n"/>
+      <c r="U5" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="V5" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>0x81_HighMage</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="H6" s="4" t="n">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>0x83_CivBoy</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="I6" s="4" t="n">
+      <c r="L6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="J6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L6" s="4" t="n">
+      <c r="O6" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="M6" s="4" t="inlineStr">
-        <is>
-          <t>Fire</t>
-        </is>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="O6" s="4" t="n">
-        <v>124</v>
-      </c>
-      <c r="P6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="R6" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="S6" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="T6" s="4" t="n"/>
-      <c r="U6" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="V6" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="W6" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="X6" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y6" s="4" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>0x81_Knight</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="4" t="n">
+      <c r="T6" s="3" t="n"/>
+      <c r="U6" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="W6" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="G7" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" s="4" t="inlineStr">
-        <is>
-          <t>SteelLance</t>
-        </is>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="O7" s="4" t="n">
-        <v>86</v>
-      </c>
-      <c r="P7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R7" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="S7" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="T7" s="4" t="n"/>
-      <c r="U7" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="V7" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="W7" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="X7" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y7" s="4" t="n">
-        <v>30</v>
-      </c>
-    </row>
+      <c r="X6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>0x81_Fighter</t>
+          <t>0x81_Soldier</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>SteelAxe</t>
+          <t>IronLance</t>
         </is>
       </c>
       <c r="N8" s="4" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="P8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T8" s="4" t="n"/>
       <c r="U8" s="4" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>0x81_Myrmidon</t>
+          <t>0x81_HighMage</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D9" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G9" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="E9" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>15</v>
-      </c>
       <c r="H9" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I9" s="4" t="n">
         <v>7</v>
@@ -23271,65 +23666,65 @@
         <v>2</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>IronSword</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="N9" s="4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="P9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="T9" s="4" t="n"/>
       <c r="U9" s="4" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>0x81_WyvernRider</t>
+          <t>0x81_Knight</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>0</v>
@@ -23338,77 +23733,77 @@
         <v>7</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H10" s="4" t="n">
         <v>12</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>2</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L10" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>SteelLance</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="O10" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="P10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="M10" s="4" t="inlineStr">
-        <is>
-          <t>IronLance</t>
-        </is>
-      </c>
-      <c r="N10" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="O10" s="4" t="n">
-        <v>106</v>
-      </c>
-      <c r="P10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="4" t="n">
-        <v>8</v>
-      </c>
       <c r="R10" s="4" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T10" s="4" t="n"/>
       <c r="U10" s="4" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>0x81_LanceCav</t>
+          <t>0x81_Fighter</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
@@ -23417,377 +23812,772 @@
         <v>10</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J11" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="K11" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>IronLance</t>
+          <t>SteelAxe</t>
         </is>
       </c>
       <c r="N11" s="4" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="P11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T11" s="4" t="n"/>
       <c r="U11" s="4" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="V11" s="4" t="n">
         <v>41</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>0x81_SwordCav</t>
+          <t>0x81_Myrmidon</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>2</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>Quickblade</t>
+          <t>IronSword</t>
         </is>
       </c>
       <c r="N12" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="P12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="T12" s="4" t="n"/>
       <c r="U12" s="4" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Captain_Hero</t>
+          <t>0x81_WyvernRider</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>2</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>Quickblade</t>
+          <t>IronLance</t>
         </is>
       </c>
       <c r="N13" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="P13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="T13" s="4" t="n"/>
       <c r="U13" s="4" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>0x81_Mercenary</t>
+          <t>0x81_LanceCav</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>2</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>Quickblade</t>
+          <t>IronLance</t>
         </is>
       </c>
       <c r="N14" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="P14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T14" s="4" t="n"/>
       <c r="U14" s="4" t="n">
         <v>34</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>0x81_Shaman</t>
+          <t>0x81_SwordCav</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>2</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Quickblade</t>
         </is>
       </c>
       <c r="N15" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T15" s="4" t="n"/>
       <c r="U15" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="V15" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="W15" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="X15" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y15" s="4" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>0x81_Archer</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>Longbow</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="O16" s="4" t="n">
+        <v>106</v>
+      </c>
+      <c r="P16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="R16" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="S16" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="T16" s="4" t="n"/>
+      <c r="U16" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="V16" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="W16" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="X16" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y16" s="4" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Captain_Hero</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>Quickblade</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="O17" s="4" t="n">
+        <v>123</v>
+      </c>
+      <c r="P17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="R17" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="S17" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="T17" s="4" t="n"/>
+      <c r="U17" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="V17" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="V15" s="4" t="n">
+      <c r="W17" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="X17" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y17" s="4" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>0x81_Mercenary</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>Quickblade</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="O18" s="4" t="n">
+        <v>115</v>
+      </c>
+      <c r="P18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="R18" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="S18" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" s="4" t="n"/>
+      <c r="U18" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="V18" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="W18" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="X18" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y18" s="4" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>0x81_Shaman</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="O19" s="4" t="n">
+        <v>118</v>
+      </c>
+      <c r="P19" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q19" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="R19" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="S19" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="T19" s="4" t="n"/>
+      <c r="U19" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="V19" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="W15" s="4" t="n">
+      <c r="W19" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="X15" s="4" t="n">
+      <c r="X19" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="Y15" s="4" t="n">
+      <c r="Y19" s="4" t="n">
         <v>23</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Recruiter_Hero</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>Quickblade</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="O20" s="4" t="n">
+        <v>129</v>
+      </c>
+      <c r="P20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="R20" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="S20" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="T20" s="4" t="n"/>
+      <c r="U20" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="V20" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="W20" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="X20" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y20" s="4" t="n">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/unit_stats.xlsx
+++ b/unit_stats.xlsx
@@ -2796,7 +2796,7 @@
         <v>15</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="U2" s="2" t="n">
         <v>40</v>
@@ -2875,7 +2875,7 @@
         <v>9</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="U3" s="2" t="n">
         <v>40</v>
@@ -2954,7 +2954,7 @@
         <v>15</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="U4" s="2" t="n">
         <v>40</v>
@@ -3337,7 +3337,7 @@
         <v>8</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="U9" s="2" t="n">
         <v>47</v>
@@ -3572,7 +3572,7 @@
         <v>12</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>36</v>
@@ -3730,7 +3730,7 @@
         <v>18</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="U14" s="2" t="n">
         <v>37</v>
@@ -4032,7 +4032,7 @@
         <v>9</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U18" s="2" t="n">
         <v>36</v>
@@ -4111,7 +4111,7 @@
         <v>14</v>
       </c>
       <c r="T19" s="2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="U19" s="2" t="n">
         <v>36</v>
@@ -4579,7 +4579,7 @@
         <v>16</v>
       </c>
       <c r="T25" s="2" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="U25" s="2" t="n">
         <v>47</v>
@@ -5234,7 +5234,7 @@
         <v>11</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>8</v>
@@ -5253,26 +5253,26 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>SteelAxe</t>
+          <t>IronAxe</t>
         </is>
       </c>
       <c r="N35" s="3" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T35" s="3" t="n"/>
       <c r="U35" s="3" t="n">
@@ -52863,7 +52863,7 @@
         <v>15</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="U2" s="2" t="n">
         <v>40</v>
@@ -52942,7 +52942,7 @@
         <v>9</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="U3" s="2" t="n">
         <v>40</v>
@@ -53098,7 +53098,7 @@
         <v>16</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="U5" s="2" t="n">
         <v>35</v>
@@ -53177,7 +53177,7 @@
         <v>16</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="U6" s="2" t="n">
         <v>35</v>
@@ -53256,7 +53256,7 @@
         <v>16</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="U7" s="2" t="n">
         <v>35</v>
@@ -53637,7 +53637,7 @@
         <v>12</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>36</v>
@@ -53716,7 +53716,7 @@
         <v>12</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="U13" s="2" t="n">
         <v>36</v>
@@ -53941,7 +53941,7 @@
         <v>8</v>
       </c>
       <c r="T16" s="2" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="U16" s="2" t="n">
         <v>42</v>
@@ -54411,7 +54411,7 @@
         <v>15</v>
       </c>
       <c r="T22" s="2" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="U22" s="2" t="n">
         <v>34</v>
@@ -54644,7 +54644,7 @@
         <v>16</v>
       </c>
       <c r="T25" s="2" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="U25" s="2" t="n">
         <v>47</v>
@@ -54800,7 +54800,7 @@
         <v>19</v>
       </c>
       <c r="T27" s="2" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="U27" s="2" t="n">
         <v>44</v>
@@ -55299,7 +55299,7 @@
         <v>13</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>9</v>
@@ -55318,26 +55318,26 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>SteelAxe</t>
+          <t>IronAxe</t>
         </is>
       </c>
       <c r="N35" s="3" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="T35" s="3" t="n"/>
       <c r="U35" s="3" t="n">

--- a/unit_stats.xlsx
+++ b/unit_stats.xlsx
@@ -21640,7 +21640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y21"/>
+  <dimension ref="A1:Y22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -22116,17 +22116,17 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>0x83_CivBoy</t>
+          <t>0x83_CivGirl</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
         <v>10</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
@@ -22141,13 +22141,13 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>1</v>
@@ -22167,29 +22167,29 @@
         <v>0</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T6" s="3" t="n"/>
       <c r="U6" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>6</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7"/>
@@ -23297,6 +23297,85 @@
       </c>
       <c r="Y21" s="4" t="n">
         <v>26</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>0x82_MageKnight_F</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="K22" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="O22" s="4" t="n">
+        <v>137</v>
+      </c>
+      <c r="P22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="R22" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="S22" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="T22" s="4" t="n"/>
+      <c r="U22" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="V22" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="W22" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="X22" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="Y22" s="4" t="n">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -23310,7 +23389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y21"/>
+  <dimension ref="A1:Y22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23786,38 +23865,38 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>0x83_CivBoy</t>
+          <t>0x83_CivGirl</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
         <v>10</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="J6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>1</v>
@@ -23837,20 +23916,20 @@
         <v>0</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T6" s="3" t="n"/>
       <c r="U6" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W6" s="3" t="n">
         <v>7</v>
@@ -23859,7 +23938,7 @@
         <v>5</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7"/>
@@ -24967,6 +25046,85 @@
       </c>
       <c r="Y21" s="4" t="n">
         <v>23</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>0x82_MageKnight_F</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K22" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="O22" s="4" t="n">
+        <v>131</v>
+      </c>
+      <c r="P22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="R22" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="S22" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="T22" s="4" t="n"/>
+      <c r="U22" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="V22" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="W22" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="X22" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y22" s="4" t="n">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/unit_stats.xlsx
+++ b/unit_stats.xlsx
@@ -21640,7 +21640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y22"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21913,7 +21913,7 @@
         <v>9</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
@@ -23099,7 +23099,7 @@
         <v>8</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
@@ -23376,6 +23376,85 @@
       </c>
       <c r="Y22" s="4" t="n">
         <v>25</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>0x81_Druid</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="O23" s="4" t="n">
+        <v>133</v>
+      </c>
+      <c r="P23" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q23" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="R23" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="S23" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="T23" s="4" t="n"/>
+      <c r="U23" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="V23" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="W23" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="X23" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="Y23" s="4" t="n">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -23389,7 +23468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y22"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23662,7 +23741,7 @@
         <v>9</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
@@ -24848,7 +24927,7 @@
         <v>8</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
@@ -25125,6 +25204,85 @@
       </c>
       <c r="Y22" s="4" t="n">
         <v>22</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>0x81_Druid</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="O23" s="4" t="n">
+        <v>128</v>
+      </c>
+      <c r="P23" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q23" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="R23" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="S23" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="T23" s="4" t="n"/>
+      <c r="U23" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="V23" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="W23" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="X23" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="Y23" s="4" t="n">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/unit_stats.xlsx
+++ b/unit_stats.xlsx
@@ -1716,7 +1716,7 @@
         <v>2</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>11</v>
@@ -1745,7 +1745,7 @@
         <v>17</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>0</v>
@@ -1875,7 +1875,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G20" s="4" t="n">
         <v>10</v>
@@ -1904,7 +1904,7 @@
         <v>18</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="P20" s="4" t="n">
         <v>0</v>
@@ -7805,7 +7805,7 @@
         <v>0</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G71" s="4" t="n">
         <v>10</v>
@@ -7834,7 +7834,7 @@
         <v>20</v>
       </c>
       <c r="O71" s="4" t="n">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="P71" s="4" t="n">
         <v>0</v>
@@ -8832,7 +8832,7 @@
         <v>0</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G84" s="4" t="n">
         <v>9</v>
@@ -8861,7 +8861,7 @@
         <v>28</v>
       </c>
       <c r="O84" s="4" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="P84" s="4" t="n">
         <v>0</v>
@@ -10992,10 +10992,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y69"/>
+  <dimension ref="A1:Y70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
@@ -11210,7 +11210,7 @@
         <v>15</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="U2" s="2" t="n">
         <v>40</v>
@@ -11289,7 +11289,7 @@
         <v>9</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U3" s="2" t="n">
         <v>40</v>
@@ -11523,9 +11523,7 @@
       <c r="S6" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="T6" s="2" t="n">
-        <v>4</v>
-      </c>
+      <c r="T6" s="2" t="n"/>
       <c r="U6" s="2" t="n">
         <v>38</v>
       </c>
@@ -11603,7 +11601,7 @@
         <v>17</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U7" s="2" t="n">
         <v>38</v>
@@ -11982,7 +11980,7 @@
         <v>13</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>39</v>
@@ -12060,7 +12058,9 @@
       <c r="S13" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="T13" s="2" t="n"/>
+      <c r="T13" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="U13" s="2" t="n">
         <v>39</v>
       </c>
@@ -12910,7 +12910,7 @@
         <v>18</v>
       </c>
       <c r="T24" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U24" s="2" t="n">
         <v>36</v>
@@ -13524,7 +13524,7 @@
         <v>15</v>
       </c>
       <c r="T32" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U32" s="2" t="n">
         <v>29</v>
@@ -14430,7 +14430,7 @@
         <v>0</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G46" s="4" t="n">
         <v>12</v>
@@ -14459,7 +14459,7 @@
         <v>25</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="P46" s="4" t="n">
         <v>0</v>
@@ -15001,7 +15001,7 @@
         <v>10</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
@@ -15046,52 +15046,52 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Muscle_Warrior</t>
+          <t>GuardUnit_PegasusKnight</t>
         </is>
       </c>
       <c r="B54" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C54" s="4" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H54" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="J54" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K54" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="I54" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="J54" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="K54" s="4" t="n">
-        <v>23</v>
-      </c>
       <c r="L54" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M54" s="4" t="inlineStr">
         <is>
-          <t>SteelBow</t>
+          <t>SteelLance</t>
         </is>
       </c>
       <c r="N54" s="4" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="P54" s="4" t="n">
         <v>0</v>
@@ -15100,26 +15100,26 @@
         <v>8</v>
       </c>
       <c r="R54" s="4" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S54" s="4" t="n">
         <v>12</v>
       </c>
       <c r="T54" s="4" t="n"/>
       <c r="U54" s="4" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="V54" s="4" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="W54" s="4" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="X54" s="4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="Y54" s="4" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55">
@@ -15163,11 +15163,11 @@
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>SilverAxe</t>
+          <t>SteelBow</t>
         </is>
       </c>
       <c r="N55" s="4" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="O55" s="4" t="n">
         <v>104</v>
@@ -15204,93 +15204,93 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>GuardUnit_Soldier</t>
+          <t>Muscle_Warrior</t>
         </is>
       </c>
       <c r="B56" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C56" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="D56" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J56" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="K56" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="L56" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M56" s="4" t="inlineStr">
+        <is>
+          <t>SilverAxe</t>
+        </is>
+      </c>
+      <c r="N56" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="D56" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="E56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G56" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="H56" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I56" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J56" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K56" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L56" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M56" s="4" t="inlineStr">
-        <is>
-          <t>IronLance</t>
-        </is>
-      </c>
-      <c r="N56" s="4" t="n">
-        <v>25</v>
-      </c>
       <c r="O56" s="4" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="P56" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q56" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R56" s="4" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="S56" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T56" s="4" t="n"/>
       <c r="U56" s="4" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="V56" s="4" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="W56" s="4" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="X56" s="4" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="Y56" s="4" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>GuardUnit_Fighter</t>
+          <t>GuardUnit_Soldier</t>
         </is>
       </c>
       <c r="B57" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C57" s="4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D57" s="4" t="n">
         <v>17</v>
@@ -15299,143 +15299,143 @@
         <v>0</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L57" s="4" t="n">
         <v>2</v>
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>IronAxe</t>
+          <t>IronLance</t>
         </is>
       </c>
       <c r="N57" s="4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="P57" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q57" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R57" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="S57" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T57" s="4" t="n"/>
       <c r="U57" s="4" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="V57" s="4" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="W57" s="4" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="X57" s="4" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="Y57" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Skull_Fighter</t>
+          <t>GuardUnit_Fighter</t>
         </is>
       </c>
       <c r="B58" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C58" s="4" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F58" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G58" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="G58" s="4" t="n">
-        <v>7</v>
-      </c>
       <c r="H58" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>2</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M58" s="4" t="inlineStr">
         <is>
-          <t>IronLance</t>
+          <t>IronAxe</t>
         </is>
       </c>
       <c r="N58" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="O58" s="4" t="n">
+        <v>109</v>
+      </c>
+      <c r="P58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="R58" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="O58" s="4" t="n">
-        <v>110</v>
-      </c>
-      <c r="P58" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="R58" s="4" t="n">
-        <v>16</v>
-      </c>
       <c r="S58" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T58" s="4" t="n"/>
       <c r="U58" s="4" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="V58" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="W58" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="W58" s="4" t="n">
-        <v>31</v>
-      </c>
       <c r="X58" s="4" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Y58" s="4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="59">
@@ -15479,26 +15479,26 @@
       </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
-          <t>SteelBlade</t>
+          <t>IronLance</t>
         </is>
       </c>
       <c r="N59" s="4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="P59" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Q59" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R59" s="4" t="n">
         <v>16</v>
       </c>
       <c r="S59" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T59" s="4" t="n"/>
       <c r="U59" s="4" t="n">
@@ -15520,80 +15520,80 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>0x82_Brigand</t>
+          <t>Skull_Fighter</t>
         </is>
       </c>
       <c r="B60" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G60" s="4" t="n">
         <v>7</v>
       </c>
       <c r="H60" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I60" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J60" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K60" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L60" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="L60" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="M60" s="4" t="inlineStr">
         <is>
-          <t>IronLance</t>
+          <t>SteelBlade</t>
         </is>
       </c>
       <c r="N60" s="4" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="P60" s="4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Q60" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R60" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="S60" s="4" t="n">
         <v>7</v>
-      </c>
-      <c r="R60" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="S60" s="4" t="n">
-        <v>11</v>
       </c>
       <c r="T60" s="4" t="n"/>
       <c r="U60" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="V60" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="W60" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="V60" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="W60" s="4" t="n">
+      <c r="X60" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="X60" s="4" t="n">
-        <v>15</v>
-      </c>
       <c r="Y60" s="4" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="61">
@@ -15637,26 +15637,26 @@
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>SteelBlade</t>
+          <t>IronLance</t>
         </is>
       </c>
       <c r="N61" s="4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="P61" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Q61" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R61" s="4" t="n">
         <v>14</v>
       </c>
       <c r="S61" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T61" s="4" t="n"/>
       <c r="U61" s="4" t="n">
@@ -15678,29 +15678,29 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>0x83_Mercenary</t>
+          <t>0x82_Brigand</t>
         </is>
       </c>
       <c r="B62" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C62" s="4" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E62" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I62" s="4" t="n">
         <v>0</v>
@@ -15709,49 +15709,49 @@
         <v>0</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L62" s="4" t="n">
         <v>2</v>
       </c>
       <c r="M62" s="4" t="inlineStr">
         <is>
-          <t>IronLance</t>
+          <t>SteelBlade</t>
         </is>
       </c>
       <c r="N62" s="4" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="P62" s="4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Q62" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R62" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="S62" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T62" s="4" t="n"/>
       <c r="U62" s="4" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="V62" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="W62" s="4" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="X62" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Y62" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63">
@@ -15773,7 +15773,7 @@
         <v>0</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G63" s="4" t="n">
         <v>8</v>
@@ -15795,26 +15795,26 @@
       </c>
       <c r="M63" s="4" t="inlineStr">
         <is>
-          <t>SteelBlade</t>
+          <t>IronLance</t>
         </is>
       </c>
       <c r="N63" s="4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O63" s="4" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P63" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Q63" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="R63" s="4" t="n">
         <v>16</v>
       </c>
       <c r="S63" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T63" s="4" t="n"/>
       <c r="U63" s="4" t="n">
@@ -15836,17 +15836,17 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>0x84_Fighter</t>
+          <t>0x83_Mercenary</t>
         </is>
       </c>
       <c r="B64" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E64" s="4" t="n">
         <v>0</v>
@@ -15855,61 +15855,61 @@
         <v>7</v>
       </c>
       <c r="G64" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H64" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H64" s="4" t="n">
-        <v>4</v>
-      </c>
       <c r="I64" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L64" s="4" t="n">
         <v>2</v>
       </c>
       <c r="M64" s="4" t="inlineStr">
         <is>
-          <t>IronLance</t>
+          <t>SteelBlade</t>
         </is>
       </c>
       <c r="N64" s="4" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="P64" s="4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Q64" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R64" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="S64" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T64" s="4" t="n"/>
       <c r="U64" s="4" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="V64" s="4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="W64" s="4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="X64" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="Y64" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="65">
@@ -15953,26 +15953,26 @@
       </c>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>SteelBlade</t>
+          <t>IronLance</t>
         </is>
       </c>
       <c r="N65" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="O65" s="4" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="P65" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Q65" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R65" s="4" t="n">
         <v>10</v>
       </c>
       <c r="S65" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T65" s="4" t="n"/>
       <c r="U65" s="4" t="n">
@@ -15994,80 +15994,80 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>0x84_CivMan</t>
+          <t>0x84_Fighter</t>
         </is>
       </c>
       <c r="B66" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E66" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L66" s="4" t="n">
         <v>2</v>
       </c>
       <c r="M66" s="4" t="inlineStr">
         <is>
-          <t>IronLance</t>
+          <t>SteelBlade</t>
         </is>
       </c>
       <c r="N66" s="4" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="P66" s="4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Q66" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="R66" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S66" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T66" s="4" t="n"/>
       <c r="U66" s="4" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="V66" s="4" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="W66" s="4" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="X66" s="4" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="Y66" s="4" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="67">
@@ -16111,26 +16111,26 @@
       </c>
       <c r="M67" s="4" t="inlineStr">
         <is>
-          <t>SteelBlade</t>
+          <t>IronLance</t>
         </is>
       </c>
       <c r="N67" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O67" s="4" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="P67" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Q67" s="4" t="n">
-        <v>-10</v>
+        <v>-2</v>
       </c>
       <c r="R67" s="4" t="n">
         <v>0</v>
       </c>
       <c r="S67" s="4" t="n">
-        <v>-6</v>
+        <v>2</v>
       </c>
       <c r="T67" s="4" t="n"/>
       <c r="U67" s="4" t="n">
@@ -16152,80 +16152,80 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>0x84_Mercenary</t>
+          <t>0x84_CivMan</t>
         </is>
       </c>
       <c r="B68" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E68" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L68" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M68" s="4" t="inlineStr">
         <is>
-          <t>IronLance</t>
+          <t>SteelBlade</t>
         </is>
       </c>
       <c r="N68" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="O68" s="4" t="n">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="P68" s="4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Q68" s="4" t="n">
-        <v>8</v>
+        <v>-10</v>
       </c>
       <c r="R68" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="S68" s="4" t="n">
-        <v>12</v>
+        <v>-6</v>
       </c>
       <c r="T68" s="4" t="n"/>
       <c r="U68" s="4" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="V68" s="4" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="W68" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="X68" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Y68" s="4" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69">
@@ -16247,7 +16247,7 @@
         <v>0</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G69" s="4" t="n">
         <v>8</v>
@@ -16269,26 +16269,26 @@
       </c>
       <c r="M69" s="4" t="inlineStr">
         <is>
-          <t>SteelBlade</t>
+          <t>IronLance</t>
         </is>
       </c>
       <c r="N69" s="4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O69" s="4" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P69" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Q69" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="R69" s="4" t="n">
         <v>16</v>
       </c>
       <c r="S69" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T69" s="4" t="n"/>
       <c r="U69" s="4" t="n">
@@ -16304,6 +16304,85 @@
         <v>12</v>
       </c>
       <c r="Y69" s="4" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>0x84_Mercenary</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C70" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="D70" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H70" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L70" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M70" s="4" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="N70" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="O70" s="4" t="n">
+        <v>99</v>
+      </c>
+      <c r="P70" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q70" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R70" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="S70" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="T70" s="4" t="n"/>
+      <c r="U70" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="V70" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="W70" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="X70" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y70" s="4" t="n">
         <v>17</v>
       </c>
     </row>
@@ -16318,10 +16397,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y69"/>
+  <dimension ref="A1:Y70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
@@ -16536,7 +16615,7 @@
         <v>15</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="U2" s="2" t="n">
         <v>40</v>
@@ -17073,7 +17152,7 @@
         <v>9</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U9" s="2" t="n">
         <v>50</v>
@@ -17151,7 +17230,9 @@
       <c r="S10" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="T10" s="2" t="n"/>
+      <c r="T10" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="U10" s="2" t="n">
         <v>50</v>
       </c>
@@ -17308,7 +17389,7 @@
         <v>13</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>39</v>
@@ -17386,7 +17467,9 @@
       <c r="S13" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="T13" s="2" t="n"/>
+      <c r="T13" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="U13" s="2" t="n">
         <v>39</v>
       </c>
@@ -17610,7 +17693,7 @@
         <v>8</v>
       </c>
       <c r="T16" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="U16" s="2" t="n">
         <v>44</v>
@@ -18846,7 +18929,7 @@
         <v>15</v>
       </c>
       <c r="T32" s="2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="U32" s="2" t="n">
         <v>29</v>
@@ -19752,7 +19835,7 @@
         <v>0</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G46" s="4" t="n">
         <v>10</v>
@@ -19781,7 +19864,7 @@
         <v>22</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="P46" s="4" t="n">
         <v>0</v>
@@ -20323,7 +20406,7 @@
         <v>10</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
@@ -20368,80 +20451,80 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Muscle_Warrior</t>
+          <t>GuardUnit_PegasusKnight</t>
         </is>
       </c>
       <c r="B54" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E54" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C54" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="D54" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="E54" s="4" t="n">
-        <v>6</v>
-      </c>
       <c r="F54" s="4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H54" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J54" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K54" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="I54" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="J54" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="K54" s="4" t="n">
-        <v>23</v>
-      </c>
       <c r="L54" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M54" s="4" t="inlineStr">
         <is>
-          <t>SteelBow</t>
+          <t>SteelLance</t>
         </is>
       </c>
       <c r="N54" s="4" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="P54" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q54" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R54" s="4" t="n">
         <v>28</v>
       </c>
       <c r="S54" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T54" s="4" t="n"/>
       <c r="U54" s="4" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="V54" s="4" t="n">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="W54" s="4" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="X54" s="4" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="Y54" s="4" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="55">
@@ -20485,11 +20568,11 @@
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>SilverAxe</t>
+          <t>SteelBow</t>
         </is>
       </c>
       <c r="N55" s="4" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="O55" s="4" t="n">
         <v>104</v>
@@ -20526,93 +20609,93 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>GuardUnit_Soldier</t>
+          <t>Muscle_Warrior</t>
         </is>
       </c>
       <c r="B56" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G56" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H56" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H56" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="I56" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J56" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="K56" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="L56" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J56" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K56" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L56" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="M56" s="4" t="inlineStr">
         <is>
-          <t>IronLance</t>
+          <t>SilverAxe</t>
         </is>
       </c>
       <c r="N56" s="4" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="O56" s="4" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="P56" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q56" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R56" s="4" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="S56" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T56" s="4" t="n"/>
       <c r="U56" s="4" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="V56" s="4" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="W56" s="4" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="X56" s="4" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Y56" s="4" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>GuardUnit_Fighter</t>
+          <t>GuardUnit_Soldier</t>
         </is>
       </c>
       <c r="B57" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C57" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D57" s="4" t="n">
         <v>14</v>
@@ -20621,83 +20704,83 @@
         <v>0</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L57" s="4" t="n">
         <v>2</v>
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>IronAxe</t>
+          <t>IronLance</t>
         </is>
       </c>
       <c r="N57" s="4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="P57" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q57" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R57" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="S57" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T57" s="4" t="n"/>
       <c r="U57" s="4" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="V57" s="4" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="W57" s="4" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="X57" s="4" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="Y57" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Skull_Fighter</t>
+          <t>GuardUnit_Fighter</t>
         </is>
       </c>
       <c r="B58" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C58" s="4" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F58" s="4" t="n">
         <v>9</v>
@@ -20706,30 +20789,30 @@
         <v>7</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I58" s="4" t="n">
         <v>7</v>
       </c>
       <c r="J58" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="L58" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K58" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="L58" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="M58" s="4" t="inlineStr">
         <is>
-          <t>IronLance</t>
+          <t>IronAxe</t>
         </is>
       </c>
       <c r="N58" s="4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="P58" s="4" t="n">
         <v>0</v>
@@ -20738,23 +20821,23 @@
         <v>7</v>
       </c>
       <c r="R58" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S58" s="4" t="n">
         <v>11</v>
       </c>
       <c r="T58" s="4" t="n"/>
       <c r="U58" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="V58" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="V58" s="4" t="n">
-        <v>39</v>
-      </c>
       <c r="W58" s="4" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="X58" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y58" s="4" t="n">
         <v>22</v>
@@ -20801,26 +20884,26 @@
       </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
-          <t>SteelBlade</t>
+          <t>IronLance</t>
         </is>
       </c>
       <c r="N59" s="4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="P59" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Q59" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R59" s="4" t="n">
         <v>16</v>
       </c>
       <c r="S59" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T59" s="4" t="n"/>
       <c r="U59" s="4" t="n">
@@ -20842,80 +20925,80 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>0x82_Brigand</t>
+          <t>Skull_Fighter</t>
         </is>
       </c>
       <c r="B60" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G60" s="4" t="n">
         <v>7</v>
       </c>
       <c r="H60" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I60" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J60" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K60" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L60" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="L60" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="M60" s="4" t="inlineStr">
         <is>
-          <t>IronLance</t>
+          <t>SteelBlade</t>
         </is>
       </c>
       <c r="N60" s="4" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="P60" s="4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Q60" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R60" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="S60" s="4" t="n">
         <v>7</v>
-      </c>
-      <c r="R60" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="S60" s="4" t="n">
-        <v>11</v>
       </c>
       <c r="T60" s="4" t="n"/>
       <c r="U60" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="V60" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="W60" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="V60" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="W60" s="4" t="n">
+      <c r="X60" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="X60" s="4" t="n">
-        <v>15</v>
-      </c>
       <c r="Y60" s="4" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="61">
@@ -20959,26 +21042,26 @@
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>SteelBlade</t>
+          <t>IronLance</t>
         </is>
       </c>
       <c r="N61" s="4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="P61" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Q61" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R61" s="4" t="n">
         <v>14</v>
       </c>
       <c r="S61" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T61" s="4" t="n"/>
       <c r="U61" s="4" t="n">
@@ -21000,29 +21083,29 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>0x83_Mercenary</t>
+          <t>0x82_Brigand</t>
         </is>
       </c>
       <c r="B62" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C62" s="4" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E62" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I62" s="4" t="n">
         <v>0</v>
@@ -21031,49 +21114,49 @@
         <v>0</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L62" s="4" t="n">
         <v>2</v>
       </c>
       <c r="M62" s="4" t="inlineStr">
         <is>
-          <t>IronLance</t>
+          <t>SteelBlade</t>
         </is>
       </c>
       <c r="N62" s="4" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="P62" s="4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Q62" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R62" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="S62" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T62" s="4" t="n"/>
       <c r="U62" s="4" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="V62" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="W62" s="4" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="X62" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Y62" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63">
@@ -21095,7 +21178,7 @@
         <v>0</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G63" s="4" t="n">
         <v>8</v>
@@ -21117,26 +21200,26 @@
       </c>
       <c r="M63" s="4" t="inlineStr">
         <is>
-          <t>SteelBlade</t>
+          <t>IronLance</t>
         </is>
       </c>
       <c r="N63" s="4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O63" s="4" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P63" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Q63" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="R63" s="4" t="n">
         <v>16</v>
       </c>
       <c r="S63" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T63" s="4" t="n"/>
       <c r="U63" s="4" t="n">
@@ -21158,17 +21241,17 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>0x84_Fighter</t>
+          <t>0x83_Mercenary</t>
         </is>
       </c>
       <c r="B64" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E64" s="4" t="n">
         <v>0</v>
@@ -21177,61 +21260,61 @@
         <v>7</v>
       </c>
       <c r="G64" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H64" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H64" s="4" t="n">
-        <v>4</v>
-      </c>
       <c r="I64" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L64" s="4" t="n">
         <v>2</v>
       </c>
       <c r="M64" s="4" t="inlineStr">
         <is>
-          <t>IronLance</t>
+          <t>SteelBlade</t>
         </is>
       </c>
       <c r="N64" s="4" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="P64" s="4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Q64" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R64" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="S64" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T64" s="4" t="n"/>
       <c r="U64" s="4" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="V64" s="4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="W64" s="4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="X64" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="Y64" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="65">
@@ -21275,26 +21358,26 @@
       </c>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>SteelBlade</t>
+          <t>IronLance</t>
         </is>
       </c>
       <c r="N65" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="O65" s="4" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="P65" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Q65" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R65" s="4" t="n">
         <v>10</v>
       </c>
       <c r="S65" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T65" s="4" t="n"/>
       <c r="U65" s="4" t="n">
@@ -21316,80 +21399,80 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>0x84_CivMan</t>
+          <t>0x84_Fighter</t>
         </is>
       </c>
       <c r="B66" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E66" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L66" s="4" t="n">
         <v>2</v>
       </c>
       <c r="M66" s="4" t="inlineStr">
         <is>
-          <t>IronLance</t>
+          <t>SteelBlade</t>
         </is>
       </c>
       <c r="N66" s="4" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="P66" s="4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Q66" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="R66" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S66" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T66" s="4" t="n"/>
       <c r="U66" s="4" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="V66" s="4" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="W66" s="4" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="X66" s="4" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="Y66" s="4" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="67">
@@ -21433,26 +21516,26 @@
       </c>
       <c r="M67" s="4" t="inlineStr">
         <is>
-          <t>SteelBlade</t>
+          <t>IronLance</t>
         </is>
       </c>
       <c r="N67" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O67" s="4" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="P67" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Q67" s="4" t="n">
-        <v>-10</v>
+        <v>-2</v>
       </c>
       <c r="R67" s="4" t="n">
         <v>0</v>
       </c>
       <c r="S67" s="4" t="n">
-        <v>-6</v>
+        <v>2</v>
       </c>
       <c r="T67" s="4" t="n"/>
       <c r="U67" s="4" t="n">
@@ -21474,80 +21557,80 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>0x84_Mercenary</t>
+          <t>0x84_CivMan</t>
         </is>
       </c>
       <c r="B68" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E68" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L68" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M68" s="4" t="inlineStr">
         <is>
-          <t>IronLance</t>
+          <t>SteelBlade</t>
         </is>
       </c>
       <c r="N68" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="O68" s="4" t="n">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="P68" s="4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Q68" s="4" t="n">
-        <v>8</v>
+        <v>-10</v>
       </c>
       <c r="R68" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="S68" s="4" t="n">
-        <v>12</v>
+        <v>-6</v>
       </c>
       <c r="T68" s="4" t="n"/>
       <c r="U68" s="4" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="V68" s="4" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="W68" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="X68" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Y68" s="4" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69">
@@ -21569,7 +21652,7 @@
         <v>0</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G69" s="4" t="n">
         <v>8</v>
@@ -21591,26 +21674,26 @@
       </c>
       <c r="M69" s="4" t="inlineStr">
         <is>
-          <t>SteelBlade</t>
+          <t>IronLance</t>
         </is>
       </c>
       <c r="N69" s="4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O69" s="4" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P69" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Q69" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="R69" s="4" t="n">
         <v>16</v>
       </c>
       <c r="S69" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T69" s="4" t="n"/>
       <c r="U69" s="4" t="n">
@@ -21626,6 +21709,85 @@
         <v>12</v>
       </c>
       <c r="Y69" s="4" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>0x84_Mercenary</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C70" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="D70" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H70" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L70" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M70" s="4" t="inlineStr">
+        <is>
+          <t>SteelBlade</t>
+        </is>
+      </c>
+      <c r="N70" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="O70" s="4" t="n">
+        <v>99</v>
+      </c>
+      <c r="P70" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q70" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R70" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="S70" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="T70" s="4" t="n"/>
+      <c r="U70" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="V70" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="W70" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="X70" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y70" s="4" t="n">
         <v>17</v>
       </c>
     </row>
@@ -22923,7 +23085,7 @@
         <v>3</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G17" s="4" t="n">
         <v>17</v>
@@ -22952,7 +23114,7 @@
         <v>27</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="P17" s="4" t="n">
         <v>0</v>
@@ -23002,7 +23164,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G18" s="4" t="n">
         <v>13</v>
@@ -23031,7 +23193,7 @@
         <v>25</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="P18" s="4" t="n">
         <v>0</v>
@@ -23160,7 +23322,7 @@
         <v>2</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G20" s="4" t="n">
         <v>22</v>
@@ -23189,7 +23351,7 @@
         <v>25</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="P20" s="4" t="n">
         <v>0</v>
@@ -24751,7 +24913,7 @@
         <v>3</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G17" s="4" t="n">
         <v>15</v>
@@ -24780,7 +24942,7 @@
         <v>24</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="P17" s="4" t="n">
         <v>0</v>
@@ -24830,7 +24992,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G18" s="4" t="n">
         <v>11</v>
@@ -24859,7 +25021,7 @@
         <v>23</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="P18" s="4" t="n">
         <v>0</v>
@@ -24988,7 +25150,7 @@
         <v>2</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G20" s="4" t="n">
         <v>22</v>
@@ -25017,7 +25179,7 @@
         <v>25</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="P20" s="4" t="n">
         <v>0</v>
@@ -26545,7 +26707,7 @@
         <v>2</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>11</v>
@@ -26574,7 +26736,7 @@
         <v>17</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>0</v>
@@ -26704,7 +26866,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G20" s="4" t="n">
         <v>8</v>
@@ -26733,7 +26895,7 @@
         <v>15</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="P20" s="4" t="n">
         <v>0</v>
@@ -29956,7 +30118,7 @@
         <v>0</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G35" s="4" t="n">
         <v>10</v>
@@ -29985,7 +30147,7 @@
         <v>18</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="P35" s="4" t="n">
         <v>0</v>
@@ -33131,7 +33293,7 @@
         <v>0</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G35" s="4" t="n">
         <v>8</v>
@@ -33160,7 +33322,7 @@
         <v>16</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="P35" s="4" t="n">
         <v>0</v>
@@ -36821,7 +36983,7 @@
         <v>0</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G42" s="4" t="n">
         <v>10</v>
@@ -36850,7 +37012,7 @@
         <v>26</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="P42" s="4" t="n">
         <v>30</v>
@@ -40732,7 +40894,7 @@
         <v>0</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G42" s="4" t="n">
         <v>9</v>
@@ -40761,7 +40923,7 @@
         <v>24</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="P42" s="4" t="n">
         <v>30</v>
@@ -45617,7 +45779,7 @@
         <v>0</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G58" s="4" t="n">
         <v>11</v>
@@ -45646,7 +45808,7 @@
         <v>27</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="P58" s="4" t="n">
         <v>35</v>
@@ -51310,7 +51472,7 @@
         <v>0</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G58" s="4" t="n">
         <v>9</v>
@@ -51339,7 +51501,7 @@
         <v>25</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="P58" s="4" t="n">
         <v>35</v>
@@ -58186,7 +58348,7 @@
         <v>0</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G71" s="4" t="n">
         <v>12</v>
@@ -58215,7 +58377,7 @@
         <v>23</v>
       </c>
       <c r="O71" s="4" t="n">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="P71" s="4" t="n">
         <v>0</v>
@@ -59213,7 +59375,7 @@
         <v>0</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G84" s="4" t="n">
         <v>11</v>
@@ -59242,7 +59404,7 @@
         <v>30</v>
       </c>
       <c r="O84" s="4" t="n">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="P84" s="4" t="n">
         <v>0</v>

--- a/unit_stats.xlsx
+++ b/unit_stats.xlsx
@@ -677,7 +677,7 @@
         <v>15</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="U2" s="2" t="n">
         <v>40</v>
@@ -756,7 +756,7 @@
         <v>9</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U3" s="2" t="n">
         <v>40</v>
@@ -914,7 +914,7 @@
         <v>14</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U5" s="2" t="n">
         <v>32</v>
@@ -993,7 +993,7 @@
         <v>14</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U6" s="2" t="n">
         <v>32</v>
@@ -1071,9 +1071,7 @@
       <c r="S7" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="T7" s="2" t="n">
-        <v>4</v>
-      </c>
+      <c r="T7" s="2" t="n"/>
       <c r="U7" s="2" t="n">
         <v>32</v>
       </c>
@@ -1707,7 +1705,7 @@
         <v>10</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>11</v>
@@ -1722,7 +1720,7 @@
         <v>11</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>0</v>
@@ -1761,19 +1759,19 @@
       </c>
       <c r="T17" s="3" t="n"/>
       <c r="U17" s="3" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18"/>
@@ -3825,7 +3823,7 @@
         <v>6</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>12</v>
@@ -3840,7 +3838,7 @@
         <v>4</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I16" s="2" t="n">
         <v>1</v>
@@ -3879,19 +3877,19 @@
         <v>46</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="W16" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="X16" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y16" s="2" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -3904,7 +3902,7 @@
         <v>6</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>12</v>
@@ -3919,7 +3917,7 @@
         <v>4</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I17" s="2" t="n">
         <v>1</v>
@@ -3956,19 +3954,19 @@
       </c>
       <c r="T17" s="2" t="n"/>
       <c r="U17" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="W17" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="X17" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y17" s="2" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -4247,17 +4245,17 @@
       <c r="L21" s="2" t="n"/>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Secula</t>
         </is>
       </c>
       <c r="N21" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>135</v>
+        <v>105</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="Q21" s="2" t="n">
         <v>14</v>
@@ -7498,7 +7496,7 @@
         <v>10</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>0</v>
@@ -7534,16 +7532,16 @@
       </c>
       <c r="T67" s="4" t="n"/>
       <c r="U67" s="4" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V67" s="4" t="n">
         <v>48</v>
       </c>
       <c r="W67" s="4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="X67" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y67" s="4" t="n">
         <v>29</v>
@@ -12233,7 +12231,7 @@
         <v>6</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>13</v>
@@ -12248,7 +12246,7 @@
         <v>4</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I16" s="2" t="n">
         <v>1</v>
@@ -12287,19 +12285,19 @@
         <v>12</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="W16" s="2" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="X16" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Y16" s="2" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
@@ -12312,7 +12310,7 @@
         <v>6</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>13</v>
@@ -12327,7 +12325,7 @@
         <v>4</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I17" s="2" t="n">
         <v>1</v>
@@ -12364,19 +12362,19 @@
       </c>
       <c r="T17" s="2" t="n"/>
       <c r="U17" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="W17" s="2" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="X17" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Y17" s="2" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -12655,17 +12653,17 @@
       <c r="L21" s="2" t="n"/>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Secula</t>
         </is>
       </c>
       <c r="N21" s="2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>138</v>
+        <v>108</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="Q21" s="2" t="n">
         <v>15</v>
@@ -17642,7 +17640,7 @@
         <v>6</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>13</v>
@@ -17657,7 +17655,7 @@
         <v>4</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I16" s="2" t="n">
         <v>1</v>
@@ -17696,19 +17694,19 @@
         <v>12</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="W16" s="2" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="X16" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Y16" s="2" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
@@ -17721,7 +17719,7 @@
         <v>6</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>13</v>
@@ -17736,7 +17734,7 @@
         <v>4</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I17" s="2" t="n">
         <v>1</v>
@@ -17773,19 +17771,19 @@
       </c>
       <c r="T17" s="2" t="n"/>
       <c r="U17" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="W17" s="2" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="X17" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Y17" s="2" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -18062,17 +18060,17 @@
       <c r="L21" s="2" t="n"/>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Secula</t>
         </is>
       </c>
       <c r="N21" s="2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>138</v>
+        <v>108</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="Q21" s="2" t="n">
         <v>15</v>
@@ -22629,7 +22627,7 @@
         <v>11</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
@@ -23182,7 +23180,7 @@
         <v>10</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
@@ -24457,7 +24455,7 @@
         <v>11</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
@@ -25010,7 +25008,7 @@
         <v>10</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
@@ -26211,7 +26209,7 @@
         <v>7</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U9" s="2" t="n">
         <v>42</v>
@@ -26367,7 +26365,7 @@
         <v>10</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="U11" s="2" t="n">
         <v>42</v>
@@ -26698,7 +26696,7 @@
         <v>10</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>11</v>
@@ -26713,7 +26711,7 @@
         <v>11</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>0</v>
@@ -26752,19 +26750,19 @@
       </c>
       <c r="T17" s="3" t="n"/>
       <c r="U17" s="3" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18"/>
@@ -27787,7 +27785,7 @@
         <v>15</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="U2" s="2" t="n">
         <v>40</v>
@@ -27866,7 +27864,7 @@
         <v>9</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="U3" s="2" t="n">
         <v>40</v>
@@ -28326,7 +28324,7 @@
         <v>7</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="U9" s="2" t="n">
         <v>43</v>
@@ -28482,7 +28480,7 @@
         <v>10</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="U11" s="2" t="n">
         <v>43</v>
@@ -28561,7 +28559,7 @@
         <v>11</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>32</v>
@@ -28719,7 +28717,7 @@
         <v>17</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="U14" s="2" t="n">
         <v>35</v>
@@ -28814,7 +28812,7 @@
         <v>6</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>12</v>
@@ -28829,7 +28827,7 @@
         <v>4</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I16" s="2" t="n">
         <v>1</v>
@@ -28865,22 +28863,22 @@
         <v>8</v>
       </c>
       <c r="T16" s="2" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="W16" s="2" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="X16" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y16" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -28893,7 +28891,7 @@
         <v>6</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>12</v>
@@ -28908,7 +28906,7 @@
         <v>4</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I17" s="2" t="n">
         <v>1</v>
@@ -28945,19 +28943,19 @@
       </c>
       <c r="T17" s="2" t="n"/>
       <c r="U17" s="2" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="W17" s="2" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="X17" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y17" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -29021,7 +29019,7 @@
         <v>8</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="U18" s="2" t="n">
         <v>35</v>
@@ -29100,7 +29098,7 @@
         <v>13</v>
       </c>
       <c r="T19" s="2" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="U19" s="2" t="n">
         <v>35</v>
@@ -29574,7 +29572,7 @@
         <v>10</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>0</v>
@@ -29610,16 +29608,16 @@
       </c>
       <c r="T28" s="4" t="n"/>
       <c r="U28" s="4" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V28" s="4" t="n">
         <v>49</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y28" s="4" t="n">
         <v>29</v>
@@ -31989,7 +31987,7 @@
         <v>6</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>12</v>
@@ -32004,7 +32002,7 @@
         <v>4</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I16" s="2" t="n">
         <v>1</v>
@@ -32043,19 +32041,19 @@
         <v>48</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="W16" s="2" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="X16" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y16" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -32068,7 +32066,7 @@
         <v>6</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>12</v>
@@ -32083,7 +32081,7 @@
         <v>4</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I17" s="2" t="n">
         <v>1</v>
@@ -32120,19 +32118,19 @@
       </c>
       <c r="T17" s="2" t="n"/>
       <c r="U17" s="2" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="W17" s="2" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="X17" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y17" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -32749,7 +32747,7 @@
         <v>10</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>0</v>
@@ -32785,16 +32783,16 @@
       </c>
       <c r="T28" s="4" t="n"/>
       <c r="U28" s="4" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V28" s="4" t="n">
         <v>45</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Y28" s="4" t="n">
         <v>27</v>
@@ -34135,7 +34133,7 @@
         <v>15</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="U2" s="2" t="n">
         <v>40</v>
@@ -34214,7 +34212,7 @@
         <v>9</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U3" s="2" t="n">
         <v>40</v>
@@ -34372,7 +34370,7 @@
         <v>15</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="U5" s="2" t="n">
         <v>33</v>
@@ -34530,7 +34528,7 @@
         <v>15</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="U7" s="2" t="n">
         <v>33</v>
@@ -35164,7 +35162,7 @@
         <v>6</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>12</v>
@@ -35179,7 +35177,7 @@
         <v>4</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I16" s="2" t="n">
         <v>1</v>
@@ -35218,19 +35216,19 @@
         <v>22</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="W16" s="2" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="X16" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y16" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -35243,7 +35241,7 @@
         <v>6</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>12</v>
@@ -35258,7 +35256,7 @@
         <v>4</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I17" s="2" t="n">
         <v>1</v>
@@ -35295,19 +35293,19 @@
       </c>
       <c r="T17" s="2" t="n"/>
       <c r="U17" s="2" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="W17" s="2" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="X17" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y17" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -35371,7 +35369,7 @@
         <v>8</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="U18" s="2" t="n">
         <v>35</v>
@@ -35450,7 +35448,7 @@
         <v>13</v>
       </c>
       <c r="T19" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="U19" s="2" t="n">
         <v>35</v>
@@ -35586,17 +35584,17 @@
       <c r="L21" s="2" t="n"/>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Secula</t>
         </is>
       </c>
       <c r="N21" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="Q21" s="2" t="n">
         <v>13</v>
@@ -37400,26 +37398,26 @@
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="N47" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="P47" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q47" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R47" s="4" t="n">
         <v>17</v>
       </c>
       <c r="S47" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T47" s="4" t="n"/>
       <c r="U47" s="4" t="n">
@@ -39075,7 +39073,7 @@
         <v>6</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>12</v>
@@ -39090,7 +39088,7 @@
         <v>4</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I16" s="2" t="n">
         <v>1</v>
@@ -39129,19 +39127,19 @@
         <v>20</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="W16" s="2" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="X16" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y16" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -39154,7 +39152,7 @@
         <v>6</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>12</v>
@@ -39169,7 +39167,7 @@
         <v>4</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I17" s="2" t="n">
         <v>1</v>
@@ -39206,19 +39204,19 @@
       </c>
       <c r="T17" s="2" t="n"/>
       <c r="U17" s="2" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="W17" s="2" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="X17" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y17" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -39497,17 +39495,17 @@
       <c r="L21" s="2" t="n"/>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Secula</t>
         </is>
       </c>
       <c r="N21" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="Q21" s="2" t="n">
         <v>13</v>
@@ -41311,26 +41309,26 @@
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="N47" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>71</v>
+        <v>116</v>
       </c>
       <c r="P47" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q47" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R47" s="4" t="n">
         <v>14</v>
       </c>
       <c r="S47" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T47" s="4" t="n"/>
       <c r="U47" s="4" t="n">
@@ -41957,7 +41955,7 @@
         <v>15</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="U2" s="2" t="n">
         <v>40</v>
@@ -42194,7 +42192,7 @@
         <v>15</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="U5" s="2" t="n">
         <v>34</v>
@@ -42273,7 +42271,7 @@
         <v>15</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U6" s="2" t="n">
         <v>34</v>
@@ -42352,7 +42350,7 @@
         <v>15</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="U7" s="2" t="n">
         <v>34</v>
@@ -42498,7 +42496,7 @@
         <v>8</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U9" s="2" t="n">
         <v>46</v>
@@ -42654,7 +42652,7 @@
         <v>11</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="U11" s="2" t="n">
         <v>46</v>
@@ -42733,7 +42731,7 @@
         <v>12</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>35</v>
@@ -42812,7 +42810,7 @@
         <v>12</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="U13" s="2" t="n">
         <v>35</v>
@@ -42891,7 +42889,7 @@
         <v>18</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="U14" s="2" t="n">
         <v>36</v>
@@ -42986,7 +42984,7 @@
         <v>6</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>12</v>
@@ -43001,7 +42999,7 @@
         <v>4</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I16" s="2" t="n">
         <v>1</v>
@@ -43037,22 +43035,22 @@
         <v>8</v>
       </c>
       <c r="T16" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="U16" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="U16" s="2" t="n">
-        <v>41</v>
-      </c>
       <c r="V16" s="2" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="W16" s="2" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="X16" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y16" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -43065,7 +43063,7 @@
         <v>6</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>12</v>
@@ -43080,7 +43078,7 @@
         <v>4</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I17" s="2" t="n">
         <v>1</v>
@@ -43117,19 +43115,19 @@
       </c>
       <c r="T17" s="2" t="n"/>
       <c r="U17" s="2" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="W17" s="2" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="X17" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y17" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -43351,7 +43349,7 @@
         <v>17</v>
       </c>
       <c r="T20" s="2" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="U20" s="2" t="n">
         <v>31</v>
@@ -43408,17 +43406,17 @@
       <c r="L21" s="2" t="n"/>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Secula</t>
         </is>
       </c>
       <c r="N21" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="Q21" s="2" t="n">
         <v>13</v>
@@ -43507,7 +43505,7 @@
         <v>14</v>
       </c>
       <c r="T22" s="2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="U22" s="2" t="n">
         <v>33</v>
@@ -43740,7 +43738,7 @@
         <v>16</v>
       </c>
       <c r="T25" s="2" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="U25" s="2" t="n">
         <v>47</v>
@@ -45630,7 +45628,7 @@
         <v>11</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>0</v>
@@ -45666,16 +45664,16 @@
       </c>
       <c r="T56" s="4" t="n"/>
       <c r="U56" s="4" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V56" s="4" t="n">
         <v>53</v>
       </c>
       <c r="W56" s="4" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="X56" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y56" s="4" t="n">
         <v>32</v>
@@ -46828,7 +46826,7 @@
       </c>
       <c r="M71" s="4" t="inlineStr">
         <is>
-          <t>LightBrand</t>
+          <t>BurningSteel</t>
         </is>
       </c>
       <c r="N71" s="4" t="n">
@@ -47648,7 +47646,7 @@
         <v>15</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U2" s="2" t="n">
         <v>40</v>
@@ -47885,7 +47883,7 @@
         <v>15</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="U5" s="2" t="n">
         <v>34</v>
@@ -47964,7 +47962,7 @@
         <v>15</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U6" s="2" t="n">
         <v>34</v>
@@ -48043,7 +48041,7 @@
         <v>15</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U7" s="2" t="n">
         <v>34</v>
@@ -48189,7 +48187,7 @@
         <v>8</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="U9" s="2" t="n">
         <v>46</v>
@@ -48677,7 +48675,7 @@
         <v>6</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>12</v>
@@ -48692,7 +48690,7 @@
         <v>4</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I16" s="2" t="n">
         <v>1</v>
@@ -48731,19 +48729,19 @@
         <v>42</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="W16" s="2" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="X16" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y16" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -48756,7 +48754,7 @@
         <v>6</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>12</v>
@@ -48771,7 +48769,7 @@
         <v>4</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I17" s="2" t="n">
         <v>1</v>
@@ -48808,19 +48806,19 @@
       </c>
       <c r="T17" s="2" t="n"/>
       <c r="U17" s="2" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="W17" s="2" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="X17" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y17" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -48884,7 +48882,7 @@
         <v>8</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="U18" s="2" t="n">
         <v>35</v>
@@ -49042,7 +49040,7 @@
         <v>17</v>
       </c>
       <c r="T20" s="2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="U20" s="2" t="n">
         <v>31</v>
@@ -49099,17 +49097,17 @@
       <c r="L21" s="2" t="n"/>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Secula</t>
         </is>
       </c>
       <c r="N21" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="Q21" s="2" t="n">
         <v>13</v>
@@ -49433,7 +49431,7 @@
         <v>16</v>
       </c>
       <c r="T25" s="2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="U25" s="2" t="n">
         <v>47</v>
@@ -51323,7 +51321,7 @@
         <v>10</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>0</v>
@@ -51359,16 +51357,16 @@
       </c>
       <c r="T56" s="4" t="n"/>
       <c r="U56" s="4" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V56" s="4" t="n">
         <v>47</v>
       </c>
       <c r="W56" s="4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X56" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y56" s="4" t="n">
         <v>28</v>
@@ -52521,7 +52519,7 @@
       </c>
       <c r="M71" s="4" t="inlineStr">
         <is>
-          <t>LightBrand</t>
+          <t>BurningSteel</t>
         </is>
       </c>
       <c r="N71" s="4" t="n">
@@ -53341,7 +53339,7 @@
         <v>15</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="U2" s="2" t="n">
         <v>40</v>
@@ -53420,7 +53418,7 @@
         <v>9</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="U3" s="2" t="n">
         <v>40</v>
@@ -53576,7 +53574,7 @@
         <v>16</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="U5" s="2" t="n">
         <v>35</v>
@@ -53655,7 +53653,7 @@
         <v>16</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="U6" s="2" t="n">
         <v>35</v>
@@ -53734,7 +53732,7 @@
         <v>16</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U7" s="2" t="n">
         <v>35</v>
@@ -53880,7 +53878,7 @@
         <v>8</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="U9" s="2" t="n">
         <v>47</v>
@@ -54036,7 +54034,7 @@
         <v>11</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="U11" s="2" t="n">
         <v>47</v>
@@ -54115,7 +54113,7 @@
         <v>12</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>36</v>
@@ -54194,7 +54192,7 @@
         <v>12</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="U13" s="2" t="n">
         <v>36</v>
@@ -54368,7 +54366,7 @@
         <v>6</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>12</v>
@@ -54383,7 +54381,7 @@
         <v>4</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I16" s="2" t="n">
         <v>1</v>
@@ -54422,19 +54420,19 @@
         <v>50</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="W16" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="X16" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y16" s="2" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -54447,7 +54445,7 @@
         <v>6</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>12</v>
@@ -54462,7 +54460,7 @@
         <v>4</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I17" s="2" t="n">
         <v>1</v>
@@ -54499,19 +54497,19 @@
       </c>
       <c r="T17" s="2" t="n"/>
       <c r="U17" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="W17" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="X17" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y17" s="2" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -54575,7 +54573,7 @@
         <v>9</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="U18" s="2" t="n">
         <v>36</v>
@@ -54654,7 +54652,7 @@
         <v>14</v>
       </c>
       <c r="T19" s="2" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="U19" s="2" t="n">
         <v>36</v>
@@ -54733,7 +54731,7 @@
         <v>18</v>
       </c>
       <c r="T20" s="2" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="U20" s="2" t="n">
         <v>32</v>
@@ -54790,17 +54788,17 @@
       <c r="L21" s="2" t="n"/>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Secula</t>
         </is>
       </c>
       <c r="N21" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>135</v>
+        <v>105</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="Q21" s="2" t="n">
         <v>14</v>
@@ -55278,7 +55276,7 @@
         <v>19</v>
       </c>
       <c r="T27" s="2" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="U27" s="2" t="n">
         <v>44</v>
@@ -58041,7 +58039,7 @@
         <v>11</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>1</v>
@@ -58077,16 +58075,16 @@
       </c>
       <c r="T67" s="4" t="n"/>
       <c r="U67" s="4" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V67" s="4" t="n">
         <v>54</v>
       </c>
       <c r="W67" s="4" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X67" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y67" s="4" t="n">
         <v>32</v>

--- a/unit_stats.xlsx
+++ b/unit_stats.xlsx
@@ -677,7 +677,7 @@
         <v>15</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="U2" s="2" t="n">
         <v>40</v>
@@ -756,7 +756,7 @@
         <v>9</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U3" s="2" t="n">
         <v>40</v>
@@ -914,7 +914,7 @@
         <v>14</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="U5" s="2" t="n">
         <v>32</v>
@@ -993,7 +993,7 @@
         <v>14</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U6" s="2" t="n">
         <v>32</v>
@@ -1071,7 +1071,9 @@
       <c r="S7" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="T7" s="2" t="n"/>
+      <c r="T7" s="2" t="n">
+        <v>6</v>
+      </c>
       <c r="U7" s="2" t="n">
         <v>32</v>
       </c>
@@ -1433,7 +1435,7 @@
         </is>
       </c>
       <c r="N12" s="2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>110</v>
@@ -1451,7 +1453,7 @@
         <v>11</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>32</v>
@@ -1530,7 +1532,7 @@
         <v>11</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U13" s="2" t="n">
         <v>32</v>
@@ -2794,7 +2796,7 @@
         <v>15</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="U2" s="2" t="n">
         <v>40</v>
@@ -2873,7 +2875,7 @@
         <v>9</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="U3" s="2" t="n">
         <v>40</v>
@@ -3552,7 +3554,7 @@
         </is>
       </c>
       <c r="N12" s="2" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>114</v>
@@ -3570,7 +3572,7 @@
         <v>12</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>36</v>
@@ -3649,7 +3651,7 @@
         <v>12</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="U13" s="2" t="n">
         <v>36</v>
@@ -3991,7 +3993,7 @@
         <v>12</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>4</v>
@@ -4021,13 +4023,13 @@
         <v>0</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="S18" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T18" s="2" t="n">
         <v>40</v>
@@ -4070,7 +4072,7 @@
         <v>12</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>4</v>
@@ -4100,13 +4102,13 @@
         <v>0</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R19" s="2" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="S19" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T19" s="2" t="n">
         <v>12</v>
@@ -4577,7 +4579,7 @@
         <v>16</v>
       </c>
       <c r="T25" s="2" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="U25" s="2" t="n">
         <v>47</v>
@@ -11960,7 +11962,7 @@
         </is>
       </c>
       <c r="N12" s="2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>116</v>
@@ -11978,7 +11980,7 @@
         <v>13</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>39</v>
@@ -12057,7 +12059,7 @@
         <v>13</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="U13" s="2" t="n">
         <v>39</v>
@@ -12399,7 +12401,7 @@
         <v>13</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>5</v>
@@ -12429,13 +12431,13 @@
         <v>0</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="S18" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T18" s="2" t="n">
         <v>4</v>
@@ -12478,7 +12480,7 @@
         <v>13</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>5</v>
@@ -12508,13 +12510,13 @@
         <v>0</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R19" s="2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="S19" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T19" s="2" t="n">
         <v>12</v>
@@ -17369,7 +17371,7 @@
         </is>
       </c>
       <c r="N12" s="2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>116</v>
@@ -17808,7 +17810,7 @@
         <v>13</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>5</v>
@@ -17838,13 +17840,13 @@
         <v>0</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="S18" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T18" s="2" t="n"/>
       <c r="U18" s="2" t="n">
@@ -17885,7 +17887,7 @@
         <v>13</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>5</v>
@@ -17915,13 +17917,13 @@
         <v>0</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R19" s="2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="S19" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T19" s="2" t="n">
         <v>16</v>
@@ -26209,7 +26211,7 @@
         <v>7</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U9" s="2" t="n">
         <v>42</v>
@@ -26365,7 +26367,7 @@
         <v>10</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="U11" s="2" t="n">
         <v>42</v>
@@ -26426,7 +26428,7 @@
         </is>
       </c>
       <c r="N12" s="2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>110</v>
@@ -26444,7 +26446,7 @@
         <v>11</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>32</v>
@@ -26522,7 +26524,9 @@
       <c r="S13" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="T13" s="2" t="n"/>
+      <c r="T13" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="U13" s="2" t="n">
         <v>32</v>
       </c>
@@ -28020,7 +28024,7 @@
         <v>14</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="U5" s="2" t="n">
         <v>32</v>
@@ -28099,7 +28103,7 @@
         <v>14</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U6" s="2" t="n">
         <v>32</v>
@@ -28178,7 +28182,7 @@
         <v>14</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="U7" s="2" t="n">
         <v>32</v>
@@ -28324,7 +28328,7 @@
         <v>7</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="U9" s="2" t="n">
         <v>43</v>
@@ -28480,7 +28484,7 @@
         <v>10</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="U11" s="2" t="n">
         <v>43</v>
@@ -28541,7 +28545,7 @@
         </is>
       </c>
       <c r="N12" s="2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>110</v>
@@ -28559,7 +28563,7 @@
         <v>11</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>32</v>
@@ -28638,7 +28642,7 @@
         <v>11</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="U13" s="2" t="n">
         <v>32</v>
@@ -31497,7 +31501,7 @@
         <v>7</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U9" s="2" t="n">
         <v>43</v>
@@ -31655,7 +31659,7 @@
         <v>10</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="U11" s="2" t="n">
         <v>43</v>
@@ -31716,7 +31720,7 @@
         </is>
       </c>
       <c r="N12" s="2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>110</v>
@@ -31734,7 +31738,7 @@
         <v>11</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>32</v>
@@ -31813,7 +31817,7 @@
         <v>11</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U13" s="2" t="n">
         <v>32</v>
@@ -34891,7 +34895,7 @@
         </is>
       </c>
       <c r="N12" s="2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>112</v>
@@ -38802,7 +38806,7 @@
         </is>
       </c>
       <c r="N12" s="2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>112</v>
@@ -38820,7 +38824,7 @@
         <v>11</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>33</v>
@@ -38899,7 +38903,7 @@
         <v>11</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U13" s="2" t="n">
         <v>33</v>
@@ -41955,7 +41959,7 @@
         <v>15</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="U2" s="2" t="n">
         <v>40</v>
@@ -42034,7 +42038,7 @@
         <v>9</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U3" s="2" t="n">
         <v>40</v>
@@ -42713,7 +42717,7 @@
         </is>
       </c>
       <c r="N12" s="2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>112</v>
@@ -42731,7 +42735,7 @@
         <v>12</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>35</v>
@@ -42810,7 +42814,7 @@
         <v>12</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="U13" s="2" t="n">
         <v>35</v>
@@ -47646,7 +47650,7 @@
         <v>15</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="U2" s="2" t="n">
         <v>40</v>
@@ -47725,7 +47729,7 @@
         <v>9</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="U3" s="2" t="n">
         <v>40</v>
@@ -47883,7 +47887,7 @@
         <v>15</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="U5" s="2" t="n">
         <v>34</v>
@@ -47962,7 +47966,7 @@
         <v>15</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U6" s="2" t="n">
         <v>34</v>
@@ -48187,7 +48191,7 @@
         <v>8</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="U9" s="2" t="n">
         <v>46</v>
@@ -48343,7 +48347,7 @@
         <v>11</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="U11" s="2" t="n">
         <v>46</v>
@@ -48404,7 +48408,7 @@
         </is>
       </c>
       <c r="N12" s="2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>112</v>
@@ -48422,7 +48426,7 @@
         <v>12</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>35</v>
@@ -48501,7 +48505,7 @@
         <v>12</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="U13" s="2" t="n">
         <v>35</v>
@@ -48882,7 +48886,7 @@
         <v>8</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="U18" s="2" t="n">
         <v>35</v>
@@ -54095,7 +54099,7 @@
         </is>
       </c>
       <c r="N12" s="2" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>114</v>
@@ -54113,7 +54117,7 @@
         <v>12</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>36</v>
@@ -54192,7 +54196,7 @@
         <v>12</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U13" s="2" t="n">
         <v>36</v>
@@ -54534,7 +54538,7 @@
         <v>12</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>4</v>
@@ -54564,13 +54568,13 @@
         <v>0</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="S18" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T18" s="2" t="n">
         <v>42</v>
@@ -54613,7 +54617,7 @@
         <v>12</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>4</v>
@@ -54643,13 +54647,13 @@
         <v>0</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R19" s="2" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="S19" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T19" s="2" t="n">
         <v>16</v>

--- a/unit_stats.xlsx
+++ b/unit_stats.xlsx
@@ -23,6 +23,8 @@
     <sheet name="Ch6 Normal" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="Ch7 Hard" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="Ch7 Normal" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Ch8 Hard" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Ch8 Normal" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25452,6 +25454,976 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Y6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="6" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="6" customWidth="1" min="17" max="17"/>
+    <col width="7" customWidth="1" min="18" max="18"/>
+    <col width="6" customWidth="1" min="19" max="19"/>
+    <col width="6" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="11" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>UnitID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Lv</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Str</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Mag</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Skl</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Spd</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Def</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Res</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Luck</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Con</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Atk</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Crit</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>AS</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>AS+4</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>WEXP</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Mag OHKO</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Phys OHKO</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Bomb OHKO</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Mag ORKO</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Phys ORKO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Ch7LowMage_LowMage</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>127</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T2" s="3" t="n"/>
+      <c r="U2" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="X2" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Ch7Wise_LowMage</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Exploitation</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="T3" s="3" t="n"/>
+      <c r="U3" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>0x81_Soldier</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>113</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="S5" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="T5" s="4" t="n"/>
+      <c r="U5" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="W5" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="X5" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y5" s="4" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>0x81_HighMage</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="O6" s="4" t="n">
+        <v>129</v>
+      </c>
+      <c r="P6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="R6" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="S6" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" s="4" t="n"/>
+      <c r="U6" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="V6" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="W6" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="X6" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y6" s="4" t="n">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Y6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="6" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="6" customWidth="1" min="17" max="17"/>
+    <col width="7" customWidth="1" min="18" max="18"/>
+    <col width="6" customWidth="1" min="19" max="19"/>
+    <col width="6" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="11" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>UnitID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Lv</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Str</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Mag</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Skl</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Spd</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Def</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Res</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Luck</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Con</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Atk</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Crit</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>AS</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>AS+4</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>WEXP</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Mag OHKO</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Phys OHKO</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Bomb OHKO</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Mag ORKO</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Phys ORKO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Ch7LowMage_LowMage</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>121</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="T2" s="3" t="n"/>
+      <c r="U2" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="X2" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Ch7Wise_LowMage</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Exploitation</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="T3" s="3" t="n"/>
+      <c r="U3" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>0x81_Soldier</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>IronLance</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>108</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="S5" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" s="4" t="n"/>
+      <c r="U5" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="W5" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="X5" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y5" s="4" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>0x81_HighMage</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="O6" s="4" t="n">
+        <v>124</v>
+      </c>
+      <c r="P6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="R6" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="S6" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="T6" s="4" t="n"/>
+      <c r="U6" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="V6" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="W6" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="X6" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y6" s="4" t="n">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
